--- a/data/ModelResults_emmeans.xlsx
+++ b/data/ModelResults_emmeans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://michiganstate-my.sharepoint.com/personal/buysseso_msu_edu/Documents/Arabidopsis/Swe_Italy/R_scripts/SW_IT_PopDiffPlasticity/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1771" documentId="13_ncr:1_{AD4A5BE6-D9C1-414A-81C8-3A9C273D7774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75FA75CC-0924-4A37-BC4C-9D19920FFA00}"/>
+  <xr:revisionPtr revIDLastSave="1832" documentId="13_ncr:1_{AD4A5BE6-D9C1-414A-81C8-3A9C273D7774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3570AA86-9C39-4DF9-BCD3-618DBFCDBAA2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8A213037-8BA5-417B-A75A-3088B4717938}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="57">
   <si>
     <t>Experiment</t>
   </si>
@@ -107,9 +107,6 @@
     <t>NumDF</t>
   </si>
   <si>
-    <t>dry Root G</t>
-  </si>
-  <si>
     <t>Root to Shoot - log</t>
   </si>
   <si>
@@ -117,9 +114,6 @@
   </si>
   <si>
     <t>Hydrated Weight (g) - log</t>
-  </si>
-  <si>
-    <t>dry Rosette G - log - bolting</t>
   </si>
   <si>
     <t>dry Rosette G - log - harvest</t>
@@ -164,9 +158,6 @@
     <t>Repro:Ros</t>
   </si>
   <si>
-    <t>below ground</t>
-  </si>
-  <si>
     <t>Avg Seed Weight</t>
   </si>
   <si>
@@ -205,11 +196,26 @@
   <si>
     <t>leaf number at bolting - log</t>
   </si>
+  <si>
+    <t>Shoot G - log - bolting</t>
+  </si>
+  <si>
+    <t>Root G - bolting</t>
+  </si>
+  <si>
+    <t>shoot G - log - bolting</t>
+  </si>
+  <si>
+    <t>root G</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -513,7 +519,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -546,6 +552,23 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="2" borderId="8" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -582,31 +605,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -633,10 +640,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -964,6 +967,8 @@
     <col min="9" max="9" width="8.42578125" customWidth="1"/>
     <col min="16" max="16" width="31.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="27" customWidth="1"/>
+    <col min="22" max="22" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" s="12" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -971,43 +976,43 @@
         <v>0</v>
       </c>
       <c r="B1" s="11"/>
-      <c r="C1" s="35">
+      <c r="C1" s="50">
         <v>2021</v>
       </c>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="35">
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="50">
         <v>2022</v>
       </c>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
       <c r="P1" s="11"/>
-      <c r="Q1" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="R1" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="S1" s="36"/>
-      <c r="T1" s="36"/>
-      <c r="U1" s="36"/>
-      <c r="V1" s="36"/>
-      <c r="W1" s="37"/>
-      <c r="X1" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="36"/>
-      <c r="AA1" s="36"/>
-      <c r="AB1" s="36"/>
-      <c r="AC1" s="37"/>
+      <c r="Q1" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="R1" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="51"/>
+      <c r="V1" s="51"/>
+      <c r="W1" s="52"/>
+      <c r="X1" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y1" s="51"/>
+      <c r="Z1" s="51"/>
+      <c r="AA1" s="51"/>
+      <c r="AB1" s="51"/>
+      <c r="AC1" s="52"/>
     </row>
     <row r="2" spans="1:29" s="16" customFormat="1" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
@@ -1033,7 +1038,7 @@
         <v>6</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>2</v>
@@ -1056,47 +1061,47 @@
       <c r="P2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="Q2" s="40"/>
+      <c r="Q2" s="55"/>
       <c r="R2" s="10" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="S2" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="T2" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="T2" s="10" t="s">
-        <v>37</v>
-      </c>
       <c r="U2" s="10" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="V2" s="10" t="s">
         <v>6</v>
       </c>
       <c r="W2" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="X2" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y2" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z2" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA2" s="10" t="s">
         <v>34</v>
-      </c>
-      <c r="Y2" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z2" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA2" s="10" t="s">
-        <v>36</v>
       </c>
       <c r="AB2" s="10" t="s">
         <v>6</v>
       </c>
       <c r="AC2" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
-        <v>38</v>
+      <c r="A3" s="53" t="s">
+        <v>36</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>9</v>
@@ -1120,19 +1125,19 @@
         <v>7.3383790508167401E-2</v>
       </c>
       <c r="I3" s="13"/>
-      <c r="J3" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="30"/>
-      <c r="P3" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q3" s="46" t="s">
-        <v>29</v>
+      <c r="J3" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="30" t="s">
+        <v>27</v>
       </c>
       <c r="R3" s="1">
         <v>-1.68843263816815</v>
@@ -1150,17 +1155,17 @@
         <v>0.60935835609726297</v>
       </c>
       <c r="W3" s="1"/>
-      <c r="X3" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y3" s="30"/>
-      <c r="Z3" s="30"/>
-      <c r="AA3" s="30"/>
-      <c r="AB3" s="30"/>
-      <c r="AC3" s="50"/>
+      <c r="X3" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y3" s="45"/>
+      <c r="Z3" s="45"/>
+      <c r="AA3" s="45"/>
+      <c r="AB3" s="45"/>
+      <c r="AC3" s="34"/>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A4" s="33"/>
+      <c r="A4" s="48"/>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1183,15 +1188,15 @@
         <v>5.8229847066576205E-7</v>
       </c>
       <c r="I4" s="1"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="47" t="s">
-        <v>30</v>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
+      <c r="M4" s="45"/>
+      <c r="N4" s="45"/>
+      <c r="O4" s="45"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="31" t="s">
+        <v>28</v>
       </c>
       <c r="R4" s="1">
         <v>-1.4713585811633001</v>
@@ -1209,15 +1214,15 @@
         <v>0.51504029973848997</v>
       </c>
       <c r="W4" s="1"/>
-      <c r="X4" s="30"/>
-      <c r="Y4" s="30"/>
-      <c r="Z4" s="30"/>
-      <c r="AA4" s="30"/>
-      <c r="AB4" s="30"/>
-      <c r="AC4" s="51"/>
+      <c r="X4" s="45"/>
+      <c r="Y4" s="45"/>
+      <c r="Z4" s="45"/>
+      <c r="AA4" s="45"/>
+      <c r="AB4" s="45"/>
+      <c r="AC4" s="35"/>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A5" s="33"/>
+      <c r="A5" s="48"/>
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1239,15 +1244,15 @@
       <c r="H5" s="1">
         <v>0.90072460165650603</v>
       </c>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="30"/>
-      <c r="M5" s="30"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="30"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="47" t="s">
-        <v>31</v>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="45"/>
+      <c r="O5" s="45"/>
+      <c r="P5" s="48"/>
+      <c r="Q5" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="R5" s="1">
         <v>-22.771753908613199</v>
@@ -1265,34 +1270,34 @@
         <v>8.4463170790804996E-8</v>
       </c>
       <c r="W5" s="1"/>
-      <c r="X5" s="30"/>
-      <c r="Y5" s="30"/>
-      <c r="Z5" s="30"/>
-      <c r="AA5" s="30"/>
-      <c r="AB5" s="30"/>
-      <c r="AC5" s="51"/>
+      <c r="X5" s="45"/>
+      <c r="Y5" s="45"/>
+      <c r="Z5" s="45"/>
+      <c r="AA5" s="45"/>
+      <c r="AB5" s="45"/>
+      <c r="AC5" s="35"/>
     </row>
     <row r="6" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="34"/>
+      <c r="A6" s="49"/>
       <c r="B6" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
+        <v>48</v>
+      </c>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
       <c r="I6" s="9"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
-      <c r="O6" s="31"/>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="48" t="s">
-        <v>32</v>
+      <c r="J6" s="46"/>
+      <c r="K6" s="46"/>
+      <c r="L6" s="46"/>
+      <c r="M6" s="46"/>
+      <c r="N6" s="46"/>
+      <c r="O6" s="46"/>
+      <c r="P6" s="49"/>
+      <c r="Q6" s="32" t="s">
+        <v>30</v>
       </c>
       <c r="R6" s="9">
         <v>-22.554679851608299</v>
@@ -1306,19 +1311,19 @@
       <c r="U6" s="9">
         <v>-8.2601678385659607</v>
       </c>
-      <c r="V6" s="56">
+      <c r="V6" s="40">
         <v>8.5628197088460896E-8</v>
       </c>
       <c r="W6" s="9"/>
-      <c r="X6" s="31"/>
-      <c r="Y6" s="31"/>
-      <c r="Z6" s="31"/>
-      <c r="AA6" s="31"/>
-      <c r="AB6" s="31"/>
-      <c r="AC6" s="52"/>
+      <c r="X6" s="46"/>
+      <c r="Y6" s="46"/>
+      <c r="Z6" s="46"/>
+      <c r="AA6" s="46"/>
+      <c r="AB6" s="46"/>
+      <c r="AC6" s="36"/>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="47" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="13" t="s">
@@ -1361,11 +1366,11 @@
       <c r="O7" s="14">
         <v>7.9655542624253594E-15</v>
       </c>
-      <c r="P7" s="38" t="s">
+      <c r="P7" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="Q7" s="46" t="s">
-        <v>29</v>
+      <c r="Q7" s="30" t="s">
+        <v>27</v>
       </c>
       <c r="R7" s="13">
         <v>7.2597547321285302E-2</v>
@@ -1379,7 +1384,7 @@
       <c r="U7" s="13">
         <v>5.9296331247311498</v>
       </c>
-      <c r="V7" s="57">
+      <c r="V7" s="41">
         <v>6.3834627239689499E-7</v>
       </c>
       <c r="W7" s="13"/>
@@ -1395,13 +1400,13 @@
       <c r="AA7" s="13">
         <v>12.064509333229401</v>
       </c>
-      <c r="AB7" s="57">
+      <c r="AB7" s="41">
         <v>3.45279360658424E-14</v>
       </c>
-      <c r="AC7" s="50"/>
+      <c r="AC7" s="34"/>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A8" s="33"/>
+      <c r="A8" s="48"/>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1442,9 +1447,9 @@
       <c r="O8" s="2">
         <v>2.49480079562349E-3</v>
       </c>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="47" t="s">
-        <v>30</v>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="31" t="s">
+        <v>28</v>
       </c>
       <c r="R8" s="1">
         <v>4.4691142052654301E-2</v>
@@ -1477,10 +1482,10 @@
       <c r="AB8" s="6">
         <v>1.1295075985629E-11</v>
       </c>
-      <c r="AC8" s="51"/>
+      <c r="AC8" s="35"/>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A9" s="33"/>
+      <c r="A9" s="48"/>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
@@ -1521,9 +1526,9 @@
       <c r="O9" s="2">
         <v>5.9886663878832899E-3</v>
       </c>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="47" t="s">
-        <v>31</v>
+      <c r="P9" s="48"/>
+      <c r="Q9" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="R9" s="1">
         <v>9.5356334172068593E-3</v>
@@ -1556,19 +1561,19 @@
       <c r="AB9" s="1">
         <v>0.49875573646093602</v>
       </c>
-      <c r="AC9" s="51"/>
+      <c r="AC9" s="35"/>
     </row>
     <row r="10" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="34"/>
+      <c r="A10" s="49"/>
       <c r="B10" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="43"/>
+        <v>48</v>
+      </c>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="58"/>
       <c r="I10" s="9"/>
       <c r="J10" s="9">
         <v>3.4846897009296399E-3</v>
@@ -1588,9 +1593,9 @@
       <c r="O10" s="9">
         <v>0.23519968422781001</v>
       </c>
-      <c r="P10" s="41"/>
-      <c r="Q10" s="48" t="s">
-        <v>32</v>
+      <c r="P10" s="56"/>
+      <c r="Q10" s="32" t="s">
+        <v>30</v>
       </c>
       <c r="R10" s="9">
         <v>-1.83707718514242E-2</v>
@@ -1623,23 +1628,23 @@
       <c r="AB10" s="19">
         <v>3.8336369037095301E-4</v>
       </c>
-      <c r="AC10" s="52"/>
+      <c r="AC10" s="36"/>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="48" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
+      <c r="C11" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
       <c r="I11" s="13"/>
       <c r="J11" s="13">
         <v>2.20343269025562E-2</v>
@@ -1659,19 +1664,19 @@
       <c r="O11" s="15">
         <v>1.20915323151938E-2</v>
       </c>
-      <c r="P11" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q11" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="R11" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="S11" s="42"/>
-      <c r="T11" s="42"/>
-      <c r="U11" s="42"/>
-      <c r="V11" s="42"/>
+      <c r="P11" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q11" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="R11" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="S11" s="44"/>
+      <c r="T11" s="44"/>
+      <c r="U11" s="44"/>
+      <c r="V11" s="44"/>
       <c r="W11" s="13"/>
       <c r="X11" s="13">
         <v>0.92269407717206897</v>
@@ -1685,22 +1690,22 @@
       <c r="AA11" s="13">
         <v>-2.3859606625496701</v>
       </c>
-      <c r="AB11" s="13">
+      <c r="AB11" s="17">
         <v>8.5821492945401895E-2</v>
       </c>
-      <c r="AC11" s="50"/>
+      <c r="AC11" s="34"/>
     </row>
     <row r="12" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="33"/>
+      <c r="A12" s="48"/>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1">
         <v>2.98483856205864E-2</v>
@@ -1720,15 +1725,15 @@
       <c r="O12" s="2">
         <v>1.05420955332634E-2</v>
       </c>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="R12" s="30"/>
-      <c r="S12" s="30"/>
-      <c r="T12" s="30"/>
-      <c r="U12" s="30"/>
-      <c r="V12" s="30"/>
+      <c r="P12" s="48"/>
+      <c r="Q12" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="R12" s="45"/>
+      <c r="S12" s="45"/>
+      <c r="T12" s="45"/>
+      <c r="U12" s="45"/>
+      <c r="V12" s="45"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1">
         <v>0.89729079192970995</v>
@@ -1745,19 +1750,19 @@
       <c r="AB12" s="2">
         <v>9.3986579024631905E-3</v>
       </c>
-      <c r="AC12" s="51"/>
+      <c r="AC12" s="35"/>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A13" s="33"/>
+      <c r="A13" s="48"/>
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="45"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1">
         <v>1.15818782663304E-3</v>
@@ -1777,15 +1782,15 @@
       <c r="O13" s="1">
         <v>0.55966903975183102</v>
       </c>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="R13" s="30"/>
-      <c r="S13" s="30"/>
-      <c r="T13" s="30"/>
-      <c r="U13" s="30"/>
-      <c r="V13" s="30"/>
+      <c r="P13" s="48"/>
+      <c r="Q13" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="R13" s="45"/>
+      <c r="S13" s="45"/>
+      <c r="T13" s="45"/>
+      <c r="U13" s="45"/>
+      <c r="V13" s="45"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1">
         <v>0.88184620079220499</v>
@@ -1799,22 +1804,22 @@
       <c r="AA13" s="1">
         <v>-2.3675986162831899</v>
       </c>
-      <c r="AB13" s="1">
+      <c r="AB13" s="3">
         <v>0.115000782535429</v>
       </c>
-      <c r="AC13" s="51"/>
+      <c r="AC13" s="35"/>
     </row>
     <row r="14" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="34"/>
+      <c r="A14" s="49"/>
       <c r="B14" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
+        <v>48</v>
+      </c>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
       <c r="I14" s="9"/>
       <c r="J14" s="9">
         <v>2.0797141885883202E-3</v>
@@ -1834,15 +1839,15 @@
       <c r="O14" s="9">
         <v>0.73598934665486404</v>
       </c>
-      <c r="P14" s="34"/>
-      <c r="Q14" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="R14" s="31"/>
-      <c r="S14" s="31"/>
-      <c r="T14" s="31"/>
-      <c r="U14" s="31"/>
-      <c r="V14" s="31"/>
+      <c r="P14" s="49"/>
+      <c r="Q14" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="R14" s="46"/>
+      <c r="S14" s="46"/>
+      <c r="T14" s="46"/>
+      <c r="U14" s="46"/>
+      <c r="V14" s="46"/>
       <c r="W14" s="9"/>
       <c r="X14" s="9">
         <v>0.85756752475770204</v>
@@ -1859,10 +1864,10 @@
       <c r="AB14" s="19">
         <v>3.7771948110335497E-2</v>
       </c>
-      <c r="AC14" s="52"/>
+      <c r="AC14" s="36"/>
     </row>
     <row r="15" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="47" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -1905,11 +1910,11 @@
       <c r="O15" s="20">
         <v>2.5984972877347698E-9</v>
       </c>
-      <c r="P15" s="32" t="s">
+      <c r="P15" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="Q15" s="49" t="s">
-        <v>29</v>
+      <c r="Q15" s="33" t="s">
+        <v>27</v>
       </c>
       <c r="R15" s="13">
         <v>1.6145215106660999</v>
@@ -1942,10 +1947,10 @@
       <c r="AB15" s="15">
         <v>6.8501877810184198E-3</v>
       </c>
-      <c r="AC15" s="53"/>
+      <c r="AC15" s="37"/>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A16" s="33"/>
+      <c r="A16" s="48"/>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
@@ -1986,9 +1991,9 @@
       <c r="O16" s="4">
         <v>2.3925201381821199E-8</v>
       </c>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="47" t="s">
-        <v>30</v>
+      <c r="P16" s="48"/>
+      <c r="Q16" s="31" t="s">
+        <v>28</v>
       </c>
       <c r="R16" s="1">
         <v>1.1848735541579101</v>
@@ -2021,10 +2026,10 @@
       <c r="AB16" s="6">
         <v>1.0448505805005201E-6</v>
       </c>
-      <c r="AC16" s="51"/>
+      <c r="AC16" s="35"/>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A17" s="33"/>
+      <c r="A17" s="48"/>
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
@@ -2065,9 +2070,9 @@
       <c r="O17" s="3">
         <v>0.107275586121823</v>
       </c>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="47" t="s">
-        <v>31</v>
+      <c r="P17" s="48"/>
+      <c r="Q17" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="R17" s="1">
         <v>1.6580739035199099</v>
@@ -2100,19 +2105,19 @@
       <c r="AB17" s="6">
         <v>5.8682974479751198E-8</v>
       </c>
-      <c r="AC17" s="51"/>
+      <c r="AC17" s="35"/>
     </row>
     <row r="18" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="34"/>
+      <c r="A18" s="49"/>
       <c r="B18" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
+        <v>48</v>
+      </c>
+      <c r="C18" s="58"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="58"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="58"/>
       <c r="I18" s="9"/>
       <c r="J18" s="9">
         <v>4.9184876384352101E-2</v>
@@ -2132,9 +2137,9 @@
       <c r="O18" s="19">
         <v>1.9087014953066299E-2</v>
       </c>
-      <c r="P18" s="34"/>
-      <c r="Q18" s="48" t="s">
-        <v>32</v>
+      <c r="P18" s="49"/>
+      <c r="Q18" s="32" t="s">
+        <v>30</v>
       </c>
       <c r="R18" s="9">
         <v>1.2168360137299099</v>
@@ -2164,26 +2169,26 @@
       <c r="AA18" s="9">
         <v>10.0741628445145</v>
       </c>
-      <c r="AB18" s="56">
+      <c r="AB18" s="40">
         <v>4.7632608968228903E-10</v>
       </c>
-      <c r="AC18" s="52"/>
+      <c r="AC18" s="36"/>
     </row>
     <row r="19" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="32" t="s">
-        <v>24</v>
+      <c r="A19" s="47" t="s">
+        <v>23</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
+      <c r="C19" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
       <c r="I19" s="8"/>
       <c r="J19" s="8">
         <v>1.4241127553301099E-4</v>
@@ -2203,19 +2208,19 @@
       <c r="O19" s="8">
         <v>0.82529746395827397</v>
       </c>
-      <c r="P19" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q19" s="49" t="s">
-        <v>29</v>
-      </c>
-      <c r="R19" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="S19" s="42"/>
-      <c r="T19" s="42"/>
-      <c r="U19" s="42"/>
-      <c r="V19" s="42"/>
+      <c r="P19" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q19" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="R19" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="S19" s="44"/>
+      <c r="T19" s="44"/>
+      <c r="U19" s="44"/>
+      <c r="V19" s="44"/>
       <c r="W19" s="13"/>
       <c r="X19" s="13">
         <v>0.92228721673858705</v>
@@ -2232,19 +2237,19 @@
       <c r="AB19" s="17">
         <v>5.3696861707003898E-2</v>
       </c>
-      <c r="AC19" s="53"/>
+      <c r="AC19" s="37"/>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A20" s="33"/>
+      <c r="A20" s="48"/>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1">
         <v>4.6725153189010001E-2</v>
@@ -2264,15 +2269,15 @@
       <c r="O20" s="2">
         <v>1.3790795758093499E-3</v>
       </c>
-      <c r="P20" s="33"/>
-      <c r="Q20" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="R20" s="30"/>
-      <c r="S20" s="30"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="30"/>
-      <c r="V20" s="30"/>
+      <c r="P20" s="48"/>
+      <c r="Q20" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="R20" s="45"/>
+      <c r="S20" s="45"/>
+      <c r="T20" s="45"/>
+      <c r="U20" s="45"/>
+      <c r="V20" s="45"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1">
         <v>1.0589700479598501</v>
@@ -2289,19 +2294,19 @@
       <c r="AB20" s="1">
         <v>0.265556672140775</v>
       </c>
-      <c r="AC20" s="51"/>
+      <c r="AC20" s="35"/>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A21" s="33"/>
+      <c r="A21" s="48"/>
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1">
         <v>2.8302586845141399E-2</v>
@@ -2321,15 +2326,15 @@
       <c r="O21" s="2">
         <v>2.3248319291652099E-3</v>
       </c>
-      <c r="P21" s="33"/>
-      <c r="Q21" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="R21" s="30"/>
-      <c r="S21" s="30"/>
-      <c r="T21" s="30"/>
-      <c r="U21" s="30"/>
-      <c r="V21" s="30"/>
+      <c r="P21" s="48"/>
+      <c r="Q21" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="R21" s="45"/>
+      <c r="S21" s="45"/>
+      <c r="T21" s="45"/>
+      <c r="U21" s="45"/>
+      <c r="V21" s="45"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1">
         <v>1.19093365397326</v>
@@ -2346,19 +2351,19 @@
       <c r="AB21" s="3">
         <v>6.6971560557577706E-2</v>
       </c>
-      <c r="AC21" s="51"/>
+      <c r="AC21" s="35"/>
     </row>
     <row r="22" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="34"/>
+      <c r="A22" s="49"/>
       <c r="B22" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
+        <v>48</v>
+      </c>
+      <c r="C22" s="46"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="46"/>
       <c r="I22" s="9"/>
       <c r="J22" s="9">
         <v>6.3796317056246301E-3</v>
@@ -2378,15 +2383,15 @@
       <c r="O22" s="9">
         <v>0.33767591593294399</v>
       </c>
-      <c r="P22" s="34"/>
-      <c r="Q22" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="R22" s="31"/>
-      <c r="S22" s="31"/>
-      <c r="T22" s="31"/>
-      <c r="U22" s="31"/>
-      <c r="V22" s="31"/>
+      <c r="P22" s="49"/>
+      <c r="Q22" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="R22" s="46"/>
+      <c r="S22" s="46"/>
+      <c r="T22" s="46"/>
+      <c r="U22" s="46"/>
+      <c r="V22" s="46"/>
       <c r="W22" s="9"/>
       <c r="X22" s="9">
         <v>1.36742984807359</v>
@@ -2403,3171 +2408,3171 @@
       <c r="AB22" s="19">
         <v>7.4212333342094105E-4</v>
       </c>
-      <c r="AC22" s="52"/>
-    </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A23" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="1" t="s">
+      <c r="AC22" s="36"/>
+    </row>
+    <row r="23" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="47" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="1">
-        <v>6176915.5049999999</v>
-      </c>
-      <c r="D23" s="1">
-        <v>6176915.5049999999</v>
-      </c>
-      <c r="E23" s="1">
-        <v>1</v>
-      </c>
-      <c r="F23" s="1">
-        <v>71.888440000000003</v>
-      </c>
-      <c r="G23" s="1">
-        <v>167.3449876</v>
-      </c>
-      <c r="H23" s="4">
-        <v>1.898803E-20</v>
-      </c>
-      <c r="I23" s="1"/>
-      <c r="J23" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="K23" s="42"/>
-      <c r="L23" s="42"/>
-      <c r="M23" s="42"/>
-      <c r="N23" s="42"/>
-      <c r="O23" s="42"/>
-      <c r="P23" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q23" s="47" t="s">
-        <v>29</v>
-      </c>
-      <c r="R23" s="13">
-        <v>529.6</v>
-      </c>
-      <c r="S23" s="13">
-        <v>60.754643373648697</v>
-      </c>
-      <c r="T23" s="13">
-        <v>73.255404219009407</v>
-      </c>
-      <c r="U23" s="13">
-        <v>8.7170291946722998</v>
-      </c>
-      <c r="V23" s="15">
-        <v>0</v>
-      </c>
+      <c r="C23" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8">
+        <v>4.0252880405239402E-2</v>
+      </c>
+      <c r="K23" s="8">
+        <v>4.0252880405239402E-2</v>
+      </c>
+      <c r="L23" s="8">
+        <v>1</v>
+      </c>
+      <c r="M23" s="8">
+        <v>107.364526662513</v>
+      </c>
+      <c r="N23" s="8">
+        <v>3.06304929618606</v>
+      </c>
+      <c r="O23" s="28">
+        <v>8.2948057027609101E-2</v>
+      </c>
+      <c r="P23" s="47" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q23" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="R23" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="S23" s="57"/>
+      <c r="T23" s="57"/>
+      <c r="U23" s="57"/>
+      <c r="V23" s="57"/>
       <c r="W23" s="13"/>
-      <c r="X23" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y23" s="44"/>
-      <c r="Z23" s="44"/>
-      <c r="AA23" s="44"/>
-      <c r="AB23" s="44"/>
-      <c r="AC23" s="51"/>
+      <c r="X23" s="13">
+        <v>1.28624977261183</v>
+      </c>
+      <c r="Y23" s="13">
+        <v>8.5806417308814706E-2</v>
+      </c>
+      <c r="Z23" s="13">
+        <v>108.356902446408</v>
+      </c>
+      <c r="AA23" s="13">
+        <v>3.77347912638702</v>
+      </c>
+      <c r="AB23" s="15">
+        <v>1.48131841462606E-3</v>
+      </c>
+      <c r="AC23" s="37"/>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A24" s="33"/>
+      <c r="A24" s="48"/>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="1">
-        <v>50157.928</v>
-      </c>
-      <c r="D24" s="1">
-        <v>50157.928</v>
-      </c>
-      <c r="E24" s="1">
-        <v>1</v>
-      </c>
-      <c r="F24" s="1">
-        <v>17.04102</v>
-      </c>
-      <c r="G24" s="1">
-        <v>1.3588785000000001</v>
-      </c>
-      <c r="H24" s="1">
-        <v>0.2597892</v>
-      </c>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
-      <c r="O24" s="30"/>
-      <c r="P24" s="33"/>
-      <c r="Q24" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="R24" s="1">
-        <v>90.5422189444065</v>
-      </c>
-      <c r="S24" s="1">
-        <v>76.168525940263294</v>
-      </c>
-      <c r="T24" s="1">
-        <v>33.630246929987997</v>
-      </c>
-      <c r="U24" s="1">
-        <v>1.1887090872077</v>
-      </c>
-      <c r="V24" s="1">
-        <v>0.63803985452722101</v>
-      </c>
+      <c r="J24" s="1">
+        <v>0.42132164214255802</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0.42132164214255802</v>
+      </c>
+      <c r="L24" s="1">
+        <v>1</v>
+      </c>
+      <c r="M24" s="1">
+        <v>13.0099671316875</v>
+      </c>
+      <c r="N24" s="1">
+        <v>32.060536946437701</v>
+      </c>
+      <c r="O24" s="4">
+        <v>7.7465741239532106E-5</v>
+      </c>
+      <c r="P24" s="48"/>
+      <c r="Q24" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="R24" s="45"/>
+      <c r="S24" s="45"/>
+      <c r="T24" s="45"/>
+      <c r="U24" s="45"/>
+      <c r="V24" s="45"/>
       <c r="W24" s="1"/>
-      <c r="X24" s="30"/>
-      <c r="Y24" s="30"/>
-      <c r="Z24" s="30"/>
-      <c r="AA24" s="30"/>
-      <c r="AB24" s="30"/>
-      <c r="AC24" s="51"/>
+      <c r="X24" s="1">
+        <v>1.0220158782055699</v>
+      </c>
+      <c r="Y24" s="1">
+        <v>6.8059773351627897E-2</v>
+      </c>
+      <c r="Z24" s="1">
+        <v>107.183693987974</v>
+      </c>
+      <c r="AA24" s="1">
+        <v>0.32701355539446397</v>
+      </c>
+      <c r="AB24" s="1">
+        <v>0.98786034140903101</v>
+      </c>
+      <c r="AC24" s="35"/>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A25" s="33"/>
+      <c r="A25" s="48"/>
       <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="1">
-        <v>5310.1710000000003</v>
-      </c>
-      <c r="D25" s="1">
-        <v>5310.1710000000003</v>
-      </c>
-      <c r="E25" s="1">
-        <v>1</v>
-      </c>
-      <c r="F25" s="1">
-        <v>71.888440000000003</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0.1438632</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0.7055884</v>
-      </c>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="45"/>
       <c r="I25" s="1"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="30"/>
-      <c r="L25" s="30"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="30"/>
-      <c r="O25" s="30"/>
-      <c r="P25" s="33"/>
-      <c r="Q25" s="47" t="s">
+      <c r="J25" s="1">
+        <v>7.8254362282741005E-2</v>
+      </c>
+      <c r="K25" s="1">
+        <v>7.8254362282741005E-2</v>
+      </c>
+      <c r="L25" s="1">
+        <v>1</v>
+      </c>
+      <c r="M25" s="1">
+        <v>106.96971991586101</v>
+      </c>
+      <c r="N25" s="1">
+        <v>5.9547780655825902</v>
+      </c>
+      <c r="O25" s="2">
+        <v>1.63202510112339E-2</v>
+      </c>
+      <c r="P25" s="48"/>
+      <c r="Q25" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="R25" s="45"/>
+      <c r="S25" s="45"/>
+      <c r="T25" s="45"/>
+      <c r="U25" s="45"/>
+      <c r="V25" s="45"/>
+      <c r="W25" s="1"/>
+      <c r="X25" s="1">
+        <v>0.45501994044807598</v>
+      </c>
+      <c r="Y25" s="1">
+        <v>7.5979776783830097E-2</v>
+      </c>
+      <c r="Z25" s="1">
+        <v>16.4330650500419</v>
+      </c>
+      <c r="AA25" s="1">
+        <v>-4.7155848945320198</v>
+      </c>
+      <c r="AB25" s="2">
+        <v>1.12704066890601E-3</v>
+      </c>
+      <c r="AC25" s="35"/>
+    </row>
+    <row r="26" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="49"/>
+      <c r="B26" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9">
+        <v>2.6614614752845599E-3</v>
+      </c>
+      <c r="K26" s="9">
+        <v>1.33073073764228E-3</v>
+      </c>
+      <c r="L26" s="9">
+        <v>2</v>
+      </c>
+      <c r="M26" s="9">
+        <v>106.998307117191</v>
+      </c>
+      <c r="N26" s="9">
+        <v>0.101262165795663</v>
+      </c>
+      <c r="O26" s="9">
+        <v>0.90378258302877301</v>
+      </c>
+      <c r="P26" s="49"/>
+      <c r="Q26" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="R26" s="46"/>
+      <c r="S26" s="46"/>
+      <c r="T26" s="46"/>
+      <c r="U26" s="46"/>
+      <c r="V26" s="46"/>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9">
+        <v>0.361545334304543</v>
+      </c>
+      <c r="Y26" s="9">
+        <v>5.9931199064228002E-2</v>
+      </c>
+      <c r="Z26" s="9">
+        <v>16.204970622986401</v>
+      </c>
+      <c r="AA26" s="9">
+        <v>-6.1374476275895002</v>
+      </c>
+      <c r="AB26" s="40">
+        <v>7.26892011232438E-5</v>
+      </c>
+      <c r="AC26" s="36"/>
+    </row>
+    <row r="27" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="R25" s="1">
-        <v>60.370790372977901</v>
-      </c>
-      <c r="S25" s="1">
-        <v>76.168525940263294</v>
-      </c>
-      <c r="T25" s="1">
-        <v>33.630246929987997</v>
-      </c>
-      <c r="U25" s="1">
-        <v>0.79259496790478601</v>
-      </c>
-      <c r="V25" s="1">
-        <v>0.85729287706349799</v>
-      </c>
-      <c r="W25" s="1"/>
-      <c r="X25" s="30"/>
-      <c r="Y25" s="30"/>
-      <c r="Z25" s="30"/>
-      <c r="AA25" s="30"/>
-      <c r="AB25" s="30"/>
-      <c r="AC25" s="51"/>
-    </row>
-    <row r="26" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="34"/>
-      <c r="B26" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="43"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="43"/>
-      <c r="H26" s="43"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31"/>
-      <c r="M26" s="31"/>
-      <c r="N26" s="31"/>
-      <c r="O26" s="31"/>
-      <c r="P26" s="34"/>
-      <c r="Q26" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="R26" s="9">
-        <v>499.42857142857201</v>
-      </c>
-      <c r="S26" s="9">
-        <v>51.347045341752903</v>
-      </c>
-      <c r="T26" s="9">
-        <v>73.255404219009407</v>
-      </c>
-      <c r="U26" s="9">
-        <v>9.7265298928984407</v>
-      </c>
-      <c r="V26" s="19">
-        <v>0</v>
-      </c>
-      <c r="W26" s="9"/>
-      <c r="X26" s="31"/>
-      <c r="Y26" s="31"/>
-      <c r="Z26" s="31"/>
-      <c r="AA26" s="31"/>
-      <c r="AB26" s="31"/>
-      <c r="AC26" s="52"/>
-    </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A27" s="33" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C27" s="13">
-        <v>0.15432652470222299</v>
-      </c>
-      <c r="D27" s="13">
-        <v>0.15432652470222299</v>
-      </c>
-      <c r="E27" s="13">
-        <v>1</v>
-      </c>
-      <c r="F27" s="13">
-        <v>73.999999999267601</v>
-      </c>
-      <c r="G27" s="13">
-        <v>34.870200464865299</v>
-      </c>
-      <c r="H27" s="14">
-        <v>9.94550983787633E-8</v>
-      </c>
-      <c r="I27" s="13"/>
-      <c r="J27" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="K27" s="44"/>
-      <c r="L27" s="44"/>
-      <c r="M27" s="44"/>
-      <c r="N27" s="44"/>
-      <c r="O27" s="44"/>
-      <c r="P27" s="33" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q27" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="R27" s="13">
-        <v>1.0647504837794699</v>
-      </c>
-      <c r="S27" s="13">
-        <v>5.7194632959268799E-2</v>
-      </c>
-      <c r="T27" s="13">
-        <v>64.060522318169802</v>
-      </c>
-      <c r="U27" s="13">
-        <v>1.1679935236511501</v>
-      </c>
-      <c r="V27" s="13">
-        <v>0.64903708255730697</v>
-      </c>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8">
+        <v>4.9920514192076698E-4</v>
+      </c>
+      <c r="K27" s="8">
+        <v>4.9920514192076698E-4</v>
+      </c>
+      <c r="L27" s="8">
+        <v>1</v>
+      </c>
+      <c r="M27" s="8">
+        <v>109.501348528158</v>
+      </c>
+      <c r="N27" s="8">
+        <v>3.3446840501390498</v>
+      </c>
+      <c r="O27" s="28">
+        <v>7.0143959578357298E-2</v>
+      </c>
+      <c r="P27" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q27" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="R27" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="S27" s="57"/>
+      <c r="T27" s="57"/>
+      <c r="U27" s="57"/>
+      <c r="V27" s="57"/>
       <c r="W27" s="13"/>
-      <c r="X27" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y27" s="30"/>
-      <c r="Z27" s="30"/>
-      <c r="AA27" s="30"/>
-      <c r="AB27" s="30"/>
-      <c r="AC27" s="50"/>
+      <c r="X27" s="13">
+        <v>7.7522088498056798E-3</v>
+      </c>
+      <c r="Y27" s="13">
+        <v>3.0776655749197002E-3</v>
+      </c>
+      <c r="Z27" s="13">
+        <v>109.122356414667</v>
+      </c>
+      <c r="AA27" s="13">
+        <v>2.5188600454121599</v>
+      </c>
+      <c r="AB27" s="17">
+        <v>6.2566828845477901E-2</v>
+      </c>
+      <c r="AC27" s="37"/>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A28" s="33"/>
+      <c r="A28" s="48"/>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="1">
-        <v>0.111292819337707</v>
-      </c>
-      <c r="D28" s="1">
-        <v>0.111292819337707</v>
-      </c>
-      <c r="E28" s="1">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1">
-        <v>73.999999999267601</v>
-      </c>
-      <c r="G28" s="1">
-        <v>25.146700660135899</v>
-      </c>
-      <c r="H28" s="4">
-        <v>3.5283045440115499E-6</v>
-      </c>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="45"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="30"/>
-      <c r="L28" s="30"/>
-      <c r="M28" s="30"/>
-      <c r="N28" s="30"/>
-      <c r="O28" s="30"/>
-      <c r="P28" s="33"/>
-      <c r="Q28" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="R28" s="1">
-        <v>1.42370872400263</v>
-      </c>
-      <c r="S28" s="1">
-        <v>6.5368840678580703E-2</v>
-      </c>
-      <c r="T28" s="1">
-        <v>63.0199737522519</v>
-      </c>
-      <c r="U28" s="1">
-        <v>7.6939839378934503</v>
-      </c>
-      <c r="V28" s="6">
-        <v>7.4586492537775898E-10</v>
-      </c>
+      <c r="J28" s="1">
+        <v>4.3245963051368403E-3</v>
+      </c>
+      <c r="K28" s="1">
+        <v>4.3245963051368403E-3</v>
+      </c>
+      <c r="L28" s="1">
+        <v>1</v>
+      </c>
+      <c r="M28" s="1">
+        <v>14.3846326295774</v>
+      </c>
+      <c r="N28" s="1">
+        <v>28.974878402548999</v>
+      </c>
+      <c r="O28" s="4">
+        <v>8.7931651517614295E-5</v>
+      </c>
+      <c r="P28" s="48"/>
+      <c r="Q28" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="R28" s="45"/>
+      <c r="S28" s="45"/>
+      <c r="T28" s="45"/>
+      <c r="U28" s="45"/>
+      <c r="V28" s="45"/>
       <c r="W28" s="1"/>
-      <c r="X28" s="30"/>
-      <c r="Y28" s="30"/>
-      <c r="Z28" s="30"/>
-      <c r="AA28" s="30"/>
-      <c r="AB28" s="30"/>
-      <c r="AC28" s="51"/>
+      <c r="X28" s="1">
+        <v>5.3703739511303996E-3</v>
+      </c>
+      <c r="Y28" s="1">
+        <v>3.0818249826465001E-3</v>
+      </c>
+      <c r="Z28" s="1">
+        <v>107.550667952098</v>
+      </c>
+      <c r="AA28" s="1">
+        <v>1.74259537169389</v>
+      </c>
+      <c r="AB28" s="1">
+        <v>0.30698034668227098</v>
+      </c>
+      <c r="AC28" s="35"/>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A29" s="33"/>
+      <c r="A29" s="48"/>
       <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="1">
-        <v>7.5267632704079004E-2</v>
-      </c>
-      <c r="D29" s="1">
-        <v>7.5267632704079004E-2</v>
-      </c>
-      <c r="E29" s="1">
-        <v>1</v>
-      </c>
-      <c r="F29" s="1">
-        <v>73.999999999270102</v>
-      </c>
-      <c r="G29" s="1">
-        <v>17.006781212570601</v>
-      </c>
-      <c r="H29" s="4">
-        <v>9.6345615419962495E-5</v>
-      </c>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="45"/>
       <c r="I29" s="1"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="30"/>
-      <c r="P29" s="33"/>
-      <c r="Q29" s="47" t="s">
+      <c r="J29" s="5">
+        <v>4.4673218852987901E-5</v>
+      </c>
+      <c r="K29" s="5">
+        <v>4.4673218852987901E-5</v>
+      </c>
+      <c r="L29" s="1">
+        <v>1</v>
+      </c>
+      <c r="M29" s="1">
+        <v>109.203333776652</v>
+      </c>
+      <c r="N29" s="1">
+        <v>0.29931142534119798</v>
+      </c>
+      <c r="O29" s="1">
+        <v>0.58543070585289902</v>
+      </c>
+      <c r="P29" s="48"/>
+      <c r="Q29" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="R29" s="45"/>
+      <c r="S29" s="45"/>
+      <c r="T29" s="45"/>
+      <c r="U29" s="45"/>
+      <c r="V29" s="45"/>
+      <c r="W29" s="1"/>
+      <c r="X29" s="1">
+        <v>-2.3309139166002101E-2</v>
+      </c>
+      <c r="Y29" s="1">
+        <v>5.0808983370555097E-3</v>
+      </c>
+      <c r="Z29" s="1">
+        <v>20.052756261989</v>
+      </c>
+      <c r="AA29" s="1">
+        <v>-4.5876019592846697</v>
+      </c>
+      <c r="AB29" s="2">
+        <v>9.4136808893374702E-4</v>
+      </c>
+      <c r="AC29" s="35"/>
+    </row>
+    <row r="30" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="49"/>
+      <c r="B30" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="46"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="46"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9">
+        <v>2.5092673060789E-4</v>
+      </c>
+      <c r="K30" s="9">
+        <v>1.25463365303945E-4</v>
+      </c>
+      <c r="L30" s="9">
+        <v>2</v>
+      </c>
+      <c r="M30" s="9">
+        <v>109.245496603218</v>
+      </c>
+      <c r="N30" s="9">
+        <v>0.84060696008511204</v>
+      </c>
+      <c r="O30" s="9">
+        <v>0.43421981831232398</v>
+      </c>
+      <c r="P30" s="49"/>
+      <c r="Q30" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="R30" s="46"/>
+      <c r="S30" s="46"/>
+      <c r="T30" s="46"/>
+      <c r="U30" s="46"/>
+      <c r="V30" s="46"/>
+      <c r="W30" s="9"/>
+      <c r="X30" s="9">
+        <v>-2.56909740646773E-2</v>
+      </c>
+      <c r="Y30" s="9">
+        <v>5.0327094016775504E-3</v>
+      </c>
+      <c r="Z30" s="9">
+        <v>20.202116157369801</v>
+      </c>
+      <c r="AA30" s="9">
+        <v>-5.1047998233543499</v>
+      </c>
+      <c r="AB30" s="19">
+        <v>2.8425104165863402E-4</v>
+      </c>
+      <c r="AC30" s="9"/>
+    </row>
+    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A31" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="1">
+        <v>6176915.5049999999</v>
+      </c>
+      <c r="D31" s="1">
+        <v>6176915.5049999999</v>
+      </c>
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" s="1">
+        <v>71.888440000000003</v>
+      </c>
+      <c r="G31" s="1">
+        <v>167.3449876</v>
+      </c>
+      <c r="H31" s="4">
+        <v>1.898803E-20</v>
+      </c>
+      <c r="I31" s="1"/>
+      <c r="J31" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="R29" s="1">
-        <v>0.72477084209590303</v>
-      </c>
-      <c r="S29" s="1">
-        <v>3.6800772932671998E-2</v>
-      </c>
-      <c r="T29" s="1">
-        <v>29.8208206010118</v>
-      </c>
-      <c r="U29" s="1">
-        <v>-6.3396373813704798</v>
-      </c>
-      <c r="V29" s="6">
-        <v>3.2178754427736301E-6</v>
-      </c>
-      <c r="W29" s="1"/>
-      <c r="X29" s="30"/>
-      <c r="Y29" s="30"/>
-      <c r="Z29" s="30"/>
-      <c r="AA29" s="30"/>
-      <c r="AB29" s="30"/>
-      <c r="AC29" s="51"/>
-    </row>
-    <row r="30" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="41"/>
-      <c r="B30" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="30"/>
-      <c r="L30" s="30"/>
-      <c r="M30" s="30"/>
-      <c r="N30" s="30"/>
-      <c r="O30" s="30"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="R30" s="9">
-        <v>0.96911209387943398</v>
-      </c>
-      <c r="S30" s="9">
-        <v>5.29253214573484E-2</v>
-      </c>
-      <c r="T30" s="9">
-        <v>32.7933881713275</v>
-      </c>
-      <c r="U30" s="9">
-        <v>-0.57450545641731199</v>
-      </c>
-      <c r="V30" s="9">
-        <v>0.93899599371116504</v>
-      </c>
-      <c r="W30" s="9"/>
-      <c r="X30" s="31"/>
-      <c r="Y30" s="31"/>
-      <c r="Z30" s="31"/>
-      <c r="AA30" s="31"/>
-      <c r="AB30" s="31"/>
-      <c r="AC30" s="51"/>
-    </row>
-    <row r="31" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="1">
-        <v>21828870577.187302</v>
-      </c>
-      <c r="D31" s="1">
-        <v>21828870577.187302</v>
-      </c>
-      <c r="E31" s="1">
-        <v>1</v>
-      </c>
-      <c r="F31" s="1">
-        <v>69.360025998764399</v>
-      </c>
-      <c r="G31" s="1">
-        <v>150.637001976226</v>
-      </c>
-      <c r="H31" s="2">
-        <v>4.7200869189182898E-19</v>
-      </c>
-      <c r="I31" s="8"/>
-      <c r="J31" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="K31" s="42"/>
-      <c r="L31" s="42"/>
-      <c r="M31" s="42"/>
-      <c r="N31" s="42"/>
-      <c r="O31" s="42"/>
-      <c r="P31" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q31" s="49" t="s">
-        <v>29</v>
+      <c r="K31" s="44"/>
+      <c r="L31" s="44"/>
+      <c r="M31" s="44"/>
+      <c r="N31" s="44"/>
+      <c r="O31" s="44"/>
+      <c r="P31" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q31" s="31" t="s">
+        <v>27</v>
       </c>
       <c r="R31" s="13">
-        <v>26952.483888888899</v>
+        <v>529.6</v>
       </c>
       <c r="S31" s="13">
-        <v>3806.71007179046</v>
+        <v>60.754643373648697</v>
       </c>
       <c r="T31" s="13">
-        <v>70.469257492222297</v>
+        <v>73.255404219009407</v>
       </c>
       <c r="U31" s="13">
-        <v>7.0802565418941903</v>
-      </c>
-      <c r="V31" s="57">
-        <v>5.1032972292475198E-9</v>
+        <v>8.7170291946722998</v>
+      </c>
+      <c r="V31" s="15">
+        <v>0</v>
       </c>
       <c r="W31" s="13"/>
-      <c r="X31" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y31" s="30"/>
-      <c r="Z31" s="30"/>
-      <c r="AA31" s="30"/>
-      <c r="AB31" s="30"/>
-      <c r="AC31" s="53"/>
+      <c r="X31" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y31" s="57"/>
+      <c r="Z31" s="57"/>
+      <c r="AA31" s="57"/>
+      <c r="AB31" s="57"/>
+      <c r="AC31" s="35"/>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A32" s="33"/>
+      <c r="A32" s="48"/>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="1">
-        <v>11545764.943964699</v>
+        <v>50157.928</v>
       </c>
       <c r="D32" s="1">
-        <v>11545764.943964699</v>
+        <v>50157.928</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
       </c>
       <c r="F32" s="1">
-        <v>16.5068331927068</v>
+        <v>17.04102</v>
       </c>
       <c r="G32" s="1">
-        <v>7.9675190272952195E-2</v>
+        <v>1.3588785000000001</v>
       </c>
       <c r="H32" s="1">
-        <v>0.78124664232875995</v>
+        <v>0.2597892</v>
       </c>
       <c r="I32" s="1"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="30"/>
-      <c r="O32" s="30"/>
-      <c r="P32" s="33"/>
-      <c r="Q32" s="47" t="s">
-        <v>30</v>
+      <c r="J32" s="45"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="45"/>
+      <c r="M32" s="45"/>
+      <c r="N32" s="45"/>
+      <c r="O32" s="45"/>
+      <c r="P32" s="48"/>
+      <c r="Q32" s="31" t="s">
+        <v>28</v>
       </c>
       <c r="R32" s="1">
-        <v>34977.103075289997</v>
+        <v>499.42857142857201</v>
       </c>
       <c r="S32" s="1">
-        <v>3313.0752900440498</v>
+        <v>51.347045341752903</v>
       </c>
       <c r="T32" s="1">
-        <v>70.865874182612103</v>
+        <v>73.255404219009407</v>
       </c>
       <c r="U32" s="1">
-        <v>10.557291945763501</v>
+        <v>9.7265298928984407</v>
       </c>
       <c r="V32" s="2">
         <v>0</v>
       </c>
       <c r="W32" s="1"/>
-      <c r="X32" s="30"/>
-      <c r="Y32" s="30"/>
-      <c r="Z32" s="30"/>
-      <c r="AA32" s="30"/>
-      <c r="AB32" s="30"/>
-      <c r="AC32" s="51"/>
+      <c r="X32" s="45"/>
+      <c r="Y32" s="45"/>
+      <c r="Z32" s="45"/>
+      <c r="AA32" s="45"/>
+      <c r="AB32" s="45"/>
+      <c r="AC32" s="35"/>
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A33" s="33"/>
+      <c r="A33" s="48"/>
       <c r="B33" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="1">
+        <v>5310.1710000000003</v>
+      </c>
+      <c r="D33" s="1">
+        <v>5310.1710000000003</v>
+      </c>
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" s="1">
+        <v>71.888440000000003</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0.1438632</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0.7055884</v>
+      </c>
+      <c r="I33" s="1"/>
+      <c r="J33" s="45"/>
+      <c r="K33" s="45"/>
+      <c r="L33" s="45"/>
+      <c r="M33" s="45"/>
+      <c r="N33" s="45"/>
+      <c r="O33" s="45"/>
+      <c r="P33" s="48"/>
+      <c r="Q33" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="R33" s="13">
+        <v>60.370790372977901</v>
+      </c>
+      <c r="S33" s="13">
+        <v>76.168525940263294</v>
+      </c>
+      <c r="T33" s="13">
+        <v>33.630246929987997</v>
+      </c>
+      <c r="U33" s="13">
+        <v>0.79259496790478601</v>
+      </c>
+      <c r="V33" s="13">
+        <v>0.85729287706349799</v>
+      </c>
+      <c r="W33" s="1"/>
+      <c r="X33" s="45"/>
+      <c r="Y33" s="45"/>
+      <c r="Z33" s="45"/>
+      <c r="AA33" s="45"/>
+      <c r="AB33" s="45"/>
+      <c r="AC33" s="35"/>
+    </row>
+    <row r="34" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="49"/>
+      <c r="B34" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="58"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="58"/>
+      <c r="F34" s="58"/>
+      <c r="G34" s="58"/>
+      <c r="H34" s="58"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="46"/>
+      <c r="K34" s="46"/>
+      <c r="L34" s="46"/>
+      <c r="M34" s="46"/>
+      <c r="N34" s="46"/>
+      <c r="O34" s="46"/>
+      <c r="P34" s="49"/>
+      <c r="Q34" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="R34" s="9">
+        <v>90.5422189444065</v>
+      </c>
+      <c r="S34" s="9">
+        <v>76.168525940263294</v>
+      </c>
+      <c r="T34" s="9">
+        <v>33.630246929987997</v>
+      </c>
+      <c r="U34" s="9">
+        <v>1.1887090872077</v>
+      </c>
+      <c r="V34" s="9">
+        <v>0.63803985452722101</v>
+      </c>
+      <c r="W34" s="9"/>
+      <c r="X34" s="46"/>
+      <c r="Y34" s="46"/>
+      <c r="Z34" s="46"/>
+      <c r="AA34" s="46"/>
+      <c r="AB34" s="46"/>
+      <c r="AC34" s="36"/>
+    </row>
+    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A35" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="13">
+        <v>0.15432652470222299</v>
+      </c>
+      <c r="D35" s="13">
+        <v>0.15432652470222299</v>
+      </c>
+      <c r="E35" s="13">
+        <v>1</v>
+      </c>
+      <c r="F35" s="13">
+        <v>73.999999999267601</v>
+      </c>
+      <c r="G35" s="13">
+        <v>34.870200464865299</v>
+      </c>
+      <c r="H35" s="14">
+        <v>9.94550983787633E-8</v>
+      </c>
+      <c r="I35" s="13"/>
+      <c r="J35" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="K35" s="57"/>
+      <c r="L35" s="57"/>
+      <c r="M35" s="57"/>
+      <c r="N35" s="57"/>
+      <c r="O35" s="57"/>
+      <c r="P35" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q35" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="R35" s="13">
+        <v>1.0647504837794699</v>
+      </c>
+      <c r="S35" s="13">
+        <v>5.7194632959268799E-2</v>
+      </c>
+      <c r="T35" s="13">
+        <v>64.060522318169802</v>
+      </c>
+      <c r="U35" s="13">
+        <v>1.1679935236511501</v>
+      </c>
+      <c r="V35" s="13">
+        <v>0.64903708255730697</v>
+      </c>
+      <c r="W35" s="13"/>
+      <c r="X35" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y35" s="45"/>
+      <c r="Z35" s="45"/>
+      <c r="AA35" s="45"/>
+      <c r="AB35" s="45"/>
+      <c r="AC35" s="34"/>
+    </row>
+    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A36" s="48"/>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="1">
+        <v>0.111292819337707</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0.111292819337707</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1">
+        <v>73.999999999267601</v>
+      </c>
+      <c r="G36" s="1">
+        <v>25.146700660135899</v>
+      </c>
+      <c r="H36" s="4">
+        <v>3.5283045440115499E-6</v>
+      </c>
+      <c r="I36" s="1"/>
+      <c r="J36" s="45"/>
+      <c r="K36" s="45"/>
+      <c r="L36" s="45"/>
+      <c r="M36" s="45"/>
+      <c r="N36" s="45"/>
+      <c r="O36" s="45"/>
+      <c r="P36" s="48"/>
+      <c r="Q36" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="R36" s="1">
+        <v>1.42370872400263</v>
+      </c>
+      <c r="S36" s="1">
+        <v>6.5368840678580703E-2</v>
+      </c>
+      <c r="T36" s="1">
+        <v>63.0199737522519</v>
+      </c>
+      <c r="U36" s="1">
+        <v>7.6939839378934503</v>
+      </c>
+      <c r="V36" s="6">
+        <v>7.4586492537775898E-10</v>
+      </c>
+      <c r="W36" s="1"/>
+      <c r="X36" s="45"/>
+      <c r="Y36" s="45"/>
+      <c r="Z36" s="45"/>
+      <c r="AA36" s="45"/>
+      <c r="AB36" s="45"/>
+      <c r="AC36" s="35"/>
+    </row>
+    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A37" s="48"/>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="1">
+        <v>7.5267632704079004E-2</v>
+      </c>
+      <c r="D37" s="1">
+        <v>7.5267632704079004E-2</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1">
+        <v>73.999999999270102</v>
+      </c>
+      <c r="G37" s="1">
+        <v>17.006781212570601</v>
+      </c>
+      <c r="H37" s="4">
+        <v>9.6345615419962495E-5</v>
+      </c>
+      <c r="I37" s="1"/>
+      <c r="J37" s="45"/>
+      <c r="K37" s="45"/>
+      <c r="L37" s="45"/>
+      <c r="M37" s="45"/>
+      <c r="N37" s="45"/>
+      <c r="O37" s="45"/>
+      <c r="P37" s="48"/>
+      <c r="Q37" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="R37" s="1">
+        <v>0.72477084209590303</v>
+      </c>
+      <c r="S37" s="1">
+        <v>3.6800772932671998E-2</v>
+      </c>
+      <c r="T37" s="1">
+        <v>29.8208206010118</v>
+      </c>
+      <c r="U37" s="1">
+        <v>-6.3396373813704798</v>
+      </c>
+      <c r="V37" s="6">
+        <v>3.2178754427736301E-6</v>
+      </c>
+      <c r="W37" s="1"/>
+      <c r="X37" s="45"/>
+      <c r="Y37" s="45"/>
+      <c r="Z37" s="45"/>
+      <c r="AA37" s="45"/>
+      <c r="AB37" s="45"/>
+      <c r="AC37" s="35"/>
+    </row>
+    <row r="38" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="56"/>
+      <c r="B38" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38" s="59"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="59"/>
+      <c r="H38" s="59"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="45"/>
+      <c r="K38" s="45"/>
+      <c r="L38" s="45"/>
+      <c r="M38" s="45"/>
+      <c r="N38" s="45"/>
+      <c r="O38" s="45"/>
+      <c r="P38" s="56"/>
+      <c r="Q38" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="R38" s="9">
+        <v>0.96911209387943398</v>
+      </c>
+      <c r="S38" s="9">
+        <v>5.29253214573484E-2</v>
+      </c>
+      <c r="T38" s="9">
+        <v>32.7933881713275</v>
+      </c>
+      <c r="U38" s="9">
+        <v>-0.57450545641731199</v>
+      </c>
+      <c r="V38" s="9">
+        <v>0.93899599371116504</v>
+      </c>
+      <c r="W38" s="9"/>
+      <c r="X38" s="46"/>
+      <c r="Y38" s="46"/>
+      <c r="Z38" s="46"/>
+      <c r="AA38" s="46"/>
+      <c r="AB38" s="46"/>
+      <c r="AC38" s="35"/>
+    </row>
+    <row r="39" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="1">
+        <v>21828870577.187302</v>
+      </c>
+      <c r="D39" s="1">
+        <v>21828870577.187302</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
+      <c r="F39" s="1">
+        <v>69.360025998764399</v>
+      </c>
+      <c r="G39" s="1">
+        <v>150.637001976226</v>
+      </c>
+      <c r="H39" s="2">
+        <v>4.7200869189182898E-19</v>
+      </c>
+      <c r="I39" s="8"/>
+      <c r="J39" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="K39" s="44"/>
+      <c r="L39" s="44"/>
+      <c r="M39" s="44"/>
+      <c r="N39" s="44"/>
+      <c r="O39" s="44"/>
+      <c r="P39" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q39" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="R39" s="13">
+        <v>26952.483888888899</v>
+      </c>
+      <c r="S39" s="13">
+        <v>3806.71007179046</v>
+      </c>
+      <c r="T39" s="13">
+        <v>70.469257492222297</v>
+      </c>
+      <c r="U39" s="13">
+        <v>7.0802565418941903</v>
+      </c>
+      <c r="V39" s="41">
+        <v>5.1032972292475198E-9</v>
+      </c>
+      <c r="W39" s="13"/>
+      <c r="X39" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y39" s="45"/>
+      <c r="Z39" s="45"/>
+      <c r="AA39" s="45"/>
+      <c r="AB39" s="45"/>
+      <c r="AC39" s="37"/>
+    </row>
+    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A40" s="48"/>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="1">
+        <v>11545764.943964699</v>
+      </c>
+      <c r="D40" s="1">
+        <v>11545764.943964699</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1">
+        <v>16.5068331927068</v>
+      </c>
+      <c r="G40" s="1">
+        <v>7.9675190272952195E-2</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0.78124664232875995</v>
+      </c>
+      <c r="I40" s="1"/>
+      <c r="J40" s="45"/>
+      <c r="K40" s="45"/>
+      <c r="L40" s="45"/>
+      <c r="M40" s="45"/>
+      <c r="N40" s="45"/>
+      <c r="O40" s="45"/>
+      <c r="P40" s="48"/>
+      <c r="Q40" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="R40" s="1">
+        <v>34977.103075289997</v>
+      </c>
+      <c r="S40" s="1">
+        <v>3313.0752900440498</v>
+      </c>
+      <c r="T40" s="1">
+        <v>70.865874182612103</v>
+      </c>
+      <c r="U40" s="1">
+        <v>10.557291945763501</v>
+      </c>
+      <c r="V40" s="2">
+        <v>0</v>
+      </c>
+      <c r="W40" s="1"/>
+      <c r="X40" s="45"/>
+      <c r="Y40" s="45"/>
+      <c r="Z40" s="45"/>
+      <c r="AA40" s="45"/>
+      <c r="AB40" s="45"/>
+      <c r="AC40" s="35"/>
+    </row>
+    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A41" s="48"/>
+      <c r="B41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="1">
         <v>366508256.45689797</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D41" s="1">
         <v>366508256.45689797</v>
       </c>
-      <c r="E33" s="1">
-        <v>1</v>
-      </c>
-      <c r="F33" s="1">
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1">
         <v>69.360026001368695</v>
       </c>
-      <c r="G33" s="1">
+      <c r="G41" s="1">
         <v>2.52920574873438</v>
       </c>
-      <c r="H33" s="3">
+      <c r="H41" s="3">
         <v>0.116304482817742</v>
       </c>
-      <c r="I33" s="1"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="30"/>
-      <c r="L33" s="30"/>
-      <c r="M33" s="30"/>
-      <c r="N33" s="30"/>
-      <c r="O33" s="30"/>
-      <c r="P33" s="33"/>
-      <c r="Q33" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="R33" s="1">
+      <c r="I41" s="1"/>
+      <c r="J41" s="45"/>
+      <c r="K41" s="45"/>
+      <c r="L41" s="45"/>
+      <c r="M41" s="45"/>
+      <c r="N41" s="45"/>
+      <c r="O41" s="45"/>
+      <c r="P41" s="48"/>
+      <c r="Q41" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="R41" s="1">
         <v>-5094.1207890139503</v>
       </c>
-      <c r="S33" s="1">
+      <c r="S41" s="1">
         <v>4592.5547243374504</v>
       </c>
-      <c r="T33" s="1">
+      <c r="T41" s="1">
         <v>34.570504227394899</v>
       </c>
-      <c r="U33" s="1">
+      <c r="U41" s="1">
         <v>-1.10921286621116</v>
       </c>
-      <c r="V33" s="1">
+      <c r="V41" s="1">
         <v>0.68637145240327702</v>
       </c>
-      <c r="W33" s="1"/>
-      <c r="X33" s="30"/>
-      <c r="Y33" s="30"/>
-      <c r="Z33" s="30"/>
-      <c r="AA33" s="30"/>
-      <c r="AB33" s="30"/>
-      <c r="AC33" s="51"/>
-    </row>
-    <row r="34" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="34"/>
-      <c r="B34" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="43"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="31"/>
-      <c r="K34" s="31"/>
-      <c r="L34" s="31"/>
-      <c r="M34" s="31"/>
-      <c r="N34" s="31"/>
-      <c r="O34" s="31"/>
-      <c r="P34" s="34"/>
-      <c r="Q34" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="R34" s="9">
+      <c r="W41" s="1"/>
+      <c r="X41" s="45"/>
+      <c r="Y41" s="45"/>
+      <c r="Z41" s="45"/>
+      <c r="AA41" s="45"/>
+      <c r="AB41" s="45"/>
+      <c r="AC41" s="35"/>
+    </row>
+    <row r="42" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="49"/>
+      <c r="B42" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" s="58"/>
+      <c r="D42" s="58"/>
+      <c r="E42" s="58"/>
+      <c r="F42" s="58"/>
+      <c r="G42" s="58"/>
+      <c r="H42" s="58"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="46"/>
+      <c r="K42" s="46"/>
+      <c r="L42" s="46"/>
+      <c r="M42" s="46"/>
+      <c r="N42" s="46"/>
+      <c r="O42" s="46"/>
+      <c r="P42" s="49"/>
+      <c r="Q42" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="R42" s="9">
         <v>2930.4983973871599</v>
       </c>
-      <c r="S34" s="9">
+      <c r="S42" s="9">
         <v>4620.0903678267196</v>
       </c>
-      <c r="T34" s="9">
+      <c r="T42" s="9">
         <v>35.121845530194101</v>
       </c>
-      <c r="U34" s="9">
+      <c r="U42" s="9">
         <v>0.63429460553293504</v>
       </c>
-      <c r="V34" s="9">
+      <c r="V42" s="9">
         <v>0.92024495942184903</v>
       </c>
-      <c r="W34" s="9"/>
-      <c r="X34" s="31"/>
-      <c r="Y34" s="31"/>
-      <c r="Z34" s="31"/>
-      <c r="AA34" s="31"/>
-      <c r="AB34" s="31"/>
-      <c r="AC34" s="52"/>
-    </row>
-    <row r="35" spans="1:29" s="24" customFormat="1" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="R35" s="54"/>
-      <c r="S35" s="54"/>
-      <c r="T35" s="54"/>
-      <c r="U35" s="54"/>
-      <c r="V35" s="54"/>
-      <c r="W35" s="54"/>
-      <c r="X35" s="54"/>
-      <c r="Y35" s="54"/>
-      <c r="Z35" s="54"/>
-      <c r="AA35" s="54"/>
-      <c r="AB35" s="54"/>
-    </row>
-    <row r="36" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="32" t="s">
+      <c r="W42" s="9"/>
+      <c r="X42" s="46"/>
+      <c r="Y42" s="46"/>
+      <c r="Z42" s="46"/>
+      <c r="AA42" s="46"/>
+      <c r="AB42" s="46"/>
+      <c r="AC42" s="36"/>
+    </row>
+    <row r="43" spans="1:29" s="24" customFormat="1" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="R43" s="1"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="1"/>
+      <c r="U43" s="1"/>
+      <c r="V43" s="1"/>
+      <c r="W43" s="38"/>
+      <c r="X43" s="38"/>
+      <c r="Y43" s="38"/>
+      <c r="Z43" s="38"/>
+      <c r="AA43" s="38"/>
+      <c r="AB43" s="38"/>
+    </row>
+    <row r="44" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="47" t="s">
         <v>10</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" s="8">
-        <v>4.1857799097373602</v>
-      </c>
-      <c r="D36" s="8">
-        <v>4.1857799097373602</v>
-      </c>
-      <c r="E36" s="8">
-        <v>1</v>
-      </c>
-      <c r="F36" s="8">
-        <v>58.775295215237101</v>
-      </c>
-      <c r="G36" s="8">
-        <v>309.45174334807001</v>
-      </c>
-      <c r="H36" s="20">
-        <v>4.2882526567544902E-25</v>
-      </c>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8">
-        <v>0.23998054577629399</v>
-      </c>
-      <c r="K36" s="8">
-        <v>0.23998054577629399</v>
-      </c>
-      <c r="L36" s="8">
-        <v>1</v>
-      </c>
-      <c r="M36" s="8">
-        <v>107.186966242618</v>
-      </c>
-      <c r="N36" s="8">
-        <v>18.487688610543501</v>
-      </c>
-      <c r="O36" s="20">
-        <v>3.7826149790259799E-5</v>
-      </c>
-      <c r="P36" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q36" s="49" t="s">
-        <v>29</v>
-      </c>
-      <c r="R36" s="13">
-        <v>3.4885582678011602</v>
-      </c>
-      <c r="S36" s="13">
-        <v>0.34077366872468301</v>
-      </c>
-      <c r="T36" s="13">
-        <v>64.365339548907201</v>
-      </c>
-      <c r="U36" s="13">
-        <v>12.791227731171601</v>
-      </c>
-      <c r="V36" s="57">
-        <v>6.8500760619372199E-12</v>
-      </c>
-      <c r="W36" s="13"/>
-      <c r="X36" s="13">
-        <v>1.18961267546949</v>
-      </c>
-      <c r="Y36" s="13">
-        <v>7.87400338973991E-2</v>
-      </c>
-      <c r="Z36" s="13">
-        <v>108.78647642397399</v>
-      </c>
-      <c r="AA36" s="13">
-        <v>2.6231865466693001</v>
-      </c>
-      <c r="AB36" s="15">
-        <v>4.8257339848542601E-2</v>
-      </c>
-      <c r="AC36" s="53"/>
-    </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A37" s="33"/>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="1">
-        <v>3.6571648177047403E-2</v>
-      </c>
-      <c r="D37" s="1">
-        <v>3.6571648177047403E-2</v>
-      </c>
-      <c r="E37" s="1">
-        <v>1</v>
-      </c>
-      <c r="F37" s="1">
-        <v>14.508066856775899</v>
-      </c>
-      <c r="G37" s="1">
-        <v>2.7037160408679202</v>
-      </c>
-      <c r="H37" s="1">
-        <v>0.121602132726155</v>
-      </c>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1">
-        <v>0.14769196366738499</v>
-      </c>
-      <c r="K37" s="1">
-        <v>0.14769196366738499</v>
-      </c>
-      <c r="L37" s="1">
-        <v>1</v>
-      </c>
-      <c r="M37" s="1">
-        <v>12.379734112886799</v>
-      </c>
-      <c r="N37" s="1">
-        <v>11.3779349310574</v>
-      </c>
-      <c r="O37" s="2">
-        <v>5.3176769657787898E-3</v>
-      </c>
-      <c r="P37" s="33"/>
-      <c r="Q37" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="R37" s="1">
-        <v>2.5133660717598598</v>
-      </c>
-      <c r="S37" s="1">
-        <v>0.19049289539514599</v>
-      </c>
-      <c r="T37" s="1">
-        <v>63.108209870006597</v>
-      </c>
-      <c r="U37" s="1">
-        <v>12.159906390122</v>
-      </c>
-      <c r="V37" s="6">
-        <v>1.4851009311200901E-11</v>
-      </c>
-      <c r="W37" s="1"/>
-      <c r="X37" s="1">
-        <v>1.4189651337265199</v>
-      </c>
-      <c r="Y37" s="1">
-        <v>9.3909089545544305E-2</v>
-      </c>
-      <c r="Z37" s="1">
-        <v>107.355412830292</v>
-      </c>
-      <c r="AA37" s="1">
-        <v>5.2874049576690796</v>
-      </c>
-      <c r="AB37" s="6">
-        <v>3.9057126667296796E-6</v>
-      </c>
-      <c r="AC37" s="51"/>
-    </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A38" s="33"/>
-      <c r="B38" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="1">
-        <v>9.5456152618234799E-2</v>
-      </c>
-      <c r="D38" s="1">
-        <v>9.5456152618234799E-2</v>
-      </c>
-      <c r="E38" s="1">
-        <v>1</v>
-      </c>
-      <c r="F38" s="1">
-        <v>58.775295214428802</v>
-      </c>
-      <c r="G38" s="1">
-        <v>7.0570057379977396</v>
-      </c>
-      <c r="H38" s="2">
-        <v>1.01489929112641E-2</v>
-      </c>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1">
-        <v>4.6084357610204602E-2</v>
-      </c>
-      <c r="K38" s="1">
-        <v>4.6084357610204602E-2</v>
-      </c>
-      <c r="L38" s="1">
-        <v>1</v>
-      </c>
-      <c r="M38" s="1">
-        <v>106.783841827976</v>
-      </c>
-      <c r="N38" s="1">
-        <v>3.5502596702509801</v>
-      </c>
-      <c r="O38" s="3">
-        <v>6.2255752292747699E-2</v>
-      </c>
-      <c r="P38" s="33"/>
-      <c r="Q38" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="R38" s="1">
-        <v>0.85617382648215601</v>
-      </c>
-      <c r="S38" s="1">
-        <v>0.172185644358718</v>
-      </c>
-      <c r="T38" s="1">
-        <v>22.028120260493001</v>
-      </c>
-      <c r="U38" s="1">
-        <v>-0.77212162831534203</v>
-      </c>
-      <c r="V38" s="1">
-        <v>0.86614626486267499</v>
-      </c>
-      <c r="W38" s="1"/>
-      <c r="X38" s="1">
-        <v>0.60978596286354803</v>
-      </c>
-      <c r="Y38" s="1">
-        <v>7.9329350713881905E-2</v>
-      </c>
-      <c r="Z38" s="1">
-        <v>18.058113399132399</v>
-      </c>
-      <c r="AA38" s="1">
-        <v>-3.8022365669794702</v>
-      </c>
-      <c r="AB38" s="2">
-        <v>6.4825232500215204E-3</v>
-      </c>
-      <c r="AC38" s="51"/>
-    </row>
-    <row r="39" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="34"/>
-      <c r="B39" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C39" s="43"/>
-      <c r="D39" s="43"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="43"/>
-      <c r="G39" s="43"/>
-      <c r="H39" s="43"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="9">
-        <v>5.2456643231190104E-3</v>
-      </c>
-      <c r="K39" s="9">
-        <v>2.6228321615595E-3</v>
-      </c>
-      <c r="L39" s="9">
-        <v>2</v>
-      </c>
-      <c r="M39" s="9">
-        <v>106.82092564483</v>
-      </c>
-      <c r="N39" s="9">
-        <v>0.202058479881251</v>
-      </c>
-      <c r="O39" s="9">
-        <v>0.81735870029617597</v>
-      </c>
-      <c r="P39" s="34"/>
-      <c r="Q39" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="R39" s="9">
-        <v>0.61683884338999295</v>
-      </c>
-      <c r="S39" s="9">
-        <v>0.127475526699626</v>
-      </c>
-      <c r="T39" s="9">
-        <v>23.947765360715401</v>
-      </c>
-      <c r="U39" s="9">
-        <v>-2.33789294579128</v>
-      </c>
-      <c r="V39" s="58">
-        <v>0.117444223101661</v>
-      </c>
-      <c r="W39" s="9"/>
-      <c r="X39" s="9">
-        <v>0.72735020244950499</v>
-      </c>
-      <c r="Y39" s="9">
-        <v>9.3762951214816995E-2</v>
-      </c>
-      <c r="Z39" s="9">
-        <v>17.935412892733801</v>
-      </c>
-      <c r="AA39" s="9">
-        <v>-2.46952451364385</v>
-      </c>
-      <c r="AB39" s="58">
-        <v>9.9463258029382301E-2</v>
-      </c>
-      <c r="AC39" s="52"/>
-    </row>
-    <row r="40" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" s="8">
-        <v>3.75533617845436</v>
-      </c>
-      <c r="D40" s="8">
-        <v>3.75533617845436</v>
-      </c>
-      <c r="E40" s="8">
-        <v>1</v>
-      </c>
-      <c r="F40" s="8">
-        <v>58.450172749992298</v>
-      </c>
-      <c r="G40" s="8">
-        <v>275.61367619126997</v>
-      </c>
-      <c r="H40" s="20">
-        <v>8.5561055144156804E-24</v>
-      </c>
-      <c r="I40" s="8"/>
-      <c r="J40" s="8">
-        <v>0.12745796635020001</v>
-      </c>
-      <c r="K40" s="8">
-        <v>0.12745796635020001</v>
-      </c>
-      <c r="L40" s="8">
-        <v>1</v>
-      </c>
-      <c r="M40" s="8">
-        <v>106.169152592015</v>
-      </c>
-      <c r="N40" s="8">
-        <v>9.7924313998268993</v>
-      </c>
-      <c r="O40" s="21">
-        <v>2.2627938793836001E-3</v>
-      </c>
-      <c r="P40" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q40" s="49" t="s">
-        <v>29</v>
-      </c>
-      <c r="R40" s="13">
-        <v>3.2377296483895002</v>
-      </c>
-      <c r="S40" s="13">
-        <v>0.31711097347862399</v>
-      </c>
-      <c r="T40" s="13">
-        <v>64.620317991065903</v>
-      </c>
-      <c r="U40" s="13">
-        <v>11.9955453640014</v>
-      </c>
-      <c r="V40" s="57">
-        <v>4.7758463850300399E-12</v>
-      </c>
-      <c r="W40" s="13"/>
-      <c r="X40" s="13">
-        <v>1.06502116132782</v>
-      </c>
-      <c r="Y40" s="13">
-        <v>7.0595370176184405E-2</v>
-      </c>
-      <c r="Z40" s="13">
-        <v>107.75630430099601</v>
-      </c>
-      <c r="AA40" s="13">
-        <v>0.95035489024084097</v>
-      </c>
-      <c r="AB40" s="13">
-        <v>0.77770115602609902</v>
-      </c>
-      <c r="AC40" s="53"/>
-    </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A41" s="33"/>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="1">
-        <v>3.8005186893600197E-2</v>
-      </c>
-      <c r="D41" s="1">
-        <v>3.8005186893600197E-2</v>
-      </c>
-      <c r="E41" s="1">
-        <v>1</v>
-      </c>
-      <c r="F41" s="1">
-        <v>14.0776142021772</v>
-      </c>
-      <c r="G41" s="1">
-        <v>2.7892973561671002</v>
-      </c>
-      <c r="H41" s="1">
-        <v>0.116971279359414</v>
-      </c>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1">
-        <v>0.116553339771977</v>
-      </c>
-      <c r="K41" s="1">
-        <v>0.116553339771977</v>
-      </c>
-      <c r="L41" s="1">
-        <v>1</v>
-      </c>
-      <c r="M41" s="1">
-        <v>12.391275226041101</v>
-      </c>
-      <c r="N41" s="1">
-        <v>8.9546429840398503</v>
-      </c>
-      <c r="O41" s="2">
-        <v>1.08776102041225E-2</v>
-      </c>
-      <c r="P41" s="33"/>
-      <c r="Q41" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="R41" s="1">
-        <v>2.4100475780322799</v>
-      </c>
-      <c r="S41" s="1">
-        <v>0.183247763022612</v>
-      </c>
-      <c r="T41" s="1">
-        <v>63.2313001359989</v>
-      </c>
-      <c r="U41" s="1">
-        <v>11.568981011960799</v>
-      </c>
-      <c r="V41" s="6">
-        <v>1.42040823547518E-11</v>
-      </c>
-      <c r="W41" s="1"/>
-      <c r="X41" s="1">
-        <v>1.33180279529643</v>
-      </c>
-      <c r="Y41" s="1">
-        <v>8.9113002620625797E-2</v>
-      </c>
-      <c r="Z41" s="1">
-        <v>106.407230170926</v>
-      </c>
-      <c r="AA41" s="1">
-        <v>4.28227214637751</v>
-      </c>
-      <c r="AB41" s="2">
-        <v>2.3530865040188899E-4</v>
-      </c>
-      <c r="AC41" s="51"/>
-    </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A42" s="33"/>
-      <c r="B42" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" s="1">
-        <v>7.7542068403545703E-2</v>
-      </c>
-      <c r="D42" s="1">
-        <v>7.7542068403545703E-2</v>
-      </c>
-      <c r="E42" s="1">
-        <v>1</v>
-      </c>
-      <c r="F42" s="1">
-        <v>58.450172750997197</v>
-      </c>
-      <c r="G42" s="1">
-        <v>5.6910096770543701</v>
-      </c>
-      <c r="H42" s="2">
-        <v>2.0312618497821299E-2</v>
-      </c>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1">
-        <v>7.3363893765149693E-2</v>
-      </c>
-      <c r="K42" s="1">
-        <v>7.3363893765149693E-2</v>
-      </c>
-      <c r="L42" s="1">
-        <v>1</v>
-      </c>
-      <c r="M42" s="1">
-        <v>105.814592900958</v>
-      </c>
-      <c r="N42" s="1">
-        <v>5.6364534716137902</v>
-      </c>
-      <c r="O42" s="2">
-        <v>1.9393437026140801E-2</v>
-      </c>
-      <c r="P42" s="33"/>
-      <c r="Q42" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="R42" s="1">
-        <v>0.85359620150672499</v>
-      </c>
-      <c r="S42" s="1">
-        <v>0.16273753063115801</v>
-      </c>
-      <c r="T42" s="1">
-        <v>22.436551986687999</v>
-      </c>
-      <c r="U42" s="1">
-        <v>-0.83030473743369204</v>
-      </c>
-      <c r="V42" s="1">
-        <v>0.83952497968902495</v>
-      </c>
-      <c r="W42" s="1"/>
-      <c r="X42" s="1">
-        <v>0.62041460191210296</v>
-      </c>
-      <c r="Y42" s="1">
-        <v>8.16466707193544E-2</v>
-      </c>
-      <c r="Z42" s="1">
-        <v>17.9186243183957</v>
-      </c>
-      <c r="AA42" s="1">
-        <v>-3.62740633544988</v>
-      </c>
-      <c r="AB42" s="2">
-        <v>9.5259666762890199E-3</v>
-      </c>
-      <c r="AC42" s="51"/>
-    </row>
-    <row r="43" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="34"/>
-      <c r="B43" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C43" s="43"/>
-      <c r="D43" s="43"/>
-      <c r="E43" s="43"/>
-      <c r="F43" s="43"/>
-      <c r="G43" s="43"/>
-      <c r="H43" s="43"/>
-      <c r="I43" s="9"/>
-      <c r="J43" s="9">
-        <v>7.5239018444935397E-3</v>
-      </c>
-      <c r="K43" s="9">
-        <v>3.7619509222467699E-3</v>
-      </c>
-      <c r="L43" s="9">
-        <v>2</v>
-      </c>
-      <c r="M43" s="9">
-        <v>105.84740366368401</v>
-      </c>
-      <c r="N43" s="9">
-        <v>0.28902584428814998</v>
-      </c>
-      <c r="O43" s="9">
-        <v>0.74958204967156605</v>
-      </c>
-      <c r="P43" s="34"/>
-      <c r="Q43" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="R43" s="9">
-        <v>0.63538580470489003</v>
-      </c>
-      <c r="S43" s="9">
-        <v>0.124810867031525</v>
-      </c>
-      <c r="T43" s="9">
-        <v>24.517870816947401</v>
-      </c>
-      <c r="U43" s="9">
-        <v>-2.3087894381868401</v>
-      </c>
-      <c r="V43" s="58">
-        <v>0.123498755965347</v>
-      </c>
-      <c r="W43" s="9"/>
-      <c r="X43" s="9">
-        <v>0.77582486721588295</v>
-      </c>
-      <c r="Y43" s="9">
-        <v>0.10141542139468999</v>
-      </c>
-      <c r="Z43" s="9">
-        <v>17.956705334484202</v>
-      </c>
-      <c r="AA43" s="9">
-        <v>-1.9417800269687</v>
-      </c>
-      <c r="AB43" s="9">
-        <v>0.24640381353586799</v>
-      </c>
-      <c r="AC43" s="52"/>
-    </row>
-    <row r="44" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="32" t="s">
-        <v>11</v>
       </c>
       <c r="B44" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="22">
-        <v>1.6044459576046901</v>
-      </c>
-      <c r="D44" s="22">
-        <v>1.6044459576046901</v>
-      </c>
-      <c r="E44" s="22">
-        <v>1</v>
-      </c>
-      <c r="F44" s="22">
-        <v>57.941257724360497</v>
-      </c>
-      <c r="G44" s="22">
-        <v>114.44647303148901</v>
-      </c>
-      <c r="H44" s="25">
-        <v>2.4310901681812699E-15</v>
+      <c r="C44" s="8">
+        <v>4.1857799097373602</v>
+      </c>
+      <c r="D44" s="8">
+        <v>4.1857799097373602</v>
+      </c>
+      <c r="E44" s="8">
+        <v>1</v>
+      </c>
+      <c r="F44" s="8">
+        <v>58.775295215237101</v>
+      </c>
+      <c r="G44" s="8">
+        <v>309.45174334807001</v>
+      </c>
+      <c r="H44" s="20">
+        <v>4.2882526567544902E-25</v>
       </c>
       <c r="I44" s="8"/>
-      <c r="J44" s="26">
-        <v>3.27228460982109E-6</v>
-      </c>
-      <c r="K44" s="26">
-        <v>3.27228460982109E-6</v>
+      <c r="J44" s="8">
+        <v>0.23998054577629399</v>
+      </c>
+      <c r="K44" s="8">
+        <v>0.23998054577629399</v>
       </c>
       <c r="L44" s="8">
         <v>1</v>
       </c>
       <c r="M44" s="8">
-        <v>108.162570470471</v>
+        <v>107.186966242618</v>
       </c>
       <c r="N44" s="8">
-        <v>0.81526923567301701</v>
-      </c>
-      <c r="O44" s="8">
-        <v>0.36857341395755699</v>
-      </c>
-      <c r="P44" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q44" s="49" t="s">
-        <v>29</v>
+        <v>18.487688610543501</v>
+      </c>
+      <c r="O44" s="20">
+        <v>3.7826149790259799E-5</v>
+      </c>
+      <c r="P44" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q44" s="33" t="s">
+        <v>27</v>
       </c>
       <c r="R44" s="13">
-        <v>2.0739376031193602</v>
+        <v>3.4885582678011602</v>
       </c>
       <c r="S44" s="13">
-        <v>0.20636183828608401</v>
+        <v>0.34077366872468301</v>
       </c>
       <c r="T44" s="13">
-        <v>64.217630489307894</v>
+        <v>64.365339548907201</v>
       </c>
       <c r="U44" s="13">
-        <v>7.3309666803809703</v>
-      </c>
-      <c r="V44" s="57">
-        <v>2.8690905207184898E-9</v>
+        <v>12.791227731171601</v>
+      </c>
+      <c r="V44" s="41">
+        <v>6.8500760619372199E-12</v>
       </c>
       <c r="W44" s="13"/>
       <c r="X44" s="13">
-        <v>-4.72831811858727E-4</v>
+        <v>1.18961267546949</v>
       </c>
       <c r="Y44" s="13">
-        <v>5.0511625514736505E-4</v>
+        <v>7.87400338973991E-2</v>
       </c>
       <c r="Z44" s="13">
-        <v>108.947220351745</v>
+        <v>108.78647642397399</v>
       </c>
       <c r="AA44" s="13">
-        <v>-0.93608512305900804</v>
-      </c>
-      <c r="AB44" s="13">
-        <v>0.78552588991913097</v>
-      </c>
-      <c r="AC44" s="53"/>
+        <v>2.6231865466693001</v>
+      </c>
+      <c r="AB44" s="15">
+        <v>4.8257339848542601E-2</v>
+      </c>
+      <c r="AC44" s="37"/>
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A45" s="33"/>
+      <c r="A45" s="48"/>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C45">
-        <v>5.7241252178794499E-2</v>
-      </c>
-      <c r="D45">
-        <v>5.7241252178794499E-2</v>
-      </c>
-      <c r="E45">
-        <v>1</v>
-      </c>
-      <c r="F45">
-        <v>14.016499111022799</v>
-      </c>
-      <c r="G45">
-        <v>4.0830664272103698</v>
-      </c>
-      <c r="H45" s="7">
-        <v>6.28474981350714E-2</v>
+      <c r="C45" s="1">
+        <v>3.6571648177047403E-2</v>
+      </c>
+      <c r="D45" s="1">
+        <v>3.6571648177047403E-2</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
+      <c r="F45" s="1">
+        <v>14.508066856775899</v>
+      </c>
+      <c r="G45" s="1">
+        <v>2.7037160408679202</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0.121602132726155</v>
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1">
-        <v>1.1254087942051899E-4</v>
+        <v>0.14769196366738499</v>
       </c>
       <c r="K45" s="1">
-        <v>1.1254087942051899E-4</v>
+        <v>0.14769196366738499</v>
       </c>
       <c r="L45" s="1">
         <v>1</v>
       </c>
       <c r="M45" s="1">
-        <v>13.1287610221782</v>
+        <v>12.379734112886799</v>
       </c>
       <c r="N45" s="1">
-        <v>28.038855933179999</v>
+        <v>11.3779349310574</v>
       </c>
       <c r="O45" s="2">
-        <v>1.4035037213878999E-4</v>
-      </c>
-      <c r="P45" s="33"/>
-      <c r="Q45" s="47" t="s">
-        <v>30</v>
+        <v>5.3176769657787898E-3</v>
+      </c>
+      <c r="P45" s="48"/>
+      <c r="Q45" s="31" t="s">
+        <v>28</v>
       </c>
       <c r="R45" s="1">
-        <v>1.8504898868847499</v>
+        <v>2.5133660717598598</v>
       </c>
       <c r="S45" s="1">
-        <v>0.14281987253321901</v>
+        <v>0.19049289539514599</v>
       </c>
       <c r="T45" s="1">
-        <v>63.037530931724902</v>
+        <v>63.108209870006597</v>
       </c>
       <c r="U45" s="1">
-        <v>7.9742737143899101</v>
+        <v>12.159906390122</v>
       </c>
       <c r="V45" s="6">
-        <v>2.5103985556995698E-10</v>
+        <v>1.4851009311200901E-11</v>
       </c>
       <c r="W45" s="1"/>
       <c r="X45" s="1">
-        <v>4.9280938617282297E-4</v>
+        <v>1.4189651337265199</v>
       </c>
       <c r="Y45" s="1">
-        <v>5.05401745277116E-4</v>
+        <v>9.3909089545544305E-2</v>
       </c>
       <c r="Z45" s="1">
-        <v>107.441893549743</v>
+        <v>107.355412830292</v>
       </c>
       <c r="AA45" s="1">
-        <v>0.97508445662887799</v>
-      </c>
-      <c r="AB45" s="1">
-        <v>0.76389978434717098</v>
-      </c>
-      <c r="AC45" s="51"/>
+        <v>5.2874049576690796</v>
+      </c>
+      <c r="AB45" s="6">
+        <v>3.9057126667296796E-6</v>
+      </c>
+      <c r="AC45" s="35"/>
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A46" s="33"/>
+      <c r="A46" s="48"/>
       <c r="B46" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C46">
-        <v>1.15277522221443E-2</v>
-      </c>
-      <c r="D46">
-        <v>1.15277522221443E-2</v>
-      </c>
-      <c r="E46">
-        <v>1</v>
-      </c>
-      <c r="F46">
-        <v>57.941257724235903</v>
-      </c>
-      <c r="G46">
-        <v>0.82228421440567401</v>
-      </c>
-      <c r="H46">
-        <v>0.36826900260683199</v>
+      <c r="C46" s="1">
+        <v>9.5456152618234799E-2</v>
+      </c>
+      <c r="D46" s="1">
+        <v>9.5456152618234799E-2</v>
+      </c>
+      <c r="E46" s="1">
+        <v>1</v>
+      </c>
+      <c r="F46" s="1">
+        <v>58.775295214428802</v>
+      </c>
+      <c r="G46" s="1">
+        <v>7.0570057379977396</v>
+      </c>
+      <c r="H46" s="2">
+        <v>1.01489929112641E-2</v>
       </c>
       <c r="I46" s="1"/>
-      <c r="J46" s="5">
-        <v>7.3359735284969697E-6</v>
-      </c>
-      <c r="K46" s="5">
-        <v>7.3359735284969697E-6</v>
+      <c r="J46" s="1">
+        <v>4.6084357610204602E-2</v>
+      </c>
+      <c r="K46" s="1">
+        <v>4.6084357610204602E-2</v>
       </c>
       <c r="L46" s="1">
         <v>1</v>
       </c>
       <c r="M46" s="1">
-        <v>107.80326229592799</v>
+        <v>106.783841827976</v>
       </c>
       <c r="N46" s="1">
-        <v>1.82771190303713</v>
-      </c>
-      <c r="O46" s="1">
-        <v>0.179227673464389</v>
-      </c>
-      <c r="P46" s="33"/>
-      <c r="Q46" s="47" t="s">
-        <v>31</v>
+        <v>3.5502596702509801</v>
+      </c>
+      <c r="O46" s="3">
+        <v>6.2255752292747699E-2</v>
+      </c>
+      <c r="P46" s="48"/>
+      <c r="Q46" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="R46" s="1">
-        <v>0.69912820784997998</v>
+        <v>0.85617382648215601</v>
       </c>
       <c r="S46" s="1">
-        <v>0.148324307575951</v>
+        <v>0.172185644358718</v>
       </c>
       <c r="T46" s="1">
-        <v>21.800179035140999</v>
+        <v>22.028120260493001</v>
       </c>
       <c r="U46" s="1">
-        <v>-1.68706510404384</v>
+        <v>-0.77212162831534203</v>
       </c>
       <c r="V46" s="1">
-        <v>0.35412379934024302</v>
+        <v>0.86614626486267499</v>
       </c>
       <c r="W46" s="1"/>
       <c r="X46" s="1">
-        <v>-4.8894271875510997E-3</v>
+        <v>0.60978596286354803</v>
       </c>
       <c r="Y46" s="1">
-        <v>9.1172534711224601E-4</v>
+        <v>7.9329350713881905E-2</v>
       </c>
       <c r="Z46" s="1">
-        <v>18.9122122903484</v>
+        <v>18.058113399132399</v>
       </c>
       <c r="AA46" s="1">
-        <v>-5.3628290614466696</v>
+        <v>-3.8022365669794702</v>
       </c>
       <c r="AB46" s="2">
-        <v>1.9550438579263299E-4</v>
-      </c>
-      <c r="AC46" s="51"/>
+        <v>6.4825232500215204E-3</v>
+      </c>
+      <c r="AC46" s="35"/>
     </row>
     <row r="47" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="34"/>
+      <c r="A47" s="49"/>
       <c r="B47" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C47" s="43"/>
-      <c r="D47" s="43"/>
-      <c r="E47" s="43"/>
-      <c r="F47" s="43"/>
-      <c r="G47" s="43"/>
-      <c r="H47" s="43"/>
+        <v>48</v>
+      </c>
+      <c r="C47" s="58"/>
+      <c r="D47" s="58"/>
+      <c r="E47" s="58"/>
+      <c r="F47" s="58"/>
+      <c r="G47" s="58"/>
+      <c r="H47" s="58"/>
       <c r="I47" s="9"/>
-      <c r="J47" s="27">
-        <v>7.2143853443936604E-6</v>
-      </c>
-      <c r="K47" s="27">
-        <v>3.6071926721968302E-6</v>
+      <c r="J47" s="9">
+        <v>5.2456643231190104E-3</v>
+      </c>
+      <c r="K47" s="9">
+        <v>2.6228321615595E-3</v>
       </c>
       <c r="L47" s="9">
         <v>2</v>
       </c>
       <c r="M47" s="9">
-        <v>107.842517864377</v>
+        <v>106.82092564483</v>
       </c>
       <c r="N47" s="9">
-        <v>0.89870948387585703</v>
+        <v>0.202058479881251</v>
       </c>
       <c r="O47" s="9">
-        <v>0.41012132536637402</v>
-      </c>
-      <c r="P47" s="34"/>
-      <c r="Q47" s="48" t="s">
-        <v>32</v>
+        <v>0.81735870029617597</v>
+      </c>
+      <c r="P47" s="49"/>
+      <c r="Q47" s="32" t="s">
+        <v>30</v>
       </c>
       <c r="R47" s="9">
-        <v>0.62380356878450904</v>
+        <v>0.61683884338999295</v>
       </c>
       <c r="S47" s="9">
-        <v>0.13578145981755799</v>
+        <v>0.127475526699626</v>
       </c>
       <c r="T47" s="9">
-        <v>23.6213122095755</v>
+        <v>23.947765360715401</v>
       </c>
       <c r="U47" s="9">
-        <v>-2.1680811723975899</v>
-      </c>
-      <c r="V47" s="9">
-        <v>0.16142822200252099</v>
+        <v>-2.33789294579128</v>
+      </c>
+      <c r="V47" s="42">
+        <v>0.117444223101661</v>
       </c>
       <c r="W47" s="9"/>
       <c r="X47" s="9">
-        <v>-3.9237859895195496E-3</v>
+        <v>0.72735020244950499</v>
       </c>
       <c r="Y47" s="9">
-        <v>9.0311675397618501E-4</v>
+        <v>9.3762951214816995E-2</v>
       </c>
       <c r="Z47" s="9">
-        <v>18.890902844266801</v>
+        <v>17.935412892733801</v>
       </c>
       <c r="AA47" s="9">
-        <v>-4.3447161978162399</v>
-      </c>
-      <c r="AB47" s="19">
-        <v>1.8370895217705301E-3</v>
-      </c>
-      <c r="AC47" s="52"/>
+        <v>-2.46952451364385</v>
+      </c>
+      <c r="AB47" s="42">
+        <v>9.9463258029382301E-2</v>
+      </c>
+      <c r="AC47" s="36"/>
     </row>
     <row r="48" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="32" t="s">
-        <v>12</v>
+      <c r="A48" s="47" t="s">
+        <v>25</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C48" s="8">
-        <v>3.2828058473639601</v>
+        <v>3.75533617845436</v>
       </c>
       <c r="D48" s="8">
-        <v>3.2828058473639601</v>
+        <v>3.75533617845436</v>
       </c>
       <c r="E48" s="8">
         <v>1</v>
       </c>
       <c r="F48" s="8">
-        <v>57.1027846481349</v>
+        <v>58.450172749992298</v>
       </c>
       <c r="G48" s="8">
-        <v>315.57785828471202</v>
+        <v>275.61367619126997</v>
       </c>
       <c r="H48" s="20">
-        <v>6.2556135251351003E-25</v>
+        <v>8.5561055144156804E-24</v>
       </c>
       <c r="I48" s="8"/>
       <c r="J48" s="8">
-        <v>4.9581564592565801</v>
+        <v>0.12745796635020001</v>
       </c>
       <c r="K48" s="8">
-        <v>4.9581564592565801</v>
+        <v>0.12745796635020001</v>
       </c>
       <c r="L48" s="8">
         <v>1</v>
       </c>
       <c r="M48" s="8">
-        <v>107.087389174327</v>
+        <v>106.169152592015</v>
       </c>
       <c r="N48" s="8">
-        <v>15.8163561438312</v>
+        <v>9.7924313998268993</v>
       </c>
       <c r="O48" s="21">
-        <v>1.2711861864362099E-4</v>
-      </c>
-      <c r="P48" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q48" s="49" t="s">
-        <v>29</v>
+        <v>2.2627938793836001E-3</v>
+      </c>
+      <c r="P48" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q48" s="33" t="s">
+        <v>27</v>
       </c>
       <c r="R48" s="13">
-        <v>3.25039616887112</v>
+        <v>3.2377296483895002</v>
       </c>
       <c r="S48" s="13">
-        <v>0.28598369641782101</v>
+        <v>0.31711097347862399</v>
       </c>
       <c r="T48" s="13">
-        <v>64.098058733478297</v>
+        <v>64.620317991065903</v>
       </c>
       <c r="U48" s="13">
-        <v>13.3975884833244</v>
-      </c>
-      <c r="V48" s="57">
-        <v>8.8387075436457995E-12</v>
+        <v>11.9955453640014</v>
+      </c>
+      <c r="V48" s="41">
+        <v>4.7758463850300399E-12</v>
       </c>
       <c r="W48" s="13"/>
       <c r="X48" s="13">
-        <v>0.231107865381736</v>
+        <v>1.06502116132782</v>
       </c>
       <c r="Y48" s="13">
-        <v>0.141033950135908</v>
+        <v>7.0595370176184405E-2</v>
       </c>
       <c r="Z48" s="13">
-        <v>109.142880527442</v>
+        <v>107.75630430099601</v>
       </c>
       <c r="AA48" s="13">
-        <v>1.63866831467904</v>
+        <v>0.95035489024084097</v>
       </c>
       <c r="AB48" s="13">
-        <v>0.361442574294079</v>
-      </c>
-      <c r="AC48" s="53"/>
+        <v>0.77770115602609902</v>
+      </c>
+      <c r="AC48" s="37"/>
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A49" s="33"/>
+      <c r="A49" s="48"/>
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="1">
-        <v>6.9098899300225596E-4</v>
+        <v>3.8005186893600197E-2</v>
       </c>
       <c r="D49" s="1">
-        <v>6.9098899300225596E-4</v>
+        <v>3.8005186893600197E-2</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
       </c>
       <c r="F49" s="1">
-        <v>13.6400199665374</v>
+        <v>14.0776142021772</v>
       </c>
       <c r="G49" s="1">
-        <v>6.6425136498724599E-2</v>
+        <v>2.7892973561671002</v>
       </c>
       <c r="H49" s="1">
-        <v>0.80046236006191795</v>
+        <v>0.116971279359414</v>
       </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1">
-        <v>1.93826224654098E-2</v>
+        <v>0.116553339771977</v>
       </c>
       <c r="K49" s="1">
-        <v>1.93826224654098E-2</v>
+        <v>0.116553339771977</v>
       </c>
       <c r="L49" s="1">
         <v>1</v>
       </c>
       <c r="M49" s="1">
-        <v>11.8724826464864</v>
+        <v>12.391275226041101</v>
       </c>
       <c r="N49" s="1">
-        <v>6.1829928610262298E-2</v>
-      </c>
-      <c r="O49" s="1">
-        <v>0.80787586394532096</v>
-      </c>
-      <c r="P49" s="33"/>
-      <c r="Q49" s="47" t="s">
-        <v>30</v>
+        <v>8.9546429840398503</v>
+      </c>
+      <c r="O49" s="2">
+        <v>1.08776102041225E-2</v>
+      </c>
+      <c r="P49" s="48"/>
+      <c r="Q49" s="31" t="s">
+        <v>28</v>
       </c>
       <c r="R49" s="1">
-        <v>2.1892524295195499</v>
+        <v>2.4100475780322799</v>
       </c>
       <c r="S49" s="1">
-        <v>0.14734976342700101</v>
+        <v>0.183247763022612</v>
       </c>
       <c r="T49" s="1">
-        <v>61.439546816495699</v>
+        <v>63.2313001359989</v>
       </c>
       <c r="U49" s="1">
-        <v>11.641762270683</v>
+        <v>11.568981011960799</v>
       </c>
       <c r="V49" s="6">
-        <v>1.9951040819421499E-11</v>
+        <v>1.42040823547518E-11</v>
       </c>
       <c r="W49" s="1"/>
       <c r="X49" s="1">
-        <v>0.67677558509185598</v>
+        <v>1.33180279529643</v>
       </c>
       <c r="Y49" s="1">
-        <v>0.14123776247129999</v>
+        <v>8.9113002620625797E-2</v>
       </c>
       <c r="Z49" s="1">
-        <v>107.564370903827</v>
+        <v>106.407230170926</v>
       </c>
       <c r="AA49" s="1">
-        <v>4.7917467202114503</v>
-      </c>
-      <c r="AB49" s="6">
-        <v>3.1319294462428497E-5</v>
-      </c>
-      <c r="AC49" s="51"/>
+        <v>4.28227214637751</v>
+      </c>
+      <c r="AB49" s="2">
+        <v>2.3530865040188899E-4</v>
+      </c>
+      <c r="AC49" s="35"/>
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A50" s="33"/>
+      <c r="A50" s="48"/>
       <c r="B50" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C50" s="1">
-        <v>0.13315844295854501</v>
+        <v>7.7542068403545703E-2</v>
       </c>
       <c r="D50" s="1">
-        <v>0.13315844295854501</v>
+        <v>7.7542068403545703E-2</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
       </c>
       <c r="F50" s="1">
-        <v>57.102784645779103</v>
+        <v>58.450172750997197</v>
       </c>
       <c r="G50" s="1">
-        <v>12.800591382864701</v>
+        <v>5.6910096770543701</v>
       </c>
       <c r="H50" s="2">
-        <v>7.1467481949516205E-4</v>
+        <v>2.0312618497821299E-2</v>
       </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1">
-        <v>1.5642063102591399</v>
+        <v>7.3363893765149693E-2</v>
       </c>
       <c r="K50" s="1">
-        <v>1.5642063102591399</v>
+        <v>7.3363893765149693E-2</v>
       </c>
       <c r="L50" s="1">
         <v>1</v>
       </c>
       <c r="M50" s="1">
-        <v>106.739383464101</v>
+        <v>105.814592900958</v>
       </c>
       <c r="N50" s="1">
-        <v>4.9897667184944403</v>
+        <v>5.6364534716137902</v>
       </c>
       <c r="O50" s="2">
-        <v>2.7582949079364601E-2</v>
-      </c>
-      <c r="P50" s="33"/>
-      <c r="Q50" s="47" t="s">
-        <v>31</v>
+        <v>1.9393437026140801E-2</v>
+      </c>
+      <c r="P50" s="48"/>
+      <c r="Q50" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="R50" s="1">
-        <v>1.1692225136694301</v>
+        <v>0.85359620150672499</v>
       </c>
       <c r="S50" s="1">
-        <v>0.196811825263492</v>
+        <v>0.16273753063115801</v>
       </c>
       <c r="T50" s="1">
-        <v>23.0448591919385</v>
+        <v>22.436551986687999</v>
       </c>
       <c r="U50" s="1">
-        <v>0.92878103054844996</v>
+        <v>-0.83030473743369204</v>
       </c>
       <c r="V50" s="1">
-        <v>0.78983763251570405</v>
+        <v>0.83952497968902495</v>
       </c>
       <c r="W50" s="1"/>
       <c r="X50" s="1">
-        <v>-0.27405008386437302</v>
+        <v>0.62041460191210296</v>
       </c>
       <c r="Y50" s="1">
-        <v>0.23047768278960401</v>
+        <v>8.16466707193544E-2</v>
       </c>
       <c r="Z50" s="1">
-        <v>20.2025121535642</v>
+        <v>17.9186243183957</v>
       </c>
       <c r="AA50" s="1">
-        <v>-1.1890525822170199</v>
-      </c>
-      <c r="AB50" s="1">
-        <v>0.64042678790185603</v>
-      </c>
-      <c r="AC50" s="51"/>
+        <v>-3.62740633544988</v>
+      </c>
+      <c r="AB50" s="2">
+        <v>9.5259666762890199E-3</v>
+      </c>
+      <c r="AC50" s="35"/>
     </row>
     <row r="51" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="34"/>
+      <c r="A51" s="49"/>
       <c r="B51" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C51" s="43"/>
-      <c r="D51" s="43"/>
-      <c r="E51" s="43"/>
-      <c r="F51" s="43"/>
-      <c r="G51" s="43"/>
-      <c r="H51" s="43"/>
+        <v>48</v>
+      </c>
+      <c r="C51" s="58"/>
+      <c r="D51" s="58"/>
+      <c r="E51" s="58"/>
+      <c r="F51" s="58"/>
+      <c r="G51" s="58"/>
+      <c r="H51" s="58"/>
       <c r="I51" s="9"/>
       <c r="J51" s="9">
-        <v>0.34951867520347901</v>
+        <v>7.5239018444935397E-3</v>
       </c>
       <c r="K51" s="9">
-        <v>0.17475933760173901</v>
+        <v>3.7619509222467699E-3</v>
       </c>
       <c r="L51" s="9">
         <v>2</v>
       </c>
       <c r="M51" s="9">
-        <v>106.790362785864</v>
+        <v>105.84740366368401</v>
       </c>
       <c r="N51" s="9">
-        <v>0.55747654308262395</v>
+        <v>0.28902584428814998</v>
       </c>
       <c r="O51" s="9">
-        <v>0.57430971602825098</v>
-      </c>
-      <c r="P51" s="34"/>
-      <c r="Q51" s="48" t="s">
-        <v>32</v>
+        <v>0.74958204967156605</v>
+      </c>
+      <c r="P51" s="49"/>
+      <c r="Q51" s="32" t="s">
+        <v>30</v>
       </c>
       <c r="R51" s="9">
-        <v>0.78751115116799897</v>
+        <v>0.63538580470489003</v>
       </c>
       <c r="S51" s="9">
-        <v>0.134642721113232</v>
+        <v>0.124810867031525</v>
       </c>
       <c r="T51" s="9">
-        <v>24.194803942637702</v>
+        <v>24.517870816947401</v>
       </c>
       <c r="U51" s="9">
-        <v>-1.39717088969851</v>
-      </c>
-      <c r="V51" s="9">
-        <v>0.513084729394649</v>
+        <v>-2.3087894381868401</v>
+      </c>
+      <c r="V51" s="42">
+        <v>0.123498755965347</v>
       </c>
       <c r="W51" s="9"/>
       <c r="X51" s="9">
-        <v>0.17161763584574699</v>
+        <v>0.77582486721588295</v>
       </c>
       <c r="Y51" s="9">
-        <v>0.22829681478081101</v>
+        <v>0.10141542139468999</v>
       </c>
       <c r="Z51" s="9">
-        <v>20.376823491681002</v>
+        <v>17.956705334484202</v>
       </c>
       <c r="AA51" s="9">
-        <v>0.75173031218380404</v>
+        <v>-1.9417800269687</v>
       </c>
       <c r="AB51" s="9">
-        <v>0.87487377567923097</v>
-      </c>
-      <c r="AC51" s="52"/>
+        <v>0.24640381353586799</v>
+      </c>
+      <c r="AC51" s="36"/>
     </row>
     <row r="52" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="32" t="s">
-        <v>14</v>
+      <c r="A52" s="47" t="s">
+        <v>11</v>
       </c>
       <c r="B52" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="8">
-        <v>0.48460569188395097</v>
-      </c>
-      <c r="D52" s="8">
-        <v>0.48460569188395097</v>
-      </c>
-      <c r="E52" s="8">
-        <v>1</v>
-      </c>
-      <c r="F52" s="8">
-        <v>66.433120310954493</v>
-      </c>
-      <c r="G52" s="8">
-        <v>275.25199949565803</v>
-      </c>
-      <c r="H52" s="20">
-        <v>2.5677289076389099E-25</v>
+      <c r="C52" s="22">
+        <v>1.6044459576046901</v>
+      </c>
+      <c r="D52" s="22">
+        <v>1.6044459576046901</v>
+      </c>
+      <c r="E52" s="22">
+        <v>1</v>
+      </c>
+      <c r="F52" s="22">
+        <v>57.941257724360497</v>
+      </c>
+      <c r="G52" s="22">
+        <v>114.44647303148901</v>
+      </c>
+      <c r="H52" s="25">
+        <v>2.4310901681812699E-15</v>
       </c>
       <c r="I52" s="8"/>
-      <c r="J52" s="8">
-        <v>0.251919036972449</v>
-      </c>
-      <c r="K52" s="8">
-        <v>0.251919036972449</v>
+      <c r="J52" s="26">
+        <v>3.27228460982109E-6</v>
+      </c>
+      <c r="K52" s="26">
+        <v>3.27228460982109E-6</v>
       </c>
       <c r="L52" s="8">
         <v>1</v>
       </c>
       <c r="M52" s="8">
-        <v>120.000000000931</v>
+        <v>108.162570470471</v>
       </c>
       <c r="N52" s="8">
-        <v>45.935699808275302</v>
-      </c>
-      <c r="O52" s="20">
-        <v>4.8525436598560696E-10</v>
-      </c>
-      <c r="P52" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q52" s="49" t="s">
-        <v>29</v>
+        <v>0.81526923567301701</v>
+      </c>
+      <c r="O52" s="8">
+        <v>0.36857341395755699</v>
+      </c>
+      <c r="P52" s="47" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q52" s="33" t="s">
+        <v>27</v>
       </c>
       <c r="R52" s="13">
-        <v>0.63093577454569305</v>
+        <v>2.0739376031193602</v>
       </c>
       <c r="S52" s="13">
-        <v>2.1808374327603901E-2</v>
+        <v>0.20636183828608401</v>
       </c>
       <c r="T52" s="13">
-        <v>68.208347437733096</v>
+        <v>64.217630489307894</v>
       </c>
       <c r="U52" s="13">
-        <v>-13.3241582807534</v>
-      </c>
-      <c r="V52" s="15">
-        <v>0</v>
+        <v>7.3309666803809703</v>
+      </c>
+      <c r="V52" s="41">
+        <v>2.8690905207184898E-9</v>
       </c>
       <c r="W52" s="13"/>
       <c r="X52" s="13">
-        <v>0.85281619998043701</v>
+        <v>-4.72831811858727E-4</v>
       </c>
       <c r="Y52" s="13">
-        <v>3.6402779797028099E-2</v>
+        <v>5.0511625514736505E-4</v>
       </c>
       <c r="Z52" s="13">
-        <v>109.756917022072</v>
+        <v>108.947220351745</v>
       </c>
       <c r="AA52" s="13">
-        <v>-3.7298776773604998</v>
-      </c>
-      <c r="AB52" s="15">
-        <v>1.7132034310097799E-3</v>
-      </c>
-      <c r="AC52" s="53"/>
+        <v>-0.93608512305900804</v>
+      </c>
+      <c r="AB52" s="13">
+        <v>0.78552588991913097</v>
+      </c>
+      <c r="AC52" s="37"/>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A53" s="33"/>
+      <c r="A53" s="48"/>
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C53" s="1">
-        <v>1.0223913414274E-2</v>
-      </c>
-      <c r="D53" s="1">
-        <v>1.0223913414274E-2</v>
-      </c>
-      <c r="E53" s="1">
-        <v>1</v>
-      </c>
-      <c r="F53" s="1">
-        <v>16.820702919437998</v>
-      </c>
-      <c r="G53" s="1">
-        <v>5.8070977231181704</v>
-      </c>
-      <c r="H53" s="2">
-        <v>2.77082234476239E-2</v>
+      <c r="C53">
+        <v>5.7241252178794499E-2</v>
+      </c>
+      <c r="D53">
+        <v>5.7241252178794499E-2</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="F53">
+        <v>14.016499111022799</v>
+      </c>
+      <c r="G53">
+        <v>4.0830664272103698</v>
+      </c>
+      <c r="H53" s="7">
+        <v>6.28474981350714E-2</v>
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1">
-        <v>0.24754938321325901</v>
+        <v>1.1254087942051899E-4</v>
       </c>
       <c r="K53" s="1">
-        <v>0.24754938321325901</v>
+        <v>1.1254087942051899E-4</v>
       </c>
       <c r="L53" s="1">
         <v>1</v>
       </c>
       <c r="M53" s="1">
-        <v>120.000000000876</v>
+        <v>13.1287610221782</v>
       </c>
       <c r="N53" s="1">
-        <v>45.138923567144403</v>
-      </c>
-      <c r="O53" s="4">
-        <v>6.5162497916437297E-10</v>
-      </c>
-      <c r="P53" s="33"/>
-      <c r="Q53" s="47" t="s">
-        <v>30</v>
+        <v>28.038855933179999</v>
+      </c>
+      <c r="O53" s="2">
+        <v>1.4035037213878999E-4</v>
+      </c>
+      <c r="P53" s="48"/>
+      <c r="Q53" s="31" t="s">
+        <v>28</v>
       </c>
       <c r="R53" s="1">
-        <v>0.76645094993192597</v>
+        <v>1.8504898868847499</v>
       </c>
       <c r="S53" s="1">
-        <v>2.07855368671831E-2</v>
+        <v>0.14281987253321901</v>
       </c>
       <c r="T53" s="1">
-        <v>65.367738446356398</v>
+        <v>63.037530931724902</v>
       </c>
       <c r="U53" s="1">
-        <v>-9.8079800133367101</v>
-      </c>
-      <c r="V53" s="2">
-        <v>0</v>
+        <v>7.9742737143899101</v>
+      </c>
+      <c r="V53" s="6">
+        <v>2.5103985556995698E-10</v>
       </c>
       <c r="W53" s="1"/>
       <c r="X53" s="1">
-        <v>0.763423356833838</v>
+        <v>4.9280938617282297E-4</v>
       </c>
       <c r="Y53" s="1">
-        <v>3.3116417525027302E-2</v>
+        <v>5.05401745277116E-4</v>
       </c>
       <c r="Z53" s="1">
-        <v>108.18375969063101</v>
+        <v>107.441893549743</v>
       </c>
       <c r="AA53" s="1">
-        <v>-6.22290869573379</v>
-      </c>
-      <c r="AB53" s="6">
-        <v>5.6421459060373997E-8</v>
-      </c>
-      <c r="AC53" s="51"/>
-    </row>
-    <row r="54" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="33"/>
+        <v>0.97508445662887799</v>
+      </c>
+      <c r="AB53" s="1">
+        <v>0.76389978434717098</v>
+      </c>
+      <c r="AC53" s="35"/>
+    </row>
+    <row r="54" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A54" s="48"/>
       <c r="B54" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C54" s="1">
-        <v>3.4754513300900097E-2</v>
-      </c>
-      <c r="D54" s="1">
-        <v>3.4754513300900097E-2</v>
-      </c>
-      <c r="E54" s="1">
-        <v>1</v>
-      </c>
-      <c r="F54" s="1">
-        <v>66.433120314017799</v>
-      </c>
-      <c r="G54" s="1">
-        <v>19.740274284401199</v>
-      </c>
-      <c r="H54" s="4">
-        <v>3.4416590783058898E-5</v>
+      <c r="C54">
+        <v>1.15277522221443E-2</v>
+      </c>
+      <c r="D54">
+        <v>1.15277522221443E-2</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="F54">
+        <v>57.941257724235903</v>
+      </c>
+      <c r="G54">
+        <v>0.82228421440567401</v>
+      </c>
+      <c r="H54">
+        <v>0.36826900260683199</v>
       </c>
       <c r="I54" s="1"/>
-      <c r="J54" s="1">
-        <v>1.81876043094546E-2</v>
-      </c>
-      <c r="K54" s="1">
-        <v>1.81876043094546E-2</v>
+      <c r="J54" s="5">
+        <v>7.3359735284969697E-6</v>
+      </c>
+      <c r="K54" s="5">
+        <v>7.3359735284969697E-6</v>
       </c>
       <c r="L54" s="1">
         <v>1</v>
       </c>
       <c r="M54" s="1">
-        <v>120.000000000876</v>
+        <v>107.80326229592799</v>
       </c>
       <c r="N54" s="1">
-        <v>3.3163842710393201</v>
-      </c>
-      <c r="O54" s="3">
-        <v>7.1083850624745398E-2</v>
-      </c>
-      <c r="P54" s="33"/>
-      <c r="Q54" s="47" t="s">
-        <v>31</v>
+        <v>1.82771190303713</v>
+      </c>
+      <c r="O54" s="1">
+        <v>0.179227673464389</v>
+      </c>
+      <c r="P54" s="48"/>
+      <c r="Q54" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="R54" s="1">
-        <v>0.83438570293307701</v>
+        <v>0.69912820784997998</v>
       </c>
       <c r="S54" s="1">
-        <v>3.3488447870679602E-2</v>
+        <v>0.148324307575951</v>
       </c>
       <c r="T54" s="1">
-        <v>30.8586362068467</v>
+        <v>21.800179035140999</v>
       </c>
       <c r="U54" s="1">
-        <v>-4.5112113615864997</v>
-      </c>
-      <c r="V54" s="2">
-        <v>4.8479551006386202E-4</v>
+        <v>-1.68706510404384</v>
+      </c>
+      <c r="V54" s="1">
+        <v>0.35412379934024302</v>
       </c>
       <c r="W54" s="1"/>
       <c r="X54" s="1">
-        <v>0.86166002670741904</v>
+        <v>-4.8894271875510997E-3</v>
       </c>
       <c r="Y54" s="1">
-        <v>3.6912066142334603E-2</v>
+        <v>9.1172534711224601E-4</v>
       </c>
       <c r="Z54" s="1">
-        <v>40.219886600149103</v>
+        <v>18.9122122903484</v>
       </c>
       <c r="AA54" s="1">
-        <v>-3.4757314012155298</v>
+        <v>-5.3628290614466696</v>
       </c>
       <c r="AB54" s="2">
-        <v>6.51926940610248E-3</v>
-      </c>
-      <c r="AC54" s="51"/>
+        <v>1.9550438579263299E-4</v>
+      </c>
+      <c r="AC54" s="35"/>
     </row>
     <row r="55" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="34"/>
+      <c r="A55" s="49"/>
       <c r="B55" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C55" s="43"/>
-      <c r="D55" s="43"/>
-      <c r="E55" s="43"/>
-      <c r="F55" s="43"/>
-      <c r="G55" s="43"/>
-      <c r="H55" s="43"/>
+        <v>48</v>
+      </c>
+      <c r="C55" s="58"/>
+      <c r="D55" s="58"/>
+      <c r="E55" s="58"/>
+      <c r="F55" s="58"/>
+      <c r="G55" s="58"/>
+      <c r="H55" s="58"/>
       <c r="I55" s="9"/>
-      <c r="J55" s="9">
-        <v>3.6858467316493698E-2</v>
-      </c>
-      <c r="K55" s="9">
-        <v>1.8429233658246901E-2</v>
+      <c r="J55" s="27">
+        <v>7.2143853443936604E-6</v>
+      </c>
+      <c r="K55" s="27">
+        <v>3.6071926721968302E-6</v>
       </c>
       <c r="L55" s="9">
         <v>2</v>
       </c>
       <c r="M55" s="9">
-        <v>120.00000000096099</v>
+        <v>107.842517864377</v>
       </c>
       <c r="N55" s="9">
-        <v>3.3604437171390802</v>
-      </c>
-      <c r="O55" s="19">
-        <v>3.8017401028842102E-2</v>
-      </c>
-      <c r="P55" s="34"/>
-      <c r="Q55" s="48" t="s">
-        <v>32</v>
+        <v>0.89870948387585703</v>
+      </c>
+      <c r="O55" s="9">
+        <v>0.41012132536637402</v>
+      </c>
+      <c r="P55" s="49"/>
+      <c r="Q55" s="32" t="s">
+        <v>30</v>
       </c>
       <c r="R55" s="9">
-        <v>1.0135987535073001</v>
+        <v>0.62380356878450904</v>
       </c>
       <c r="S55" s="9">
-        <v>4.3185412023769597E-2</v>
+        <v>0.13578145981755799</v>
       </c>
       <c r="T55" s="9">
-        <v>33.635517105315301</v>
+        <v>23.6213122095755</v>
       </c>
       <c r="U55" s="9">
-        <v>0.31702372661387901</v>
+        <v>-2.1680811723975899</v>
       </c>
       <c r="V55" s="9">
-        <v>0.98877074255840203</v>
+        <v>0.16142822200252099</v>
       </c>
       <c r="W55" s="9"/>
       <c r="X55" s="9">
-        <v>0.77134016691240403</v>
+        <v>-3.9237859895195496E-3</v>
       </c>
       <c r="Y55" s="9">
-        <v>3.3538164823331003E-2</v>
+        <v>9.0311675397618501E-4</v>
       </c>
       <c r="Z55" s="9">
-        <v>47.071378613344201</v>
+        <v>18.890902844266801</v>
       </c>
       <c r="AA55" s="9">
-        <v>-5.9711021561995201</v>
-      </c>
-      <c r="AB55" s="56">
-        <v>1.7432415013729501E-6</v>
-      </c>
-      <c r="AC55" s="52"/>
+        <v>-4.3447161978162399</v>
+      </c>
+      <c r="AB55" s="19">
+        <v>1.8370895217705301E-3</v>
+      </c>
+      <c r="AC55" s="36"/>
     </row>
     <row r="56" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="32" t="s">
-        <v>27</v>
+      <c r="A56" s="47" t="s">
+        <v>12</v>
       </c>
       <c r="B56" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C56" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="D56" s="42"/>
-      <c r="E56" s="42"/>
-      <c r="F56" s="42"/>
-      <c r="G56" s="42"/>
-      <c r="H56" s="42"/>
+      <c r="C56" s="8">
+        <v>3.2828058473639601</v>
+      </c>
+      <c r="D56" s="8">
+        <v>3.2828058473639601</v>
+      </c>
+      <c r="E56" s="8">
+        <v>1</v>
+      </c>
+      <c r="F56" s="8">
+        <v>57.1027846481349</v>
+      </c>
+      <c r="G56" s="8">
+        <v>315.57785828471202</v>
+      </c>
+      <c r="H56" s="20">
+        <v>6.2556135251351003E-25</v>
+      </c>
       <c r="I56" s="8"/>
       <c r="J56" s="8">
-        <v>4.0252880405239402E-2</v>
+        <v>4.9581564592565801</v>
       </c>
       <c r="K56" s="8">
-        <v>4.0252880405239402E-2</v>
+        <v>4.9581564592565801</v>
       </c>
       <c r="L56" s="8">
         <v>1</v>
       </c>
       <c r="M56" s="8">
-        <v>107.364526662513</v>
+        <v>107.087389174327</v>
       </c>
       <c r="N56" s="8">
-        <v>3.06304929618606</v>
-      </c>
-      <c r="O56" s="28">
-        <v>8.2948057027609101E-2</v>
-      </c>
-      <c r="P56" s="32" t="s">
+        <v>15.8163561438312</v>
+      </c>
+      <c r="O56" s="21">
+        <v>1.2711861864362099E-4</v>
+      </c>
+      <c r="P56" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q56" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="Q56" s="49" t="s">
-        <v>29</v>
-      </c>
-      <c r="R56" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="S56" s="44"/>
-      <c r="T56" s="44"/>
-      <c r="U56" s="44"/>
-      <c r="V56" s="44"/>
+      <c r="R56" s="13">
+        <v>3.25039616887112</v>
+      </c>
+      <c r="S56" s="13">
+        <v>0.28598369641782101</v>
+      </c>
+      <c r="T56" s="13">
+        <v>64.098058733478297</v>
+      </c>
+      <c r="U56" s="13">
+        <v>13.3975884833244</v>
+      </c>
+      <c r="V56" s="41">
+        <v>8.8387075436457995E-12</v>
+      </c>
       <c r="W56" s="13"/>
       <c r="X56" s="13">
-        <v>1.28624977261183</v>
+        <v>0.231107865381736</v>
       </c>
       <c r="Y56" s="13">
-        <v>8.5806417308814706E-2</v>
+        <v>0.141033950135908</v>
       </c>
       <c r="Z56" s="13">
-        <v>108.356902446408</v>
+        <v>109.142880527442</v>
       </c>
       <c r="AA56" s="13">
-        <v>3.77347912638702</v>
-      </c>
-      <c r="AB56" s="15">
-        <v>1.48131841462606E-3</v>
-      </c>
-      <c r="AC56" s="53"/>
+        <v>1.63866831467904</v>
+      </c>
+      <c r="AB56" s="13">
+        <v>0.361442574294079</v>
+      </c>
+      <c r="AC56" s="37"/>
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A57" s="33"/>
+      <c r="A57" s="48"/>
       <c r="B57" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C57" s="30"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="30"/>
-      <c r="F57" s="30"/>
-      <c r="G57" s="30"/>
-      <c r="H57" s="30"/>
+      <c r="C57" s="1">
+        <v>6.9098899300225596E-4</v>
+      </c>
+      <c r="D57" s="1">
+        <v>6.9098899300225596E-4</v>
+      </c>
+      <c r="E57" s="1">
+        <v>1</v>
+      </c>
+      <c r="F57" s="1">
+        <v>13.6400199665374</v>
+      </c>
+      <c r="G57" s="1">
+        <v>6.6425136498724599E-2</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0.80046236006191795</v>
+      </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1">
-        <v>0.42132164214255802</v>
+        <v>1.93826224654098E-2</v>
       </c>
       <c r="K57" s="1">
-        <v>0.42132164214255802</v>
+        <v>1.93826224654098E-2</v>
       </c>
       <c r="L57" s="1">
         <v>1</v>
       </c>
       <c r="M57" s="1">
-        <v>13.0099671316875</v>
+        <v>11.8724826464864</v>
       </c>
       <c r="N57" s="1">
-        <v>32.060536946437701</v>
-      </c>
-      <c r="O57" s="4">
-        <v>7.7465741239532106E-5</v>
-      </c>
-      <c r="P57" s="33"/>
-      <c r="Q57" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="R57" s="30"/>
-      <c r="S57" s="30"/>
-      <c r="T57" s="30"/>
-      <c r="U57" s="30"/>
-      <c r="V57" s="30"/>
+        <v>6.1829928610262298E-2</v>
+      </c>
+      <c r="O57" s="1">
+        <v>0.80787586394532096</v>
+      </c>
+      <c r="P57" s="48"/>
+      <c r="Q57" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="R57" s="1">
+        <v>2.1892524295195499</v>
+      </c>
+      <c r="S57" s="1">
+        <v>0.14734976342700101</v>
+      </c>
+      <c r="T57" s="1">
+        <v>61.439546816495699</v>
+      </c>
+      <c r="U57" s="1">
+        <v>11.641762270683</v>
+      </c>
+      <c r="V57" s="6">
+        <v>1.9951040819421499E-11</v>
+      </c>
       <c r="W57" s="1"/>
       <c r="X57" s="1">
-        <v>1.0220158782055699</v>
+        <v>0.67677558509185598</v>
       </c>
       <c r="Y57" s="1">
-        <v>6.8059773351627897E-2</v>
+        <v>0.14123776247129999</v>
       </c>
       <c r="Z57" s="1">
-        <v>107.183693987974</v>
+        <v>107.564370903827</v>
       </c>
       <c r="AA57" s="1">
-        <v>0.32701355539446397</v>
-      </c>
-      <c r="AB57" s="1">
-        <v>0.98786034140903101</v>
-      </c>
-      <c r="AC57" s="51"/>
+        <v>4.7917467202114503</v>
+      </c>
+      <c r="AB57" s="6">
+        <v>3.1319294462428497E-5</v>
+      </c>
+      <c r="AC57" s="35"/>
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A58" s="33"/>
+      <c r="A58" s="48"/>
       <c r="B58" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C58" s="30"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
-      <c r="G58" s="30"/>
-      <c r="H58" s="30"/>
+      <c r="C58" s="1">
+        <v>0.13315844295854501</v>
+      </c>
+      <c r="D58" s="1">
+        <v>0.13315844295854501</v>
+      </c>
+      <c r="E58" s="1">
+        <v>1</v>
+      </c>
+      <c r="F58" s="1">
+        <v>57.102784645779103</v>
+      </c>
+      <c r="G58" s="1">
+        <v>12.800591382864701</v>
+      </c>
+      <c r="H58" s="2">
+        <v>7.1467481949516205E-4</v>
+      </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1">
-        <v>7.8254362282741005E-2</v>
+        <v>1.5642063102591399</v>
       </c>
       <c r="K58" s="1">
-        <v>7.8254362282741005E-2</v>
+        <v>1.5642063102591399</v>
       </c>
       <c r="L58" s="1">
         <v>1</v>
       </c>
       <c r="M58" s="1">
-        <v>106.96971991586101</v>
+        <v>106.739383464101</v>
       </c>
       <c r="N58" s="1">
-        <v>5.9547780655825902</v>
+        <v>4.9897667184944403</v>
       </c>
       <c r="O58" s="2">
-        <v>1.63202510112339E-2</v>
-      </c>
-      <c r="P58" s="33"/>
-      <c r="Q58" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="R58" s="30"/>
-      <c r="S58" s="30"/>
-      <c r="T58" s="30"/>
-      <c r="U58" s="30"/>
-      <c r="V58" s="30"/>
+        <v>2.7582949079364601E-2</v>
+      </c>
+      <c r="P58" s="48"/>
+      <c r="Q58" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="R58" s="1">
+        <v>1.1692225136694301</v>
+      </c>
+      <c r="S58" s="1">
+        <v>0.196811825263492</v>
+      </c>
+      <c r="T58" s="1">
+        <v>23.0448591919385</v>
+      </c>
+      <c r="U58" s="1">
+        <v>0.92878103054844996</v>
+      </c>
+      <c r="V58" s="1">
+        <v>0.78983763251570405</v>
+      </c>
       <c r="W58" s="1"/>
       <c r="X58" s="1">
-        <v>0.45501994044807598</v>
+        <v>-0.27405008386437302</v>
       </c>
       <c r="Y58" s="1">
-        <v>7.5979776783830097E-2</v>
+        <v>0.23047768278960401</v>
       </c>
       <c r="Z58" s="1">
-        <v>16.4330650500419</v>
+        <v>20.2025121535642</v>
       </c>
       <c r="AA58" s="1">
-        <v>-4.7155848945320198</v>
-      </c>
-      <c r="AB58" s="2">
-        <v>1.12704066890601E-3</v>
-      </c>
-      <c r="AC58" s="51"/>
+        <v>-1.1890525822170199</v>
+      </c>
+      <c r="AB58" s="1">
+        <v>0.64042678790185603</v>
+      </c>
+      <c r="AC58" s="35"/>
     </row>
     <row r="59" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="34"/>
+      <c r="A59" s="49"/>
       <c r="B59" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C59" s="31"/>
-      <c r="D59" s="31"/>
-      <c r="E59" s="31"/>
-      <c r="F59" s="31"/>
-      <c r="G59" s="31"/>
-      <c r="H59" s="31"/>
+        <v>48</v>
+      </c>
+      <c r="C59" s="58"/>
+      <c r="D59" s="58"/>
+      <c r="E59" s="58"/>
+      <c r="F59" s="58"/>
+      <c r="G59" s="58"/>
+      <c r="H59" s="58"/>
       <c r="I59" s="9"/>
       <c r="J59" s="9">
-        <v>2.6614614752845599E-3</v>
+        <v>0.34951867520347901</v>
       </c>
       <c r="K59" s="9">
-        <v>1.33073073764228E-3</v>
+        <v>0.17475933760173901</v>
       </c>
       <c r="L59" s="9">
         <v>2</v>
       </c>
       <c r="M59" s="9">
-        <v>106.998307117191</v>
+        <v>106.790362785864</v>
       </c>
       <c r="N59" s="9">
-        <v>0.101262165795663</v>
+        <v>0.55747654308262395</v>
       </c>
       <c r="O59" s="9">
-        <v>0.90378258302877301</v>
-      </c>
-      <c r="P59" s="34"/>
-      <c r="Q59" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="R59" s="31"/>
-      <c r="S59" s="31"/>
-      <c r="T59" s="31"/>
-      <c r="U59" s="31"/>
-      <c r="V59" s="31"/>
+        <v>0.57430971602825098</v>
+      </c>
+      <c r="P59" s="49"/>
+      <c r="Q59" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="R59" s="9">
+        <v>0.78751115116799897</v>
+      </c>
+      <c r="S59" s="9">
+        <v>0.134642721113232</v>
+      </c>
+      <c r="T59" s="9">
+        <v>24.194803942637702</v>
+      </c>
+      <c r="U59" s="9">
+        <v>-1.39717088969851</v>
+      </c>
+      <c r="V59" s="9">
+        <v>0.513084729394649</v>
+      </c>
       <c r="W59" s="9"/>
       <c r="X59" s="9">
-        <v>0.361545334304543</v>
+        <v>0.17161763584574699</v>
       </c>
       <c r="Y59" s="9">
-        <v>5.9931199064228002E-2</v>
+        <v>0.22829681478081101</v>
       </c>
       <c r="Z59" s="9">
-        <v>16.204970622986401</v>
+        <v>20.376823491681002</v>
       </c>
       <c r="AA59" s="9">
-        <v>-6.1374476275895002</v>
-      </c>
-      <c r="AB59" s="56">
-        <v>7.26892011232438E-5</v>
-      </c>
-      <c r="AC59" s="52"/>
+        <v>0.75173031218380404</v>
+      </c>
+      <c r="AB59" s="9">
+        <v>0.87487377567923097</v>
+      </c>
+      <c r="AC59" s="36"/>
     </row>
     <row r="60" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="32" t="s">
-        <v>28</v>
+      <c r="A60" s="47" t="s">
+        <v>14</v>
       </c>
       <c r="B60" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C60" s="8">
-        <v>1.1481734714944201</v>
+        <v>0.48460569188395097</v>
       </c>
       <c r="D60" s="8">
-        <v>1.1481734714944201</v>
+        <v>0.48460569188395097</v>
       </c>
       <c r="E60" s="8">
         <v>1</v>
       </c>
       <c r="F60" s="8">
-        <v>57.458627569308902</v>
+        <v>66.433120310954493</v>
       </c>
       <c r="G60" s="8">
-        <v>62.871367396090498</v>
+        <v>275.25199949565803</v>
       </c>
       <c r="H60" s="20">
-        <v>8.5554572534297795E-11</v>
+        <v>2.5677289076389099E-25</v>
       </c>
       <c r="I60" s="8"/>
-      <c r="J60" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="K60" s="42"/>
-      <c r="L60" s="42"/>
-      <c r="M60" s="42"/>
-      <c r="N60" s="42"/>
-      <c r="O60" s="42"/>
-      <c r="P60" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q60" s="49" t="s">
-        <v>29</v>
+      <c r="J60" s="8">
+        <v>0.251919036972449</v>
+      </c>
+      <c r="K60" s="8">
+        <v>0.251919036972449</v>
+      </c>
+      <c r="L60" s="8">
+        <v>1</v>
+      </c>
+      <c r="M60" s="8">
+        <v>120.000000000931</v>
+      </c>
+      <c r="N60" s="8">
+        <v>45.935699808275302</v>
+      </c>
+      <c r="O60" s="20">
+        <v>4.8525436598560696E-10</v>
+      </c>
+      <c r="P60" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q60" s="33" t="s">
+        <v>27</v>
       </c>
       <c r="R60" s="13">
-        <v>1.89134861613022</v>
+        <v>0.63093577454569305</v>
       </c>
       <c r="S60" s="13">
-        <v>0.21484737680985</v>
+        <v>2.1808374327603901E-2</v>
       </c>
       <c r="T60" s="13">
-        <v>62.148851945988298</v>
+        <v>68.208347437733096</v>
       </c>
       <c r="U60" s="13">
-        <v>5.6102048802882196</v>
-      </c>
-      <c r="V60" s="57">
-        <v>2.9455467435157701E-6</v>
+        <v>-13.3241582807534</v>
+      </c>
+      <c r="V60" s="15">
+        <v>0</v>
       </c>
       <c r="W60" s="13"/>
-      <c r="X60" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y60" s="44"/>
-      <c r="Z60" s="44"/>
-      <c r="AA60" s="44"/>
-      <c r="AB60" s="44"/>
-      <c r="AC60" s="53"/>
+      <c r="X60" s="13">
+        <v>0.85281619998043701</v>
+      </c>
+      <c r="Y60" s="13">
+        <v>3.6402779797028099E-2</v>
+      </c>
+      <c r="Z60" s="13">
+        <v>109.756917022072</v>
+      </c>
+      <c r="AA60" s="13">
+        <v>-3.7298776773604998</v>
+      </c>
+      <c r="AB60" s="15">
+        <v>1.7132034310097799E-3</v>
+      </c>
+      <c r="AC60" s="37"/>
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A61" s="33"/>
+      <c r="A61" s="48"/>
       <c r="B61" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C61" s="1">
-        <v>9.2911254906166099E-2</v>
+        <v>1.0223913414274E-2</v>
       </c>
       <c r="D61" s="1">
-        <v>9.2911254906166099E-2</v>
+        <v>1.0223913414274E-2</v>
       </c>
       <c r="E61" s="1">
         <v>1</v>
       </c>
       <c r="F61" s="1">
-        <v>14.883763903298201</v>
+        <v>16.820702919437998</v>
       </c>
       <c r="G61" s="1">
-        <v>5.0876089610695701</v>
+        <v>5.8070977231181704</v>
       </c>
       <c r="H61" s="2">
-        <v>3.9589780561885203E-2</v>
+        <v>2.77082234476239E-2</v>
       </c>
       <c r="I61" s="1"/>
-      <c r="J61" s="30"/>
-      <c r="K61" s="30"/>
-      <c r="L61" s="30"/>
-      <c r="M61" s="30"/>
-      <c r="N61" s="30"/>
-      <c r="O61" s="30"/>
-      <c r="P61" s="33"/>
-      <c r="Q61" s="47" t="s">
-        <v>30</v>
+      <c r="J61" s="1">
+        <v>0.24754938321325901</v>
+      </c>
+      <c r="K61" s="1">
+        <v>0.24754938321325901</v>
+      </c>
+      <c r="L61" s="1">
+        <v>1</v>
+      </c>
+      <c r="M61" s="1">
+        <v>120.000000000876</v>
+      </c>
+      <c r="N61" s="1">
+        <v>45.138923567144403</v>
+      </c>
+      <c r="O61" s="4">
+        <v>6.5162497916437297E-10</v>
+      </c>
+      <c r="P61" s="48"/>
+      <c r="Q61" s="31" t="s">
+        <v>28</v>
       </c>
       <c r="R61" s="1">
-        <v>1.66799515271489</v>
+        <v>0.76645094993192597</v>
       </c>
       <c r="S61" s="1">
-        <v>0.15075896963304</v>
+        <v>2.07855368671831E-2</v>
       </c>
       <c r="T61" s="1">
-        <v>61.514580454863498</v>
+        <v>65.367738446356398</v>
       </c>
       <c r="U61" s="1">
-        <v>5.6605831266398603</v>
-      </c>
-      <c r="V61" s="6">
-        <v>2.49244059158382E-6</v>
+        <v>-9.8079800133367101</v>
+      </c>
+      <c r="V61" s="2">
+        <v>0</v>
       </c>
       <c r="W61" s="1"/>
-      <c r="X61" s="30"/>
-      <c r="Y61" s="30"/>
-      <c r="Z61" s="30"/>
-      <c r="AA61" s="30"/>
-      <c r="AB61" s="30"/>
-      <c r="AC61" s="51"/>
-    </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A62" s="33"/>
+      <c r="X61" s="1">
+        <v>0.763423356833838</v>
+      </c>
+      <c r="Y61" s="1">
+        <v>3.3116417525027302E-2</v>
+      </c>
+      <c r="Z61" s="1">
+        <v>108.18375969063101</v>
+      </c>
+      <c r="AA61" s="1">
+        <v>-6.22290869573379</v>
+      </c>
+      <c r="AB61" s="6">
+        <v>5.6421459060373997E-8</v>
+      </c>
+      <c r="AC61" s="35"/>
+    </row>
+    <row r="62" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="48"/>
       <c r="B62" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C62" s="1">
-        <v>1.37366591368214E-2</v>
+        <v>3.4754513300900097E-2</v>
       </c>
       <c r="D62" s="1">
-        <v>1.37366591368214E-2</v>
+        <v>3.4754513300900097E-2</v>
       </c>
       <c r="E62" s="1">
         <v>1</v>
       </c>
       <c r="F62" s="1">
-        <v>57.458627570771498</v>
+        <v>66.433120314017799</v>
       </c>
       <c r="G62" s="1">
-        <v>0.75218820572632805</v>
-      </c>
-      <c r="H62" s="1">
-        <v>0.38939195861388898</v>
+        <v>19.740274284401199</v>
+      </c>
+      <c r="H62" s="4">
+        <v>3.4416590783058898E-5</v>
       </c>
       <c r="I62" s="1"/>
-      <c r="J62" s="30"/>
-      <c r="K62" s="30"/>
-      <c r="L62" s="30"/>
-      <c r="M62" s="30"/>
-      <c r="N62" s="30"/>
-      <c r="O62" s="30"/>
-      <c r="P62" s="33"/>
-      <c r="Q62" s="47" t="s">
-        <v>31</v>
+      <c r="J62" s="1">
+        <v>1.81876043094546E-2</v>
+      </c>
+      <c r="K62" s="1">
+        <v>1.81876043094546E-2</v>
+      </c>
+      <c r="L62" s="1">
+        <v>1</v>
+      </c>
+      <c r="M62" s="1">
+        <v>120.000000000876</v>
+      </c>
+      <c r="N62" s="1">
+        <v>3.3163842710393201</v>
+      </c>
+      <c r="O62" s="3">
+        <v>7.1083850624745398E-2</v>
+      </c>
+      <c r="P62" s="48"/>
+      <c r="Q62" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="R62" s="1">
-        <v>0.62197037241022901</v>
+        <v>0.83438570293307701</v>
       </c>
       <c r="S62" s="1">
-        <v>0.15294515378255399</v>
+        <v>3.3488447870679602E-2</v>
       </c>
       <c r="T62" s="1">
-        <v>21.507071906541999</v>
+        <v>30.8586362068467</v>
       </c>
       <c r="U62" s="1">
-        <v>-1.93108835287197</v>
-      </c>
-      <c r="V62" s="1">
-        <v>0.24503008385552599</v>
+        <v>-4.5112113615864997</v>
+      </c>
+      <c r="V62" s="2">
+        <v>4.8479551006386202E-4</v>
       </c>
       <c r="W62" s="1"/>
-      <c r="X62" s="30"/>
-      <c r="Y62" s="30"/>
-      <c r="Z62" s="30"/>
-      <c r="AA62" s="30"/>
-      <c r="AB62" s="30"/>
-      <c r="AC62" s="51"/>
+      <c r="X62" s="1">
+        <v>0.86166002670741904</v>
+      </c>
+      <c r="Y62" s="1">
+        <v>3.6912066142334603E-2</v>
+      </c>
+      <c r="Z62" s="1">
+        <v>40.219886600149103</v>
+      </c>
+      <c r="AA62" s="1">
+        <v>-3.4757314012155298</v>
+      </c>
+      <c r="AB62" s="2">
+        <v>6.51926940610248E-3</v>
+      </c>
+      <c r="AC62" s="35"/>
     </row>
     <row r="63" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="34"/>
+      <c r="A63" s="49"/>
       <c r="B63" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C63" s="43"/>
-      <c r="D63" s="43"/>
-      <c r="E63" s="43"/>
-      <c r="F63" s="43"/>
-      <c r="G63" s="43"/>
-      <c r="H63" s="43"/>
+        <v>48</v>
+      </c>
+      <c r="C63" s="58"/>
+      <c r="D63" s="58"/>
+      <c r="E63" s="58"/>
+      <c r="F63" s="58"/>
+      <c r="G63" s="58"/>
+      <c r="H63" s="58"/>
       <c r="I63" s="9"/>
-      <c r="J63" s="31"/>
-      <c r="K63" s="31"/>
-      <c r="L63" s="31"/>
-      <c r="M63" s="31"/>
-      <c r="N63" s="31"/>
-      <c r="O63" s="31"/>
-      <c r="P63" s="34"/>
-      <c r="Q63" s="48" t="s">
-        <v>32</v>
+      <c r="J63" s="9">
+        <v>3.6858467316493698E-2</v>
+      </c>
+      <c r="K63" s="9">
+        <v>1.8429233658246901E-2</v>
+      </c>
+      <c r="L63" s="9">
+        <v>2</v>
+      </c>
+      <c r="M63" s="9">
+        <v>120.00000000096099</v>
+      </c>
+      <c r="N63" s="9">
+        <v>3.3604437171390802</v>
+      </c>
+      <c r="O63" s="19">
+        <v>3.8017401028842102E-2</v>
+      </c>
+      <c r="P63" s="49"/>
+      <c r="Q63" s="32" t="s">
+        <v>30</v>
       </c>
       <c r="R63" s="9">
-        <v>0.54852054109157</v>
+        <v>1.0135987535073001</v>
       </c>
       <c r="S63" s="9">
-        <v>0.138689132631619</v>
+        <v>4.3185412023769597E-2</v>
       </c>
       <c r="T63" s="9">
-        <v>23.424366595514599</v>
+        <v>33.635517105315301</v>
       </c>
       <c r="U63" s="9">
-        <v>-2.3751200702861999</v>
-      </c>
-      <c r="V63" s="58">
-        <v>0.109927732737644</v>
+        <v>0.31702372661387901</v>
+      </c>
+      <c r="V63" s="9">
+        <v>0.98877074255840203</v>
       </c>
       <c r="W63" s="9"/>
-      <c r="X63" s="31"/>
-      <c r="Y63" s="31"/>
-      <c r="Z63" s="31"/>
-      <c r="AA63" s="31"/>
-      <c r="AB63" s="31"/>
-      <c r="AC63" s="52"/>
+      <c r="X63" s="9">
+        <v>0.77134016691240403</v>
+      </c>
+      <c r="Y63" s="9">
+        <v>3.3538164823331003E-2</v>
+      </c>
+      <c r="Z63" s="9">
+        <v>47.071378613344201</v>
+      </c>
+      <c r="AA63" s="9">
+        <v>-5.9711021561995201</v>
+      </c>
+      <c r="AB63" s="40">
+        <v>1.7432415013729501E-6</v>
+      </c>
+      <c r="AC63" s="36"/>
     </row>
     <row r="64" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="32" t="s">
-        <v>18</v>
+      <c r="A64" s="47" t="s">
+        <v>26</v>
       </c>
       <c r="B64" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C64" s="8">
-        <v>10.9358082393645</v>
+        <v>1.1481734714944201</v>
       </c>
       <c r="D64" s="8">
-        <v>10.9358082393645</v>
+        <v>1.1481734714944201</v>
       </c>
       <c r="E64" s="8">
         <v>1</v>
       </c>
       <c r="F64" s="8">
-        <v>67.383586408567496</v>
+        <v>57.458627569308902</v>
       </c>
       <c r="G64" s="8">
-        <v>224.10765385608801</v>
+        <v>62.871367396090498</v>
       </c>
       <c r="H64" s="20">
-        <v>4.0821399088527701E-23</v>
+        <v>8.5554572534297795E-11</v>
       </c>
       <c r="I64" s="8"/>
-      <c r="J64" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="K64" s="42"/>
-      <c r="L64" s="42"/>
-      <c r="M64" s="42"/>
-      <c r="N64" s="42"/>
-      <c r="O64" s="42"/>
-      <c r="P64" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q64" s="49" t="s">
-        <v>29</v>
+      <c r="J64" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="K64" s="44"/>
+      <c r="L64" s="44"/>
+      <c r="M64" s="44"/>
+      <c r="N64" s="44"/>
+      <c r="O64" s="44"/>
+      <c r="P64" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q64" s="33" t="s">
+        <v>27</v>
       </c>
       <c r="R64" s="13">
-        <v>5.1765111889964999</v>
+        <v>1.89134861613022</v>
       </c>
       <c r="S64" s="13">
-        <v>0.94034664213896701</v>
+        <v>0.21484737680985</v>
       </c>
       <c r="T64" s="13">
-        <v>66.362964163016898</v>
+        <v>62.148851945988298</v>
       </c>
       <c r="U64" s="13">
-        <v>9.0507731513692704</v>
-      </c>
-      <c r="V64" s="15">
-        <v>0</v>
+        <v>5.6102048802882196</v>
+      </c>
+      <c r="V64" s="41">
+        <v>2.9455467435157701E-6</v>
       </c>
       <c r="W64" s="13"/>
-      <c r="X64" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y64" s="44"/>
-      <c r="Z64" s="44"/>
-      <c r="AA64" s="44"/>
-      <c r="AB64" s="44"/>
-      <c r="AC64" s="53"/>
+      <c r="X64" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y64" s="57"/>
+      <c r="Z64" s="57"/>
+      <c r="AA64" s="57"/>
+      <c r="AB64" s="57"/>
+      <c r="AC64" s="37"/>
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A65" s="33"/>
+      <c r="A65" s="48"/>
       <c r="B65" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C65" s="1">
-        <v>3.35549271707291E-3</v>
+        <v>9.2911254906166099E-2</v>
       </c>
       <c r="D65" s="1">
-        <v>3.35549271707291E-3</v>
+        <v>9.2911254906166099E-2</v>
       </c>
       <c r="E65" s="1">
         <v>1</v>
       </c>
       <c r="F65" s="1">
-        <v>19.7769266057722</v>
+        <v>14.883763903298201</v>
       </c>
       <c r="G65" s="1">
-        <v>6.8764153859934604E-2</v>
-      </c>
-      <c r="H65" s="1">
-        <v>0.79585674296255904</v>
+        <v>5.0876089610695701</v>
+      </c>
+      <c r="H65" s="2">
+        <v>3.9589780561885203E-2</v>
       </c>
       <c r="I65" s="1"/>
-      <c r="J65" s="30"/>
-      <c r="K65" s="30"/>
-      <c r="L65" s="30"/>
-      <c r="M65" s="30"/>
-      <c r="N65" s="30"/>
-      <c r="O65" s="30"/>
-      <c r="P65" s="33"/>
-      <c r="Q65" s="47" t="s">
-        <v>30</v>
+      <c r="J65" s="45"/>
+      <c r="K65" s="45"/>
+      <c r="L65" s="45"/>
+      <c r="M65" s="45"/>
+      <c r="N65" s="45"/>
+      <c r="O65" s="45"/>
+      <c r="P65" s="48"/>
+      <c r="Q65" s="31" t="s">
+        <v>28</v>
       </c>
       <c r="R65" s="1">
-        <v>6.2310950070500803</v>
+        <v>1.66799515271489</v>
       </c>
       <c r="S65" s="1">
-        <v>0.90768007232021097</v>
+        <v>0.15075896963304</v>
       </c>
       <c r="T65" s="1">
-        <v>63.998198019156597</v>
+        <v>61.514580454863498</v>
       </c>
       <c r="U65" s="1">
-        <v>12.559615644592</v>
+        <v>5.6605831266398603</v>
       </c>
       <c r="V65" s="6">
-        <v>9.5166097224819201E-12</v>
+        <v>2.49244059158382E-6</v>
       </c>
       <c r="W65" s="1"/>
-      <c r="X65" s="30"/>
-      <c r="Y65" s="30"/>
-      <c r="Z65" s="30"/>
-      <c r="AA65" s="30"/>
-      <c r="AB65" s="30"/>
-      <c r="AC65" s="51"/>
+      <c r="X65" s="45"/>
+      <c r="Y65" s="45"/>
+      <c r="Z65" s="45"/>
+      <c r="AA65" s="45"/>
+      <c r="AB65" s="45"/>
+      <c r="AC65" s="35"/>
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A66" s="33"/>
+      <c r="A66" s="48"/>
       <c r="B66" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C66" s="1">
-        <v>3.11592623939527E-2</v>
+        <v>1.37366591368214E-2</v>
       </c>
       <c r="D66" s="1">
-        <v>3.11592623939527E-2</v>
+        <v>1.37366591368214E-2</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
       </c>
       <c r="F66" s="1">
-        <v>67.3835864091361</v>
+        <v>57.458627570771498</v>
       </c>
       <c r="G66" s="1">
-        <v>0.63854715062201595</v>
+        <v>0.75218820572632805</v>
       </c>
       <c r="H66" s="1">
-        <v>0.42704513346780898</v>
+        <v>0.38939195861388898</v>
       </c>
       <c r="I66" s="1"/>
-      <c r="J66" s="30"/>
-      <c r="K66" s="30"/>
-      <c r="L66" s="30"/>
-      <c r="M66" s="30"/>
-      <c r="N66" s="30"/>
-      <c r="O66" s="30"/>
-      <c r="P66" s="33"/>
-      <c r="Q66" s="47" t="s">
-        <v>31</v>
+      <c r="J66" s="45"/>
+      <c r="K66" s="45"/>
+      <c r="L66" s="45"/>
+      <c r="M66" s="45"/>
+      <c r="N66" s="45"/>
+      <c r="O66" s="45"/>
+      <c r="P66" s="48"/>
+      <c r="Q66" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="R66" s="1">
-        <v>0.87043623763491396</v>
+        <v>0.62197037241022901</v>
       </c>
       <c r="S66" s="1">
-        <v>0.179797852023692</v>
+        <v>0.15294515378255399</v>
       </c>
       <c r="T66" s="1">
-        <v>32.074175256944102</v>
+        <v>21.507071906541999</v>
       </c>
       <c r="U66" s="1">
-        <v>-0.67176777469391802</v>
+        <v>-1.93108835287197</v>
       </c>
       <c r="V66" s="1">
-        <v>0.90697094516344701</v>
+        <v>0.24503008385552599</v>
       </c>
       <c r="W66" s="1"/>
-      <c r="X66" s="30"/>
-      <c r="Y66" s="30"/>
-      <c r="Z66" s="30"/>
-      <c r="AA66" s="30"/>
-      <c r="AB66" s="30"/>
-      <c r="AC66" s="51"/>
+      <c r="X66" s="45"/>
+      <c r="Y66" s="45"/>
+      <c r="Z66" s="45"/>
+      <c r="AA66" s="45"/>
+      <c r="AB66" s="45"/>
+      <c r="AC66" s="35"/>
     </row>
     <row r="67" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="34"/>
+      <c r="A67" s="49"/>
       <c r="B67" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C67" s="43"/>
-      <c r="D67" s="43"/>
-      <c r="E67" s="43"/>
-      <c r="F67" s="43"/>
-      <c r="G67" s="43"/>
-      <c r="H67" s="43"/>
+        <v>48</v>
+      </c>
+      <c r="C67" s="58"/>
+      <c r="D67" s="58"/>
+      <c r="E67" s="58"/>
+      <c r="F67" s="58"/>
+      <c r="G67" s="58"/>
+      <c r="H67" s="58"/>
       <c r="I67" s="9"/>
-      <c r="J67" s="31"/>
-      <c r="K67" s="31"/>
-      <c r="L67" s="31"/>
-      <c r="M67" s="31"/>
-      <c r="N67" s="31"/>
-      <c r="O67" s="31"/>
-      <c r="P67" s="34"/>
-      <c r="Q67" s="48" t="s">
-        <v>32</v>
+      <c r="J67" s="46"/>
+      <c r="K67" s="46"/>
+      <c r="L67" s="46"/>
+      <c r="M67" s="46"/>
+      <c r="N67" s="46"/>
+      <c r="O67" s="46"/>
+      <c r="P67" s="49"/>
+      <c r="Q67" s="32" t="s">
+        <v>30</v>
       </c>
       <c r="R67" s="9">
-        <v>1.0477657047880899</v>
+        <v>0.54852054109157</v>
       </c>
       <c r="S67" s="9">
-        <v>0.22829484029702099</v>
+        <v>0.138689132631619</v>
       </c>
       <c r="T67" s="9">
-        <v>33.7659320002318</v>
+        <v>23.424366595514599</v>
       </c>
       <c r="U67" s="9">
-        <v>0.21414739088603499</v>
-      </c>
-      <c r="V67" s="9">
-        <v>0.99646171487333202</v>
+        <v>-2.3751200702861999</v>
+      </c>
+      <c r="V67" s="42">
+        <v>0.109927732737644</v>
       </c>
       <c r="W67" s="9"/>
-      <c r="X67" s="31"/>
-      <c r="Y67" s="31"/>
-      <c r="Z67" s="31"/>
-      <c r="AA67" s="31"/>
-      <c r="AB67" s="31"/>
-      <c r="AC67" s="52"/>
+      <c r="X67" s="46"/>
+      <c r="Y67" s="46"/>
+      <c r="Z67" s="46"/>
+      <c r="AA67" s="46"/>
+      <c r="AB67" s="46"/>
+      <c r="AC67" s="36"/>
     </row>
     <row r="68" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="32" t="s">
-        <v>23</v>
+      <c r="A68" s="47" t="s">
+        <v>18</v>
       </c>
       <c r="B68" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C68" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="D68" s="42"/>
-      <c r="E68" s="42"/>
-      <c r="F68" s="42"/>
-      <c r="G68" s="42"/>
-      <c r="H68" s="42"/>
+      <c r="C68" s="8">
+        <v>10.9358082393645</v>
+      </c>
+      <c r="D68" s="8">
+        <v>10.9358082393645</v>
+      </c>
+      <c r="E68" s="8">
+        <v>1</v>
+      </c>
+      <c r="F68" s="8">
+        <v>67.383586408567496</v>
+      </c>
+      <c r="G68" s="8">
+        <v>224.10765385608801</v>
+      </c>
+      <c r="H68" s="20">
+        <v>4.0821399088527701E-23</v>
+      </c>
       <c r="I68" s="8"/>
-      <c r="J68" s="8">
-        <v>4.9920514192076698E-4</v>
-      </c>
-      <c r="K68" s="8">
-        <v>4.9920514192076698E-4</v>
-      </c>
-      <c r="L68" s="8">
-        <v>1</v>
-      </c>
-      <c r="M68" s="8">
-        <v>109.501348528158</v>
-      </c>
-      <c r="N68" s="8">
-        <v>3.3446840501390498</v>
-      </c>
-      <c r="O68" s="28">
-        <v>7.0143959578357298E-2</v>
-      </c>
-      <c r="P68" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q68" s="49" t="s">
-        <v>29</v>
-      </c>
-      <c r="R68" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="S68" s="44"/>
-      <c r="T68" s="44"/>
-      <c r="U68" s="44"/>
-      <c r="V68" s="44"/>
+      <c r="J68" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="K68" s="44"/>
+      <c r="L68" s="44"/>
+      <c r="M68" s="44"/>
+      <c r="N68" s="44"/>
+      <c r="O68" s="44"/>
+      <c r="P68" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q68" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="R68" s="13">
+        <v>5.1765111889964999</v>
+      </c>
+      <c r="S68" s="13">
+        <v>0.94034664213896701</v>
+      </c>
+      <c r="T68" s="13">
+        <v>66.362964163016898</v>
+      </c>
+      <c r="U68" s="13">
+        <v>9.0507731513692704</v>
+      </c>
+      <c r="V68" s="15">
+        <v>0</v>
+      </c>
       <c r="W68" s="13"/>
-      <c r="X68" s="13">
-        <v>7.7522088498056798E-3</v>
-      </c>
-      <c r="Y68" s="13">
-        <v>3.0776655749197002E-3</v>
-      </c>
-      <c r="Z68" s="13">
-        <v>109.122356414667</v>
-      </c>
-      <c r="AA68" s="13">
-        <v>2.5188600454121599</v>
-      </c>
-      <c r="AB68" s="13">
-        <v>6.2566828845477901E-2</v>
-      </c>
-      <c r="AC68" s="53"/>
+      <c r="X68" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y68" s="57"/>
+      <c r="Z68" s="57"/>
+      <c r="AA68" s="57"/>
+      <c r="AB68" s="57"/>
+      <c r="AC68" s="37"/>
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A69" s="33"/>
+      <c r="A69" s="48"/>
       <c r="B69" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C69" s="30"/>
-      <c r="D69" s="30"/>
-      <c r="E69" s="30"/>
-      <c r="F69" s="30"/>
-      <c r="G69" s="30"/>
-      <c r="H69" s="30"/>
+      <c r="C69" s="1">
+        <v>3.35549271707291E-3</v>
+      </c>
+      <c r="D69" s="1">
+        <v>3.35549271707291E-3</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1</v>
+      </c>
+      <c r="F69" s="1">
+        <v>19.7769266057722</v>
+      </c>
+      <c r="G69" s="1">
+        <v>6.8764153859934604E-2</v>
+      </c>
+      <c r="H69" s="1">
+        <v>0.79585674296255904</v>
+      </c>
       <c r="I69" s="1"/>
-      <c r="J69" s="1">
-        <v>4.3245963051368403E-3</v>
-      </c>
-      <c r="K69" s="1">
-        <v>4.3245963051368403E-3</v>
-      </c>
-      <c r="L69" s="1">
-        <v>1</v>
-      </c>
-      <c r="M69" s="1">
-        <v>14.3846326295774</v>
-      </c>
-      <c r="N69" s="1">
-        <v>28.974878402548999</v>
-      </c>
-      <c r="O69" s="4">
-        <v>8.7931651517614295E-5</v>
-      </c>
-      <c r="P69" s="33"/>
-      <c r="Q69" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="R69" s="30"/>
-      <c r="S69" s="30"/>
-      <c r="T69" s="30"/>
-      <c r="U69" s="30"/>
-      <c r="V69" s="30"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="45"/>
+      <c r="L69" s="45"/>
+      <c r="M69" s="45"/>
+      <c r="N69" s="45"/>
+      <c r="O69" s="45"/>
+      <c r="P69" s="48"/>
+      <c r="Q69" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="R69" s="1">
+        <v>6.2310950070500803</v>
+      </c>
+      <c r="S69" s="1">
+        <v>0.90768007232021097</v>
+      </c>
+      <c r="T69" s="1">
+        <v>63.998198019156597</v>
+      </c>
+      <c r="U69" s="1">
+        <v>12.559615644592</v>
+      </c>
+      <c r="V69" s="6">
+        <v>9.5166097224819201E-12</v>
+      </c>
       <c r="W69" s="1"/>
-      <c r="X69" s="1">
-        <v>-2.3309139166002101E-2</v>
-      </c>
-      <c r="Y69" s="1">
-        <v>5.0808983370555097E-3</v>
-      </c>
-      <c r="Z69" s="1">
-        <v>20.052756261989</v>
-      </c>
-      <c r="AA69" s="1">
-        <v>-4.5876019592846697</v>
-      </c>
-      <c r="AB69" s="2">
-        <v>9.4136808893374702E-4</v>
-      </c>
-      <c r="AC69" s="51"/>
+      <c r="X69" s="45"/>
+      <c r="Y69" s="45"/>
+      <c r="Z69" s="45"/>
+      <c r="AA69" s="45"/>
+      <c r="AB69" s="45"/>
+      <c r="AC69" s="35"/>
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A70" s="33"/>
+      <c r="A70" s="48"/>
       <c r="B70" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
+      <c r="C70" s="1">
+        <v>3.11592623939527E-2</v>
+      </c>
+      <c r="D70" s="1">
+        <v>3.11592623939527E-2</v>
+      </c>
+      <c r="E70" s="1">
+        <v>1</v>
+      </c>
+      <c r="F70" s="1">
+        <v>67.3835864091361</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0.63854715062201595</v>
+      </c>
+      <c r="H70" s="1">
+        <v>0.42704513346780898</v>
+      </c>
       <c r="I70" s="1"/>
-      <c r="J70" s="5">
-        <v>4.4673218852987901E-5</v>
-      </c>
-      <c r="K70" s="5">
-        <v>4.4673218852987901E-5</v>
-      </c>
-      <c r="L70" s="1">
-        <v>1</v>
-      </c>
-      <c r="M70" s="1">
-        <v>109.203333776652</v>
-      </c>
-      <c r="N70" s="1">
-        <v>0.29931142534119798</v>
-      </c>
-      <c r="O70" s="1">
-        <v>0.58543070585289902</v>
-      </c>
-      <c r="P70" s="33"/>
-      <c r="Q70" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="R70" s="30"/>
-      <c r="S70" s="30"/>
-      <c r="T70" s="30"/>
-      <c r="U70" s="30"/>
-      <c r="V70" s="30"/>
+      <c r="J70" s="45"/>
+      <c r="K70" s="45"/>
+      <c r="L70" s="45"/>
+      <c r="M70" s="45"/>
+      <c r="N70" s="45"/>
+      <c r="O70" s="45"/>
+      <c r="P70" s="48"/>
+      <c r="Q70" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="R70" s="1">
+        <v>0.87043623763491396</v>
+      </c>
+      <c r="S70" s="1">
+        <v>0.179797852023692</v>
+      </c>
+      <c r="T70" s="1">
+        <v>32.074175256944102</v>
+      </c>
+      <c r="U70" s="1">
+        <v>-0.67176777469391802</v>
+      </c>
+      <c r="V70" s="1">
+        <v>0.90697094516344701</v>
+      </c>
       <c r="W70" s="1"/>
-      <c r="X70" s="1">
-        <v>-2.56909740646773E-2</v>
-      </c>
-      <c r="Y70" s="1">
-        <v>5.0327094016775504E-3</v>
-      </c>
-      <c r="Z70" s="1">
-        <v>20.202116157369801</v>
-      </c>
-      <c r="AA70" s="1">
-        <v>-5.1047998233543499</v>
-      </c>
-      <c r="AB70" s="2">
-        <v>2.8425104165863402E-4</v>
-      </c>
-      <c r="AC70" s="51"/>
+      <c r="X70" s="45"/>
+      <c r="Y70" s="45"/>
+      <c r="Z70" s="45"/>
+      <c r="AA70" s="45"/>
+      <c r="AB70" s="45"/>
+      <c r="AC70" s="35"/>
     </row>
     <row r="71" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="34"/>
+      <c r="A71" s="49"/>
       <c r="B71" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C71" s="31"/>
-      <c r="D71" s="31"/>
-      <c r="E71" s="31"/>
-      <c r="F71" s="31"/>
-      <c r="G71" s="31"/>
-      <c r="H71" s="31"/>
+        <v>48</v>
+      </c>
+      <c r="C71" s="58"/>
+      <c r="D71" s="58"/>
+      <c r="E71" s="58"/>
+      <c r="F71" s="58"/>
+      <c r="G71" s="58"/>
+      <c r="H71" s="58"/>
       <c r="I71" s="9"/>
-      <c r="J71" s="9">
-        <v>2.5092673060789E-4</v>
-      </c>
-      <c r="K71" s="9">
-        <v>1.25463365303945E-4</v>
-      </c>
-      <c r="L71" s="9">
-        <v>2</v>
-      </c>
-      <c r="M71" s="9">
-        <v>109.245496603218</v>
-      </c>
-      <c r="N71" s="9">
-        <v>0.84060696008511204</v>
-      </c>
-      <c r="O71" s="9">
-        <v>0.43421981831232398</v>
-      </c>
-      <c r="P71" s="34"/>
-      <c r="Q71" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="R71" s="31"/>
-      <c r="S71" s="31"/>
-      <c r="T71" s="31"/>
-      <c r="U71" s="31"/>
-      <c r="V71" s="31"/>
+      <c r="J71" s="46"/>
+      <c r="K71" s="46"/>
+      <c r="L71" s="46"/>
+      <c r="M71" s="46"/>
+      <c r="N71" s="46"/>
+      <c r="O71" s="46"/>
+      <c r="P71" s="49"/>
+      <c r="Q71" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="R71" s="9">
+        <v>1.0477657047880899</v>
+      </c>
+      <c r="S71" s="9">
+        <v>0.22829484029702099</v>
+      </c>
+      <c r="T71" s="9">
+        <v>33.7659320002318</v>
+      </c>
+      <c r="U71" s="9">
+        <v>0.21414739088603499</v>
+      </c>
+      <c r="V71" s="9">
+        <v>0.99646171487333202</v>
+      </c>
       <c r="W71" s="9"/>
-      <c r="X71" s="9">
-        <v>5.3703739511303996E-3</v>
-      </c>
-      <c r="Y71" s="9">
-        <v>3.0818249826465001E-3</v>
-      </c>
-      <c r="Z71" s="9">
-        <v>107.550667952098</v>
-      </c>
-      <c r="AA71" s="9">
-        <v>1.74259537169389</v>
-      </c>
-      <c r="AB71" s="9">
-        <v>0.30698034668227098</v>
-      </c>
-      <c r="AC71" s="9"/>
+      <c r="X71" s="46"/>
+      <c r="Y71" s="46"/>
+      <c r="Z71" s="46"/>
+      <c r="AA71" s="46"/>
+      <c r="AB71" s="46"/>
+      <c r="AC71" s="36"/>
     </row>
     <row r="72" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="32" t="s">
+      <c r="A72" s="47" t="s">
         <v>16</v>
       </c>
       <c r="B72" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C72" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="D72" s="42"/>
-      <c r="E72" s="42"/>
-      <c r="F72" s="42"/>
-      <c r="G72" s="42"/>
-      <c r="H72" s="42"/>
+      <c r="C72" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="D72" s="44"/>
+      <c r="E72" s="44"/>
+      <c r="F72" s="44"/>
+      <c r="G72" s="44"/>
+      <c r="H72" s="44"/>
       <c r="I72" s="8"/>
       <c r="J72" s="8">
         <v>7.7190184322692705E-4</v>
@@ -5587,19 +5592,19 @@
       <c r="O72" s="8">
         <v>0.71627332791354703</v>
       </c>
-      <c r="P72" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q72" s="49" t="s">
-        <v>29</v>
-      </c>
-      <c r="R72" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="S72" s="44"/>
-      <c r="T72" s="44"/>
-      <c r="U72" s="44"/>
-      <c r="V72" s="44"/>
+      <c r="P72" s="47" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q72" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="R72" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="S72" s="57"/>
+      <c r="T72" s="57"/>
+      <c r="U72" s="57"/>
+      <c r="V72" s="57"/>
       <c r="W72" s="13"/>
       <c r="X72" s="13">
         <v>0.96246045193694896</v>
@@ -5619,16 +5624,16 @@
       <c r="AC72" s="13"/>
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A73" s="33"/>
+      <c r="A73" s="48"/>
       <c r="B73" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C73" s="30"/>
-      <c r="D73" s="30"/>
-      <c r="E73" s="30"/>
-      <c r="F73" s="30"/>
-      <c r="G73" s="30"/>
-      <c r="H73" s="30"/>
+      <c r="C73" s="45"/>
+      <c r="D73" s="45"/>
+      <c r="E73" s="45"/>
+      <c r="F73" s="45"/>
+      <c r="G73" s="45"/>
+      <c r="H73" s="45"/>
       <c r="I73" s="1"/>
       <c r="J73" s="1">
         <v>0.26383928794443301</v>
@@ -5648,15 +5653,15 @@
       <c r="O73" s="4">
         <v>8.8402488312841299E-6</v>
       </c>
-      <c r="P73" s="33"/>
-      <c r="Q73" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="R73" s="30"/>
-      <c r="S73" s="30"/>
-      <c r="T73" s="30"/>
-      <c r="U73" s="30"/>
-      <c r="V73" s="30"/>
+      <c r="P73" s="48"/>
+      <c r="Q73" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="R73" s="45"/>
+      <c r="S73" s="45"/>
+      <c r="T73" s="45"/>
+      <c r="U73" s="45"/>
+      <c r="V73" s="45"/>
       <c r="W73" s="1"/>
       <c r="X73" s="1">
         <v>1.0284695041493801</v>
@@ -5676,16 +5681,16 @@
       <c r="AC73" s="1"/>
     </row>
     <row r="74" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A74" s="33"/>
+      <c r="A74" s="48"/>
       <c r="B74" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C74" s="30"/>
-      <c r="D74" s="30"/>
-      <c r="E74" s="30"/>
-      <c r="F74" s="30"/>
-      <c r="G74" s="30"/>
-      <c r="H74" s="30"/>
+      <c r="C74" s="45"/>
+      <c r="D74" s="45"/>
+      <c r="E74" s="45"/>
+      <c r="F74" s="45"/>
+      <c r="G74" s="45"/>
+      <c r="H74" s="45"/>
       <c r="I74" s="1"/>
       <c r="J74" s="1">
         <v>6.5298294112546198E-3</v>
@@ -5705,15 +5710,15 @@
       <c r="O74" s="1">
         <v>0.29157119540922299</v>
       </c>
-      <c r="P74" s="33"/>
-      <c r="Q74" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="R74" s="30"/>
-      <c r="S74" s="30"/>
-      <c r="T74" s="30"/>
-      <c r="U74" s="30"/>
-      <c r="V74" s="30"/>
+      <c r="P74" s="48"/>
+      <c r="Q74" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="R74" s="45"/>
+      <c r="S74" s="45"/>
+      <c r="T74" s="45"/>
+      <c r="U74" s="45"/>
+      <c r="V74" s="45"/>
       <c r="W74" s="1"/>
       <c r="X74" s="1">
         <v>0.59461928503453898</v>
@@ -5733,16 +5738,16 @@
       <c r="AC74" s="1"/>
     </row>
     <row r="75" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="34"/>
+      <c r="A75" s="49"/>
       <c r="B75" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C75" s="31"/>
-      <c r="D75" s="31"/>
-      <c r="E75" s="31"/>
-      <c r="F75" s="31"/>
-      <c r="G75" s="31"/>
-      <c r="H75" s="31"/>
+        <v>48</v>
+      </c>
+      <c r="C75" s="46"/>
+      <c r="D75" s="46"/>
+      <c r="E75" s="46"/>
+      <c r="F75" s="46"/>
+      <c r="G75" s="46"/>
+      <c r="H75" s="46"/>
       <c r="I75" s="9"/>
       <c r="J75" s="9">
         <v>7.3489818378573097E-3</v>
@@ -5762,15 +5767,15 @@
       <c r="O75" s="9">
         <v>0.53343128963438502</v>
       </c>
-      <c r="P75" s="34"/>
-      <c r="Q75" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="R75" s="31"/>
-      <c r="S75" s="31"/>
-      <c r="T75" s="31"/>
-      <c r="U75" s="31"/>
-      <c r="V75" s="31"/>
+      <c r="P75" s="49"/>
+      <c r="Q75" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="R75" s="46"/>
+      <c r="S75" s="46"/>
+      <c r="T75" s="46"/>
+      <c r="U75" s="46"/>
+      <c r="V75" s="46"/>
       <c r="W75" s="9"/>
       <c r="X75" s="9">
         <v>0.63540044685097696</v>
@@ -5784,13 +5789,13 @@
       <c r="AA75" s="9">
         <v>-5.7760586849782101</v>
       </c>
-      <c r="AB75" s="56">
+      <c r="AB75" s="40">
         <v>7.9364409904192397E-5</v>
       </c>
       <c r="AC75" s="9"/>
     </row>
     <row r="76" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="32" t="s">
+      <c r="A76" s="47" t="s">
         <v>17</v>
       </c>
       <c r="B76" s="8" t="s">
@@ -5815,19 +5820,19 @@
         <v>4.1643897411378698E-17</v>
       </c>
       <c r="I76" s="8"/>
-      <c r="J76" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="K76" s="42"/>
-      <c r="L76" s="42"/>
-      <c r="M76" s="42"/>
-      <c r="N76" s="42"/>
-      <c r="O76" s="42"/>
-      <c r="P76" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q76" s="49" t="s">
-        <v>29</v>
+      <c r="J76" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="K76" s="44"/>
+      <c r="L76" s="44"/>
+      <c r="M76" s="44"/>
+      <c r="N76" s="44"/>
+      <c r="O76" s="44"/>
+      <c r="P76" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q76" s="33" t="s">
+        <v>27</v>
       </c>
       <c r="R76" s="13">
         <v>-8.3740558709758908</v>
@@ -5841,21 +5846,21 @@
       <c r="U76" s="13">
         <v>-6.5887216259403703</v>
       </c>
-      <c r="V76" s="57">
+      <c r="V76" s="41">
         <v>5.3435041391658398E-8</v>
       </c>
       <c r="W76" s="13"/>
-      <c r="X76" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y76" s="44"/>
-      <c r="Z76" s="44"/>
-      <c r="AA76" s="44"/>
-      <c r="AB76" s="44"/>
+      <c r="X76" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y76" s="57"/>
+      <c r="Z76" s="57"/>
+      <c r="AA76" s="57"/>
+      <c r="AB76" s="57"/>
       <c r="AC76" s="13"/>
     </row>
     <row r="77" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A77" s="33"/>
+      <c r="A77" s="48"/>
       <c r="B77" s="1" t="s">
         <v>7</v>
       </c>
@@ -5878,15 +5883,15 @@
         <v>4.6861954719532999E-4</v>
       </c>
       <c r="I77" s="1"/>
-      <c r="J77" s="30"/>
-      <c r="K77" s="30"/>
-      <c r="L77" s="30"/>
-      <c r="M77" s="30"/>
-      <c r="N77" s="30"/>
-      <c r="O77" s="30"/>
-      <c r="P77" s="33"/>
-      <c r="Q77" s="47" t="s">
-        <v>30</v>
+      <c r="J77" s="45"/>
+      <c r="K77" s="45"/>
+      <c r="L77" s="45"/>
+      <c r="M77" s="45"/>
+      <c r="N77" s="45"/>
+      <c r="O77" s="45"/>
+      <c r="P77" s="48"/>
+      <c r="Q77" s="31" t="s">
+        <v>28</v>
       </c>
       <c r="R77" s="1">
         <v>-10.150777804234499</v>
@@ -5904,15 +5909,15 @@
         <v>1.2034151453121901E-11</v>
       </c>
       <c r="W77" s="1"/>
-      <c r="X77" s="30"/>
-      <c r="Y77" s="30"/>
-      <c r="Z77" s="30"/>
-      <c r="AA77" s="30"/>
-      <c r="AB77" s="30"/>
+      <c r="X77" s="45"/>
+      <c r="Y77" s="45"/>
+      <c r="Z77" s="45"/>
+      <c r="AA77" s="45"/>
+      <c r="AB77" s="45"/>
       <c r="AC77" s="1"/>
     </row>
     <row r="78" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="33"/>
+      <c r="A78" s="48"/>
       <c r="B78" s="1" t="s">
         <v>8</v>
       </c>
@@ -5935,15 +5940,15 @@
         <v>0.27294624360005199</v>
       </c>
       <c r="I78" s="1"/>
-      <c r="J78" s="30"/>
-      <c r="K78" s="30"/>
-      <c r="L78" s="30"/>
-      <c r="M78" s="30"/>
-      <c r="N78" s="30"/>
-      <c r="O78" s="30"/>
-      <c r="P78" s="33"/>
-      <c r="Q78" s="47" t="s">
-        <v>31</v>
+      <c r="J78" s="45"/>
+      <c r="K78" s="45"/>
+      <c r="L78" s="45"/>
+      <c r="M78" s="45"/>
+      <c r="N78" s="45"/>
+      <c r="O78" s="45"/>
+      <c r="P78" s="48"/>
+      <c r="Q78" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="R78" s="1">
         <v>-7.86992683231641</v>
@@ -5961,34 +5966,34 @@
         <v>5.9764406718529903E-3</v>
       </c>
       <c r="W78" s="1"/>
-      <c r="X78" s="30"/>
-      <c r="Y78" s="30"/>
-      <c r="Z78" s="30"/>
-      <c r="AA78" s="30"/>
-      <c r="AB78" s="30"/>
+      <c r="X78" s="45"/>
+      <c r="Y78" s="45"/>
+      <c r="Z78" s="45"/>
+      <c r="AA78" s="45"/>
+      <c r="AB78" s="45"/>
       <c r="AC78" s="1"/>
     </row>
     <row r="79" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="34"/>
+      <c r="A79" s="49"/>
       <c r="B79" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C79" s="43"/>
-      <c r="D79" s="43"/>
-      <c r="E79" s="43"/>
-      <c r="F79" s="43"/>
-      <c r="G79" s="43"/>
-      <c r="H79" s="43"/>
+        <v>48</v>
+      </c>
+      <c r="C79" s="58"/>
+      <c r="D79" s="58"/>
+      <c r="E79" s="58"/>
+      <c r="F79" s="58"/>
+      <c r="G79" s="58"/>
+      <c r="H79" s="58"/>
       <c r="I79" s="9"/>
-      <c r="J79" s="31"/>
-      <c r="K79" s="31"/>
-      <c r="L79" s="31"/>
-      <c r="M79" s="31"/>
-      <c r="N79" s="31"/>
-      <c r="O79" s="31"/>
-      <c r="P79" s="34"/>
-      <c r="Q79" s="48" t="s">
-        <v>32</v>
+      <c r="J79" s="46"/>
+      <c r="K79" s="46"/>
+      <c r="L79" s="46"/>
+      <c r="M79" s="46"/>
+      <c r="N79" s="46"/>
+      <c r="O79" s="46"/>
+      <c r="P79" s="49"/>
+      <c r="Q79" s="32" t="s">
+        <v>30</v>
       </c>
       <c r="R79" s="9">
         <v>-9.6466487655750495</v>
@@ -6006,15 +6011,15 @@
         <v>9.8108965488741305E-4</v>
       </c>
       <c r="W79" s="9"/>
-      <c r="X79" s="31"/>
-      <c r="Y79" s="31"/>
-      <c r="Z79" s="31"/>
-      <c r="AA79" s="31"/>
-      <c r="AB79" s="31"/>
+      <c r="X79" s="46"/>
+      <c r="Y79" s="46"/>
+      <c r="Z79" s="46"/>
+      <c r="AA79" s="46"/>
+      <c r="AB79" s="46"/>
       <c r="AC79" s="9"/>
     </row>
     <row r="80" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="32" t="s">
+      <c r="A80" s="47" t="s">
         <v>19</v>
       </c>
       <c r="B80" s="8" t="s">
@@ -6039,19 +6044,19 @@
         <v>6.4779999000469503E-17</v>
       </c>
       <c r="I80" s="8"/>
-      <c r="J80" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="K80" s="42"/>
-      <c r="L80" s="42"/>
-      <c r="M80" s="42"/>
-      <c r="N80" s="42"/>
-      <c r="O80" s="42"/>
-      <c r="P80" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q80" s="49" t="s">
-        <v>29</v>
+      <c r="J80" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="K80" s="44"/>
+      <c r="L80" s="44"/>
+      <c r="M80" s="44"/>
+      <c r="N80" s="44"/>
+      <c r="O80" s="44"/>
+      <c r="P80" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q80" s="33" t="s">
+        <v>27</v>
       </c>
       <c r="R80" s="13">
         <v>2.9177136151243199</v>
@@ -6065,21 +6070,21 @@
       <c r="U80" s="13">
         <v>6.4135823376221897</v>
       </c>
-      <c r="V80" s="57">
+      <c r="V80" s="41">
         <v>1.14162453601629E-7</v>
       </c>
       <c r="W80" s="13"/>
-      <c r="X80" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y80" s="44"/>
-      <c r="Z80" s="44"/>
-      <c r="AA80" s="44"/>
-      <c r="AB80" s="44"/>
-      <c r="AC80" s="50"/>
+      <c r="X80" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y80" s="57"/>
+      <c r="Z80" s="57"/>
+      <c r="AA80" s="57"/>
+      <c r="AB80" s="57"/>
+      <c r="AC80" s="34"/>
     </row>
     <row r="81" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A81" s="33"/>
+      <c r="A81" s="48"/>
       <c r="B81" s="1" t="s">
         <v>7</v>
       </c>
@@ -6102,15 +6107,15 @@
         <v>1.4106574908243E-2</v>
       </c>
       <c r="I81" s="1"/>
-      <c r="J81" s="30"/>
-      <c r="K81" s="30"/>
-      <c r="L81" s="30"/>
-      <c r="M81" s="30"/>
-      <c r="N81" s="30"/>
-      <c r="O81" s="30"/>
-      <c r="P81" s="33"/>
-      <c r="Q81" s="47" t="s">
-        <v>30</v>
+      <c r="J81" s="45"/>
+      <c r="K81" s="45"/>
+      <c r="L81" s="45"/>
+      <c r="M81" s="45"/>
+      <c r="N81" s="45"/>
+      <c r="O81" s="45"/>
+      <c r="P81" s="48"/>
+      <c r="Q81" s="31" t="s">
+        <v>28</v>
       </c>
       <c r="R81" s="1">
         <v>3.7301111316362499</v>
@@ -6128,15 +6133,15 @@
         <v>1.6875612018907301E-11</v>
       </c>
       <c r="W81" s="1"/>
-      <c r="X81" s="30"/>
-      <c r="Y81" s="30"/>
-      <c r="Z81" s="30"/>
-      <c r="AA81" s="30"/>
-      <c r="AB81" s="30"/>
-      <c r="AC81" s="51"/>
+      <c r="X81" s="45"/>
+      <c r="Y81" s="45"/>
+      <c r="Z81" s="45"/>
+      <c r="AA81" s="45"/>
+      <c r="AB81" s="45"/>
+      <c r="AC81" s="35"/>
     </row>
     <row r="82" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A82" s="33"/>
+      <c r="A82" s="48"/>
       <c r="B82" s="1" t="s">
         <v>8</v>
       </c>
@@ -6159,15 +6164,15 @@
         <v>0.25735376158301099</v>
       </c>
       <c r="I82" s="1"/>
-      <c r="J82" s="30"/>
-      <c r="K82" s="30"/>
-      <c r="L82" s="30"/>
-      <c r="M82" s="30"/>
-      <c r="N82" s="30"/>
-      <c r="O82" s="30"/>
-      <c r="P82" s="33"/>
-      <c r="Q82" s="47" t="s">
-        <v>31</v>
+      <c r="J82" s="45"/>
+      <c r="K82" s="45"/>
+      <c r="L82" s="45"/>
+      <c r="M82" s="45"/>
+      <c r="N82" s="45"/>
+      <c r="O82" s="45"/>
+      <c r="P82" s="48"/>
+      <c r="Q82" s="31" t="s">
+        <v>29</v>
       </c>
       <c r="R82" s="1">
         <v>1.37224989644095</v>
@@ -6185,34 +6190,34 @@
         <v>0.37476551599412999</v>
       </c>
       <c r="W82" s="1"/>
-      <c r="X82" s="30"/>
-      <c r="Y82" s="30"/>
-      <c r="Z82" s="30"/>
-      <c r="AA82" s="30"/>
-      <c r="AB82" s="30"/>
-      <c r="AC82" s="51"/>
+      <c r="X82" s="45"/>
+      <c r="Y82" s="45"/>
+      <c r="Z82" s="45"/>
+      <c r="AA82" s="45"/>
+      <c r="AB82" s="45"/>
+      <c r="AC82" s="35"/>
     </row>
     <row r="83" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="34"/>
+      <c r="A83" s="49"/>
       <c r="B83" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C83" s="43"/>
-      <c r="D83" s="43"/>
-      <c r="E83" s="43"/>
-      <c r="F83" s="43"/>
-      <c r="G83" s="43"/>
-      <c r="H83" s="43"/>
+        <v>48</v>
+      </c>
+      <c r="C83" s="58"/>
+      <c r="D83" s="58"/>
+      <c r="E83" s="58"/>
+      <c r="F83" s="58"/>
+      <c r="G83" s="58"/>
+      <c r="H83" s="58"/>
       <c r="I83" s="9"/>
-      <c r="J83" s="31"/>
-      <c r="K83" s="31"/>
-      <c r="L83" s="31"/>
-      <c r="M83" s="31"/>
-      <c r="N83" s="31"/>
-      <c r="O83" s="31"/>
-      <c r="P83" s="34"/>
-      <c r="Q83" s="48" t="s">
-        <v>32</v>
+      <c r="J83" s="46"/>
+      <c r="K83" s="46"/>
+      <c r="L83" s="46"/>
+      <c r="M83" s="46"/>
+      <c r="N83" s="46"/>
+      <c r="O83" s="46"/>
+      <c r="P83" s="49"/>
+      <c r="Q83" s="32" t="s">
+        <v>30</v>
       </c>
       <c r="R83" s="9">
         <v>1.7543341428603401</v>
@@ -6226,20 +6231,20 @@
       <c r="U83" s="9">
         <v>2.7458766153504999</v>
       </c>
-      <c r="V83" s="9">
+      <c r="V83" s="19">
         <v>4.5827702542128403E-2</v>
       </c>
       <c r="W83" s="9"/>
-      <c r="X83" s="31"/>
-      <c r="Y83" s="31"/>
-      <c r="Z83" s="31"/>
-      <c r="AA83" s="31"/>
-      <c r="AB83" s="31"/>
-      <c r="AC83" s="52"/>
+      <c r="X83" s="46"/>
+      <c r="Y83" s="46"/>
+      <c r="Z83" s="46"/>
+      <c r="AA83" s="46"/>
+      <c r="AB83" s="46"/>
+      <c r="AC83" s="36"/>
     </row>
     <row r="84" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="32" t="s">
-        <v>49</v>
+      <c r="A84" s="47" t="s">
+        <v>46</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>9</v>
@@ -6263,21 +6268,21 @@
         <v>0.38079976992345599</v>
       </c>
       <c r="I84" s="8"/>
-      <c r="J84" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="K84" s="42"/>
-      <c r="L84" s="42"/>
-      <c r="M84" s="42"/>
-      <c r="N84" s="42"/>
-      <c r="O84" s="42"/>
-      <c r="P84" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q84" s="49" t="s">
-        <v>29</v>
-      </c>
-      <c r="R84" s="55">
+      <c r="J84" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="K84" s="44"/>
+      <c r="L84" s="44"/>
+      <c r="M84" s="44"/>
+      <c r="N84" s="44"/>
+      <c r="O84" s="44"/>
+      <c r="P84" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q84" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="R84" s="39">
         <v>-1.65441347008876E-5</v>
       </c>
       <c r="S84" s="13">
@@ -6289,21 +6294,21 @@
       <c r="U84" s="13">
         <v>-1.1861521821923401E-2</v>
       </c>
-      <c r="V84" s="13">
+      <c r="V84" s="43">
         <v>0.99999939343423405</v>
       </c>
       <c r="W84" s="13"/>
-      <c r="X84" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y84" s="44"/>
-      <c r="Z84" s="44"/>
-      <c r="AA84" s="44"/>
-      <c r="AB84" s="44"/>
-      <c r="AC84" s="53"/>
+      <c r="X84" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y84" s="57"/>
+      <c r="Z84" s="57"/>
+      <c r="AA84" s="57"/>
+      <c r="AB84" s="57"/>
+      <c r="AC84" s="37"/>
     </row>
     <row r="85" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A85" s="33"/>
+      <c r="A85" s="48"/>
       <c r="B85" s="1" t="s">
         <v>7</v>
       </c>
@@ -6326,41 +6331,41 @@
         <v>5.7804446105462802E-3</v>
       </c>
       <c r="I85" s="1"/>
-      <c r="J85" s="30"/>
-      <c r="K85" s="30"/>
-      <c r="L85" s="30"/>
-      <c r="M85" s="30"/>
-      <c r="N85" s="30"/>
-      <c r="O85" s="30"/>
-      <c r="P85" s="33"/>
-      <c r="Q85" s="47" t="s">
-        <v>30</v>
+      <c r="J85" s="45"/>
+      <c r="K85" s="45"/>
+      <c r="L85" s="45"/>
+      <c r="M85" s="45"/>
+      <c r="N85" s="45"/>
+      <c r="O85" s="45"/>
+      <c r="P85" s="48"/>
+      <c r="Q85" s="31" t="s">
+        <v>28</v>
       </c>
       <c r="R85" s="1">
-        <v>-4.7357111792336601E-3</v>
+        <v>1.6280035456013801E-3</v>
       </c>
       <c r="S85" s="1">
-        <v>1.45559347836175E-3</v>
+        <v>1.1877502326311899E-3</v>
       </c>
       <c r="T85" s="1">
-        <v>33.175075568647898</v>
+        <v>60.830326285509202</v>
       </c>
       <c r="U85" s="1">
-        <v>-3.25345726649148</v>
-      </c>
-      <c r="V85" s="2">
-        <v>1.33110134354993E-2</v>
+        <v>1.37066152535698</v>
+      </c>
+      <c r="V85" s="1">
+        <v>0.52237983670065102</v>
       </c>
       <c r="W85" s="1"/>
-      <c r="X85" s="30"/>
-      <c r="Y85" s="30"/>
-      <c r="Z85" s="30"/>
-      <c r="AA85" s="30"/>
-      <c r="AB85" s="30"/>
-      <c r="AC85" s="51"/>
+      <c r="X85" s="45"/>
+      <c r="Y85" s="45"/>
+      <c r="Z85" s="45"/>
+      <c r="AA85" s="45"/>
+      <c r="AB85" s="45"/>
+      <c r="AC85" s="35"/>
     </row>
     <row r="86" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A86" s="33"/>
+      <c r="A86" s="48"/>
       <c r="B86" s="1" t="s">
         <v>8</v>
       </c>
@@ -6383,93 +6388,93 @@
         <v>0.37116202943872301</v>
       </c>
       <c r="I86" s="1"/>
-      <c r="J86" s="30"/>
-      <c r="K86" s="30"/>
-      <c r="L86" s="30"/>
-      <c r="M86" s="30"/>
-      <c r="N86" s="30"/>
-      <c r="O86" s="30"/>
-      <c r="P86" s="33"/>
-      <c r="Q86" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="R86" s="1">
+      <c r="J86" s="45"/>
+      <c r="K86" s="45"/>
+      <c r="L86" s="45"/>
+      <c r="M86" s="45"/>
+      <c r="N86" s="45"/>
+      <c r="O86" s="45"/>
+      <c r="P86" s="48"/>
+      <c r="Q86" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="R86" s="13">
+        <v>-4.7357111792336601E-3</v>
+      </c>
+      <c r="S86" s="13">
+        <v>1.45559347836175E-3</v>
+      </c>
+      <c r="T86" s="13">
+        <v>33.175075568647898</v>
+      </c>
+      <c r="U86" s="13">
+        <v>-3.25345726649148</v>
+      </c>
+      <c r="V86" s="15">
+        <v>1.33110134354993E-2</v>
+      </c>
+      <c r="W86" s="1"/>
+      <c r="X86" s="45"/>
+      <c r="Y86" s="45"/>
+      <c r="Z86" s="45"/>
+      <c r="AA86" s="45"/>
+      <c r="AB86" s="45"/>
+      <c r="AC86" s="35"/>
+    </row>
+    <row r="87" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="49"/>
+      <c r="B87" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C87" s="58"/>
+      <c r="D87" s="58"/>
+      <c r="E87" s="58"/>
+      <c r="F87" s="58"/>
+      <c r="G87" s="58"/>
+      <c r="H87" s="58"/>
+      <c r="I87" s="9"/>
+      <c r="J87" s="46"/>
+      <c r="K87" s="46"/>
+      <c r="L87" s="46"/>
+      <c r="M87" s="46"/>
+      <c r="N87" s="46"/>
+      <c r="O87" s="46"/>
+      <c r="P87" s="49"/>
+      <c r="Q87" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="R87" s="9">
         <v>-3.0911634989313902E-3</v>
       </c>
-      <c r="S86" s="1">
+      <c r="S87" s="9">
         <v>1.5710422017598299E-3</v>
       </c>
-      <c r="T86" s="1">
+      <c r="T87" s="9">
         <v>35.526741286073303</v>
       </c>
-      <c r="U86" s="1">
+      <c r="U87" s="9">
         <v>-1.96758781875418</v>
       </c>
-      <c r="V86" s="1">
+      <c r="V87" s="9">
         <v>0.21931254615242901</v>
       </c>
-      <c r="W86" s="1"/>
-      <c r="X86" s="30"/>
-      <c r="Y86" s="30"/>
-      <c r="Z86" s="30"/>
-      <c r="AA86" s="30"/>
-      <c r="AB86" s="30"/>
-      <c r="AC86" s="51"/>
-    </row>
-    <row r="87" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="34"/>
-      <c r="B87" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C87" s="43"/>
-      <c r="D87" s="43"/>
-      <c r="E87" s="43"/>
-      <c r="F87" s="43"/>
-      <c r="G87" s="43"/>
-      <c r="H87" s="43"/>
-      <c r="I87" s="9"/>
-      <c r="J87" s="31"/>
-      <c r="K87" s="31"/>
-      <c r="L87" s="31"/>
-      <c r="M87" s="31"/>
-      <c r="N87" s="31"/>
-      <c r="O87" s="31"/>
-      <c r="P87" s="34"/>
-      <c r="Q87" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="R87" s="9">
-        <v>1.6280035456013801E-3</v>
-      </c>
-      <c r="S87" s="9">
-        <v>1.1877502326311899E-3</v>
-      </c>
-      <c r="T87" s="9">
-        <v>60.830326285509202</v>
-      </c>
-      <c r="U87" s="9">
-        <v>1.37066152535698</v>
-      </c>
-      <c r="V87" s="9">
-        <v>0.52237983670065102</v>
-      </c>
       <c r="W87" s="9"/>
-      <c r="X87" s="31"/>
-      <c r="Y87" s="31"/>
-      <c r="Z87" s="31"/>
-      <c r="AA87" s="31"/>
-      <c r="AB87" s="31"/>
-      <c r="AC87" s="52"/>
+      <c r="X87" s="46"/>
+      <c r="Y87" s="46"/>
+      <c r="Z87" s="46"/>
+      <c r="AA87" s="46"/>
+      <c r="AB87" s="46"/>
+      <c r="AC87" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="91">
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="J27:O30"/>
-    <mergeCell ref="X23:AB26"/>
-    <mergeCell ref="X27:AB30"/>
-    <mergeCell ref="C30:H30"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="J23:O26"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="J35:O38"/>
+    <mergeCell ref="X31:AB34"/>
+    <mergeCell ref="X35:AB38"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="J31:O34"/>
     <mergeCell ref="J3:O6"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="C1:I1"/>
@@ -6481,30 +6486,30 @@
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="A11:A14"/>
     <mergeCell ref="C11:H14"/>
+    <mergeCell ref="A68:A71"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="C23:H26"/>
     <mergeCell ref="A64:A67"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A56:A59"/>
-    <mergeCell ref="C56:H59"/>
+    <mergeCell ref="C67:H67"/>
+    <mergeCell ref="A44:A47"/>
+    <mergeCell ref="C47:H47"/>
+    <mergeCell ref="A48:A51"/>
+    <mergeCell ref="C51:H51"/>
+    <mergeCell ref="A52:A55"/>
+    <mergeCell ref="C55:H55"/>
     <mergeCell ref="A60:A63"/>
     <mergeCell ref="C63:H63"/>
-    <mergeCell ref="A36:A39"/>
-    <mergeCell ref="C39:H39"/>
-    <mergeCell ref="A40:A43"/>
-    <mergeCell ref="C43:H43"/>
-    <mergeCell ref="A44:A47"/>
-    <mergeCell ref="C47:H47"/>
-    <mergeCell ref="A52:A55"/>
-    <mergeCell ref="C55:H55"/>
-    <mergeCell ref="A48:A51"/>
-    <mergeCell ref="C51:H51"/>
+    <mergeCell ref="A56:A59"/>
+    <mergeCell ref="C59:H59"/>
     <mergeCell ref="A19:A22"/>
     <mergeCell ref="C19:H22"/>
-    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="A31:A34"/>
     <mergeCell ref="A84:A87"/>
     <mergeCell ref="J84:O87"/>
     <mergeCell ref="C87:H87"/>
-    <mergeCell ref="A68:A71"/>
-    <mergeCell ref="C68:H71"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="C27:H30"/>
     <mergeCell ref="A80:A83"/>
     <mergeCell ref="J80:O83"/>
     <mergeCell ref="C83:H83"/>
@@ -6513,46 +6518,46 @@
     <mergeCell ref="C79:H79"/>
     <mergeCell ref="A72:A75"/>
     <mergeCell ref="C72:H75"/>
-    <mergeCell ref="J31:O34"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="P31:P34"/>
-    <mergeCell ref="X31:AB34"/>
-    <mergeCell ref="P68:P71"/>
-    <mergeCell ref="R68:V71"/>
+    <mergeCell ref="J39:O42"/>
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="P39:P42"/>
+    <mergeCell ref="X39:AB42"/>
+    <mergeCell ref="P27:P30"/>
+    <mergeCell ref="R27:V30"/>
+    <mergeCell ref="J68:O71"/>
+    <mergeCell ref="C71:H71"/>
     <mergeCell ref="J64:O67"/>
-    <mergeCell ref="C67:H67"/>
-    <mergeCell ref="J60:O63"/>
     <mergeCell ref="X84:AB87"/>
     <mergeCell ref="P19:P22"/>
     <mergeCell ref="R19:V22"/>
     <mergeCell ref="P84:P87"/>
-    <mergeCell ref="P64:P67"/>
-    <mergeCell ref="X64:AB67"/>
+    <mergeCell ref="P68:P71"/>
+    <mergeCell ref="X68:AB71"/>
     <mergeCell ref="R72:V75"/>
     <mergeCell ref="P76:P79"/>
     <mergeCell ref="X80:AB83"/>
-    <mergeCell ref="R56:V59"/>
-    <mergeCell ref="P52:P55"/>
+    <mergeCell ref="R23:V26"/>
     <mergeCell ref="P60:P63"/>
+    <mergeCell ref="P64:P67"/>
     <mergeCell ref="P72:P75"/>
-    <mergeCell ref="P56:P59"/>
+    <mergeCell ref="P23:P26"/>
     <mergeCell ref="X76:AB79"/>
-    <mergeCell ref="X60:AB63"/>
+    <mergeCell ref="X64:AB67"/>
     <mergeCell ref="R11:V14"/>
     <mergeCell ref="P80:P83"/>
     <mergeCell ref="X1:AC1"/>
-    <mergeCell ref="P48:P51"/>
+    <mergeCell ref="P56:P59"/>
     <mergeCell ref="P3:P6"/>
     <mergeCell ref="X3:AB6"/>
     <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="P36:P39"/>
-    <mergeCell ref="P40:P43"/>
+    <mergeCell ref="P44:P47"/>
+    <mergeCell ref="P48:P51"/>
     <mergeCell ref="R1:W1"/>
-    <mergeCell ref="P44:P47"/>
+    <mergeCell ref="P52:P55"/>
     <mergeCell ref="P15:P18"/>
     <mergeCell ref="P7:P10"/>
-    <mergeCell ref="P23:P26"/>
-    <mergeCell ref="P27:P30"/>
+    <mergeCell ref="P31:P34"/>
+    <mergeCell ref="P35:P38"/>
     <mergeCell ref="P11:P14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/ModelResults_emmeans.xlsx
+++ b/data/ModelResults_emmeans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://michiganstate-my.sharepoint.com/personal/buysseso_msu_edu/Documents/Arabidopsis/Swe_Italy/R_scripts/SW_IT_PopDiffPlasticity/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1832" documentId="13_ncr:1_{AD4A5BE6-D9C1-414A-81C8-3A9C273D7774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3570AA86-9C39-4DF9-BCD3-618DBFCDBAA2}"/>
+  <xr:revisionPtr revIDLastSave="1852" documentId="13_ncr:1_{AD4A5BE6-D9C1-414A-81C8-3A9C273D7774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D784E2C-AB2D-4609-84AA-56118F5163A1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8A213037-8BA5-417B-A75A-3088B4717938}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{8A213037-8BA5-417B-A75A-3088B4717938}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelResults_ManuTraits" sheetId="5" r:id="rId1"/>
@@ -566,14 +566,14 @@
     <xf numFmtId="11" fontId="0" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -584,17 +584,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -606,6 +603,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -964,7 +964,10 @@
   <cols>
     <col min="1" max="1" width="24.42578125" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.42578125" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="31.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="27" customWidth="1"/>
     <col min="22" max="22" width="20.7109375" bestFit="1" customWidth="1"/>
@@ -976,43 +979,43 @@
         <v>0</v>
       </c>
       <c r="B1" s="11"/>
-      <c r="C1" s="50">
+      <c r="C1" s="44">
         <v>2021</v>
       </c>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="50">
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="44">
         <v>2022</v>
       </c>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
       <c r="P1" s="11"/>
-      <c r="Q1" s="54" t="s">
+      <c r="Q1" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="R1" s="50" t="s">
+      <c r="R1" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
-      <c r="W1" s="52"/>
-      <c r="X1" s="50" t="s">
+      <c r="S1" s="45"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="45"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="Y1" s="51"/>
-      <c r="Z1" s="51"/>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="51"/>
-      <c r="AC1" s="52"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
+      <c r="AB1" s="45"/>
+      <c r="AC1" s="46"/>
     </row>
     <row r="2" spans="1:29" s="16" customFormat="1" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
@@ -1061,7 +1064,7 @@
       <c r="P2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="Q2" s="55"/>
+      <c r="Q2" s="54"/>
       <c r="R2" s="10" t="s">
         <v>49</v>
       </c>
@@ -1100,7 +1103,7 @@
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="50" t="s">
         <v>36</v>
       </c>
       <c r="B3" s="13" t="s">
@@ -1125,15 +1128,15 @@
         <v>7.3383790508167401E-2</v>
       </c>
       <c r="I3" s="13"/>
-      <c r="J3" s="45" t="s">
+      <c r="J3" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="53" t="s">
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="50" t="s">
         <v>36</v>
       </c>
       <c r="Q3" s="30" t="s">
@@ -1155,13 +1158,13 @@
         <v>0.60935835609726297</v>
       </c>
       <c r="W3" s="1"/>
-      <c r="X3" s="45" t="s">
+      <c r="X3" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="Y3" s="45"/>
-      <c r="Z3" s="45"/>
-      <c r="AA3" s="45"/>
-      <c r="AB3" s="45"/>
+      <c r="Y3" s="51"/>
+      <c r="Z3" s="51"/>
+      <c r="AA3" s="51"/>
+      <c r="AB3" s="51"/>
       <c r="AC3" s="34"/>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
@@ -1188,12 +1191,12 @@
         <v>5.8229847066576205E-7</v>
       </c>
       <c r="I4" s="1"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="45"/>
-      <c r="M4" s="45"/>
-      <c r="N4" s="45"/>
-      <c r="O4" s="45"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="51"/>
+      <c r="O4" s="51"/>
       <c r="P4" s="48"/>
       <c r="Q4" s="31" t="s">
         <v>28</v>
@@ -1214,11 +1217,11 @@
         <v>0.51504029973848997</v>
       </c>
       <c r="W4" s="1"/>
-      <c r="X4" s="45"/>
-      <c r="Y4" s="45"/>
-      <c r="Z4" s="45"/>
-      <c r="AA4" s="45"/>
-      <c r="AB4" s="45"/>
+      <c r="X4" s="51"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
+      <c r="AB4" s="51"/>
       <c r="AC4" s="35"/>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
@@ -1244,12 +1247,12 @@
       <c r="H5" s="1">
         <v>0.90072460165650603</v>
       </c>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="51"/>
+      <c r="M5" s="51"/>
+      <c r="N5" s="51"/>
+      <c r="O5" s="51"/>
       <c r="P5" s="48"/>
       <c r="Q5" s="31" t="s">
         <v>29</v>
@@ -1270,11 +1273,11 @@
         <v>8.4463170790804996E-8</v>
       </c>
       <c r="W5" s="1"/>
-      <c r="X5" s="45"/>
-      <c r="Y5" s="45"/>
-      <c r="Z5" s="45"/>
-      <c r="AA5" s="45"/>
-      <c r="AB5" s="45"/>
+      <c r="X5" s="51"/>
+      <c r="Y5" s="51"/>
+      <c r="Z5" s="51"/>
+      <c r="AA5" s="51"/>
+      <c r="AB5" s="51"/>
       <c r="AC5" s="35"/>
     </row>
     <row r="6" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1289,12 +1292,12 @@
       <c r="G6" s="58"/>
       <c r="H6" s="58"/>
       <c r="I6" s="9"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46"/>
-      <c r="M6" s="46"/>
-      <c r="N6" s="46"/>
-      <c r="O6" s="46"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="52"/>
+      <c r="N6" s="52"/>
+      <c r="O6" s="52"/>
       <c r="P6" s="49"/>
       <c r="Q6" s="32" t="s">
         <v>30</v>
@@ -1315,11 +1318,11 @@
         <v>8.5628197088460896E-8</v>
       </c>
       <c r="W6" s="9"/>
-      <c r="X6" s="46"/>
-      <c r="Y6" s="46"/>
-      <c r="Z6" s="46"/>
-      <c r="AA6" s="46"/>
-      <c r="AB6" s="46"/>
+      <c r="X6" s="52"/>
+      <c r="Y6" s="52"/>
+      <c r="Z6" s="52"/>
+      <c r="AA6" s="52"/>
+      <c r="AB6" s="52"/>
       <c r="AC6" s="36"/>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.25">
@@ -1366,7 +1369,7 @@
       <c r="O7" s="14">
         <v>7.9655542624253594E-15</v>
       </c>
-      <c r="P7" s="53" t="s">
+      <c r="P7" s="50" t="s">
         <v>15</v>
       </c>
       <c r="Q7" s="30" t="s">
@@ -1593,7 +1596,7 @@
       <c r="O10" s="9">
         <v>0.23519968422781001</v>
       </c>
-      <c r="P10" s="56"/>
+      <c r="P10" s="55"/>
       <c r="Q10" s="32" t="s">
         <v>30</v>
       </c>
@@ -1637,14 +1640,14 @@
       <c r="B11" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="45" t="s">
+      <c r="C11" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
       <c r="I11" s="13"/>
       <c r="J11" s="13">
         <v>2.20343269025562E-2</v>
@@ -1664,19 +1667,19 @@
       <c r="O11" s="15">
         <v>1.20915323151938E-2</v>
       </c>
-      <c r="P11" s="53" t="s">
+      <c r="P11" s="50" t="s">
         <v>51</v>
       </c>
       <c r="Q11" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="R11" s="44" t="s">
+      <c r="R11" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="S11" s="44"/>
-      <c r="T11" s="44"/>
-      <c r="U11" s="44"/>
-      <c r="V11" s="44"/>
+      <c r="S11" s="57"/>
+      <c r="T11" s="57"/>
+      <c r="U11" s="57"/>
+      <c r="V11" s="57"/>
       <c r="W11" s="13"/>
       <c r="X11" s="13">
         <v>0.92269407717206897</v>
@@ -1700,12 +1703,12 @@
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1">
         <v>2.98483856205864E-2</v>
@@ -1729,11 +1732,11 @@
       <c r="Q12" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="R12" s="45"/>
-      <c r="S12" s="45"/>
-      <c r="T12" s="45"/>
-      <c r="U12" s="45"/>
-      <c r="V12" s="45"/>
+      <c r="R12" s="51"/>
+      <c r="S12" s="51"/>
+      <c r="T12" s="51"/>
+      <c r="U12" s="51"/>
+      <c r="V12" s="51"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1">
         <v>0.89729079192970995</v>
@@ -1757,12 +1760,12 @@
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1">
         <v>1.15818782663304E-3</v>
@@ -1786,11 +1789,11 @@
       <c r="Q13" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="R13" s="45"/>
-      <c r="S13" s="45"/>
-      <c r="T13" s="45"/>
-      <c r="U13" s="45"/>
-      <c r="V13" s="45"/>
+      <c r="R13" s="51"/>
+      <c r="S13" s="51"/>
+      <c r="T13" s="51"/>
+      <c r="U13" s="51"/>
+      <c r="V13" s="51"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1">
         <v>0.88184620079220499</v>
@@ -1814,12 +1817,12 @@
       <c r="B14" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
       <c r="I14" s="9"/>
       <c r="J14" s="9">
         <v>2.0797141885883202E-3</v>
@@ -1843,11 +1846,11 @@
       <c r="Q14" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="R14" s="46"/>
-      <c r="S14" s="46"/>
-      <c r="T14" s="46"/>
-      <c r="U14" s="46"/>
-      <c r="V14" s="46"/>
+      <c r="R14" s="52"/>
+      <c r="S14" s="52"/>
+      <c r="T14" s="52"/>
+      <c r="U14" s="52"/>
+      <c r="V14" s="52"/>
       <c r="W14" s="9"/>
       <c r="X14" s="9">
         <v>0.85756752475770204</v>
@@ -2181,14 +2184,14 @@
       <c r="B19" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="44" t="s">
+      <c r="C19" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
       <c r="I19" s="8"/>
       <c r="J19" s="8">
         <v>1.4241127553301099E-4</v>
@@ -2214,13 +2217,13 @@
       <c r="Q19" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="R19" s="44" t="s">
+      <c r="R19" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="S19" s="44"/>
-      <c r="T19" s="44"/>
-      <c r="U19" s="44"/>
-      <c r="V19" s="44"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="57"/>
       <c r="W19" s="13"/>
       <c r="X19" s="13">
         <v>0.92228721673858705</v>
@@ -2244,12 +2247,12 @@
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1">
         <v>4.6725153189010001E-2</v>
@@ -2273,11 +2276,11 @@
       <c r="Q20" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="R20" s="45"/>
-      <c r="S20" s="45"/>
-      <c r="T20" s="45"/>
-      <c r="U20" s="45"/>
-      <c r="V20" s="45"/>
+      <c r="R20" s="51"/>
+      <c r="S20" s="51"/>
+      <c r="T20" s="51"/>
+      <c r="U20" s="51"/>
+      <c r="V20" s="51"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1">
         <v>1.0589700479598501</v>
@@ -2301,12 +2304,12 @@
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1">
         <v>2.8302586845141399E-2</v>
@@ -2330,11 +2333,11 @@
       <c r="Q21" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="R21" s="45"/>
-      <c r="S21" s="45"/>
-      <c r="T21" s="45"/>
-      <c r="U21" s="45"/>
-      <c r="V21" s="45"/>
+      <c r="R21" s="51"/>
+      <c r="S21" s="51"/>
+      <c r="T21" s="51"/>
+      <c r="U21" s="51"/>
+      <c r="V21" s="51"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1">
         <v>1.19093365397326</v>
@@ -2358,12 +2361,12 @@
       <c r="B22" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="46"/>
-      <c r="H22" s="46"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="52"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
       <c r="I22" s="9"/>
       <c r="J22" s="9">
         <v>6.3796317056246301E-3</v>
@@ -2387,11 +2390,11 @@
       <c r="Q22" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="R22" s="46"/>
-      <c r="S22" s="46"/>
-      <c r="T22" s="46"/>
-      <c r="U22" s="46"/>
-      <c r="V22" s="46"/>
+      <c r="R22" s="52"/>
+      <c r="S22" s="52"/>
+      <c r="T22" s="52"/>
+      <c r="U22" s="52"/>
+      <c r="V22" s="52"/>
       <c r="W22" s="9"/>
       <c r="X22" s="9">
         <v>1.36742984807359</v>
@@ -2417,14 +2420,14 @@
       <c r="B23" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="44" t="s">
+      <c r="C23" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="44"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
       <c r="I23" s="8"/>
       <c r="J23" s="8">
         <v>4.0252880405239402E-2</v>
@@ -2450,13 +2453,13 @@
       <c r="Q23" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="R23" s="57" t="s">
+      <c r="R23" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="S23" s="57"/>
-      <c r="T23" s="57"/>
-      <c r="U23" s="57"/>
-      <c r="V23" s="57"/>
+      <c r="S23" s="56"/>
+      <c r="T23" s="56"/>
+      <c r="U23" s="56"/>
+      <c r="V23" s="56"/>
       <c r="W23" s="13"/>
       <c r="X23" s="13">
         <v>1.28624977261183</v>
@@ -2480,12 +2483,12 @@
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="45"/>
-      <c r="H24" s="45"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1">
         <v>0.42132164214255802</v>
@@ -2509,11 +2512,11 @@
       <c r="Q24" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="R24" s="45"/>
-      <c r="S24" s="45"/>
-      <c r="T24" s="45"/>
-      <c r="U24" s="45"/>
-      <c r="V24" s="45"/>
+      <c r="R24" s="51"/>
+      <c r="S24" s="51"/>
+      <c r="T24" s="51"/>
+      <c r="U24" s="51"/>
+      <c r="V24" s="51"/>
       <c r="W24" s="1"/>
       <c r="X24" s="1">
         <v>1.0220158782055699</v>
@@ -2537,12 +2540,12 @@
       <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="45"/>
-      <c r="H25" s="45"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1">
         <v>7.8254362282741005E-2</v>
@@ -2566,11 +2569,11 @@
       <c r="Q25" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="R25" s="45"/>
-      <c r="S25" s="45"/>
-      <c r="T25" s="45"/>
-      <c r="U25" s="45"/>
-      <c r="V25" s="45"/>
+      <c r="R25" s="51"/>
+      <c r="S25" s="51"/>
+      <c r="T25" s="51"/>
+      <c r="U25" s="51"/>
+      <c r="V25" s="51"/>
       <c r="W25" s="1"/>
       <c r="X25" s="1">
         <v>0.45501994044807598</v>
@@ -2594,12 +2597,12 @@
       <c r="B26" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="46"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="52"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="52"/>
       <c r="I26" s="9"/>
       <c r="J26" s="9">
         <v>2.6614614752845599E-3</v>
@@ -2623,11 +2626,11 @@
       <c r="Q26" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="R26" s="46"/>
-      <c r="S26" s="46"/>
-      <c r="T26" s="46"/>
-      <c r="U26" s="46"/>
-      <c r="V26" s="46"/>
+      <c r="R26" s="52"/>
+      <c r="S26" s="52"/>
+      <c r="T26" s="52"/>
+      <c r="U26" s="52"/>
+      <c r="V26" s="52"/>
       <c r="W26" s="9"/>
       <c r="X26" s="9">
         <v>0.361545334304543</v>
@@ -2653,14 +2656,14 @@
       <c r="B27" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C27" s="44" t="s">
+      <c r="C27" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="44"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="57"/>
       <c r="I27" s="8"/>
       <c r="J27" s="8">
         <v>4.9920514192076698E-4</v>
@@ -2686,13 +2689,13 @@
       <c r="Q27" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="R27" s="57" t="s">
+      <c r="R27" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="S27" s="57"/>
-      <c r="T27" s="57"/>
-      <c r="U27" s="57"/>
-      <c r="V27" s="57"/>
+      <c r="S27" s="56"/>
+      <c r="T27" s="56"/>
+      <c r="U27" s="56"/>
+      <c r="V27" s="56"/>
       <c r="W27" s="13"/>
       <c r="X27" s="13">
         <v>7.7522088498056798E-3</v>
@@ -2716,12 +2719,12 @@
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="45"/>
-      <c r="H28" s="45"/>
+      <c r="C28" s="51"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="51"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1">
         <v>4.3245963051368403E-3</v>
@@ -2745,11 +2748,11 @@
       <c r="Q28" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="R28" s="45"/>
-      <c r="S28" s="45"/>
-      <c r="T28" s="45"/>
-      <c r="U28" s="45"/>
-      <c r="V28" s="45"/>
+      <c r="R28" s="51"/>
+      <c r="S28" s="51"/>
+      <c r="T28" s="51"/>
+      <c r="U28" s="51"/>
+      <c r="V28" s="51"/>
       <c r="W28" s="1"/>
       <c r="X28" s="1">
         <v>5.3703739511303996E-3</v>
@@ -2773,12 +2776,12 @@
       <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="45"/>
-      <c r="H29" s="45"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="51"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="51"/>
       <c r="I29" s="1"/>
       <c r="J29" s="5">
         <v>4.4673218852987901E-5</v>
@@ -2802,11 +2805,11 @@
       <c r="Q29" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="R29" s="45"/>
-      <c r="S29" s="45"/>
-      <c r="T29" s="45"/>
-      <c r="U29" s="45"/>
-      <c r="V29" s="45"/>
+      <c r="R29" s="51"/>
+      <c r="S29" s="51"/>
+      <c r="T29" s="51"/>
+      <c r="U29" s="51"/>
+      <c r="V29" s="51"/>
       <c r="W29" s="1"/>
       <c r="X29" s="1">
         <v>-2.3309139166002101E-2</v>
@@ -2830,12 +2833,12 @@
       <c r="B30" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="46"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="46"/>
-      <c r="H30" s="46"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
       <c r="I30" s="9"/>
       <c r="J30" s="9">
         <v>2.5092673060789E-4</v>
@@ -2859,11 +2862,11 @@
       <c r="Q30" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="R30" s="46"/>
-      <c r="S30" s="46"/>
-      <c r="T30" s="46"/>
-      <c r="U30" s="46"/>
-      <c r="V30" s="46"/>
+      <c r="R30" s="52"/>
+      <c r="S30" s="52"/>
+      <c r="T30" s="52"/>
+      <c r="U30" s="52"/>
+      <c r="V30" s="52"/>
       <c r="W30" s="9"/>
       <c r="X30" s="9">
         <v>-2.56909740646773E-2</v>
@@ -2908,14 +2911,14 @@
         <v>1.898803E-20</v>
       </c>
       <c r="I31" s="1"/>
-      <c r="J31" s="44" t="s">
+      <c r="J31" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="K31" s="44"/>
-      <c r="L31" s="44"/>
-      <c r="M31" s="44"/>
-      <c r="N31" s="44"/>
-      <c r="O31" s="44"/>
+      <c r="K31" s="57"/>
+      <c r="L31" s="57"/>
+      <c r="M31" s="57"/>
+      <c r="N31" s="57"/>
+      <c r="O31" s="57"/>
       <c r="P31" s="47" t="s">
         <v>42</v>
       </c>
@@ -2938,13 +2941,13 @@
         <v>0</v>
       </c>
       <c r="W31" s="13"/>
-      <c r="X31" s="57" t="s">
+      <c r="X31" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="Y31" s="57"/>
-      <c r="Z31" s="57"/>
-      <c r="AA31" s="57"/>
-      <c r="AB31" s="57"/>
+      <c r="Y31" s="56"/>
+      <c r="Z31" s="56"/>
+      <c r="AA31" s="56"/>
+      <c r="AB31" s="56"/>
       <c r="AC31" s="35"/>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.25">
@@ -2971,12 +2974,12 @@
         <v>0.2597892</v>
       </c>
       <c r="I32" s="1"/>
-      <c r="J32" s="45"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="45"/>
-      <c r="M32" s="45"/>
-      <c r="N32" s="45"/>
-      <c r="O32" s="45"/>
+      <c r="J32" s="51"/>
+      <c r="K32" s="51"/>
+      <c r="L32" s="51"/>
+      <c r="M32" s="51"/>
+      <c r="N32" s="51"/>
+      <c r="O32" s="51"/>
       <c r="P32" s="48"/>
       <c r="Q32" s="31" t="s">
         <v>28</v>
@@ -2997,11 +3000,11 @@
         <v>0</v>
       </c>
       <c r="W32" s="1"/>
-      <c r="X32" s="45"/>
-      <c r="Y32" s="45"/>
-      <c r="Z32" s="45"/>
-      <c r="AA32" s="45"/>
-      <c r="AB32" s="45"/>
+      <c r="X32" s="51"/>
+      <c r="Y32" s="51"/>
+      <c r="Z32" s="51"/>
+      <c r="AA32" s="51"/>
+      <c r="AB32" s="51"/>
       <c r="AC32" s="35"/>
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.25">
@@ -3028,12 +3031,12 @@
         <v>0.7055884</v>
       </c>
       <c r="I33" s="1"/>
-      <c r="J33" s="45"/>
-      <c r="K33" s="45"/>
-      <c r="L33" s="45"/>
-      <c r="M33" s="45"/>
-      <c r="N33" s="45"/>
-      <c r="O33" s="45"/>
+      <c r="J33" s="51"/>
+      <c r="K33" s="51"/>
+      <c r="L33" s="51"/>
+      <c r="M33" s="51"/>
+      <c r="N33" s="51"/>
+      <c r="O33" s="51"/>
       <c r="P33" s="48"/>
       <c r="Q33" s="31" t="s">
         <v>29</v>
@@ -3054,11 +3057,11 @@
         <v>0.85729287706349799</v>
       </c>
       <c r="W33" s="1"/>
-      <c r="X33" s="45"/>
-      <c r="Y33" s="45"/>
-      <c r="Z33" s="45"/>
-      <c r="AA33" s="45"/>
-      <c r="AB33" s="45"/>
+      <c r="X33" s="51"/>
+      <c r="Y33" s="51"/>
+      <c r="Z33" s="51"/>
+      <c r="AA33" s="51"/>
+      <c r="AB33" s="51"/>
       <c r="AC33" s="35"/>
     </row>
     <row r="34" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3073,12 +3076,12 @@
       <c r="G34" s="58"/>
       <c r="H34" s="58"/>
       <c r="I34" s="9"/>
-      <c r="J34" s="46"/>
-      <c r="K34" s="46"/>
-      <c r="L34" s="46"/>
-      <c r="M34" s="46"/>
-      <c r="N34" s="46"/>
-      <c r="O34" s="46"/>
+      <c r="J34" s="52"/>
+      <c r="K34" s="52"/>
+      <c r="L34" s="52"/>
+      <c r="M34" s="52"/>
+      <c r="N34" s="52"/>
+      <c r="O34" s="52"/>
       <c r="P34" s="49"/>
       <c r="Q34" s="32" t="s">
         <v>30</v>
@@ -3099,11 +3102,11 @@
         <v>0.63803985452722101</v>
       </c>
       <c r="W34" s="9"/>
-      <c r="X34" s="46"/>
-      <c r="Y34" s="46"/>
-      <c r="Z34" s="46"/>
-      <c r="AA34" s="46"/>
-      <c r="AB34" s="46"/>
+      <c r="X34" s="52"/>
+      <c r="Y34" s="52"/>
+      <c r="Z34" s="52"/>
+      <c r="AA34" s="52"/>
+      <c r="AB34" s="52"/>
       <c r="AC34" s="36"/>
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.25">
@@ -3132,14 +3135,14 @@
         <v>9.94550983787633E-8</v>
       </c>
       <c r="I35" s="13"/>
-      <c r="J35" s="57" t="s">
+      <c r="J35" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="K35" s="57"/>
-      <c r="L35" s="57"/>
-      <c r="M35" s="57"/>
-      <c r="N35" s="57"/>
-      <c r="O35" s="57"/>
+      <c r="K35" s="56"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="56"/>
+      <c r="N35" s="56"/>
+      <c r="O35" s="56"/>
       <c r="P35" s="48" t="s">
         <v>47</v>
       </c>
@@ -3162,13 +3165,13 @@
         <v>0.64903708255730697</v>
       </c>
       <c r="W35" s="13"/>
-      <c r="X35" s="45" t="s">
+      <c r="X35" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="Y35" s="45"/>
-      <c r="Z35" s="45"/>
-      <c r="AA35" s="45"/>
-      <c r="AB35" s="45"/>
+      <c r="Y35" s="51"/>
+      <c r="Z35" s="51"/>
+      <c r="AA35" s="51"/>
+      <c r="AB35" s="51"/>
       <c r="AC35" s="34"/>
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.25">
@@ -3195,12 +3198,12 @@
         <v>3.5283045440115499E-6</v>
       </c>
       <c r="I36" s="1"/>
-      <c r="J36" s="45"/>
-      <c r="K36" s="45"/>
-      <c r="L36" s="45"/>
-      <c r="M36" s="45"/>
-      <c r="N36" s="45"/>
-      <c r="O36" s="45"/>
+      <c r="J36" s="51"/>
+      <c r="K36" s="51"/>
+      <c r="L36" s="51"/>
+      <c r="M36" s="51"/>
+      <c r="N36" s="51"/>
+      <c r="O36" s="51"/>
       <c r="P36" s="48"/>
       <c r="Q36" s="31" t="s">
         <v>28</v>
@@ -3221,11 +3224,11 @@
         <v>7.4586492537775898E-10</v>
       </c>
       <c r="W36" s="1"/>
-      <c r="X36" s="45"/>
-      <c r="Y36" s="45"/>
-      <c r="Z36" s="45"/>
-      <c r="AA36" s="45"/>
-      <c r="AB36" s="45"/>
+      <c r="X36" s="51"/>
+      <c r="Y36" s="51"/>
+      <c r="Z36" s="51"/>
+      <c r="AA36" s="51"/>
+      <c r="AB36" s="51"/>
       <c r="AC36" s="35"/>
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.25">
@@ -3252,12 +3255,12 @@
         <v>9.6345615419962495E-5</v>
       </c>
       <c r="I37" s="1"/>
-      <c r="J37" s="45"/>
-      <c r="K37" s="45"/>
-      <c r="L37" s="45"/>
-      <c r="M37" s="45"/>
-      <c r="N37" s="45"/>
-      <c r="O37" s="45"/>
+      <c r="J37" s="51"/>
+      <c r="K37" s="51"/>
+      <c r="L37" s="51"/>
+      <c r="M37" s="51"/>
+      <c r="N37" s="51"/>
+      <c r="O37" s="51"/>
       <c r="P37" s="48"/>
       <c r="Q37" s="31" t="s">
         <v>29</v>
@@ -3278,15 +3281,15 @@
         <v>3.2178754427736301E-6</v>
       </c>
       <c r="W37" s="1"/>
-      <c r="X37" s="45"/>
-      <c r="Y37" s="45"/>
-      <c r="Z37" s="45"/>
-      <c r="AA37" s="45"/>
-      <c r="AB37" s="45"/>
+      <c r="X37" s="51"/>
+      <c r="Y37" s="51"/>
+      <c r="Z37" s="51"/>
+      <c r="AA37" s="51"/>
+      <c r="AB37" s="51"/>
       <c r="AC37" s="35"/>
     </row>
     <row r="38" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="56"/>
+      <c r="A38" s="55"/>
       <c r="B38" s="9" t="s">
         <v>48</v>
       </c>
@@ -3297,13 +3300,13 @@
       <c r="G38" s="59"/>
       <c r="H38" s="59"/>
       <c r="I38" s="1"/>
-      <c r="J38" s="45"/>
-      <c r="K38" s="45"/>
-      <c r="L38" s="45"/>
-      <c r="M38" s="45"/>
-      <c r="N38" s="45"/>
-      <c r="O38" s="45"/>
-      <c r="P38" s="56"/>
+      <c r="J38" s="51"/>
+      <c r="K38" s="51"/>
+      <c r="L38" s="51"/>
+      <c r="M38" s="51"/>
+      <c r="N38" s="51"/>
+      <c r="O38" s="51"/>
+      <c r="P38" s="55"/>
       <c r="Q38" s="31" t="s">
         <v>30</v>
       </c>
@@ -3323,11 +3326,11 @@
         <v>0.93899599371116504</v>
       </c>
       <c r="W38" s="9"/>
-      <c r="X38" s="46"/>
-      <c r="Y38" s="46"/>
-      <c r="Z38" s="46"/>
-      <c r="AA38" s="46"/>
-      <c r="AB38" s="46"/>
+      <c r="X38" s="52"/>
+      <c r="Y38" s="52"/>
+      <c r="Z38" s="52"/>
+      <c r="AA38" s="52"/>
+      <c r="AB38" s="52"/>
       <c r="AC38" s="35"/>
     </row>
     <row r="39" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
@@ -3356,14 +3359,14 @@
         <v>4.7200869189182898E-19</v>
       </c>
       <c r="I39" s="8"/>
-      <c r="J39" s="44" t="s">
+      <c r="J39" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="K39" s="44"/>
-      <c r="L39" s="44"/>
-      <c r="M39" s="44"/>
-      <c r="N39" s="44"/>
-      <c r="O39" s="44"/>
+      <c r="K39" s="57"/>
+      <c r="L39" s="57"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="57"/>
+      <c r="O39" s="57"/>
       <c r="P39" s="47" t="s">
         <v>20</v>
       </c>
@@ -3386,13 +3389,13 @@
         <v>5.1032972292475198E-9</v>
       </c>
       <c r="W39" s="13"/>
-      <c r="X39" s="45" t="s">
+      <c r="X39" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="Y39" s="45"/>
-      <c r="Z39" s="45"/>
-      <c r="AA39" s="45"/>
-      <c r="AB39" s="45"/>
+      <c r="Y39" s="51"/>
+      <c r="Z39" s="51"/>
+      <c r="AA39" s="51"/>
+      <c r="AB39" s="51"/>
       <c r="AC39" s="37"/>
     </row>
     <row r="40" spans="1:29" x14ac:dyDescent="0.25">
@@ -3419,12 +3422,12 @@
         <v>0.78124664232875995</v>
       </c>
       <c r="I40" s="1"/>
-      <c r="J40" s="45"/>
-      <c r="K40" s="45"/>
-      <c r="L40" s="45"/>
-      <c r="M40" s="45"/>
-      <c r="N40" s="45"/>
-      <c r="O40" s="45"/>
+      <c r="J40" s="51"/>
+      <c r="K40" s="51"/>
+      <c r="L40" s="51"/>
+      <c r="M40" s="51"/>
+      <c r="N40" s="51"/>
+      <c r="O40" s="51"/>
       <c r="P40" s="48"/>
       <c r="Q40" s="31" t="s">
         <v>28</v>
@@ -3445,11 +3448,11 @@
         <v>0</v>
       </c>
       <c r="W40" s="1"/>
-      <c r="X40" s="45"/>
-      <c r="Y40" s="45"/>
-      <c r="Z40" s="45"/>
-      <c r="AA40" s="45"/>
-      <c r="AB40" s="45"/>
+      <c r="X40" s="51"/>
+      <c r="Y40" s="51"/>
+      <c r="Z40" s="51"/>
+      <c r="AA40" s="51"/>
+      <c r="AB40" s="51"/>
       <c r="AC40" s="35"/>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.25">
@@ -3476,12 +3479,12 @@
         <v>0.116304482817742</v>
       </c>
       <c r="I41" s="1"/>
-      <c r="J41" s="45"/>
-      <c r="K41" s="45"/>
-      <c r="L41" s="45"/>
-      <c r="M41" s="45"/>
-      <c r="N41" s="45"/>
-      <c r="O41" s="45"/>
+      <c r="J41" s="51"/>
+      <c r="K41" s="51"/>
+      <c r="L41" s="51"/>
+      <c r="M41" s="51"/>
+      <c r="N41" s="51"/>
+      <c r="O41" s="51"/>
       <c r="P41" s="48"/>
       <c r="Q41" s="31" t="s">
         <v>29</v>
@@ -3502,11 +3505,11 @@
         <v>0.68637145240327702</v>
       </c>
       <c r="W41" s="1"/>
-      <c r="X41" s="45"/>
-      <c r="Y41" s="45"/>
-      <c r="Z41" s="45"/>
-      <c r="AA41" s="45"/>
-      <c r="AB41" s="45"/>
+      <c r="X41" s="51"/>
+      <c r="Y41" s="51"/>
+      <c r="Z41" s="51"/>
+      <c r="AA41" s="51"/>
+      <c r="AB41" s="51"/>
       <c r="AC41" s="35"/>
     </row>
     <row r="42" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3521,12 +3524,12 @@
       <c r="G42" s="58"/>
       <c r="H42" s="58"/>
       <c r="I42" s="9"/>
-      <c r="J42" s="46"/>
-      <c r="K42" s="46"/>
-      <c r="L42" s="46"/>
-      <c r="M42" s="46"/>
-      <c r="N42" s="46"/>
-      <c r="O42" s="46"/>
+      <c r="J42" s="52"/>
+      <c r="K42" s="52"/>
+      <c r="L42" s="52"/>
+      <c r="M42" s="52"/>
+      <c r="N42" s="52"/>
+      <c r="O42" s="52"/>
       <c r="P42" s="49"/>
       <c r="Q42" s="32" t="s">
         <v>30</v>
@@ -3547,11 +3550,11 @@
         <v>0.92024495942184903</v>
       </c>
       <c r="W42" s="9"/>
-      <c r="X42" s="46"/>
-      <c r="Y42" s="46"/>
-      <c r="Z42" s="46"/>
-      <c r="AA42" s="46"/>
-      <c r="AB42" s="46"/>
+      <c r="X42" s="52"/>
+      <c r="Y42" s="52"/>
+      <c r="Z42" s="52"/>
+      <c r="AA42" s="52"/>
+      <c r="AB42" s="52"/>
       <c r="AC42" s="36"/>
     </row>
     <row r="43" spans="1:29" s="24" customFormat="1" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5136,14 +5139,14 @@
         <v>8.5554572534297795E-11</v>
       </c>
       <c r="I64" s="8"/>
-      <c r="J64" s="44" t="s">
+      <c r="J64" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="K64" s="44"/>
-      <c r="L64" s="44"/>
-      <c r="M64" s="44"/>
-      <c r="N64" s="44"/>
-      <c r="O64" s="44"/>
+      <c r="K64" s="57"/>
+      <c r="L64" s="57"/>
+      <c r="M64" s="57"/>
+      <c r="N64" s="57"/>
+      <c r="O64" s="57"/>
       <c r="P64" s="47" t="s">
         <v>26</v>
       </c>
@@ -5166,13 +5169,13 @@
         <v>2.9455467435157701E-6</v>
       </c>
       <c r="W64" s="13"/>
-      <c r="X64" s="57" t="s">
+      <c r="X64" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="Y64" s="57"/>
-      <c r="Z64" s="57"/>
-      <c r="AA64" s="57"/>
-      <c r="AB64" s="57"/>
+      <c r="Y64" s="56"/>
+      <c r="Z64" s="56"/>
+      <c r="AA64" s="56"/>
+      <c r="AB64" s="56"/>
       <c r="AC64" s="37"/>
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.25">
@@ -5199,12 +5202,12 @@
         <v>3.9589780561885203E-2</v>
       </c>
       <c r="I65" s="1"/>
-      <c r="J65" s="45"/>
-      <c r="K65" s="45"/>
-      <c r="L65" s="45"/>
-      <c r="M65" s="45"/>
-      <c r="N65" s="45"/>
-      <c r="O65" s="45"/>
+      <c r="J65" s="51"/>
+      <c r="K65" s="51"/>
+      <c r="L65" s="51"/>
+      <c r="M65" s="51"/>
+      <c r="N65" s="51"/>
+      <c r="O65" s="51"/>
       <c r="P65" s="48"/>
       <c r="Q65" s="31" t="s">
         <v>28</v>
@@ -5225,11 +5228,11 @@
         <v>2.49244059158382E-6</v>
       </c>
       <c r="W65" s="1"/>
-      <c r="X65" s="45"/>
-      <c r="Y65" s="45"/>
-      <c r="Z65" s="45"/>
-      <c r="AA65" s="45"/>
-      <c r="AB65" s="45"/>
+      <c r="X65" s="51"/>
+      <c r="Y65" s="51"/>
+      <c r="Z65" s="51"/>
+      <c r="AA65" s="51"/>
+      <c r="AB65" s="51"/>
       <c r="AC65" s="35"/>
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.25">
@@ -5256,12 +5259,12 @@
         <v>0.38939195861388898</v>
       </c>
       <c r="I66" s="1"/>
-      <c r="J66" s="45"/>
-      <c r="K66" s="45"/>
-      <c r="L66" s="45"/>
-      <c r="M66" s="45"/>
-      <c r="N66" s="45"/>
-      <c r="O66" s="45"/>
+      <c r="J66" s="51"/>
+      <c r="K66" s="51"/>
+      <c r="L66" s="51"/>
+      <c r="M66" s="51"/>
+      <c r="N66" s="51"/>
+      <c r="O66" s="51"/>
       <c r="P66" s="48"/>
       <c r="Q66" s="31" t="s">
         <v>29</v>
@@ -5282,11 +5285,11 @@
         <v>0.24503008385552599</v>
       </c>
       <c r="W66" s="1"/>
-      <c r="X66" s="45"/>
-      <c r="Y66" s="45"/>
-      <c r="Z66" s="45"/>
-      <c r="AA66" s="45"/>
-      <c r="AB66" s="45"/>
+      <c r="X66" s="51"/>
+      <c r="Y66" s="51"/>
+      <c r="Z66" s="51"/>
+      <c r="AA66" s="51"/>
+      <c r="AB66" s="51"/>
       <c r="AC66" s="35"/>
     </row>
     <row r="67" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5301,12 +5304,12 @@
       <c r="G67" s="58"/>
       <c r="H67" s="58"/>
       <c r="I67" s="9"/>
-      <c r="J67" s="46"/>
-      <c r="K67" s="46"/>
-      <c r="L67" s="46"/>
-      <c r="M67" s="46"/>
-      <c r="N67" s="46"/>
-      <c r="O67" s="46"/>
+      <c r="J67" s="52"/>
+      <c r="K67" s="52"/>
+      <c r="L67" s="52"/>
+      <c r="M67" s="52"/>
+      <c r="N67" s="52"/>
+      <c r="O67" s="52"/>
       <c r="P67" s="49"/>
       <c r="Q67" s="32" t="s">
         <v>30</v>
@@ -5327,11 +5330,11 @@
         <v>0.109927732737644</v>
       </c>
       <c r="W67" s="9"/>
-      <c r="X67" s="46"/>
-      <c r="Y67" s="46"/>
-      <c r="Z67" s="46"/>
-      <c r="AA67" s="46"/>
-      <c r="AB67" s="46"/>
+      <c r="X67" s="52"/>
+      <c r="Y67" s="52"/>
+      <c r="Z67" s="52"/>
+      <c r="AA67" s="52"/>
+      <c r="AB67" s="52"/>
       <c r="AC67" s="36"/>
     </row>
     <row r="68" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
@@ -5360,14 +5363,14 @@
         <v>4.0821399088527701E-23</v>
       </c>
       <c r="I68" s="8"/>
-      <c r="J68" s="44" t="s">
+      <c r="J68" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="K68" s="44"/>
-      <c r="L68" s="44"/>
-      <c r="M68" s="44"/>
-      <c r="N68" s="44"/>
-      <c r="O68" s="44"/>
+      <c r="K68" s="57"/>
+      <c r="L68" s="57"/>
+      <c r="M68" s="57"/>
+      <c r="N68" s="57"/>
+      <c r="O68" s="57"/>
       <c r="P68" s="47" t="s">
         <v>41</v>
       </c>
@@ -5390,13 +5393,13 @@
         <v>0</v>
       </c>
       <c r="W68" s="13"/>
-      <c r="X68" s="57" t="s">
+      <c r="X68" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="Y68" s="57"/>
-      <c r="Z68" s="57"/>
-      <c r="AA68" s="57"/>
-      <c r="AB68" s="57"/>
+      <c r="Y68" s="56"/>
+      <c r="Z68" s="56"/>
+      <c r="AA68" s="56"/>
+      <c r="AB68" s="56"/>
       <c r="AC68" s="37"/>
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.25">
@@ -5423,12 +5426,12 @@
         <v>0.79585674296255904</v>
       </c>
       <c r="I69" s="1"/>
-      <c r="J69" s="45"/>
-      <c r="K69" s="45"/>
-      <c r="L69" s="45"/>
-      <c r="M69" s="45"/>
-      <c r="N69" s="45"/>
-      <c r="O69" s="45"/>
+      <c r="J69" s="51"/>
+      <c r="K69" s="51"/>
+      <c r="L69" s="51"/>
+      <c r="M69" s="51"/>
+      <c r="N69" s="51"/>
+      <c r="O69" s="51"/>
       <c r="P69" s="48"/>
       <c r="Q69" s="31" t="s">
         <v>28</v>
@@ -5449,11 +5452,11 @@
         <v>9.5166097224819201E-12</v>
       </c>
       <c r="W69" s="1"/>
-      <c r="X69" s="45"/>
-      <c r="Y69" s="45"/>
-      <c r="Z69" s="45"/>
-      <c r="AA69" s="45"/>
-      <c r="AB69" s="45"/>
+      <c r="X69" s="51"/>
+      <c r="Y69" s="51"/>
+      <c r="Z69" s="51"/>
+      <c r="AA69" s="51"/>
+      <c r="AB69" s="51"/>
       <c r="AC69" s="35"/>
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.25">
@@ -5480,12 +5483,12 @@
         <v>0.42704513346780898</v>
       </c>
       <c r="I70" s="1"/>
-      <c r="J70" s="45"/>
-      <c r="K70" s="45"/>
-      <c r="L70" s="45"/>
-      <c r="M70" s="45"/>
-      <c r="N70" s="45"/>
-      <c r="O70" s="45"/>
+      <c r="J70" s="51"/>
+      <c r="K70" s="51"/>
+      <c r="L70" s="51"/>
+      <c r="M70" s="51"/>
+      <c r="N70" s="51"/>
+      <c r="O70" s="51"/>
       <c r="P70" s="48"/>
       <c r="Q70" s="31" t="s">
         <v>29</v>
@@ -5506,11 +5509,11 @@
         <v>0.90697094516344701</v>
       </c>
       <c r="W70" s="1"/>
-      <c r="X70" s="45"/>
-      <c r="Y70" s="45"/>
-      <c r="Z70" s="45"/>
-      <c r="AA70" s="45"/>
-      <c r="AB70" s="45"/>
+      <c r="X70" s="51"/>
+      <c r="Y70" s="51"/>
+      <c r="Z70" s="51"/>
+      <c r="AA70" s="51"/>
+      <c r="AB70" s="51"/>
       <c r="AC70" s="35"/>
     </row>
     <row r="71" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5525,12 +5528,12 @@
       <c r="G71" s="58"/>
       <c r="H71" s="58"/>
       <c r="I71" s="9"/>
-      <c r="J71" s="46"/>
-      <c r="K71" s="46"/>
-      <c r="L71" s="46"/>
-      <c r="M71" s="46"/>
-      <c r="N71" s="46"/>
-      <c r="O71" s="46"/>
+      <c r="J71" s="52"/>
+      <c r="K71" s="52"/>
+      <c r="L71" s="52"/>
+      <c r="M71" s="52"/>
+      <c r="N71" s="52"/>
+      <c r="O71" s="52"/>
       <c r="P71" s="49"/>
       <c r="Q71" s="32" t="s">
         <v>30</v>
@@ -5551,11 +5554,11 @@
         <v>0.99646171487333202</v>
       </c>
       <c r="W71" s="9"/>
-      <c r="X71" s="46"/>
-      <c r="Y71" s="46"/>
-      <c r="Z71" s="46"/>
-      <c r="AA71" s="46"/>
-      <c r="AB71" s="46"/>
+      <c r="X71" s="52"/>
+      <c r="Y71" s="52"/>
+      <c r="Z71" s="52"/>
+      <c r="AA71" s="52"/>
+      <c r="AB71" s="52"/>
       <c r="AC71" s="36"/>
     </row>
     <row r="72" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
@@ -5565,14 +5568,14 @@
       <c r="B72" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C72" s="44" t="s">
+      <c r="C72" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="D72" s="44"/>
-      <c r="E72" s="44"/>
-      <c r="F72" s="44"/>
-      <c r="G72" s="44"/>
-      <c r="H72" s="44"/>
+      <c r="D72" s="57"/>
+      <c r="E72" s="57"/>
+      <c r="F72" s="57"/>
+      <c r="G72" s="57"/>
+      <c r="H72" s="57"/>
       <c r="I72" s="8"/>
       <c r="J72" s="8">
         <v>7.7190184322692705E-4</v>
@@ -5598,13 +5601,13 @@
       <c r="Q72" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="R72" s="57" t="s">
+      <c r="R72" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="S72" s="57"/>
-      <c r="T72" s="57"/>
-      <c r="U72" s="57"/>
-      <c r="V72" s="57"/>
+      <c r="S72" s="56"/>
+      <c r="T72" s="56"/>
+      <c r="U72" s="56"/>
+      <c r="V72" s="56"/>
       <c r="W72" s="13"/>
       <c r="X72" s="13">
         <v>0.96246045193694896</v>
@@ -5628,12 +5631,12 @@
       <c r="B73" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C73" s="45"/>
-      <c r="D73" s="45"/>
-      <c r="E73" s="45"/>
-      <c r="F73" s="45"/>
-      <c r="G73" s="45"/>
-      <c r="H73" s="45"/>
+      <c r="C73" s="51"/>
+      <c r="D73" s="51"/>
+      <c r="E73" s="51"/>
+      <c r="F73" s="51"/>
+      <c r="G73" s="51"/>
+      <c r="H73" s="51"/>
       <c r="I73" s="1"/>
       <c r="J73" s="1">
         <v>0.26383928794443301</v>
@@ -5657,11 +5660,11 @@
       <c r="Q73" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="R73" s="45"/>
-      <c r="S73" s="45"/>
-      <c r="T73" s="45"/>
-      <c r="U73" s="45"/>
-      <c r="V73" s="45"/>
+      <c r="R73" s="51"/>
+      <c r="S73" s="51"/>
+      <c r="T73" s="51"/>
+      <c r="U73" s="51"/>
+      <c r="V73" s="51"/>
       <c r="W73" s="1"/>
       <c r="X73" s="1">
         <v>1.0284695041493801</v>
@@ -5685,12 +5688,12 @@
       <c r="B74" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C74" s="45"/>
-      <c r="D74" s="45"/>
-      <c r="E74" s="45"/>
-      <c r="F74" s="45"/>
-      <c r="G74" s="45"/>
-      <c r="H74" s="45"/>
+      <c r="C74" s="51"/>
+      <c r="D74" s="51"/>
+      <c r="E74" s="51"/>
+      <c r="F74" s="51"/>
+      <c r="G74" s="51"/>
+      <c r="H74" s="51"/>
       <c r="I74" s="1"/>
       <c r="J74" s="1">
         <v>6.5298294112546198E-3</v>
@@ -5714,11 +5717,11 @@
       <c r="Q74" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="R74" s="45"/>
-      <c r="S74" s="45"/>
-      <c r="T74" s="45"/>
-      <c r="U74" s="45"/>
-      <c r="V74" s="45"/>
+      <c r="R74" s="51"/>
+      <c r="S74" s="51"/>
+      <c r="T74" s="51"/>
+      <c r="U74" s="51"/>
+      <c r="V74" s="51"/>
       <c r="W74" s="1"/>
       <c r="X74" s="1">
         <v>0.59461928503453898</v>
@@ -5742,12 +5745,12 @@
       <c r="B75" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C75" s="46"/>
-      <c r="D75" s="46"/>
-      <c r="E75" s="46"/>
-      <c r="F75" s="46"/>
-      <c r="G75" s="46"/>
-      <c r="H75" s="46"/>
+      <c r="C75" s="52"/>
+      <c r="D75" s="52"/>
+      <c r="E75" s="52"/>
+      <c r="F75" s="52"/>
+      <c r="G75" s="52"/>
+      <c r="H75" s="52"/>
       <c r="I75" s="9"/>
       <c r="J75" s="9">
         <v>7.3489818378573097E-3</v>
@@ -5771,11 +5774,11 @@
       <c r="Q75" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="R75" s="46"/>
-      <c r="S75" s="46"/>
-      <c r="T75" s="46"/>
-      <c r="U75" s="46"/>
-      <c r="V75" s="46"/>
+      <c r="R75" s="52"/>
+      <c r="S75" s="52"/>
+      <c r="T75" s="52"/>
+      <c r="U75" s="52"/>
+      <c r="V75" s="52"/>
       <c r="W75" s="9"/>
       <c r="X75" s="9">
         <v>0.63540044685097696</v>
@@ -5820,14 +5823,14 @@
         <v>4.1643897411378698E-17</v>
       </c>
       <c r="I76" s="8"/>
-      <c r="J76" s="44" t="s">
+      <c r="J76" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="K76" s="44"/>
-      <c r="L76" s="44"/>
-      <c r="M76" s="44"/>
-      <c r="N76" s="44"/>
-      <c r="O76" s="44"/>
+      <c r="K76" s="57"/>
+      <c r="L76" s="57"/>
+      <c r="M76" s="57"/>
+      <c r="N76" s="57"/>
+      <c r="O76" s="57"/>
       <c r="P76" s="47" t="s">
         <v>38</v>
       </c>
@@ -5850,13 +5853,13 @@
         <v>5.3435041391658398E-8</v>
       </c>
       <c r="W76" s="13"/>
-      <c r="X76" s="57" t="s">
+      <c r="X76" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="Y76" s="57"/>
-      <c r="Z76" s="57"/>
-      <c r="AA76" s="57"/>
-      <c r="AB76" s="57"/>
+      <c r="Y76" s="56"/>
+      <c r="Z76" s="56"/>
+      <c r="AA76" s="56"/>
+      <c r="AB76" s="56"/>
       <c r="AC76" s="13"/>
     </row>
     <row r="77" spans="1:29" x14ac:dyDescent="0.25">
@@ -5883,12 +5886,12 @@
         <v>4.6861954719532999E-4</v>
       </c>
       <c r="I77" s="1"/>
-      <c r="J77" s="45"/>
-      <c r="K77" s="45"/>
-      <c r="L77" s="45"/>
-      <c r="M77" s="45"/>
-      <c r="N77" s="45"/>
-      <c r="O77" s="45"/>
+      <c r="J77" s="51"/>
+      <c r="K77" s="51"/>
+      <c r="L77" s="51"/>
+      <c r="M77" s="51"/>
+      <c r="N77" s="51"/>
+      <c r="O77" s="51"/>
       <c r="P77" s="48"/>
       <c r="Q77" s="31" t="s">
         <v>28</v>
@@ -5909,11 +5912,11 @@
         <v>1.2034151453121901E-11</v>
       </c>
       <c r="W77" s="1"/>
-      <c r="X77" s="45"/>
-      <c r="Y77" s="45"/>
-      <c r="Z77" s="45"/>
-      <c r="AA77" s="45"/>
-      <c r="AB77" s="45"/>
+      <c r="X77" s="51"/>
+      <c r="Y77" s="51"/>
+      <c r="Z77" s="51"/>
+      <c r="AA77" s="51"/>
+      <c r="AB77" s="51"/>
       <c r="AC77" s="1"/>
     </row>
     <row r="78" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5940,12 +5943,12 @@
         <v>0.27294624360005199</v>
       </c>
       <c r="I78" s="1"/>
-      <c r="J78" s="45"/>
-      <c r="K78" s="45"/>
-      <c r="L78" s="45"/>
-      <c r="M78" s="45"/>
-      <c r="N78" s="45"/>
-      <c r="O78" s="45"/>
+      <c r="J78" s="51"/>
+      <c r="K78" s="51"/>
+      <c r="L78" s="51"/>
+      <c r="M78" s="51"/>
+      <c r="N78" s="51"/>
+      <c r="O78" s="51"/>
       <c r="P78" s="48"/>
       <c r="Q78" s="31" t="s">
         <v>29</v>
@@ -5966,11 +5969,11 @@
         <v>5.9764406718529903E-3</v>
       </c>
       <c r="W78" s="1"/>
-      <c r="X78" s="45"/>
-      <c r="Y78" s="45"/>
-      <c r="Z78" s="45"/>
-      <c r="AA78" s="45"/>
-      <c r="AB78" s="45"/>
+      <c r="X78" s="51"/>
+      <c r="Y78" s="51"/>
+      <c r="Z78" s="51"/>
+      <c r="AA78" s="51"/>
+      <c r="AB78" s="51"/>
       <c r="AC78" s="1"/>
     </row>
     <row r="79" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5985,12 +5988,12 @@
       <c r="G79" s="58"/>
       <c r="H79" s="58"/>
       <c r="I79" s="9"/>
-      <c r="J79" s="46"/>
-      <c r="K79" s="46"/>
-      <c r="L79" s="46"/>
-      <c r="M79" s="46"/>
-      <c r="N79" s="46"/>
-      <c r="O79" s="46"/>
+      <c r="J79" s="52"/>
+      <c r="K79" s="52"/>
+      <c r="L79" s="52"/>
+      <c r="M79" s="52"/>
+      <c r="N79" s="52"/>
+      <c r="O79" s="52"/>
       <c r="P79" s="49"/>
       <c r="Q79" s="32" t="s">
         <v>30</v>
@@ -6011,11 +6014,11 @@
         <v>9.8108965488741305E-4</v>
       </c>
       <c r="W79" s="9"/>
-      <c r="X79" s="46"/>
-      <c r="Y79" s="46"/>
-      <c r="Z79" s="46"/>
-      <c r="AA79" s="46"/>
-      <c r="AB79" s="46"/>
+      <c r="X79" s="52"/>
+      <c r="Y79" s="52"/>
+      <c r="Z79" s="52"/>
+      <c r="AA79" s="52"/>
+      <c r="AB79" s="52"/>
       <c r="AC79" s="9"/>
     </row>
     <row r="80" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
@@ -6044,14 +6047,14 @@
         <v>6.4779999000469503E-17</v>
       </c>
       <c r="I80" s="8"/>
-      <c r="J80" s="44" t="s">
+      <c r="J80" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="K80" s="44"/>
-      <c r="L80" s="44"/>
-      <c r="M80" s="44"/>
-      <c r="N80" s="44"/>
-      <c r="O80" s="44"/>
+      <c r="K80" s="57"/>
+      <c r="L80" s="57"/>
+      <c r="M80" s="57"/>
+      <c r="N80" s="57"/>
+      <c r="O80" s="57"/>
       <c r="P80" s="47" t="s">
         <v>39</v>
       </c>
@@ -6074,13 +6077,13 @@
         <v>1.14162453601629E-7</v>
       </c>
       <c r="W80" s="13"/>
-      <c r="X80" s="57" t="s">
+      <c r="X80" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="Y80" s="57"/>
-      <c r="Z80" s="57"/>
-      <c r="AA80" s="57"/>
-      <c r="AB80" s="57"/>
+      <c r="Y80" s="56"/>
+      <c r="Z80" s="56"/>
+      <c r="AA80" s="56"/>
+      <c r="AB80" s="56"/>
       <c r="AC80" s="34"/>
     </row>
     <row r="81" spans="1:29" x14ac:dyDescent="0.25">
@@ -6107,12 +6110,12 @@
         <v>1.4106574908243E-2</v>
       </c>
       <c r="I81" s="1"/>
-      <c r="J81" s="45"/>
-      <c r="K81" s="45"/>
-      <c r="L81" s="45"/>
-      <c r="M81" s="45"/>
-      <c r="N81" s="45"/>
-      <c r="O81" s="45"/>
+      <c r="J81" s="51"/>
+      <c r="K81" s="51"/>
+      <c r="L81" s="51"/>
+      <c r="M81" s="51"/>
+      <c r="N81" s="51"/>
+      <c r="O81" s="51"/>
       <c r="P81" s="48"/>
       <c r="Q81" s="31" t="s">
         <v>28</v>
@@ -6133,11 +6136,11 @@
         <v>1.6875612018907301E-11</v>
       </c>
       <c r="W81" s="1"/>
-      <c r="X81" s="45"/>
-      <c r="Y81" s="45"/>
-      <c r="Z81" s="45"/>
-      <c r="AA81" s="45"/>
-      <c r="AB81" s="45"/>
+      <c r="X81" s="51"/>
+      <c r="Y81" s="51"/>
+      <c r="Z81" s="51"/>
+      <c r="AA81" s="51"/>
+      <c r="AB81" s="51"/>
       <c r="AC81" s="35"/>
     </row>
     <row r="82" spans="1:29" x14ac:dyDescent="0.25">
@@ -6164,12 +6167,12 @@
         <v>0.25735376158301099</v>
       </c>
       <c r="I82" s="1"/>
-      <c r="J82" s="45"/>
-      <c r="K82" s="45"/>
-      <c r="L82" s="45"/>
-      <c r="M82" s="45"/>
-      <c r="N82" s="45"/>
-      <c r="O82" s="45"/>
+      <c r="J82" s="51"/>
+      <c r="K82" s="51"/>
+      <c r="L82" s="51"/>
+      <c r="M82" s="51"/>
+      <c r="N82" s="51"/>
+      <c r="O82" s="51"/>
       <c r="P82" s="48"/>
       <c r="Q82" s="31" t="s">
         <v>29</v>
@@ -6190,11 +6193,11 @@
         <v>0.37476551599412999</v>
       </c>
       <c r="W82" s="1"/>
-      <c r="X82" s="45"/>
-      <c r="Y82" s="45"/>
-      <c r="Z82" s="45"/>
-      <c r="AA82" s="45"/>
-      <c r="AB82" s="45"/>
+      <c r="X82" s="51"/>
+      <c r="Y82" s="51"/>
+      <c r="Z82" s="51"/>
+      <c r="AA82" s="51"/>
+      <c r="AB82" s="51"/>
       <c r="AC82" s="35"/>
     </row>
     <row r="83" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6209,12 +6212,12 @@
       <c r="G83" s="58"/>
       <c r="H83" s="58"/>
       <c r="I83" s="9"/>
-      <c r="J83" s="46"/>
-      <c r="K83" s="46"/>
-      <c r="L83" s="46"/>
-      <c r="M83" s="46"/>
-      <c r="N83" s="46"/>
-      <c r="O83" s="46"/>
+      <c r="J83" s="52"/>
+      <c r="K83" s="52"/>
+      <c r="L83" s="52"/>
+      <c r="M83" s="52"/>
+      <c r="N83" s="52"/>
+      <c r="O83" s="52"/>
       <c r="P83" s="49"/>
       <c r="Q83" s="32" t="s">
         <v>30</v>
@@ -6235,11 +6238,11 @@
         <v>4.5827702542128403E-2</v>
       </c>
       <c r="W83" s="9"/>
-      <c r="X83" s="46"/>
-      <c r="Y83" s="46"/>
-      <c r="Z83" s="46"/>
-      <c r="AA83" s="46"/>
-      <c r="AB83" s="46"/>
+      <c r="X83" s="52"/>
+      <c r="Y83" s="52"/>
+      <c r="Z83" s="52"/>
+      <c r="AA83" s="52"/>
+      <c r="AB83" s="52"/>
       <c r="AC83" s="36"/>
     </row>
     <row r="84" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
@@ -6268,14 +6271,14 @@
         <v>0.38079976992345599</v>
       </c>
       <c r="I84" s="8"/>
-      <c r="J84" s="44" t="s">
+      <c r="J84" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="K84" s="44"/>
-      <c r="L84" s="44"/>
-      <c r="M84" s="44"/>
-      <c r="N84" s="44"/>
-      <c r="O84" s="44"/>
+      <c r="K84" s="57"/>
+      <c r="L84" s="57"/>
+      <c r="M84" s="57"/>
+      <c r="N84" s="57"/>
+      <c r="O84" s="57"/>
       <c r="P84" s="47" t="s">
         <v>40</v>
       </c>
@@ -6298,13 +6301,13 @@
         <v>0.99999939343423405</v>
       </c>
       <c r="W84" s="13"/>
-      <c r="X84" s="57" t="s">
+      <c r="X84" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="Y84" s="57"/>
-      <c r="Z84" s="57"/>
-      <c r="AA84" s="57"/>
-      <c r="AB84" s="57"/>
+      <c r="Y84" s="56"/>
+      <c r="Z84" s="56"/>
+      <c r="AA84" s="56"/>
+      <c r="AB84" s="56"/>
       <c r="AC84" s="37"/>
     </row>
     <row r="85" spans="1:29" x14ac:dyDescent="0.25">
@@ -6331,12 +6334,12 @@
         <v>5.7804446105462802E-3</v>
       </c>
       <c r="I85" s="1"/>
-      <c r="J85" s="45"/>
-      <c r="K85" s="45"/>
-      <c r="L85" s="45"/>
-      <c r="M85" s="45"/>
-      <c r="N85" s="45"/>
-      <c r="O85" s="45"/>
+      <c r="J85" s="51"/>
+      <c r="K85" s="51"/>
+      <c r="L85" s="51"/>
+      <c r="M85" s="51"/>
+      <c r="N85" s="51"/>
+      <c r="O85" s="51"/>
       <c r="P85" s="48"/>
       <c r="Q85" s="31" t="s">
         <v>28</v>
@@ -6357,11 +6360,11 @@
         <v>0.52237983670065102</v>
       </c>
       <c r="W85" s="1"/>
-      <c r="X85" s="45"/>
-      <c r="Y85" s="45"/>
-      <c r="Z85" s="45"/>
-      <c r="AA85" s="45"/>
-      <c r="AB85" s="45"/>
+      <c r="X85" s="51"/>
+      <c r="Y85" s="51"/>
+      <c r="Z85" s="51"/>
+      <c r="AA85" s="51"/>
+      <c r="AB85" s="51"/>
       <c r="AC85" s="35"/>
     </row>
     <row r="86" spans="1:29" x14ac:dyDescent="0.25">
@@ -6388,12 +6391,12 @@
         <v>0.37116202943872301</v>
       </c>
       <c r="I86" s="1"/>
-      <c r="J86" s="45"/>
-      <c r="K86" s="45"/>
-      <c r="L86" s="45"/>
-      <c r="M86" s="45"/>
-      <c r="N86" s="45"/>
-      <c r="O86" s="45"/>
+      <c r="J86" s="51"/>
+      <c r="K86" s="51"/>
+      <c r="L86" s="51"/>
+      <c r="M86" s="51"/>
+      <c r="N86" s="51"/>
+      <c r="O86" s="51"/>
       <c r="P86" s="48"/>
       <c r="Q86" s="31" t="s">
         <v>29</v>
@@ -6414,11 +6417,11 @@
         <v>1.33110134354993E-2</v>
       </c>
       <c r="W86" s="1"/>
-      <c r="X86" s="45"/>
-      <c r="Y86" s="45"/>
-      <c r="Z86" s="45"/>
-      <c r="AA86" s="45"/>
-      <c r="AB86" s="45"/>
+      <c r="X86" s="51"/>
+      <c r="Y86" s="51"/>
+      <c r="Z86" s="51"/>
+      <c r="AA86" s="51"/>
+      <c r="AB86" s="51"/>
       <c r="AC86" s="35"/>
     </row>
     <row r="87" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6433,12 +6436,12 @@
       <c r="G87" s="58"/>
       <c r="H87" s="58"/>
       <c r="I87" s="9"/>
-      <c r="J87" s="46"/>
-      <c r="K87" s="46"/>
-      <c r="L87" s="46"/>
-      <c r="M87" s="46"/>
-      <c r="N87" s="46"/>
-      <c r="O87" s="46"/>
+      <c r="J87" s="52"/>
+      <c r="K87" s="52"/>
+      <c r="L87" s="52"/>
+      <c r="M87" s="52"/>
+      <c r="N87" s="52"/>
+      <c r="O87" s="52"/>
       <c r="P87" s="49"/>
       <c r="Q87" s="32" t="s">
         <v>30</v>
@@ -6459,11 +6462,11 @@
         <v>0.21931254615242901</v>
       </c>
       <c r="W87" s="9"/>
-      <c r="X87" s="46"/>
-      <c r="Y87" s="46"/>
-      <c r="Z87" s="46"/>
-      <c r="AA87" s="46"/>
-      <c r="AB87" s="46"/>
+      <c r="X87" s="52"/>
+      <c r="Y87" s="52"/>
+      <c r="Z87" s="52"/>
+      <c r="AA87" s="52"/>
+      <c r="AB87" s="52"/>
       <c r="AC87" s="36"/>
     </row>
   </sheetData>
@@ -6518,13 +6521,11 @@
     <mergeCell ref="C79:H79"/>
     <mergeCell ref="A72:A75"/>
     <mergeCell ref="C72:H75"/>
-    <mergeCell ref="J39:O42"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="P39:P42"/>
     <mergeCell ref="X39:AB42"/>
     <mergeCell ref="P27:P30"/>
     <mergeCell ref="R27:V30"/>
-    <mergeCell ref="J68:O71"/>
     <mergeCell ref="C71:H71"/>
     <mergeCell ref="J64:O67"/>
     <mergeCell ref="X84:AB87"/>
@@ -6540,11 +6541,12 @@
     <mergeCell ref="P60:P63"/>
     <mergeCell ref="P64:P67"/>
     <mergeCell ref="P72:P75"/>
-    <mergeCell ref="P23:P26"/>
+    <mergeCell ref="J39:O42"/>
     <mergeCell ref="X76:AB79"/>
     <mergeCell ref="X64:AB67"/>
     <mergeCell ref="R11:V14"/>
     <mergeCell ref="P80:P83"/>
+    <mergeCell ref="J68:O71"/>
     <mergeCell ref="X1:AC1"/>
     <mergeCell ref="P56:P59"/>
     <mergeCell ref="P3:P6"/>
@@ -6559,6 +6561,7 @@
     <mergeCell ref="P31:P34"/>
     <mergeCell ref="P35:P38"/>
     <mergeCell ref="P11:P14"/>
+    <mergeCell ref="P23:P26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/ModelResults_emmeans.xlsx
+++ b/data/ModelResults_emmeans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://michiganstate-my.sharepoint.com/personal/buysseso_msu_edu/Documents/Arabidopsis/Swe_Italy/R_scripts/SW_IT_PopDiffPlasticity/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1852" documentId="13_ncr:1_{AD4A5BE6-D9C1-414A-81C8-3A9C273D7774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D784E2C-AB2D-4609-84AA-56118F5163A1}"/>
+  <xr:revisionPtr revIDLastSave="1879" documentId="13_ncr:1_{AD4A5BE6-D9C1-414A-81C8-3A9C273D7774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA782CDE-42DB-4A72-8878-6AF36F7D59F2}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{8A213037-8BA5-417B-A75A-3088B4717938}"/>
+    <workbookView xWindow="15510" yWindow="2175" windowWidth="12375" windowHeight="10320" xr2:uid="{8A213037-8BA5-417B-A75A-3088B4717938}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelResults_ManuTraits" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="60">
   <si>
     <t>Experiment</t>
   </si>
@@ -207,6 +207,15 @@
   </si>
   <si>
     <t>root G</t>
+  </si>
+  <si>
+    <t>Total Biomass - bolting</t>
+  </si>
+  <si>
+    <t>total biomass</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -519,7 +528,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -566,6 +575,30 @@
     <xf numFmtId="11" fontId="0" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -578,20 +611,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -599,21 +623,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -959,7 +969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A69572B-FB2B-42F9-9C34-22CDDD22EAA2}">
-  <dimension ref="A1:AC87"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.42578125" customWidth="1"/>
@@ -979,43 +989,43 @@
         <v>0</v>
       </c>
       <c r="B1" s="11"/>
-      <c r="C1" s="44">
+      <c r="C1" s="52">
         <v>2021</v>
       </c>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="44">
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="52">
         <v>2022</v>
       </c>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
       <c r="P1" s="11"/>
-      <c r="Q1" s="53" t="s">
+      <c r="Q1" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="R1" s="44" t="s">
+      <c r="R1" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
-      <c r="V1" s="45"/>
-      <c r="W1" s="46"/>
-      <c r="X1" s="44" t="s">
+      <c r="S1" s="53"/>
+      <c r="T1" s="53"/>
+      <c r="U1" s="53"/>
+      <c r="V1" s="53"/>
+      <c r="W1" s="54"/>
+      <c r="X1" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="Y1" s="45"/>
-      <c r="Z1" s="45"/>
-      <c r="AA1" s="45"/>
-      <c r="AB1" s="45"/>
-      <c r="AC1" s="46"/>
+      <c r="Y1" s="53"/>
+      <c r="Z1" s="53"/>
+      <c r="AA1" s="53"/>
+      <c r="AB1" s="53"/>
+      <c r="AC1" s="54"/>
     </row>
     <row r="2" spans="1:29" s="16" customFormat="1" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
@@ -1064,7 +1074,7 @@
       <c r="P2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="Q2" s="54"/>
+      <c r="Q2" s="59"/>
       <c r="R2" s="10" t="s">
         <v>49</v>
       </c>
@@ -1103,7 +1113,7 @@
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="57" t="s">
         <v>36</v>
       </c>
       <c r="B3" s="13" t="s">
@@ -1128,15 +1138,15 @@
         <v>7.3383790508167401E-2</v>
       </c>
       <c r="I3" s="13"/>
-      <c r="J3" s="51" t="s">
+      <c r="J3" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="51"/>
-      <c r="P3" s="50" t="s">
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="57" t="s">
         <v>36</v>
       </c>
       <c r="Q3" s="30" t="s">
@@ -1158,17 +1168,17 @@
         <v>0.60935835609726297</v>
       </c>
       <c r="W3" s="1"/>
-      <c r="X3" s="51" t="s">
+      <c r="X3" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="Y3" s="51"/>
-      <c r="Z3" s="51"/>
-      <c r="AA3" s="51"/>
-      <c r="AB3" s="51"/>
+      <c r="Y3" s="47"/>
+      <c r="Z3" s="47"/>
+      <c r="AA3" s="47"/>
+      <c r="AB3" s="47"/>
       <c r="AC3" s="34"/>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A4" s="48"/>
+      <c r="A4" s="44"/>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1191,13 +1201,13 @@
         <v>5.8229847066576205E-7</v>
       </c>
       <c r="I4" s="1"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
-      <c r="M4" s="51"/>
-      <c r="N4" s="51"/>
-      <c r="O4" s="51"/>
-      <c r="P4" s="48"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="47"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="44"/>
       <c r="Q4" s="31" t="s">
         <v>28</v>
       </c>
@@ -1217,15 +1227,15 @@
         <v>0.51504029973848997</v>
       </c>
       <c r="W4" s="1"/>
-      <c r="X4" s="51"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="51"/>
-      <c r="AB4" s="51"/>
+      <c r="X4" s="47"/>
+      <c r="Y4" s="47"/>
+      <c r="Z4" s="47"/>
+      <c r="AA4" s="47"/>
+      <c r="AB4" s="47"/>
       <c r="AC4" s="35"/>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A5" s="48"/>
+      <c r="A5" s="44"/>
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1247,13 +1257,13 @@
       <c r="H5" s="1">
         <v>0.90072460165650603</v>
       </c>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="51"/>
-      <c r="M5" s="51"/>
-      <c r="N5" s="51"/>
-      <c r="O5" s="51"/>
-      <c r="P5" s="48"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="47"/>
+      <c r="N5" s="47"/>
+      <c r="O5" s="47"/>
+      <c r="P5" s="44"/>
       <c r="Q5" s="31" t="s">
         <v>29</v>
       </c>
@@ -1273,32 +1283,32 @@
         <v>8.4463170790804996E-8</v>
       </c>
       <c r="W5" s="1"/>
-      <c r="X5" s="51"/>
-      <c r="Y5" s="51"/>
-      <c r="Z5" s="51"/>
-      <c r="AA5" s="51"/>
-      <c r="AB5" s="51"/>
+      <c r="X5" s="47"/>
+      <c r="Y5" s="47"/>
+      <c r="Z5" s="47"/>
+      <c r="AA5" s="47"/>
+      <c r="AB5" s="47"/>
       <c r="AC5" s="35"/>
     </row>
     <row r="6" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="49"/>
+      <c r="A6" s="56"/>
       <c r="B6" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="50"/>
       <c r="I6" s="9"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="52"/>
-      <c r="N6" s="52"/>
-      <c r="O6" s="52"/>
-      <c r="P6" s="49"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48"/>
+      <c r="N6" s="48"/>
+      <c r="O6" s="48"/>
+      <c r="P6" s="56"/>
       <c r="Q6" s="32" t="s">
         <v>30</v>
       </c>
@@ -1318,15 +1328,15 @@
         <v>8.5628197088460896E-8</v>
       </c>
       <c r="W6" s="9"/>
-      <c r="X6" s="52"/>
-      <c r="Y6" s="52"/>
-      <c r="Z6" s="52"/>
-      <c r="AA6" s="52"/>
-      <c r="AB6" s="52"/>
+      <c r="X6" s="48"/>
+      <c r="Y6" s="48"/>
+      <c r="Z6" s="48"/>
+      <c r="AA6" s="48"/>
+      <c r="AB6" s="48"/>
       <c r="AC6" s="36"/>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="55" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="13" t="s">
@@ -1369,7 +1379,7 @@
       <c r="O7" s="14">
         <v>7.9655542624253594E-15</v>
       </c>
-      <c r="P7" s="50" t="s">
+      <c r="P7" s="57" t="s">
         <v>15</v>
       </c>
       <c r="Q7" s="30" t="s">
@@ -1409,7 +1419,7 @@
       <c r="AC7" s="34"/>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A8" s="48"/>
+      <c r="A8" s="44"/>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1450,7 +1460,7 @@
       <c r="O8" s="2">
         <v>2.49480079562349E-3</v>
       </c>
-      <c r="P8" s="48"/>
+      <c r="P8" s="44"/>
       <c r="Q8" s="31" t="s">
         <v>28</v>
       </c>
@@ -1488,7 +1498,7 @@
       <c r="AC8" s="35"/>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A9" s="48"/>
+      <c r="A9" s="44"/>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
@@ -1529,7 +1539,7 @@
       <c r="O9" s="2">
         <v>5.9886663878832899E-3</v>
       </c>
-      <c r="P9" s="48"/>
+      <c r="P9" s="44"/>
       <c r="Q9" s="31" t="s">
         <v>29</v>
       </c>
@@ -1567,16 +1577,16 @@
       <c r="AC9" s="35"/>
     </row>
     <row r="10" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="49"/>
+      <c r="A10" s="56"/>
       <c r="B10" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58"/>
-      <c r="H10" s="58"/>
+      <c r="C10" s="50"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="50"/>
+      <c r="H10" s="50"/>
       <c r="I10" s="9"/>
       <c r="J10" s="9">
         <v>3.4846897009296399E-3</v>
@@ -1596,7 +1606,7 @@
       <c r="O10" s="9">
         <v>0.23519968422781001</v>
       </c>
-      <c r="P10" s="55"/>
+      <c r="P10" s="45"/>
       <c r="Q10" s="32" t="s">
         <v>30</v>
       </c>
@@ -1634,20 +1644,20 @@
       <c r="AC10" s="36"/>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="44" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="C11" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47"/>
       <c r="I11" s="13"/>
       <c r="J11" s="13">
         <v>2.20343269025562E-2</v>
@@ -1667,19 +1677,19 @@
       <c r="O11" s="15">
         <v>1.20915323151938E-2</v>
       </c>
-      <c r="P11" s="50" t="s">
+      <c r="P11" s="57" t="s">
         <v>51</v>
       </c>
       <c r="Q11" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="R11" s="57" t="s">
+      <c r="R11" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="S11" s="57"/>
-      <c r="T11" s="57"/>
-      <c r="U11" s="57"/>
-      <c r="V11" s="57"/>
+      <c r="S11" s="51"/>
+      <c r="T11" s="51"/>
+      <c r="U11" s="51"/>
+      <c r="V11" s="51"/>
       <c r="W11" s="13"/>
       <c r="X11" s="13">
         <v>0.92269407717206897</v>
@@ -1699,16 +1709,16 @@
       <c r="AC11" s="34"/>
     </row>
     <row r="12" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="48"/>
+      <c r="A12" s="44"/>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1">
         <v>2.98483856205864E-2</v>
@@ -1728,15 +1738,15 @@
       <c r="O12" s="2">
         <v>1.05420955332634E-2</v>
       </c>
-      <c r="P12" s="48"/>
+      <c r="P12" s="44"/>
       <c r="Q12" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="R12" s="51"/>
-      <c r="S12" s="51"/>
-      <c r="T12" s="51"/>
-      <c r="U12" s="51"/>
-      <c r="V12" s="51"/>
+      <c r="R12" s="47"/>
+      <c r="S12" s="47"/>
+      <c r="T12" s="47"/>
+      <c r="U12" s="47"/>
+      <c r="V12" s="47"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1">
         <v>0.89729079192970995</v>
@@ -1756,16 +1766,16 @@
       <c r="AC12" s="35"/>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A13" s="48"/>
+      <c r="A13" s="44"/>
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1">
         <v>1.15818782663304E-3</v>
@@ -1785,15 +1795,15 @@
       <c r="O13" s="1">
         <v>0.55966903975183102</v>
       </c>
-      <c r="P13" s="48"/>
+      <c r="P13" s="44"/>
       <c r="Q13" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="R13" s="51"/>
-      <c r="S13" s="51"/>
-      <c r="T13" s="51"/>
-      <c r="U13" s="51"/>
-      <c r="V13" s="51"/>
+      <c r="R13" s="47"/>
+      <c r="S13" s="47"/>
+      <c r="T13" s="47"/>
+      <c r="U13" s="47"/>
+      <c r="V13" s="47"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1">
         <v>0.88184620079220499</v>
@@ -1813,16 +1823,16 @@
       <c r="AC13" s="35"/>
     </row>
     <row r="14" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="49"/>
+      <c r="A14" s="56"/>
       <c r="B14" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
       <c r="I14" s="9"/>
       <c r="J14" s="9">
         <v>2.0797141885883202E-3</v>
@@ -1842,15 +1852,15 @@
       <c r="O14" s="9">
         <v>0.73598934665486404</v>
       </c>
-      <c r="P14" s="49"/>
+      <c r="P14" s="56"/>
       <c r="Q14" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="R14" s="52"/>
-      <c r="S14" s="52"/>
-      <c r="T14" s="52"/>
-      <c r="U14" s="52"/>
-      <c r="V14" s="52"/>
+      <c r="R14" s="48"/>
+      <c r="S14" s="48"/>
+      <c r="T14" s="48"/>
+      <c r="U14" s="48"/>
+      <c r="V14" s="48"/>
       <c r="W14" s="9"/>
       <c r="X14" s="9">
         <v>0.85756752475770204</v>
@@ -1870,7 +1880,7 @@
       <c r="AC14" s="36"/>
     </row>
     <row r="15" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="47" t="s">
+      <c r="A15" s="55" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -1913,7 +1923,7 @@
       <c r="O15" s="20">
         <v>2.5984972877347698E-9</v>
       </c>
-      <c r="P15" s="47" t="s">
+      <c r="P15" s="55" t="s">
         <v>13</v>
       </c>
       <c r="Q15" s="33" t="s">
@@ -1953,7 +1963,7 @@
       <c r="AC15" s="37"/>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A16" s="48"/>
+      <c r="A16" s="44"/>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
@@ -1994,7 +2004,7 @@
       <c r="O16" s="4">
         <v>2.3925201381821199E-8</v>
       </c>
-      <c r="P16" s="48"/>
+      <c r="P16" s="44"/>
       <c r="Q16" s="31" t="s">
         <v>28</v>
       </c>
@@ -2032,7 +2042,7 @@
       <c r="AC16" s="35"/>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A17" s="48"/>
+      <c r="A17" s="44"/>
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
@@ -2073,7 +2083,7 @@
       <c r="O17" s="3">
         <v>0.107275586121823</v>
       </c>
-      <c r="P17" s="48"/>
+      <c r="P17" s="44"/>
       <c r="Q17" s="31" t="s">
         <v>29</v>
       </c>
@@ -2111,16 +2121,16 @@
       <c r="AC17" s="35"/>
     </row>
     <row r="18" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="49"/>
+      <c r="A18" s="56"/>
       <c r="B18" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="58"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="50"/>
       <c r="I18" s="9"/>
       <c r="J18" s="9">
         <v>4.9184876384352101E-2</v>
@@ -2140,7 +2150,7 @@
       <c r="O18" s="19">
         <v>1.9087014953066299E-2</v>
       </c>
-      <c r="P18" s="49"/>
+      <c r="P18" s="56"/>
       <c r="Q18" s="32" t="s">
         <v>30</v>
       </c>
@@ -2178,20 +2188,20 @@
       <c r="AC18" s="36"/>
     </row>
     <row r="19" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="55" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="57" t="s">
+      <c r="C19" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
       <c r="I19" s="8"/>
       <c r="J19" s="8">
         <v>1.4241127553301099E-4</v>
@@ -2211,19 +2221,19 @@
       <c r="O19" s="8">
         <v>0.82529746395827397</v>
       </c>
-      <c r="P19" s="47" t="s">
+      <c r="P19" s="55" t="s">
         <v>23</v>
       </c>
       <c r="Q19" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="R19" s="57" t="s">
+      <c r="R19" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="S19" s="57"/>
-      <c r="T19" s="57"/>
-      <c r="U19" s="57"/>
-      <c r="V19" s="57"/>
+      <c r="S19" s="51"/>
+      <c r="T19" s="51"/>
+      <c r="U19" s="51"/>
+      <c r="V19" s="51"/>
       <c r="W19" s="13"/>
       <c r="X19" s="13">
         <v>0.92228721673858705</v>
@@ -2243,16 +2253,16 @@
       <c r="AC19" s="37"/>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A20" s="48"/>
+      <c r="A20" s="44"/>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1">
         <v>4.6725153189010001E-2</v>
@@ -2272,15 +2282,15 @@
       <c r="O20" s="2">
         <v>1.3790795758093499E-3</v>
       </c>
-      <c r="P20" s="48"/>
+      <c r="P20" s="44"/>
       <c r="Q20" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="R20" s="51"/>
-      <c r="S20" s="51"/>
-      <c r="T20" s="51"/>
-      <c r="U20" s="51"/>
-      <c r="V20" s="51"/>
+      <c r="R20" s="47"/>
+      <c r="S20" s="47"/>
+      <c r="T20" s="47"/>
+      <c r="U20" s="47"/>
+      <c r="V20" s="47"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1">
         <v>1.0589700479598501</v>
@@ -2300,16 +2310,16 @@
       <c r="AC20" s="35"/>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A21" s="48"/>
+      <c r="A21" s="44"/>
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="51"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="47"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1">
         <v>2.8302586845141399E-2</v>
@@ -2329,15 +2339,15 @@
       <c r="O21" s="2">
         <v>2.3248319291652099E-3</v>
       </c>
-      <c r="P21" s="48"/>
+      <c r="P21" s="44"/>
       <c r="Q21" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="R21" s="51"/>
-      <c r="S21" s="51"/>
-      <c r="T21" s="51"/>
-      <c r="U21" s="51"/>
-      <c r="V21" s="51"/>
+      <c r="R21" s="47"/>
+      <c r="S21" s="47"/>
+      <c r="T21" s="47"/>
+      <c r="U21" s="47"/>
+      <c r="V21" s="47"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1">
         <v>1.19093365397326</v>
@@ -2357,16 +2367,16 @@
       <c r="AC21" s="35"/>
     </row>
     <row r="22" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="49"/>
+      <c r="A22" s="56"/>
       <c r="B22" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="52"/>
-      <c r="D22" s="52"/>
-      <c r="E22" s="52"/>
-      <c r="F22" s="52"/>
-      <c r="G22" s="52"/>
-      <c r="H22" s="52"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48"/>
       <c r="I22" s="9"/>
       <c r="J22" s="9">
         <v>6.3796317056246301E-3</v>
@@ -2386,15 +2396,15 @@
       <c r="O22" s="9">
         <v>0.33767591593294399</v>
       </c>
-      <c r="P22" s="49"/>
+      <c r="P22" s="56"/>
       <c r="Q22" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="R22" s="52"/>
-      <c r="S22" s="52"/>
-      <c r="T22" s="52"/>
-      <c r="U22" s="52"/>
-      <c r="V22" s="52"/>
+      <c r="R22" s="48"/>
+      <c r="S22" s="48"/>
+      <c r="T22" s="48"/>
+      <c r="U22" s="48"/>
+      <c r="V22" s="48"/>
       <c r="W22" s="9"/>
       <c r="X22" s="9">
         <v>1.36742984807359</v>
@@ -2414,20 +2424,20 @@
       <c r="AC22" s="36"/>
     </row>
     <row r="23" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="47" t="s">
+      <c r="A23" s="55" t="s">
         <v>53</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="57" t="s">
+      <c r="C23" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="57"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="57"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
       <c r="I23" s="8"/>
       <c r="J23" s="8">
         <v>4.0252880405239402E-2</v>
@@ -2447,19 +2457,19 @@
       <c r="O23" s="28">
         <v>8.2948057027609101E-2</v>
       </c>
-      <c r="P23" s="47" t="s">
+      <c r="P23" s="55" t="s">
         <v>55</v>
       </c>
       <c r="Q23" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="R23" s="56" t="s">
+      <c r="R23" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="S23" s="56"/>
-      <c r="T23" s="56"/>
-      <c r="U23" s="56"/>
-      <c r="V23" s="56"/>
+      <c r="S23" s="46"/>
+      <c r="T23" s="46"/>
+      <c r="U23" s="46"/>
+      <c r="V23" s="46"/>
       <c r="W23" s="13"/>
       <c r="X23" s="13">
         <v>1.28624977261183</v>
@@ -2479,16 +2489,16 @@
       <c r="AC23" s="37"/>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A24" s="48"/>
+      <c r="A24" s="44"/>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1">
         <v>0.42132164214255802</v>
@@ -2508,15 +2518,15 @@
       <c r="O24" s="4">
         <v>7.7465741239532106E-5</v>
       </c>
-      <c r="P24" s="48"/>
+      <c r="P24" s="44"/>
       <c r="Q24" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="R24" s="51"/>
-      <c r="S24" s="51"/>
-      <c r="T24" s="51"/>
-      <c r="U24" s="51"/>
-      <c r="V24" s="51"/>
+      <c r="R24" s="47"/>
+      <c r="S24" s="47"/>
+      <c r="T24" s="47"/>
+      <c r="U24" s="47"/>
+      <c r="V24" s="47"/>
       <c r="W24" s="1"/>
       <c r="X24" s="1">
         <v>1.0220158782055699</v>
@@ -2536,16 +2546,16 @@
       <c r="AC24" s="35"/>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A25" s="48"/>
+      <c r="A25" s="44"/>
       <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="47"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1">
         <v>7.8254362282741005E-2</v>
@@ -2565,15 +2575,15 @@
       <c r="O25" s="2">
         <v>1.63202510112339E-2</v>
       </c>
-      <c r="P25" s="48"/>
+      <c r="P25" s="44"/>
       <c r="Q25" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="R25" s="51"/>
-      <c r="S25" s="51"/>
-      <c r="T25" s="51"/>
-      <c r="U25" s="51"/>
-      <c r="V25" s="51"/>
+      <c r="R25" s="47"/>
+      <c r="S25" s="47"/>
+      <c r="T25" s="47"/>
+      <c r="U25" s="47"/>
+      <c r="V25" s="47"/>
       <c r="W25" s="1"/>
       <c r="X25" s="1">
         <v>0.45501994044807598</v>
@@ -2593,16 +2603,16 @@
       <c r="AC25" s="35"/>
     </row>
     <row r="26" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="49"/>
+      <c r="A26" s="56"/>
       <c r="B26" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="52"/>
-      <c r="D26" s="52"/>
-      <c r="E26" s="52"/>
-      <c r="F26" s="52"/>
-      <c r="G26" s="52"/>
-      <c r="H26" s="52"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="48"/>
       <c r="I26" s="9"/>
       <c r="J26" s="9">
         <v>2.6614614752845599E-3</v>
@@ -2622,15 +2632,15 @@
       <c r="O26" s="9">
         <v>0.90378258302877301</v>
       </c>
-      <c r="P26" s="49"/>
+      <c r="P26" s="56"/>
       <c r="Q26" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="R26" s="52"/>
-      <c r="S26" s="52"/>
-      <c r="T26" s="52"/>
-      <c r="U26" s="52"/>
-      <c r="V26" s="52"/>
+      <c r="R26" s="48"/>
+      <c r="S26" s="48"/>
+      <c r="T26" s="48"/>
+      <c r="U26" s="48"/>
+      <c r="V26" s="48"/>
       <c r="W26" s="9"/>
       <c r="X26" s="9">
         <v>0.361545334304543</v>
@@ -2650,20 +2660,20 @@
       <c r="AC26" s="36"/>
     </row>
     <row r="27" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="55" t="s">
         <v>54</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C27" s="57" t="s">
+      <c r="C27" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="57"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="57"/>
-      <c r="H27" s="57"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="51"/>
       <c r="I27" s="8"/>
       <c r="J27" s="8">
         <v>4.9920514192076698E-4</v>
@@ -2683,19 +2693,19 @@
       <c r="O27" s="28">
         <v>7.0143959578357298E-2</v>
       </c>
-      <c r="P27" s="47" t="s">
+      <c r="P27" s="55" t="s">
         <v>56</v>
       </c>
       <c r="Q27" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="R27" s="56" t="s">
+      <c r="R27" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="S27" s="56"/>
-      <c r="T27" s="56"/>
-      <c r="U27" s="56"/>
-      <c r="V27" s="56"/>
+      <c r="S27" s="46"/>
+      <c r="T27" s="46"/>
+      <c r="U27" s="46"/>
+      <c r="V27" s="46"/>
       <c r="W27" s="13"/>
       <c r="X27" s="13">
         <v>7.7522088498056798E-3</v>
@@ -2715,16 +2725,16 @@
       <c r="AC27" s="37"/>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A28" s="48"/>
+      <c r="A28" s="44"/>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="51"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="47"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1">
         <v>4.3245963051368403E-3</v>
@@ -2744,15 +2754,15 @@
       <c r="O28" s="4">
         <v>8.7931651517614295E-5</v>
       </c>
-      <c r="P28" s="48"/>
+      <c r="P28" s="44"/>
       <c r="Q28" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="R28" s="51"/>
-      <c r="S28" s="51"/>
-      <c r="T28" s="51"/>
-      <c r="U28" s="51"/>
-      <c r="V28" s="51"/>
+      <c r="R28" s="47"/>
+      <c r="S28" s="47"/>
+      <c r="T28" s="47"/>
+      <c r="U28" s="47"/>
+      <c r="V28" s="47"/>
       <c r="W28" s="1"/>
       <c r="X28" s="1">
         <v>5.3703739511303996E-3</v>
@@ -2772,16 +2782,16 @@
       <c r="AC28" s="35"/>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A29" s="48"/>
+      <c r="A29" s="44"/>
       <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="51"/>
+      <c r="C29" s="47"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="47"/>
+      <c r="H29" s="47"/>
       <c r="I29" s="1"/>
       <c r="J29" s="5">
         <v>4.4673218852987901E-5</v>
@@ -2801,15 +2811,15 @@
       <c r="O29" s="1">
         <v>0.58543070585289902</v>
       </c>
-      <c r="P29" s="48"/>
+      <c r="P29" s="44"/>
       <c r="Q29" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="R29" s="51"/>
-      <c r="S29" s="51"/>
-      <c r="T29" s="51"/>
-      <c r="U29" s="51"/>
-      <c r="V29" s="51"/>
+      <c r="R29" s="47"/>
+      <c r="S29" s="47"/>
+      <c r="T29" s="47"/>
+      <c r="U29" s="47"/>
+      <c r="V29" s="47"/>
       <c r="W29" s="1"/>
       <c r="X29" s="1">
         <v>-2.3309139166002101E-2</v>
@@ -2829,16 +2839,16 @@
       <c r="AC29" s="35"/>
     </row>
     <row r="30" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="49"/>
+      <c r="A30" s="56"/>
       <c r="B30" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="48"/>
       <c r="I30" s="9"/>
       <c r="J30" s="9">
         <v>2.5092673060789E-4</v>
@@ -2858,15 +2868,15 @@
       <c r="O30" s="9">
         <v>0.43421981831232398</v>
       </c>
-      <c r="P30" s="49"/>
+      <c r="P30" s="56"/>
       <c r="Q30" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="R30" s="52"/>
-      <c r="S30" s="52"/>
-      <c r="T30" s="52"/>
-      <c r="U30" s="52"/>
-      <c r="V30" s="52"/>
+      <c r="R30" s="48"/>
+      <c r="S30" s="48"/>
+      <c r="T30" s="48"/>
+      <c r="U30" s="48"/>
+      <c r="V30" s="48"/>
       <c r="W30" s="9"/>
       <c r="X30" s="9">
         <v>-2.56909740646773E-2</v>
@@ -2885,3599 +2895,3891 @@
       </c>
       <c r="AC30" s="9"/>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="1" t="s">
+    <row r="31" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="55" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C31" s="1">
-        <v>6176915.5049999999</v>
-      </c>
-      <c r="D31" s="1">
-        <v>6176915.5049999999</v>
-      </c>
-      <c r="E31" s="1">
-        <v>1</v>
-      </c>
-      <c r="F31" s="1">
-        <v>71.888440000000003</v>
-      </c>
-      <c r="G31" s="1">
-        <v>167.3449876</v>
-      </c>
-      <c r="H31" s="4">
-        <v>1.898803E-20</v>
-      </c>
-      <c r="I31" s="1"/>
-      <c r="J31" s="57" t="s">
+      <c r="C31" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="K31" s="57"/>
-      <c r="L31" s="57"/>
-      <c r="M31" s="57"/>
-      <c r="N31" s="57"/>
-      <c r="O31" s="57"/>
-      <c r="P31" s="47" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q31" s="31" t="s">
+      <c r="D31" s="51"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="51"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="1">
+        <v>3.7149905287115703E-2</v>
+      </c>
+      <c r="K31" s="1">
+        <v>3.7149905287115703E-2</v>
+      </c>
+      <c r="L31" s="1">
+        <v>1</v>
+      </c>
+      <c r="M31" s="1">
+        <v>108.980451970386</v>
+      </c>
+      <c r="N31" s="1">
+        <v>2.8874908407386299</v>
+      </c>
+      <c r="O31" s="3">
+        <v>9.2122703153001695E-2</v>
+      </c>
+      <c r="P31" s="55" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q31" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="R31" s="13">
-        <v>529.6</v>
-      </c>
-      <c r="S31" s="13">
-        <v>60.754643373648697</v>
-      </c>
-      <c r="T31" s="13">
-        <v>73.255404219009407</v>
-      </c>
-      <c r="U31" s="13">
-        <v>8.7170291946722998</v>
-      </c>
-      <c r="V31" s="15">
-        <v>0</v>
-      </c>
+      <c r="R31" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="S31" s="46"/>
+      <c r="T31" s="46"/>
+      <c r="U31" s="46"/>
+      <c r="V31" s="46"/>
       <c r="W31" s="13"/>
-      <c r="X31" s="56" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y31" s="56"/>
-      <c r="Z31" s="56"/>
-      <c r="AA31" s="56"/>
-      <c r="AB31" s="56"/>
-      <c r="AC31" s="35"/>
+      <c r="X31" s="13">
+        <v>8.3389930000000001E-2</v>
+      </c>
+      <c r="Y31" s="13">
+        <v>2.8614819999999999E-2</v>
+      </c>
+      <c r="Z31" s="13">
+        <v>108.82</v>
+      </c>
+      <c r="AA31" s="13">
+        <v>2.9140000000000001</v>
+      </c>
+      <c r="AB31" s="60">
+        <v>2.2200000000000001E-2</v>
+      </c>
+      <c r="AC31" s="37"/>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A32" s="48"/>
+      <c r="A32" s="44"/>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="1">
-        <v>50157.928</v>
-      </c>
-      <c r="D32" s="1">
-        <v>50157.928</v>
-      </c>
-      <c r="E32" s="1">
-        <v>1</v>
-      </c>
-      <c r="F32" s="1">
-        <v>17.04102</v>
-      </c>
-      <c r="G32" s="1">
-        <v>1.3588785000000001</v>
-      </c>
-      <c r="H32" s="1">
-        <v>0.2597892</v>
-      </c>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="47"/>
       <c r="I32" s="1"/>
-      <c r="J32" s="51"/>
-      <c r="K32" s="51"/>
-      <c r="L32" s="51"/>
-      <c r="M32" s="51"/>
-      <c r="N32" s="51"/>
-      <c r="O32" s="51"/>
-      <c r="P32" s="48"/>
+      <c r="J32" s="1">
+        <v>0.41180178005361601</v>
+      </c>
+      <c r="K32" s="1">
+        <v>0.41180178005361601</v>
+      </c>
+      <c r="L32" s="1">
+        <v>1</v>
+      </c>
+      <c r="M32" s="1">
+        <v>14.182890100648899</v>
+      </c>
+      <c r="N32" s="1">
+        <v>32.007453556471702</v>
+      </c>
+      <c r="O32" s="4">
+        <v>5.6287391440117501E-5</v>
+      </c>
+      <c r="P32" s="44"/>
       <c r="Q32" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="R32" s="1">
-        <v>499.42857142857201</v>
-      </c>
-      <c r="S32" s="1">
-        <v>51.347045341752903</v>
-      </c>
-      <c r="T32" s="1">
-        <v>73.255404219009407</v>
-      </c>
-      <c r="U32" s="1">
-        <v>9.7265298928984407</v>
-      </c>
-      <c r="V32" s="2">
-        <v>0</v>
-      </c>
+      <c r="R32" s="47"/>
+      <c r="S32" s="47"/>
+      <c r="T32" s="47"/>
+      <c r="U32" s="47"/>
+      <c r="V32" s="47"/>
       <c r="W32" s="1"/>
-      <c r="X32" s="51"/>
-      <c r="Y32" s="51"/>
-      <c r="Z32" s="51"/>
-      <c r="AA32" s="51"/>
-      <c r="AB32" s="51"/>
+      <c r="X32" s="1">
+        <v>3.5242599999999999E-2</v>
+      </c>
+      <c r="Y32" s="1">
+        <v>2.861476E-2</v>
+      </c>
+      <c r="Z32" s="1">
+        <v>107.37</v>
+      </c>
+      <c r="AA32" s="1">
+        <v>1.232</v>
+      </c>
+      <c r="AB32">
+        <v>0.60819999999999996</v>
+      </c>
       <c r="AC32" s="35"/>
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A33" s="48"/>
+      <c r="A33" s="44"/>
       <c r="B33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="1">
-        <v>5310.1710000000003</v>
-      </c>
-      <c r="D33" s="1">
-        <v>5310.1710000000003</v>
-      </c>
-      <c r="E33" s="1">
-        <v>1</v>
-      </c>
-      <c r="F33" s="1">
-        <v>71.888440000000003</v>
-      </c>
-      <c r="G33" s="1">
-        <v>0.1438632</v>
-      </c>
-      <c r="H33" s="1">
-        <v>0.7055884</v>
-      </c>
+      <c r="C33" s="47"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="47"/>
       <c r="I33" s="1"/>
-      <c r="J33" s="51"/>
-      <c r="K33" s="51"/>
-      <c r="L33" s="51"/>
-      <c r="M33" s="51"/>
-      <c r="N33" s="51"/>
-      <c r="O33" s="51"/>
-      <c r="P33" s="48"/>
+      <c r="J33" s="1">
+        <v>1.8225292212328801E-2</v>
+      </c>
+      <c r="K33" s="1">
+        <v>1.8225292212328801E-2</v>
+      </c>
+      <c r="L33" s="1">
+        <v>1</v>
+      </c>
+      <c r="M33" s="1">
+        <v>108.626126088578</v>
+      </c>
+      <c r="N33" s="1">
+        <v>1.4165679273248699</v>
+      </c>
+      <c r="O33" s="1">
+        <v>0.236563800903767</v>
+      </c>
+      <c r="P33" s="44"/>
       <c r="Q33" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="R33" s="13">
-        <v>60.370790372977901</v>
-      </c>
-      <c r="S33" s="13">
-        <v>76.168525940263294</v>
-      </c>
-      <c r="T33" s="13">
-        <v>33.630246929987997</v>
-      </c>
-      <c r="U33" s="13">
-        <v>0.79259496790478601</v>
-      </c>
-      <c r="V33" s="13">
-        <v>0.85729287706349799</v>
-      </c>
+      <c r="R33" s="47"/>
+      <c r="S33" s="47"/>
+      <c r="T33" s="47"/>
+      <c r="U33" s="47"/>
+      <c r="V33" s="47"/>
       <c r="W33" s="1"/>
-      <c r="X33" s="51"/>
-      <c r="Y33" s="51"/>
-      <c r="Z33" s="51"/>
-      <c r="AA33" s="51"/>
-      <c r="AB33" s="51"/>
+      <c r="X33" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y33" s="1"/>
+      <c r="Z33" s="1"/>
+      <c r="AA33" s="1"/>
+      <c r="AB33" s="60">
+        <v>7.4698056395894297E-4</v>
+      </c>
       <c r="AC33" s="35"/>
     </row>
-    <row r="34" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="49"/>
+    <row r="34" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="56"/>
       <c r="B34" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="58"/>
-      <c r="D34" s="58"/>
-      <c r="E34" s="58"/>
-      <c r="F34" s="58"/>
-      <c r="G34" s="58"/>
-      <c r="H34" s="58"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="48"/>
+      <c r="H34" s="48"/>
       <c r="I34" s="9"/>
-      <c r="J34" s="52"/>
-      <c r="K34" s="52"/>
-      <c r="L34" s="52"/>
-      <c r="M34" s="52"/>
-      <c r="N34" s="52"/>
-      <c r="O34" s="52"/>
-      <c r="P34" s="49"/>
+      <c r="J34" s="1">
+        <v>7.0583620092449098E-3</v>
+      </c>
+      <c r="K34" s="1">
+        <v>3.5291810046224502E-3</v>
+      </c>
+      <c r="L34" s="1">
+        <v>2</v>
+      </c>
+      <c r="M34" s="1">
+        <v>108.659631467902</v>
+      </c>
+      <c r="N34" s="1">
+        <v>0.274306966529208</v>
+      </c>
+      <c r="O34" s="1">
+        <v>0.76062348164929805</v>
+      </c>
+      <c r="P34" s="56"/>
       <c r="Q34" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="R34" s="9">
-        <v>90.5422189444065</v>
-      </c>
-      <c r="S34" s="9">
-        <v>76.168525940263294</v>
-      </c>
-      <c r="T34" s="9">
-        <v>33.630246929987997</v>
-      </c>
-      <c r="U34" s="9">
-        <v>1.1887090872077</v>
-      </c>
-      <c r="V34" s="9">
-        <v>0.63803985452722101</v>
-      </c>
+      <c r="R34" s="48"/>
+      <c r="S34" s="48"/>
+      <c r="T34" s="48"/>
+      <c r="U34" s="48"/>
+      <c r="V34" s="48"/>
       <c r="W34" s="9"/>
-      <c r="X34" s="52"/>
-      <c r="Y34" s="52"/>
-      <c r="Z34" s="52"/>
-      <c r="AA34" s="52"/>
-      <c r="AB34" s="52"/>
-      <c r="AC34" s="36"/>
+      <c r="X34" s="9"/>
+      <c r="Y34" s="9"/>
+      <c r="Z34" s="9"/>
+      <c r="AA34" s="9"/>
+      <c r="AB34" s="60">
+        <v>1.08004634556402E-4</v>
+      </c>
+      <c r="AC34" s="9"/>
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A35" s="48" t="s">
-        <v>47</v>
-      </c>
-      <c r="B35" s="13" t="s">
+      <c r="A35" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="13">
-        <v>0.15432652470222299</v>
-      </c>
-      <c r="D35" s="13">
-        <v>0.15432652470222299</v>
-      </c>
-      <c r="E35" s="13">
-        <v>1</v>
-      </c>
-      <c r="F35" s="13">
-        <v>73.999999999267601</v>
-      </c>
-      <c r="G35" s="13">
-        <v>34.870200464865299</v>
-      </c>
-      <c r="H35" s="14">
-        <v>9.94550983787633E-8</v>
-      </c>
-      <c r="I35" s="13"/>
-      <c r="J35" s="56" t="s">
+      <c r="C35" s="1">
+        <v>6176915.5049999999</v>
+      </c>
+      <c r="D35" s="1">
+        <v>6176915.5049999999</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1">
+        <v>71.888440000000003</v>
+      </c>
+      <c r="G35" s="1">
+        <v>167.3449876</v>
+      </c>
+      <c r="H35" s="4">
+        <v>1.898803E-20</v>
+      </c>
+      <c r="I35" s="1"/>
+      <c r="J35" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="K35" s="56"/>
-      <c r="L35" s="56"/>
-      <c r="M35" s="56"/>
-      <c r="N35" s="56"/>
-      <c r="O35" s="56"/>
-      <c r="P35" s="48" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q35" s="30" t="s">
+      <c r="K35" s="51"/>
+      <c r="L35" s="51"/>
+      <c r="M35" s="51"/>
+      <c r="N35" s="51"/>
+      <c r="O35" s="51"/>
+      <c r="P35" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q35" s="31" t="s">
         <v>27</v>
       </c>
       <c r="R35" s="13">
-        <v>1.0647504837794699</v>
+        <v>529.6</v>
       </c>
       <c r="S35" s="13">
-        <v>5.7194632959268799E-2</v>
+        <v>60.754643373648697</v>
       </c>
       <c r="T35" s="13">
-        <v>64.060522318169802</v>
+        <v>73.255404219009407</v>
       </c>
       <c r="U35" s="13">
-        <v>1.1679935236511501</v>
-      </c>
-      <c r="V35" s="13">
-        <v>0.64903708255730697</v>
+        <v>8.7170291946722998</v>
+      </c>
+      <c r="V35" s="15">
+        <v>0</v>
       </c>
       <c r="W35" s="13"/>
-      <c r="X35" s="51" t="s">
+      <c r="X35" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="Y35" s="51"/>
-      <c r="Z35" s="51"/>
-      <c r="AA35" s="51"/>
-      <c r="AB35" s="51"/>
-      <c r="AC35" s="34"/>
+      <c r="Y35" s="46"/>
+      <c r="Z35" s="46"/>
+      <c r="AA35" s="46"/>
+      <c r="AB35" s="46"/>
+      <c r="AC35" s="35"/>
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A36" s="48"/>
+      <c r="A36" s="44"/>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="1">
-        <v>0.111292819337707</v>
+        <v>50157.928</v>
       </c>
       <c r="D36" s="1">
-        <v>0.111292819337707</v>
+        <v>50157.928</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
       </c>
       <c r="F36" s="1">
-        <v>73.999999999267601</v>
+        <v>17.04102</v>
       </c>
       <c r="G36" s="1">
-        <v>25.146700660135899</v>
-      </c>
-      <c r="H36" s="4">
-        <v>3.5283045440115499E-6</v>
+        <v>1.3588785000000001</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0.2597892</v>
       </c>
       <c r="I36" s="1"/>
-      <c r="J36" s="51"/>
-      <c r="K36" s="51"/>
-      <c r="L36" s="51"/>
-      <c r="M36" s="51"/>
-      <c r="N36" s="51"/>
-      <c r="O36" s="51"/>
-      <c r="P36" s="48"/>
+      <c r="J36" s="47"/>
+      <c r="K36" s="47"/>
+      <c r="L36" s="47"/>
+      <c r="M36" s="47"/>
+      <c r="N36" s="47"/>
+      <c r="O36" s="47"/>
+      <c r="P36" s="44"/>
       <c r="Q36" s="31" t="s">
         <v>28</v>
       </c>
       <c r="R36" s="1">
-        <v>1.42370872400263</v>
+        <v>499.42857142857201</v>
       </c>
       <c r="S36" s="1">
-        <v>6.5368840678580703E-2</v>
+        <v>51.347045341752903</v>
       </c>
       <c r="T36" s="1">
-        <v>63.0199737522519</v>
+        <v>73.255404219009407</v>
       </c>
       <c r="U36" s="1">
-        <v>7.6939839378934503</v>
-      </c>
-      <c r="V36" s="6">
-        <v>7.4586492537775898E-10</v>
+        <v>9.7265298928984407</v>
+      </c>
+      <c r="V36" s="2">
+        <v>0</v>
       </c>
       <c r="W36" s="1"/>
-      <c r="X36" s="51"/>
-      <c r="Y36" s="51"/>
-      <c r="Z36" s="51"/>
-      <c r="AA36" s="51"/>
-      <c r="AB36" s="51"/>
+      <c r="X36" s="47"/>
+      <c r="Y36" s="47"/>
+      <c r="Z36" s="47"/>
+      <c r="AA36" s="47"/>
+      <c r="AB36" s="47"/>
       <c r="AC36" s="35"/>
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A37" s="48"/>
+      <c r="A37" s="44"/>
       <c r="B37" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="1">
-        <v>7.5267632704079004E-2</v>
+        <v>5310.1710000000003</v>
       </c>
       <c r="D37" s="1">
-        <v>7.5267632704079004E-2</v>
+        <v>5310.1710000000003</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
       </c>
       <c r="F37" s="1">
-        <v>73.999999999270102</v>
+        <v>71.888440000000003</v>
       </c>
       <c r="G37" s="1">
-        <v>17.006781212570601</v>
-      </c>
-      <c r="H37" s="4">
-        <v>9.6345615419962495E-5</v>
+        <v>0.1438632</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0.7055884</v>
       </c>
       <c r="I37" s="1"/>
-      <c r="J37" s="51"/>
-      <c r="K37" s="51"/>
-      <c r="L37" s="51"/>
-      <c r="M37" s="51"/>
-      <c r="N37" s="51"/>
-      <c r="O37" s="51"/>
-      <c r="P37" s="48"/>
+      <c r="J37" s="47"/>
+      <c r="K37" s="47"/>
+      <c r="L37" s="47"/>
+      <c r="M37" s="47"/>
+      <c r="N37" s="47"/>
+      <c r="O37" s="47"/>
+      <c r="P37" s="44"/>
       <c r="Q37" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="R37" s="1">
-        <v>0.72477084209590303</v>
-      </c>
-      <c r="S37" s="1">
-        <v>3.6800772932671998E-2</v>
-      </c>
-      <c r="T37" s="1">
-        <v>29.8208206010118</v>
-      </c>
-      <c r="U37" s="1">
-        <v>-6.3396373813704798</v>
-      </c>
-      <c r="V37" s="6">
-        <v>3.2178754427736301E-6</v>
+      <c r="R37" s="13">
+        <v>60.370790372977901</v>
+      </c>
+      <c r="S37" s="13">
+        <v>76.168525940263294</v>
+      </c>
+      <c r="T37" s="13">
+        <v>33.630246929987997</v>
+      </c>
+      <c r="U37" s="13">
+        <v>0.79259496790478601</v>
+      </c>
+      <c r="V37" s="13">
+        <v>0.85729287706349799</v>
       </c>
       <c r="W37" s="1"/>
-      <c r="X37" s="51"/>
-      <c r="Y37" s="51"/>
-      <c r="Z37" s="51"/>
-      <c r="AA37" s="51"/>
-      <c r="AB37" s="51"/>
+      <c r="X37" s="47"/>
+      <c r="Y37" s="47"/>
+      <c r="Z37" s="47"/>
+      <c r="AA37" s="47"/>
+      <c r="AB37" s="47"/>
       <c r="AC37" s="35"/>
     </row>
     <row r="38" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="55"/>
+      <c r="A38" s="56"/>
       <c r="B38" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C38" s="59"/>
-      <c r="D38" s="59"/>
-      <c r="E38" s="59"/>
-      <c r="F38" s="59"/>
-      <c r="G38" s="59"/>
-      <c r="H38" s="59"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="51"/>
-      <c r="K38" s="51"/>
-      <c r="L38" s="51"/>
-      <c r="M38" s="51"/>
-      <c r="N38" s="51"/>
-      <c r="O38" s="51"/>
-      <c r="P38" s="55"/>
-      <c r="Q38" s="31" t="s">
+      <c r="C38" s="50"/>
+      <c r="D38" s="50"/>
+      <c r="E38" s="50"/>
+      <c r="F38" s="50"/>
+      <c r="G38" s="50"/>
+      <c r="H38" s="50"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="48"/>
+      <c r="K38" s="48"/>
+      <c r="L38" s="48"/>
+      <c r="M38" s="48"/>
+      <c r="N38" s="48"/>
+      <c r="O38" s="48"/>
+      <c r="P38" s="56"/>
+      <c r="Q38" s="32" t="s">
         <v>30</v>
       </c>
       <c r="R38" s="9">
-        <v>0.96911209387943398</v>
+        <v>90.5422189444065</v>
       </c>
       <c r="S38" s="9">
-        <v>5.29253214573484E-2</v>
+        <v>76.168525940263294</v>
       </c>
       <c r="T38" s="9">
-        <v>32.7933881713275</v>
+        <v>33.630246929987997</v>
       </c>
       <c r="U38" s="9">
-        <v>-0.57450545641731199</v>
+        <v>1.1887090872077</v>
       </c>
       <c r="V38" s="9">
-        <v>0.93899599371116504</v>
+        <v>0.63803985452722101</v>
       </c>
       <c r="W38" s="9"/>
-      <c r="X38" s="52"/>
-      <c r="Y38" s="52"/>
-      <c r="Z38" s="52"/>
-      <c r="AA38" s="52"/>
-      <c r="AB38" s="52"/>
-      <c r="AC38" s="35"/>
-    </row>
-    <row r="39" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="B39" s="8" t="s">
+      <c r="X38" s="48"/>
+      <c r="Y38" s="48"/>
+      <c r="Z38" s="48"/>
+      <c r="AA38" s="48"/>
+      <c r="AB38" s="48"/>
+      <c r="AC38" s="36"/>
+    </row>
+    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A39" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C39" s="1">
-        <v>21828870577.187302</v>
-      </c>
-      <c r="D39" s="1">
-        <v>21828870577.187302</v>
-      </c>
-      <c r="E39" s="1">
-        <v>1</v>
-      </c>
-      <c r="F39" s="1">
-        <v>69.360025998764399</v>
-      </c>
-      <c r="G39" s="1">
-        <v>150.637001976226</v>
-      </c>
-      <c r="H39" s="2">
-        <v>4.7200869189182898E-19</v>
-      </c>
-      <c r="I39" s="8"/>
-      <c r="J39" s="57" t="s">
+      <c r="C39" s="13">
+        <v>0.15432652470222299</v>
+      </c>
+      <c r="D39" s="13">
+        <v>0.15432652470222299</v>
+      </c>
+      <c r="E39" s="13">
+        <v>1</v>
+      </c>
+      <c r="F39" s="13">
+        <v>73.999999999267601</v>
+      </c>
+      <c r="G39" s="13">
+        <v>34.870200464865299</v>
+      </c>
+      <c r="H39" s="14">
+        <v>9.94550983787633E-8</v>
+      </c>
+      <c r="I39" s="13"/>
+      <c r="J39" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="K39" s="57"/>
-      <c r="L39" s="57"/>
-      <c r="M39" s="57"/>
-      <c r="N39" s="57"/>
-      <c r="O39" s="57"/>
-      <c r="P39" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q39" s="33" t="s">
+      <c r="K39" s="46"/>
+      <c r="L39" s="46"/>
+      <c r="M39" s="46"/>
+      <c r="N39" s="46"/>
+      <c r="O39" s="46"/>
+      <c r="P39" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q39" s="30" t="s">
         <v>27</v>
       </c>
       <c r="R39" s="13">
-        <v>26952.483888888899</v>
+        <v>1.0647504837794699</v>
       </c>
       <c r="S39" s="13">
-        <v>3806.71007179046</v>
+        <v>5.7194632959268799E-2</v>
       </c>
       <c r="T39" s="13">
-        <v>70.469257492222297</v>
+        <v>64.060522318169802</v>
       </c>
       <c r="U39" s="13">
-        <v>7.0802565418941903</v>
-      </c>
-      <c r="V39" s="41">
-        <v>5.1032972292475198E-9</v>
+        <v>1.1679935236511501</v>
+      </c>
+      <c r="V39" s="13">
+        <v>0.64903708255730697</v>
       </c>
       <c r="W39" s="13"/>
-      <c r="X39" s="51" t="s">
+      <c r="X39" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="Y39" s="51"/>
-      <c r="Z39" s="51"/>
-      <c r="AA39" s="51"/>
-      <c r="AB39" s="51"/>
-      <c r="AC39" s="37"/>
+      <c r="Y39" s="47"/>
+      <c r="Z39" s="47"/>
+      <c r="AA39" s="47"/>
+      <c r="AB39" s="47"/>
+      <c r="AC39" s="34"/>
     </row>
     <row r="40" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A40" s="48"/>
+      <c r="A40" s="44"/>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="1">
-        <v>11545764.943964699</v>
+        <v>0.111292819337707</v>
       </c>
       <c r="D40" s="1">
-        <v>11545764.943964699</v>
+        <v>0.111292819337707</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
       </c>
       <c r="F40" s="1">
-        <v>16.5068331927068</v>
+        <v>73.999999999267601</v>
       </c>
       <c r="G40" s="1">
-        <v>7.9675190272952195E-2</v>
-      </c>
-      <c r="H40" s="1">
-        <v>0.78124664232875995</v>
+        <v>25.146700660135899</v>
+      </c>
+      <c r="H40" s="4">
+        <v>3.5283045440115499E-6</v>
       </c>
       <c r="I40" s="1"/>
-      <c r="J40" s="51"/>
-      <c r="K40" s="51"/>
-      <c r="L40" s="51"/>
-      <c r="M40" s="51"/>
-      <c r="N40" s="51"/>
-      <c r="O40" s="51"/>
-      <c r="P40" s="48"/>
+      <c r="J40" s="47"/>
+      <c r="K40" s="47"/>
+      <c r="L40" s="47"/>
+      <c r="M40" s="47"/>
+      <c r="N40" s="47"/>
+      <c r="O40" s="47"/>
+      <c r="P40" s="44"/>
       <c r="Q40" s="31" t="s">
         <v>28</v>
       </c>
       <c r="R40" s="1">
-        <v>34977.103075289997</v>
+        <v>1.42370872400263</v>
       </c>
       <c r="S40" s="1">
-        <v>3313.0752900440498</v>
+        <v>6.5368840678580703E-2</v>
       </c>
       <c r="T40" s="1">
-        <v>70.865874182612103</v>
+        <v>63.0199737522519</v>
       </c>
       <c r="U40" s="1">
-        <v>10.557291945763501</v>
-      </c>
-      <c r="V40" s="2">
-        <v>0</v>
+        <v>7.6939839378934503</v>
+      </c>
+      <c r="V40" s="6">
+        <v>7.4586492537775898E-10</v>
       </c>
       <c r="W40" s="1"/>
-      <c r="X40" s="51"/>
-      <c r="Y40" s="51"/>
-      <c r="Z40" s="51"/>
-      <c r="AA40" s="51"/>
-      <c r="AB40" s="51"/>
+      <c r="X40" s="47"/>
+      <c r="Y40" s="47"/>
+      <c r="Z40" s="47"/>
+      <c r="AA40" s="47"/>
+      <c r="AB40" s="47"/>
       <c r="AC40" s="35"/>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A41" s="48"/>
+      <c r="A41" s="44"/>
       <c r="B41" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="1">
-        <v>366508256.45689797</v>
+        <v>7.5267632704079004E-2</v>
       </c>
       <c r="D41" s="1">
-        <v>366508256.45689797</v>
+        <v>7.5267632704079004E-2</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
       </c>
       <c r="F41" s="1">
-        <v>69.360026001368695</v>
+        <v>73.999999999270102</v>
       </c>
       <c r="G41" s="1">
-        <v>2.52920574873438</v>
-      </c>
-      <c r="H41" s="3">
-        <v>0.116304482817742</v>
+        <v>17.006781212570601</v>
+      </c>
+      <c r="H41" s="4">
+        <v>9.6345615419962495E-5</v>
       </c>
       <c r="I41" s="1"/>
-      <c r="J41" s="51"/>
-      <c r="K41" s="51"/>
-      <c r="L41" s="51"/>
-      <c r="M41" s="51"/>
-      <c r="N41" s="51"/>
-      <c r="O41" s="51"/>
-      <c r="P41" s="48"/>
+      <c r="J41" s="47"/>
+      <c r="K41" s="47"/>
+      <c r="L41" s="47"/>
+      <c r="M41" s="47"/>
+      <c r="N41" s="47"/>
+      <c r="O41" s="47"/>
+      <c r="P41" s="44"/>
       <c r="Q41" s="31" t="s">
         <v>29</v>
       </c>
       <c r="R41" s="1">
-        <v>-5094.1207890139503</v>
+        <v>0.72477084209590303</v>
       </c>
       <c r="S41" s="1">
-        <v>4592.5547243374504</v>
+        <v>3.6800772932671998E-2</v>
       </c>
       <c r="T41" s="1">
-        <v>34.570504227394899</v>
+        <v>29.8208206010118</v>
       </c>
       <c r="U41" s="1">
-        <v>-1.10921286621116</v>
-      </c>
-      <c r="V41" s="1">
-        <v>0.68637145240327702</v>
+        <v>-6.3396373813704798</v>
+      </c>
+      <c r="V41" s="6">
+        <v>3.2178754427736301E-6</v>
       </c>
       <c r="W41" s="1"/>
-      <c r="X41" s="51"/>
-      <c r="Y41" s="51"/>
-      <c r="Z41" s="51"/>
-      <c r="AA41" s="51"/>
-      <c r="AB41" s="51"/>
+      <c r="X41" s="47"/>
+      <c r="Y41" s="47"/>
+      <c r="Z41" s="47"/>
+      <c r="AA41" s="47"/>
+      <c r="AB41" s="47"/>
       <c r="AC41" s="35"/>
     </row>
-    <row r="42" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="49"/>
+    <row r="42" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="45"/>
       <c r="B42" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C42" s="58"/>
-      <c r="D42" s="58"/>
-      <c r="E42" s="58"/>
-      <c r="F42" s="58"/>
-      <c r="G42" s="58"/>
-      <c r="H42" s="58"/>
-      <c r="I42" s="9"/>
-      <c r="J42" s="52"/>
-      <c r="K42" s="52"/>
-      <c r="L42" s="52"/>
-      <c r="M42" s="52"/>
-      <c r="N42" s="52"/>
-      <c r="O42" s="52"/>
-      <c r="P42" s="49"/>
-      <c r="Q42" s="32" t="s">
+      <c r="C42" s="49"/>
+      <c r="D42" s="49"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="49"/>
+      <c r="G42" s="49"/>
+      <c r="H42" s="49"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="47"/>
+      <c r="K42" s="47"/>
+      <c r="L42" s="47"/>
+      <c r="M42" s="47"/>
+      <c r="N42" s="47"/>
+      <c r="O42" s="47"/>
+      <c r="P42" s="45"/>
+      <c r="Q42" s="31" t="s">
         <v>30</v>
       </c>
       <c r="R42" s="9">
+        <v>0.96911209387943398</v>
+      </c>
+      <c r="S42" s="9">
+        <v>5.29253214573484E-2</v>
+      </c>
+      <c r="T42" s="9">
+        <v>32.7933881713275</v>
+      </c>
+      <c r="U42" s="9">
+        <v>-0.57450545641731199</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0.93899599371116504</v>
+      </c>
+      <c r="W42" s="9"/>
+      <c r="X42" s="48"/>
+      <c r="Y42" s="48"/>
+      <c r="Z42" s="48"/>
+      <c r="AA42" s="48"/>
+      <c r="AB42" s="48"/>
+      <c r="AC42" s="35"/>
+    </row>
+    <row r="43" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="1">
+        <v>21828870577.187302</v>
+      </c>
+      <c r="D43" s="1">
+        <v>21828870577.187302</v>
+      </c>
+      <c r="E43" s="1">
+        <v>1</v>
+      </c>
+      <c r="F43" s="1">
+        <v>69.360025998764399</v>
+      </c>
+      <c r="G43" s="1">
+        <v>150.637001976226</v>
+      </c>
+      <c r="H43" s="2">
+        <v>4.7200869189182898E-19</v>
+      </c>
+      <c r="I43" s="8"/>
+      <c r="J43" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="K43" s="51"/>
+      <c r="L43" s="51"/>
+      <c r="M43" s="51"/>
+      <c r="N43" s="51"/>
+      <c r="O43" s="51"/>
+      <c r="P43" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q43" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="R43" s="13">
+        <v>26952.483888888899</v>
+      </c>
+      <c r="S43" s="13">
+        <v>3806.71007179046</v>
+      </c>
+      <c r="T43" s="13">
+        <v>70.469257492222297</v>
+      </c>
+      <c r="U43" s="13">
+        <v>7.0802565418941903</v>
+      </c>
+      <c r="V43" s="41">
+        <v>5.1032972292475198E-9</v>
+      </c>
+      <c r="W43" s="13"/>
+      <c r="X43" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y43" s="47"/>
+      <c r="Z43" s="47"/>
+      <c r="AA43" s="47"/>
+      <c r="AB43" s="47"/>
+      <c r="AC43" s="37"/>
+    </row>
+    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A44" s="44"/>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="1">
+        <v>11545764.943964699</v>
+      </c>
+      <c r="D44" s="1">
+        <v>11545764.943964699</v>
+      </c>
+      <c r="E44" s="1">
+        <v>1</v>
+      </c>
+      <c r="F44" s="1">
+        <v>16.5068331927068</v>
+      </c>
+      <c r="G44" s="1">
+        <v>7.9675190272952195E-2</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0.78124664232875995</v>
+      </c>
+      <c r="I44" s="1"/>
+      <c r="J44" s="47"/>
+      <c r="K44" s="47"/>
+      <c r="L44" s="47"/>
+      <c r="M44" s="47"/>
+      <c r="N44" s="47"/>
+      <c r="O44" s="47"/>
+      <c r="P44" s="44"/>
+      <c r="Q44" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="R44" s="1">
+        <v>34977.103075289997</v>
+      </c>
+      <c r="S44" s="1">
+        <v>3313.0752900440498</v>
+      </c>
+      <c r="T44" s="1">
+        <v>70.865874182612103</v>
+      </c>
+      <c r="U44" s="1">
+        <v>10.557291945763501</v>
+      </c>
+      <c r="V44" s="2">
+        <v>0</v>
+      </c>
+      <c r="W44" s="1"/>
+      <c r="X44" s="47"/>
+      <c r="Y44" s="47"/>
+      <c r="Z44" s="47"/>
+      <c r="AA44" s="47"/>
+      <c r="AB44" s="47"/>
+      <c r="AC44" s="35"/>
+    </row>
+    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A45" s="44"/>
+      <c r="B45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="1">
+        <v>366508256.45689797</v>
+      </c>
+      <c r="D45" s="1">
+        <v>366508256.45689797</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
+      <c r="F45" s="1">
+        <v>69.360026001368695</v>
+      </c>
+      <c r="G45" s="1">
+        <v>2.52920574873438</v>
+      </c>
+      <c r="H45" s="3">
+        <v>0.116304482817742</v>
+      </c>
+      <c r="I45" s="1"/>
+      <c r="J45" s="47"/>
+      <c r="K45" s="47"/>
+      <c r="L45" s="47"/>
+      <c r="M45" s="47"/>
+      <c r="N45" s="47"/>
+      <c r="O45" s="47"/>
+      <c r="P45" s="44"/>
+      <c r="Q45" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="R45" s="1">
+        <v>-5094.1207890139503</v>
+      </c>
+      <c r="S45" s="1">
+        <v>4592.5547243374504</v>
+      </c>
+      <c r="T45" s="1">
+        <v>34.570504227394899</v>
+      </c>
+      <c r="U45" s="1">
+        <v>-1.10921286621116</v>
+      </c>
+      <c r="V45" s="1">
+        <v>0.68637145240327702</v>
+      </c>
+      <c r="W45" s="1"/>
+      <c r="X45" s="47"/>
+      <c r="Y45" s="47"/>
+      <c r="Z45" s="47"/>
+      <c r="AA45" s="47"/>
+      <c r="AB45" s="47"/>
+      <c r="AC45" s="35"/>
+    </row>
+    <row r="46" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="56"/>
+      <c r="B46" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C46" s="50"/>
+      <c r="D46" s="50"/>
+      <c r="E46" s="50"/>
+      <c r="F46" s="50"/>
+      <c r="G46" s="50"/>
+      <c r="H46" s="50"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="48"/>
+      <c r="K46" s="48"/>
+      <c r="L46" s="48"/>
+      <c r="M46" s="48"/>
+      <c r="N46" s="48"/>
+      <c r="O46" s="48"/>
+      <c r="P46" s="56"/>
+      <c r="Q46" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="R46" s="9">
         <v>2930.4983973871599</v>
       </c>
-      <c r="S42" s="9">
+      <c r="S46" s="9">
         <v>4620.0903678267196</v>
       </c>
-      <c r="T42" s="9">
+      <c r="T46" s="9">
         <v>35.121845530194101</v>
       </c>
-      <c r="U42" s="9">
+      <c r="U46" s="9">
         <v>0.63429460553293504</v>
       </c>
-      <c r="V42" s="9">
+      <c r="V46" s="9">
         <v>0.92024495942184903</v>
       </c>
-      <c r="W42" s="9"/>
-      <c r="X42" s="52"/>
-      <c r="Y42" s="52"/>
-      <c r="Z42" s="52"/>
-      <c r="AA42" s="52"/>
-      <c r="AB42" s="52"/>
-      <c r="AC42" s="36"/>
-    </row>
-    <row r="43" spans="1:29" s="24" customFormat="1" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="23" t="s">
+      <c r="W46" s="9"/>
+      <c r="X46" s="48"/>
+      <c r="Y46" s="48"/>
+      <c r="Z46" s="48"/>
+      <c r="AA46" s="48"/>
+      <c r="AB46" s="48"/>
+      <c r="AC46" s="36"/>
+    </row>
+    <row r="47" spans="1:29" s="24" customFormat="1" ht="31.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="R43" s="1"/>
-      <c r="S43" s="1"/>
-      <c r="T43" s="1"/>
-      <c r="U43" s="1"/>
-      <c r="V43" s="1"/>
-      <c r="W43" s="38"/>
-      <c r="X43" s="38"/>
-      <c r="Y43" s="38"/>
-      <c r="Z43" s="38"/>
-      <c r="AA43" s="38"/>
-      <c r="AB43" s="38"/>
-    </row>
-    <row r="44" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="47" t="s">
+      <c r="R47" s="1"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="1"/>
+      <c r="U47" s="1"/>
+      <c r="V47" s="1"/>
+      <c r="W47" s="38"/>
+      <c r="X47" s="38"/>
+      <c r="Y47" s="38"/>
+      <c r="Z47" s="38"/>
+      <c r="AA47" s="38"/>
+      <c r="AB47" s="38"/>
+    </row>
+    <row r="48" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="55" t="s">
         <v>10</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" s="8">
-        <v>4.1857799097373602</v>
-      </c>
-      <c r="D44" s="8">
-        <v>4.1857799097373602</v>
-      </c>
-      <c r="E44" s="8">
-        <v>1</v>
-      </c>
-      <c r="F44" s="8">
-        <v>58.775295215237101</v>
-      </c>
-      <c r="G44" s="8">
-        <v>309.45174334807001</v>
-      </c>
-      <c r="H44" s="20">
-        <v>4.2882526567544902E-25</v>
-      </c>
-      <c r="I44" s="8"/>
-      <c r="J44" s="8">
-        <v>0.23998054577629399</v>
-      </c>
-      <c r="K44" s="8">
-        <v>0.23998054577629399</v>
-      </c>
-      <c r="L44" s="8">
-        <v>1</v>
-      </c>
-      <c r="M44" s="8">
-        <v>107.186966242618</v>
-      </c>
-      <c r="N44" s="8">
-        <v>18.487688610543501</v>
-      </c>
-      <c r="O44" s="20">
-        <v>3.7826149790259799E-5</v>
-      </c>
-      <c r="P44" s="47" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q44" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="R44" s="13">
-        <v>3.4885582678011602</v>
-      </c>
-      <c r="S44" s="13">
-        <v>0.34077366872468301</v>
-      </c>
-      <c r="T44" s="13">
-        <v>64.365339548907201</v>
-      </c>
-      <c r="U44" s="13">
-        <v>12.791227731171601</v>
-      </c>
-      <c r="V44" s="41">
-        <v>6.8500760619372199E-12</v>
-      </c>
-      <c r="W44" s="13"/>
-      <c r="X44" s="13">
-        <v>1.18961267546949</v>
-      </c>
-      <c r="Y44" s="13">
-        <v>7.87400338973991E-2</v>
-      </c>
-      <c r="Z44" s="13">
-        <v>108.78647642397399</v>
-      </c>
-      <c r="AA44" s="13">
-        <v>2.6231865466693001</v>
-      </c>
-      <c r="AB44" s="15">
-        <v>4.8257339848542601E-2</v>
-      </c>
-      <c r="AC44" s="37"/>
-    </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A45" s="48"/>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="1">
-        <v>3.6571648177047403E-2</v>
-      </c>
-      <c r="D45" s="1">
-        <v>3.6571648177047403E-2</v>
-      </c>
-      <c r="E45" s="1">
-        <v>1</v>
-      </c>
-      <c r="F45" s="1">
-        <v>14.508066856775899</v>
-      </c>
-      <c r="G45" s="1">
-        <v>2.7037160408679202</v>
-      </c>
-      <c r="H45" s="1">
-        <v>0.121602132726155</v>
-      </c>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1">
-        <v>0.14769196366738499</v>
-      </c>
-      <c r="K45" s="1">
-        <v>0.14769196366738499</v>
-      </c>
-      <c r="L45" s="1">
-        <v>1</v>
-      </c>
-      <c r="M45" s="1">
-        <v>12.379734112886799</v>
-      </c>
-      <c r="N45" s="1">
-        <v>11.3779349310574</v>
-      </c>
-      <c r="O45" s="2">
-        <v>5.3176769657787898E-3</v>
-      </c>
-      <c r="P45" s="48"/>
-      <c r="Q45" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="R45" s="1">
-        <v>2.5133660717598598</v>
-      </c>
-      <c r="S45" s="1">
-        <v>0.19049289539514599</v>
-      </c>
-      <c r="T45" s="1">
-        <v>63.108209870006597</v>
-      </c>
-      <c r="U45" s="1">
-        <v>12.159906390122</v>
-      </c>
-      <c r="V45" s="6">
-        <v>1.4851009311200901E-11</v>
-      </c>
-      <c r="W45" s="1"/>
-      <c r="X45" s="1">
-        <v>1.4189651337265199</v>
-      </c>
-      <c r="Y45" s="1">
-        <v>9.3909089545544305E-2</v>
-      </c>
-      <c r="Z45" s="1">
-        <v>107.355412830292</v>
-      </c>
-      <c r="AA45" s="1">
-        <v>5.2874049576690796</v>
-      </c>
-      <c r="AB45" s="6">
-        <v>3.9057126667296796E-6</v>
-      </c>
-      <c r="AC45" s="35"/>
-    </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A46" s="48"/>
-      <c r="B46" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C46" s="1">
-        <v>9.5456152618234799E-2</v>
-      </c>
-      <c r="D46" s="1">
-        <v>9.5456152618234799E-2</v>
-      </c>
-      <c r="E46" s="1">
-        <v>1</v>
-      </c>
-      <c r="F46" s="1">
-        <v>58.775295214428802</v>
-      </c>
-      <c r="G46" s="1">
-        <v>7.0570057379977396</v>
-      </c>
-      <c r="H46" s="2">
-        <v>1.01489929112641E-2</v>
-      </c>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1">
-        <v>4.6084357610204602E-2</v>
-      </c>
-      <c r="K46" s="1">
-        <v>4.6084357610204602E-2</v>
-      </c>
-      <c r="L46" s="1">
-        <v>1</v>
-      </c>
-      <c r="M46" s="1">
-        <v>106.783841827976</v>
-      </c>
-      <c r="N46" s="1">
-        <v>3.5502596702509801</v>
-      </c>
-      <c r="O46" s="3">
-        <v>6.2255752292747699E-2</v>
-      </c>
-      <c r="P46" s="48"/>
-      <c r="Q46" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="R46" s="1">
-        <v>0.85617382648215601</v>
-      </c>
-      <c r="S46" s="1">
-        <v>0.172185644358718</v>
-      </c>
-      <c r="T46" s="1">
-        <v>22.028120260493001</v>
-      </c>
-      <c r="U46" s="1">
-        <v>-0.77212162831534203</v>
-      </c>
-      <c r="V46" s="1">
-        <v>0.86614626486267499</v>
-      </c>
-      <c r="W46" s="1"/>
-      <c r="X46" s="1">
-        <v>0.60978596286354803</v>
-      </c>
-      <c r="Y46" s="1">
-        <v>7.9329350713881905E-2</v>
-      </c>
-      <c r="Z46" s="1">
-        <v>18.058113399132399</v>
-      </c>
-      <c r="AA46" s="1">
-        <v>-3.8022365669794702</v>
-      </c>
-      <c r="AB46" s="2">
-        <v>6.4825232500215204E-3</v>
-      </c>
-      <c r="AC46" s="35"/>
-    </row>
-    <row r="47" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="49"/>
-      <c r="B47" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C47" s="58"/>
-      <c r="D47" s="58"/>
-      <c r="E47" s="58"/>
-      <c r="F47" s="58"/>
-      <c r="G47" s="58"/>
-      <c r="H47" s="58"/>
-      <c r="I47" s="9"/>
-      <c r="J47" s="9">
-        <v>5.2456643231190104E-3</v>
-      </c>
-      <c r="K47" s="9">
-        <v>2.6228321615595E-3</v>
-      </c>
-      <c r="L47" s="9">
-        <v>2</v>
-      </c>
-      <c r="M47" s="9">
-        <v>106.82092564483</v>
-      </c>
-      <c r="N47" s="9">
-        <v>0.202058479881251</v>
-      </c>
-      <c r="O47" s="9">
-        <v>0.81735870029617597</v>
-      </c>
-      <c r="P47" s="49"/>
-      <c r="Q47" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="R47" s="9">
-        <v>0.61683884338999295</v>
-      </c>
-      <c r="S47" s="9">
-        <v>0.127475526699626</v>
-      </c>
-      <c r="T47" s="9">
-        <v>23.947765360715401</v>
-      </c>
-      <c r="U47" s="9">
-        <v>-2.33789294579128</v>
-      </c>
-      <c r="V47" s="42">
-        <v>0.117444223101661</v>
-      </c>
-      <c r="W47" s="9"/>
-      <c r="X47" s="9">
-        <v>0.72735020244950499</v>
-      </c>
-      <c r="Y47" s="9">
-        <v>9.3762951214816995E-2</v>
-      </c>
-      <c r="Z47" s="9">
-        <v>17.935412892733801</v>
-      </c>
-      <c r="AA47" s="9">
-        <v>-2.46952451364385</v>
-      </c>
-      <c r="AB47" s="42">
-        <v>9.9463258029382301E-2</v>
-      </c>
-      <c r="AC47" s="36"/>
-    </row>
-    <row r="48" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="47" t="s">
-        <v>25</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C48" s="8">
-        <v>3.75533617845436</v>
+        <v>4.1857799097373602</v>
       </c>
       <c r="D48" s="8">
-        <v>3.75533617845436</v>
+        <v>4.1857799097373602</v>
       </c>
       <c r="E48" s="8">
         <v>1</v>
       </c>
       <c r="F48" s="8">
-        <v>58.450172749992298</v>
+        <v>58.775295215237101</v>
       </c>
       <c r="G48" s="8">
-        <v>275.61367619126997</v>
+        <v>309.45174334807001</v>
       </c>
       <c r="H48" s="20">
-        <v>8.5561055144156804E-24</v>
+        <v>4.2882526567544902E-25</v>
       </c>
       <c r="I48" s="8"/>
       <c r="J48" s="8">
-        <v>0.12745796635020001</v>
+        <v>0.23998054577629399</v>
       </c>
       <c r="K48" s="8">
-        <v>0.12745796635020001</v>
+        <v>0.23998054577629399</v>
       </c>
       <c r="L48" s="8">
         <v>1</v>
       </c>
       <c r="M48" s="8">
-        <v>106.169152592015</v>
+        <v>107.186966242618</v>
       </c>
       <c r="N48" s="8">
-        <v>9.7924313998268993</v>
-      </c>
-      <c r="O48" s="21">
-        <v>2.2627938793836001E-3</v>
-      </c>
-      <c r="P48" s="47" t="s">
-        <v>25</v>
+        <v>18.487688610543501</v>
+      </c>
+      <c r="O48" s="20">
+        <v>3.7826149790259799E-5</v>
+      </c>
+      <c r="P48" s="55" t="s">
+        <v>10</v>
       </c>
       <c r="Q48" s="33" t="s">
         <v>27</v>
       </c>
       <c r="R48" s="13">
-        <v>3.2377296483895002</v>
+        <v>3.4885582678011602</v>
       </c>
       <c r="S48" s="13">
-        <v>0.31711097347862399</v>
+        <v>0.34077366872468301</v>
       </c>
       <c r="T48" s="13">
-        <v>64.620317991065903</v>
+        <v>64.365339548907201</v>
       </c>
       <c r="U48" s="13">
-        <v>11.9955453640014</v>
+        <v>12.791227731171601</v>
       </c>
       <c r="V48" s="41">
-        <v>4.7758463850300399E-12</v>
+        <v>6.8500760619372199E-12</v>
       </c>
       <c r="W48" s="13"/>
       <c r="X48" s="13">
-        <v>1.06502116132782</v>
+        <v>1.18961267546949</v>
       </c>
       <c r="Y48" s="13">
-        <v>7.0595370176184405E-2</v>
+        <v>7.87400338973991E-2</v>
       </c>
       <c r="Z48" s="13">
-        <v>107.75630430099601</v>
+        <v>108.78647642397399</v>
       </c>
       <c r="AA48" s="13">
-        <v>0.95035489024084097</v>
-      </c>
-      <c r="AB48" s="13">
-        <v>0.77770115602609902</v>
+        <v>2.6231865466693001</v>
+      </c>
+      <c r="AB48" s="15">
+        <v>4.8257339848542601E-2</v>
       </c>
       <c r="AC48" s="37"/>
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A49" s="48"/>
+      <c r="A49" s="44"/>
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="1">
-        <v>3.8005186893600197E-2</v>
+        <v>3.6571648177047403E-2</v>
       </c>
       <c r="D49" s="1">
-        <v>3.8005186893600197E-2</v>
+        <v>3.6571648177047403E-2</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
       </c>
       <c r="F49" s="1">
-        <v>14.0776142021772</v>
+        <v>14.508066856775899</v>
       </c>
       <c r="G49" s="1">
-        <v>2.7892973561671002</v>
+        <v>2.7037160408679202</v>
       </c>
       <c r="H49" s="1">
-        <v>0.116971279359414</v>
+        <v>0.121602132726155</v>
       </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1">
-        <v>0.116553339771977</v>
+        <v>0.14769196366738499</v>
       </c>
       <c r="K49" s="1">
-        <v>0.116553339771977</v>
+        <v>0.14769196366738499</v>
       </c>
       <c r="L49" s="1">
         <v>1</v>
       </c>
       <c r="M49" s="1">
-        <v>12.391275226041101</v>
+        <v>12.379734112886799</v>
       </c>
       <c r="N49" s="1">
-        <v>8.9546429840398503</v>
+        <v>11.3779349310574</v>
       </c>
       <c r="O49" s="2">
-        <v>1.08776102041225E-2</v>
-      </c>
-      <c r="P49" s="48"/>
+        <v>5.3176769657787898E-3</v>
+      </c>
+      <c r="P49" s="44"/>
       <c r="Q49" s="31" t="s">
         <v>28</v>
       </c>
       <c r="R49" s="1">
-        <v>2.4100475780322799</v>
+        <v>2.5133660717598598</v>
       </c>
       <c r="S49" s="1">
-        <v>0.183247763022612</v>
+        <v>0.19049289539514599</v>
       </c>
       <c r="T49" s="1">
-        <v>63.2313001359989</v>
+        <v>63.108209870006597</v>
       </c>
       <c r="U49" s="1">
-        <v>11.568981011960799</v>
+        <v>12.159906390122</v>
       </c>
       <c r="V49" s="6">
-        <v>1.42040823547518E-11</v>
+        <v>1.4851009311200901E-11</v>
       </c>
       <c r="W49" s="1"/>
       <c r="X49" s="1">
-        <v>1.33180279529643</v>
+        <v>1.4189651337265199</v>
       </c>
       <c r="Y49" s="1">
-        <v>8.9113002620625797E-2</v>
+        <v>9.3909089545544305E-2</v>
       </c>
       <c r="Z49" s="1">
-        <v>106.407230170926</v>
+        <v>107.355412830292</v>
       </c>
       <c r="AA49" s="1">
-        <v>4.28227214637751</v>
-      </c>
-      <c r="AB49" s="2">
-        <v>2.3530865040188899E-4</v>
+        <v>5.2874049576690796</v>
+      </c>
+      <c r="AB49" s="6">
+        <v>3.9057126667296796E-6</v>
       </c>
       <c r="AC49" s="35"/>
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A50" s="48"/>
+      <c r="A50" s="44"/>
       <c r="B50" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C50" s="1">
-        <v>7.7542068403545703E-2</v>
+        <v>9.5456152618234799E-2</v>
       </c>
       <c r="D50" s="1">
-        <v>7.7542068403545703E-2</v>
+        <v>9.5456152618234799E-2</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
       </c>
       <c r="F50" s="1">
-        <v>58.450172750997197</v>
+        <v>58.775295214428802</v>
       </c>
       <c r="G50" s="1">
-        <v>5.6910096770543701</v>
+        <v>7.0570057379977396</v>
       </c>
       <c r="H50" s="2">
-        <v>2.0312618497821299E-2</v>
+        <v>1.01489929112641E-2</v>
       </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1">
-        <v>7.3363893765149693E-2</v>
+        <v>4.6084357610204602E-2</v>
       </c>
       <c r="K50" s="1">
-        <v>7.3363893765149693E-2</v>
+        <v>4.6084357610204602E-2</v>
       </c>
       <c r="L50" s="1">
         <v>1</v>
       </c>
       <c r="M50" s="1">
-        <v>105.814592900958</v>
+        <v>106.783841827976</v>
       </c>
       <c r="N50" s="1">
-        <v>5.6364534716137902</v>
-      </c>
-      <c r="O50" s="2">
-        <v>1.9393437026140801E-2</v>
-      </c>
-      <c r="P50" s="48"/>
+        <v>3.5502596702509801</v>
+      </c>
+      <c r="O50" s="3">
+        <v>6.2255752292747699E-2</v>
+      </c>
+      <c r="P50" s="44"/>
       <c r="Q50" s="31" t="s">
         <v>29</v>
       </c>
       <c r="R50" s="1">
-        <v>0.85359620150672499</v>
+        <v>0.85617382648215601</v>
       </c>
       <c r="S50" s="1">
-        <v>0.16273753063115801</v>
+        <v>0.172185644358718</v>
       </c>
       <c r="T50" s="1">
-        <v>22.436551986687999</v>
+        <v>22.028120260493001</v>
       </c>
       <c r="U50" s="1">
-        <v>-0.83030473743369204</v>
+        <v>-0.77212162831534203</v>
       </c>
       <c r="V50" s="1">
-        <v>0.83952497968902495</v>
+        <v>0.86614626486267499</v>
       </c>
       <c r="W50" s="1"/>
       <c r="X50" s="1">
-        <v>0.62041460191210296</v>
+        <v>0.60978596286354803</v>
       </c>
       <c r="Y50" s="1">
-        <v>8.16466707193544E-2</v>
+        <v>7.9329350713881905E-2</v>
       </c>
       <c r="Z50" s="1">
-        <v>17.9186243183957</v>
+        <v>18.058113399132399</v>
       </c>
       <c r="AA50" s="1">
-        <v>-3.62740633544988</v>
+        <v>-3.8022365669794702</v>
       </c>
       <c r="AB50" s="2">
-        <v>9.5259666762890199E-3</v>
+        <v>6.4825232500215204E-3</v>
       </c>
       <c r="AC50" s="35"/>
     </row>
     <row r="51" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="49"/>
+      <c r="A51" s="56"/>
       <c r="B51" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C51" s="58"/>
-      <c r="D51" s="58"/>
-      <c r="E51" s="58"/>
-      <c r="F51" s="58"/>
-      <c r="G51" s="58"/>
-      <c r="H51" s="58"/>
+      <c r="C51" s="50"/>
+      <c r="D51" s="50"/>
+      <c r="E51" s="50"/>
+      <c r="F51" s="50"/>
+      <c r="G51" s="50"/>
+      <c r="H51" s="50"/>
       <c r="I51" s="9"/>
       <c r="J51" s="9">
-        <v>7.5239018444935397E-3</v>
+        <v>5.2456643231190104E-3</v>
       </c>
       <c r="K51" s="9">
-        <v>3.7619509222467699E-3</v>
+        <v>2.6228321615595E-3</v>
       </c>
       <c r="L51" s="9">
         <v>2</v>
       </c>
       <c r="M51" s="9">
-        <v>105.84740366368401</v>
+        <v>106.82092564483</v>
       </c>
       <c r="N51" s="9">
-        <v>0.28902584428814998</v>
+        <v>0.202058479881251</v>
       </c>
       <c r="O51" s="9">
-        <v>0.74958204967156605</v>
-      </c>
-      <c r="P51" s="49"/>
+        <v>0.81735870029617597</v>
+      </c>
+      <c r="P51" s="56"/>
       <c r="Q51" s="32" t="s">
         <v>30</v>
       </c>
       <c r="R51" s="9">
-        <v>0.63538580470489003</v>
+        <v>0.61683884338999295</v>
       </c>
       <c r="S51" s="9">
-        <v>0.124810867031525</v>
+        <v>0.127475526699626</v>
       </c>
       <c r="T51" s="9">
-        <v>24.517870816947401</v>
+        <v>23.947765360715401</v>
       </c>
       <c r="U51" s="9">
-        <v>-2.3087894381868401</v>
+        <v>-2.33789294579128</v>
       </c>
       <c r="V51" s="42">
-        <v>0.123498755965347</v>
+        <v>0.117444223101661</v>
       </c>
       <c r="W51" s="9"/>
       <c r="X51" s="9">
-        <v>0.77582486721588295</v>
+        <v>0.72735020244950499</v>
       </c>
       <c r="Y51" s="9">
-        <v>0.10141542139468999</v>
+        <v>9.3762951214816995E-2</v>
       </c>
       <c r="Z51" s="9">
-        <v>17.956705334484202</v>
+        <v>17.935412892733801</v>
       </c>
       <c r="AA51" s="9">
-        <v>-1.9417800269687</v>
-      </c>
-      <c r="AB51" s="9">
-        <v>0.24640381353586799</v>
+        <v>-2.46952451364385</v>
+      </c>
+      <c r="AB51" s="42">
+        <v>9.9463258029382301E-2</v>
       </c>
       <c r="AC51" s="36"/>
     </row>
     <row r="52" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="47" t="s">
-        <v>11</v>
+      <c r="A52" s="55" t="s">
+        <v>25</v>
       </c>
       <c r="B52" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="22">
-        <v>1.6044459576046901</v>
-      </c>
-      <c r="D52" s="22">
-        <v>1.6044459576046901</v>
-      </c>
-      <c r="E52" s="22">
-        <v>1</v>
-      </c>
-      <c r="F52" s="22">
-        <v>57.941257724360497</v>
-      </c>
-      <c r="G52" s="22">
-        <v>114.44647303148901</v>
-      </c>
-      <c r="H52" s="25">
-        <v>2.4310901681812699E-15</v>
+      <c r="C52" s="8">
+        <v>3.75533617845436</v>
+      </c>
+      <c r="D52" s="8">
+        <v>3.75533617845436</v>
+      </c>
+      <c r="E52" s="8">
+        <v>1</v>
+      </c>
+      <c r="F52" s="8">
+        <v>58.450172749992298</v>
+      </c>
+      <c r="G52" s="8">
+        <v>275.61367619126997</v>
+      </c>
+      <c r="H52" s="20">
+        <v>8.5561055144156804E-24</v>
       </c>
       <c r="I52" s="8"/>
-      <c r="J52" s="26">
-        <v>3.27228460982109E-6</v>
-      </c>
-      <c r="K52" s="26">
-        <v>3.27228460982109E-6</v>
+      <c r="J52" s="8">
+        <v>0.12745796635020001</v>
+      </c>
+      <c r="K52" s="8">
+        <v>0.12745796635020001</v>
       </c>
       <c r="L52" s="8">
         <v>1</v>
       </c>
       <c r="M52" s="8">
-        <v>108.162570470471</v>
+        <v>106.169152592015</v>
       </c>
       <c r="N52" s="8">
-        <v>0.81526923567301701</v>
-      </c>
-      <c r="O52" s="8">
-        <v>0.36857341395755699</v>
-      </c>
-      <c r="P52" s="47" t="s">
-        <v>11</v>
+        <v>9.7924313998268993</v>
+      </c>
+      <c r="O52" s="21">
+        <v>2.2627938793836001E-3</v>
+      </c>
+      <c r="P52" s="55" t="s">
+        <v>25</v>
       </c>
       <c r="Q52" s="33" t="s">
         <v>27</v>
       </c>
       <c r="R52" s="13">
-        <v>2.0739376031193602</v>
+        <v>3.2377296483895002</v>
       </c>
       <c r="S52" s="13">
-        <v>0.20636183828608401</v>
+        <v>0.31711097347862399</v>
       </c>
       <c r="T52" s="13">
-        <v>64.217630489307894</v>
+        <v>64.620317991065903</v>
       </c>
       <c r="U52" s="13">
-        <v>7.3309666803809703</v>
+        <v>11.9955453640014</v>
       </c>
       <c r="V52" s="41">
-        <v>2.8690905207184898E-9</v>
+        <v>4.7758463850300399E-12</v>
       </c>
       <c r="W52" s="13"/>
       <c r="X52" s="13">
-        <v>-4.72831811858727E-4</v>
+        <v>1.06502116132782</v>
       </c>
       <c r="Y52" s="13">
-        <v>5.0511625514736505E-4</v>
+        <v>7.0595370176184405E-2</v>
       </c>
       <c r="Z52" s="13">
-        <v>108.947220351745</v>
+        <v>107.75630430099601</v>
       </c>
       <c r="AA52" s="13">
-        <v>-0.93608512305900804</v>
+        <v>0.95035489024084097</v>
       </c>
       <c r="AB52" s="13">
-        <v>0.78552588991913097</v>
+        <v>0.77770115602609902</v>
       </c>
       <c r="AC52" s="37"/>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A53" s="48"/>
+      <c r="A53" s="44"/>
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C53">
-        <v>5.7241252178794499E-2</v>
-      </c>
-      <c r="D53">
-        <v>5.7241252178794499E-2</v>
-      </c>
-      <c r="E53">
-        <v>1</v>
-      </c>
-      <c r="F53">
-        <v>14.016499111022799</v>
-      </c>
-      <c r="G53">
-        <v>4.0830664272103698</v>
-      </c>
-      <c r="H53" s="7">
-        <v>6.28474981350714E-2</v>
+      <c r="C53" s="1">
+        <v>3.8005186893600197E-2</v>
+      </c>
+      <c r="D53" s="1">
+        <v>3.8005186893600197E-2</v>
+      </c>
+      <c r="E53" s="1">
+        <v>1</v>
+      </c>
+      <c r="F53" s="1">
+        <v>14.0776142021772</v>
+      </c>
+      <c r="G53" s="1">
+        <v>2.7892973561671002</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0.116971279359414</v>
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1">
-        <v>1.1254087942051899E-4</v>
+        <v>0.116553339771977</v>
       </c>
       <c r="K53" s="1">
-        <v>1.1254087942051899E-4</v>
+        <v>0.116553339771977</v>
       </c>
       <c r="L53" s="1">
         <v>1</v>
       </c>
       <c r="M53" s="1">
-        <v>13.1287610221782</v>
+        <v>12.391275226041101</v>
       </c>
       <c r="N53" s="1">
-        <v>28.038855933179999</v>
+        <v>8.9546429840398503</v>
       </c>
       <c r="O53" s="2">
-        <v>1.4035037213878999E-4</v>
-      </c>
-      <c r="P53" s="48"/>
+        <v>1.08776102041225E-2</v>
+      </c>
+      <c r="P53" s="44"/>
       <c r="Q53" s="31" t="s">
         <v>28</v>
       </c>
       <c r="R53" s="1">
-        <v>1.8504898868847499</v>
+        <v>2.4100475780322799</v>
       </c>
       <c r="S53" s="1">
-        <v>0.14281987253321901</v>
+        <v>0.183247763022612</v>
       </c>
       <c r="T53" s="1">
-        <v>63.037530931724902</v>
+        <v>63.2313001359989</v>
       </c>
       <c r="U53" s="1">
-        <v>7.9742737143899101</v>
+        <v>11.568981011960799</v>
       </c>
       <c r="V53" s="6">
-        <v>2.5103985556995698E-10</v>
+        <v>1.42040823547518E-11</v>
       </c>
       <c r="W53" s="1"/>
       <c r="X53" s="1">
-        <v>4.9280938617282297E-4</v>
+        <v>1.33180279529643</v>
       </c>
       <c r="Y53" s="1">
-        <v>5.05401745277116E-4</v>
+        <v>8.9113002620625797E-2</v>
       </c>
       <c r="Z53" s="1">
-        <v>107.441893549743</v>
+        <v>106.407230170926</v>
       </c>
       <c r="AA53" s="1">
-        <v>0.97508445662887799</v>
-      </c>
-      <c r="AB53" s="1">
-        <v>0.76389978434717098</v>
+        <v>4.28227214637751</v>
+      </c>
+      <c r="AB53" s="2">
+        <v>2.3530865040188899E-4</v>
       </c>
       <c r="AC53" s="35"/>
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A54" s="48"/>
+      <c r="A54" s="44"/>
       <c r="B54" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C54">
-        <v>1.15277522221443E-2</v>
-      </c>
-      <c r="D54">
-        <v>1.15277522221443E-2</v>
-      </c>
-      <c r="E54">
-        <v>1</v>
-      </c>
-      <c r="F54">
-        <v>57.941257724235903</v>
-      </c>
-      <c r="G54">
-        <v>0.82228421440567401</v>
-      </c>
-      <c r="H54">
-        <v>0.36826900260683199</v>
+      <c r="C54" s="1">
+        <v>7.7542068403545703E-2</v>
+      </c>
+      <c r="D54" s="1">
+        <v>7.7542068403545703E-2</v>
+      </c>
+      <c r="E54" s="1">
+        <v>1</v>
+      </c>
+      <c r="F54" s="1">
+        <v>58.450172750997197</v>
+      </c>
+      <c r="G54" s="1">
+        <v>5.6910096770543701</v>
+      </c>
+      <c r="H54" s="2">
+        <v>2.0312618497821299E-2</v>
       </c>
       <c r="I54" s="1"/>
-      <c r="J54" s="5">
-        <v>7.3359735284969697E-6</v>
-      </c>
-      <c r="K54" s="5">
-        <v>7.3359735284969697E-6</v>
+      <c r="J54" s="1">
+        <v>7.3363893765149693E-2</v>
+      </c>
+      <c r="K54" s="1">
+        <v>7.3363893765149693E-2</v>
       </c>
       <c r="L54" s="1">
         <v>1</v>
       </c>
       <c r="M54" s="1">
-        <v>107.80326229592799</v>
+        <v>105.814592900958</v>
       </c>
       <c r="N54" s="1">
-        <v>1.82771190303713</v>
-      </c>
-      <c r="O54" s="1">
-        <v>0.179227673464389</v>
-      </c>
-      <c r="P54" s="48"/>
+        <v>5.6364534716137902</v>
+      </c>
+      <c r="O54" s="2">
+        <v>1.9393437026140801E-2</v>
+      </c>
+      <c r="P54" s="44"/>
       <c r="Q54" s="31" t="s">
         <v>29</v>
       </c>
       <c r="R54" s="1">
-        <v>0.69912820784997998</v>
+        <v>0.85359620150672499</v>
       </c>
       <c r="S54" s="1">
-        <v>0.148324307575951</v>
+        <v>0.16273753063115801</v>
       </c>
       <c r="T54" s="1">
-        <v>21.800179035140999</v>
+        <v>22.436551986687999</v>
       </c>
       <c r="U54" s="1">
-        <v>-1.68706510404384</v>
+        <v>-0.83030473743369204</v>
       </c>
       <c r="V54" s="1">
-        <v>0.35412379934024302</v>
+        <v>0.83952497968902495</v>
       </c>
       <c r="W54" s="1"/>
       <c r="X54" s="1">
-        <v>-4.8894271875510997E-3</v>
+        <v>0.62041460191210296</v>
       </c>
       <c r="Y54" s="1">
-        <v>9.1172534711224601E-4</v>
+        <v>8.16466707193544E-2</v>
       </c>
       <c r="Z54" s="1">
-        <v>18.9122122903484</v>
+        <v>17.9186243183957</v>
       </c>
       <c r="AA54" s="1">
-        <v>-5.3628290614466696</v>
+        <v>-3.62740633544988</v>
       </c>
       <c r="AB54" s="2">
-        <v>1.9550438579263299E-4</v>
+        <v>9.5259666762890199E-3</v>
       </c>
       <c r="AC54" s="35"/>
     </row>
     <row r="55" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="49"/>
+      <c r="A55" s="56"/>
       <c r="B55" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C55" s="58"/>
-      <c r="D55" s="58"/>
-      <c r="E55" s="58"/>
-      <c r="F55" s="58"/>
-      <c r="G55" s="58"/>
-      <c r="H55" s="58"/>
+      <c r="C55" s="50"/>
+      <c r="D55" s="50"/>
+      <c r="E55" s="50"/>
+      <c r="F55" s="50"/>
+      <c r="G55" s="50"/>
+      <c r="H55" s="50"/>
       <c r="I55" s="9"/>
-      <c r="J55" s="27">
-        <v>7.2143853443936604E-6</v>
-      </c>
-      <c r="K55" s="27">
-        <v>3.6071926721968302E-6</v>
+      <c r="J55" s="9">
+        <v>7.5239018444935397E-3</v>
+      </c>
+      <c r="K55" s="9">
+        <v>3.7619509222467699E-3</v>
       </c>
       <c r="L55" s="9">
         <v>2</v>
       </c>
       <c r="M55" s="9">
-        <v>107.842517864377</v>
+        <v>105.84740366368401</v>
       </c>
       <c r="N55" s="9">
-        <v>0.89870948387585703</v>
+        <v>0.28902584428814998</v>
       </c>
       <c r="O55" s="9">
-        <v>0.41012132536637402</v>
-      </c>
-      <c r="P55" s="49"/>
+        <v>0.74958204967156605</v>
+      </c>
+      <c r="P55" s="56"/>
       <c r="Q55" s="32" t="s">
         <v>30</v>
       </c>
       <c r="R55" s="9">
-        <v>0.62380356878450904</v>
+        <v>0.63538580470489003</v>
       </c>
       <c r="S55" s="9">
-        <v>0.13578145981755799</v>
+        <v>0.124810867031525</v>
       </c>
       <c r="T55" s="9">
-        <v>23.6213122095755</v>
+        <v>24.517870816947401</v>
       </c>
       <c r="U55" s="9">
-        <v>-2.1680811723975899</v>
-      </c>
-      <c r="V55" s="9">
-        <v>0.16142822200252099</v>
+        <v>-2.3087894381868401</v>
+      </c>
+      <c r="V55" s="42">
+        <v>0.123498755965347</v>
       </c>
       <c r="W55" s="9"/>
       <c r="X55" s="9">
-        <v>-3.9237859895195496E-3</v>
+        <v>0.77582486721588295</v>
       </c>
       <c r="Y55" s="9">
-        <v>9.0311675397618501E-4</v>
+        <v>0.10141542139468999</v>
       </c>
       <c r="Z55" s="9">
-        <v>18.890902844266801</v>
+        <v>17.956705334484202</v>
       </c>
       <c r="AA55" s="9">
-        <v>-4.3447161978162399</v>
-      </c>
-      <c r="AB55" s="19">
-        <v>1.8370895217705301E-3</v>
+        <v>-1.9417800269687</v>
+      </c>
+      <c r="AB55" s="9">
+        <v>0.24640381353586799</v>
       </c>
       <c r="AC55" s="36"/>
     </row>
     <row r="56" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="47" t="s">
-        <v>12</v>
+      <c r="A56" s="55" t="s">
+        <v>11</v>
       </c>
       <c r="B56" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C56" s="8">
-        <v>3.2828058473639601</v>
-      </c>
-      <c r="D56" s="8">
-        <v>3.2828058473639601</v>
-      </c>
-      <c r="E56" s="8">
-        <v>1</v>
-      </c>
-      <c r="F56" s="8">
-        <v>57.1027846481349</v>
-      </c>
-      <c r="G56" s="8">
-        <v>315.57785828471202</v>
-      </c>
-      <c r="H56" s="20">
-        <v>6.2556135251351003E-25</v>
+      <c r="C56" s="22">
+        <v>1.6044459576046901</v>
+      </c>
+      <c r="D56" s="22">
+        <v>1.6044459576046901</v>
+      </c>
+      <c r="E56" s="22">
+        <v>1</v>
+      </c>
+      <c r="F56" s="22">
+        <v>57.941257724360497</v>
+      </c>
+      <c r="G56" s="22">
+        <v>114.44647303148901</v>
+      </c>
+      <c r="H56" s="25">
+        <v>2.4310901681812699E-15</v>
       </c>
       <c r="I56" s="8"/>
-      <c r="J56" s="8">
-        <v>4.9581564592565801</v>
-      </c>
-      <c r="K56" s="8">
-        <v>4.9581564592565801</v>
+      <c r="J56" s="26">
+        <v>3.27228460982109E-6</v>
+      </c>
+      <c r="K56" s="26">
+        <v>3.27228460982109E-6</v>
       </c>
       <c r="L56" s="8">
         <v>1</v>
       </c>
       <c r="M56" s="8">
-        <v>107.087389174327</v>
+        <v>108.162570470471</v>
       </c>
       <c r="N56" s="8">
-        <v>15.8163561438312</v>
-      </c>
-      <c r="O56" s="21">
-        <v>1.2711861864362099E-4</v>
-      </c>
-      <c r="P56" s="47" t="s">
-        <v>12</v>
+        <v>0.81526923567301701</v>
+      </c>
+      <c r="O56" s="8">
+        <v>0.36857341395755699</v>
+      </c>
+      <c r="P56" s="55" t="s">
+        <v>11</v>
       </c>
       <c r="Q56" s="33" t="s">
         <v>27</v>
       </c>
       <c r="R56" s="13">
-        <v>3.25039616887112</v>
+        <v>2.0739376031193602</v>
       </c>
       <c r="S56" s="13">
-        <v>0.28598369641782101</v>
+        <v>0.20636183828608401</v>
       </c>
       <c r="T56" s="13">
-        <v>64.098058733478297</v>
+        <v>64.217630489307894</v>
       </c>
       <c r="U56" s="13">
-        <v>13.3975884833244</v>
+        <v>7.3309666803809703</v>
       </c>
       <c r="V56" s="41">
-        <v>8.8387075436457995E-12</v>
+        <v>2.8690905207184898E-9</v>
       </c>
       <c r="W56" s="13"/>
       <c r="X56" s="13">
-        <v>0.231107865381736</v>
+        <v>-4.72831811858727E-4</v>
       </c>
       <c r="Y56" s="13">
-        <v>0.141033950135908</v>
+        <v>5.0511625514736505E-4</v>
       </c>
       <c r="Z56" s="13">
-        <v>109.142880527442</v>
+        <v>108.947220351745</v>
       </c>
       <c r="AA56" s="13">
-        <v>1.63866831467904</v>
+        <v>-0.93608512305900804</v>
       </c>
       <c r="AB56" s="13">
-        <v>0.361442574294079</v>
+        <v>0.78552588991913097</v>
       </c>
       <c r="AC56" s="37"/>
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A57" s="48"/>
+      <c r="A57" s="44"/>
       <c r="B57" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C57" s="1">
-        <v>6.9098899300225596E-4</v>
-      </c>
-      <c r="D57" s="1">
-        <v>6.9098899300225596E-4</v>
-      </c>
-      <c r="E57" s="1">
-        <v>1</v>
-      </c>
-      <c r="F57" s="1">
-        <v>13.6400199665374</v>
-      </c>
-      <c r="G57" s="1">
-        <v>6.6425136498724599E-2</v>
-      </c>
-      <c r="H57" s="1">
-        <v>0.80046236006191795</v>
+      <c r="C57">
+        <v>5.7241252178794499E-2</v>
+      </c>
+      <c r="D57">
+        <v>5.7241252178794499E-2</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+      <c r="F57">
+        <v>14.016499111022799</v>
+      </c>
+      <c r="G57">
+        <v>4.0830664272103698</v>
+      </c>
+      <c r="H57" s="7">
+        <v>6.28474981350714E-2</v>
       </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1">
-        <v>1.93826224654098E-2</v>
+        <v>1.1254087942051899E-4</v>
       </c>
       <c r="K57" s="1">
-        <v>1.93826224654098E-2</v>
+        <v>1.1254087942051899E-4</v>
       </c>
       <c r="L57" s="1">
         <v>1</v>
       </c>
       <c r="M57" s="1">
-        <v>11.8724826464864</v>
+        <v>13.1287610221782</v>
       </c>
       <c r="N57" s="1">
-        <v>6.1829928610262298E-2</v>
-      </c>
-      <c r="O57" s="1">
-        <v>0.80787586394532096</v>
-      </c>
-      <c r="P57" s="48"/>
+        <v>28.038855933179999</v>
+      </c>
+      <c r="O57" s="2">
+        <v>1.4035037213878999E-4</v>
+      </c>
+      <c r="P57" s="44"/>
       <c r="Q57" s="31" t="s">
         <v>28</v>
       </c>
       <c r="R57" s="1">
-        <v>2.1892524295195499</v>
+        <v>1.8504898868847499</v>
       </c>
       <c r="S57" s="1">
-        <v>0.14734976342700101</v>
+        <v>0.14281987253321901</v>
       </c>
       <c r="T57" s="1">
-        <v>61.439546816495699</v>
+        <v>63.037530931724902</v>
       </c>
       <c r="U57" s="1">
-        <v>11.641762270683</v>
+        <v>7.9742737143899101</v>
       </c>
       <c r="V57" s="6">
-        <v>1.9951040819421499E-11</v>
+        <v>2.5103985556995698E-10</v>
       </c>
       <c r="W57" s="1"/>
       <c r="X57" s="1">
-        <v>0.67677558509185598</v>
+        <v>4.9280938617282297E-4</v>
       </c>
       <c r="Y57" s="1">
-        <v>0.14123776247129999</v>
+        <v>5.05401745277116E-4</v>
       </c>
       <c r="Z57" s="1">
-        <v>107.564370903827</v>
+        <v>107.441893549743</v>
       </c>
       <c r="AA57" s="1">
-        <v>4.7917467202114503</v>
-      </c>
-      <c r="AB57" s="6">
-        <v>3.1319294462428497E-5</v>
+        <v>0.97508445662887799</v>
+      </c>
+      <c r="AB57" s="1">
+        <v>0.76389978434717098</v>
       </c>
       <c r="AC57" s="35"/>
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A58" s="48"/>
+      <c r="A58" s="44"/>
       <c r="B58" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C58" s="1">
-        <v>0.13315844295854501</v>
-      </c>
-      <c r="D58" s="1">
-        <v>0.13315844295854501</v>
-      </c>
-      <c r="E58" s="1">
-        <v>1</v>
-      </c>
-      <c r="F58" s="1">
-        <v>57.102784645779103</v>
-      </c>
-      <c r="G58" s="1">
-        <v>12.800591382864701</v>
-      </c>
-      <c r="H58" s="2">
-        <v>7.1467481949516205E-4</v>
+      <c r="C58">
+        <v>1.15277522221443E-2</v>
+      </c>
+      <c r="D58">
+        <v>1.15277522221443E-2</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+      <c r="F58">
+        <v>57.941257724235903</v>
+      </c>
+      <c r="G58">
+        <v>0.82228421440567401</v>
+      </c>
+      <c r="H58">
+        <v>0.36826900260683199</v>
       </c>
       <c r="I58" s="1"/>
-      <c r="J58" s="1">
-        <v>1.5642063102591399</v>
-      </c>
-      <c r="K58" s="1">
-        <v>1.5642063102591399</v>
+      <c r="J58" s="5">
+        <v>7.3359735284969697E-6</v>
+      </c>
+      <c r="K58" s="5">
+        <v>7.3359735284969697E-6</v>
       </c>
       <c r="L58" s="1">
         <v>1</v>
       </c>
       <c r="M58" s="1">
-        <v>106.739383464101</v>
+        <v>107.80326229592799</v>
       </c>
       <c r="N58" s="1">
-        <v>4.9897667184944403</v>
-      </c>
-      <c r="O58" s="2">
-        <v>2.7582949079364601E-2</v>
-      </c>
-      <c r="P58" s="48"/>
+        <v>1.82771190303713</v>
+      </c>
+      <c r="O58" s="1">
+        <v>0.179227673464389</v>
+      </c>
+      <c r="P58" s="44"/>
       <c r="Q58" s="31" t="s">
         <v>29</v>
       </c>
       <c r="R58" s="1">
-        <v>1.1692225136694301</v>
+        <v>0.69912820784997998</v>
       </c>
       <c r="S58" s="1">
-        <v>0.196811825263492</v>
+        <v>0.148324307575951</v>
       </c>
       <c r="T58" s="1">
-        <v>23.0448591919385</v>
+        <v>21.800179035140999</v>
       </c>
       <c r="U58" s="1">
-        <v>0.92878103054844996</v>
+        <v>-1.68706510404384</v>
       </c>
       <c r="V58" s="1">
-        <v>0.78983763251570405</v>
+        <v>0.35412379934024302</v>
       </c>
       <c r="W58" s="1"/>
       <c r="X58" s="1">
-        <v>-0.27405008386437302</v>
+        <v>-4.8894271875510997E-3</v>
       </c>
       <c r="Y58" s="1">
-        <v>0.23047768278960401</v>
+        <v>9.1172534711224601E-4</v>
       </c>
       <c r="Z58" s="1">
-        <v>20.2025121535642</v>
+        <v>18.9122122903484</v>
       </c>
       <c r="AA58" s="1">
-        <v>-1.1890525822170199</v>
-      </c>
-      <c r="AB58" s="1">
-        <v>0.64042678790185603</v>
+        <v>-5.3628290614466696</v>
+      </c>
+      <c r="AB58" s="2">
+        <v>1.9550438579263299E-4</v>
       </c>
       <c r="AC58" s="35"/>
     </row>
     <row r="59" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="49"/>
+      <c r="A59" s="56"/>
       <c r="B59" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C59" s="58"/>
-      <c r="D59" s="58"/>
-      <c r="E59" s="58"/>
-      <c r="F59" s="58"/>
-      <c r="G59" s="58"/>
-      <c r="H59" s="58"/>
+      <c r="C59" s="50"/>
+      <c r="D59" s="50"/>
+      <c r="E59" s="50"/>
+      <c r="F59" s="50"/>
+      <c r="G59" s="50"/>
+      <c r="H59" s="50"/>
       <c r="I59" s="9"/>
-      <c r="J59" s="9">
-        <v>0.34951867520347901</v>
-      </c>
-      <c r="K59" s="9">
-        <v>0.17475933760173901</v>
+      <c r="J59" s="27">
+        <v>7.2143853443936604E-6</v>
+      </c>
+      <c r="K59" s="27">
+        <v>3.6071926721968302E-6</v>
       </c>
       <c r="L59" s="9">
         <v>2</v>
       </c>
       <c r="M59" s="9">
-        <v>106.790362785864</v>
+        <v>107.842517864377</v>
       </c>
       <c r="N59" s="9">
-        <v>0.55747654308262395</v>
+        <v>0.89870948387585703</v>
       </c>
       <c r="O59" s="9">
-        <v>0.57430971602825098</v>
-      </c>
-      <c r="P59" s="49"/>
+        <v>0.41012132536637402</v>
+      </c>
+      <c r="P59" s="56"/>
       <c r="Q59" s="32" t="s">
         <v>30</v>
       </c>
       <c r="R59" s="9">
-        <v>0.78751115116799897</v>
+        <v>0.62380356878450904</v>
       </c>
       <c r="S59" s="9">
-        <v>0.134642721113232</v>
+        <v>0.13578145981755799</v>
       </c>
       <c r="T59" s="9">
-        <v>24.194803942637702</v>
+        <v>23.6213122095755</v>
       </c>
       <c r="U59" s="9">
-        <v>-1.39717088969851</v>
+        <v>-2.1680811723975899</v>
       </c>
       <c r="V59" s="9">
-        <v>0.513084729394649</v>
+        <v>0.16142822200252099</v>
       </c>
       <c r="W59" s="9"/>
       <c r="X59" s="9">
-        <v>0.17161763584574699</v>
+        <v>-3.9237859895195496E-3</v>
       </c>
       <c r="Y59" s="9">
-        <v>0.22829681478081101</v>
+        <v>9.0311675397618501E-4</v>
       </c>
       <c r="Z59" s="9">
-        <v>20.376823491681002</v>
+        <v>18.890902844266801</v>
       </c>
       <c r="AA59" s="9">
-        <v>0.75173031218380404</v>
-      </c>
-      <c r="AB59" s="9">
-        <v>0.87487377567923097</v>
+        <v>-4.3447161978162399</v>
+      </c>
+      <c r="AB59" s="19">
+        <v>1.8370895217705301E-3</v>
       </c>
       <c r="AC59" s="36"/>
     </row>
     <row r="60" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="47" t="s">
-        <v>14</v>
+      <c r="A60" s="55" t="s">
+        <v>12</v>
       </c>
       <c r="B60" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C60" s="8">
-        <v>0.48460569188395097</v>
+        <v>3.2828058473639601</v>
       </c>
       <c r="D60" s="8">
-        <v>0.48460569188395097</v>
+        <v>3.2828058473639601</v>
       </c>
       <c r="E60" s="8">
         <v>1</v>
       </c>
       <c r="F60" s="8">
-        <v>66.433120310954493</v>
+        <v>57.1027846481349</v>
       </c>
       <c r="G60" s="8">
-        <v>275.25199949565803</v>
+        <v>315.57785828471202</v>
       </c>
       <c r="H60" s="20">
-        <v>2.5677289076389099E-25</v>
+        <v>6.2556135251351003E-25</v>
       </c>
       <c r="I60" s="8"/>
       <c r="J60" s="8">
-        <v>0.251919036972449</v>
+        <v>4.9581564592565801</v>
       </c>
       <c r="K60" s="8">
-        <v>0.251919036972449</v>
+        <v>4.9581564592565801</v>
       </c>
       <c r="L60" s="8">
         <v>1</v>
       </c>
       <c r="M60" s="8">
-        <v>120.000000000931</v>
+        <v>107.087389174327</v>
       </c>
       <c r="N60" s="8">
-        <v>45.935699808275302</v>
-      </c>
-      <c r="O60" s="20">
-        <v>4.8525436598560696E-10</v>
-      </c>
-      <c r="P60" s="47" t="s">
-        <v>14</v>
+        <v>15.8163561438312</v>
+      </c>
+      <c r="O60" s="21">
+        <v>1.2711861864362099E-4</v>
+      </c>
+      <c r="P60" s="55" t="s">
+        <v>12</v>
       </c>
       <c r="Q60" s="33" t="s">
         <v>27</v>
       </c>
       <c r="R60" s="13">
-        <v>0.63093577454569305</v>
+        <v>3.25039616887112</v>
       </c>
       <c r="S60" s="13">
-        <v>2.1808374327603901E-2</v>
+        <v>0.28598369641782101</v>
       </c>
       <c r="T60" s="13">
-        <v>68.208347437733096</v>
+        <v>64.098058733478297</v>
       </c>
       <c r="U60" s="13">
-        <v>-13.3241582807534</v>
-      </c>
-      <c r="V60" s="15">
-        <v>0</v>
+        <v>13.3975884833244</v>
+      </c>
+      <c r="V60" s="41">
+        <v>8.8387075436457995E-12</v>
       </c>
       <c r="W60" s="13"/>
       <c r="X60" s="13">
-        <v>0.85281619998043701</v>
+        <v>0.231107865381736</v>
       </c>
       <c r="Y60" s="13">
-        <v>3.6402779797028099E-2</v>
+        <v>0.141033950135908</v>
       </c>
       <c r="Z60" s="13">
-        <v>109.756917022072</v>
+        <v>109.142880527442</v>
       </c>
       <c r="AA60" s="13">
-        <v>-3.7298776773604998</v>
-      </c>
-      <c r="AB60" s="15">
-        <v>1.7132034310097799E-3</v>
+        <v>1.63866831467904</v>
+      </c>
+      <c r="AB60" s="13">
+        <v>0.361442574294079</v>
       </c>
       <c r="AC60" s="37"/>
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A61" s="48"/>
+      <c r="A61" s="44"/>
       <c r="B61" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C61" s="1">
-        <v>1.0223913414274E-2</v>
+        <v>6.9098899300225596E-4</v>
       </c>
       <c r="D61" s="1">
-        <v>1.0223913414274E-2</v>
+        <v>6.9098899300225596E-4</v>
       </c>
       <c r="E61" s="1">
         <v>1</v>
       </c>
       <c r="F61" s="1">
-        <v>16.820702919437998</v>
+        <v>13.6400199665374</v>
       </c>
       <c r="G61" s="1">
-        <v>5.8070977231181704</v>
-      </c>
-      <c r="H61" s="2">
-        <v>2.77082234476239E-2</v>
+        <v>6.6425136498724599E-2</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0.80046236006191795</v>
       </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1">
-        <v>0.24754938321325901</v>
+        <v>1.93826224654098E-2</v>
       </c>
       <c r="K61" s="1">
-        <v>0.24754938321325901</v>
+        <v>1.93826224654098E-2</v>
       </c>
       <c r="L61" s="1">
         <v>1</v>
       </c>
       <c r="M61" s="1">
-        <v>120.000000000876</v>
+        <v>11.8724826464864</v>
       </c>
       <c r="N61" s="1">
-        <v>45.138923567144403</v>
-      </c>
-      <c r="O61" s="4">
-        <v>6.5162497916437297E-10</v>
-      </c>
-      <c r="P61" s="48"/>
+        <v>6.1829928610262298E-2</v>
+      </c>
+      <c r="O61" s="1">
+        <v>0.80787586394532096</v>
+      </c>
+      <c r="P61" s="44"/>
       <c r="Q61" s="31" t="s">
         <v>28</v>
       </c>
       <c r="R61" s="1">
-        <v>0.76645094993192597</v>
+        <v>2.1892524295195499</v>
       </c>
       <c r="S61" s="1">
-        <v>2.07855368671831E-2</v>
+        <v>0.14734976342700101</v>
       </c>
       <c r="T61" s="1">
-        <v>65.367738446356398</v>
+        <v>61.439546816495699</v>
       </c>
       <c r="U61" s="1">
-        <v>-9.8079800133367101</v>
-      </c>
-      <c r="V61" s="2">
-        <v>0</v>
+        <v>11.641762270683</v>
+      </c>
+      <c r="V61" s="6">
+        <v>1.9951040819421499E-11</v>
       </c>
       <c r="W61" s="1"/>
       <c r="X61" s="1">
-        <v>0.763423356833838</v>
+        <v>0.67677558509185598</v>
       </c>
       <c r="Y61" s="1">
-        <v>3.3116417525027302E-2</v>
+        <v>0.14123776247129999</v>
       </c>
       <c r="Z61" s="1">
-        <v>108.18375969063101</v>
+        <v>107.564370903827</v>
       </c>
       <c r="AA61" s="1">
-        <v>-6.22290869573379</v>
+        <v>4.7917467202114503</v>
       </c>
       <c r="AB61" s="6">
-        <v>5.6421459060373997E-8</v>
+        <v>3.1319294462428497E-5</v>
       </c>
       <c r="AC61" s="35"/>
     </row>
-    <row r="62" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="48"/>
+    <row r="62" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A62" s="44"/>
       <c r="B62" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C62" s="1">
-        <v>3.4754513300900097E-2</v>
+        <v>0.13315844295854501</v>
       </c>
       <c r="D62" s="1">
-        <v>3.4754513300900097E-2</v>
+        <v>0.13315844295854501</v>
       </c>
       <c r="E62" s="1">
         <v>1</v>
       </c>
       <c r="F62" s="1">
-        <v>66.433120314017799</v>
+        <v>57.102784645779103</v>
       </c>
       <c r="G62" s="1">
-        <v>19.740274284401199</v>
-      </c>
-      <c r="H62" s="4">
-        <v>3.4416590783058898E-5</v>
+        <v>12.800591382864701</v>
+      </c>
+      <c r="H62" s="2">
+        <v>7.1467481949516205E-4</v>
       </c>
       <c r="I62" s="1"/>
       <c r="J62" s="1">
-        <v>1.81876043094546E-2</v>
+        <v>1.5642063102591399</v>
       </c>
       <c r="K62" s="1">
-        <v>1.81876043094546E-2</v>
+        <v>1.5642063102591399</v>
       </c>
       <c r="L62" s="1">
         <v>1</v>
       </c>
       <c r="M62" s="1">
-        <v>120.000000000876</v>
+        <v>106.739383464101</v>
       </c>
       <c r="N62" s="1">
-        <v>3.3163842710393201</v>
-      </c>
-      <c r="O62" s="3">
-        <v>7.1083850624745398E-2</v>
-      </c>
-      <c r="P62" s="48"/>
+        <v>4.9897667184944403</v>
+      </c>
+      <c r="O62" s="2">
+        <v>2.7582949079364601E-2</v>
+      </c>
+      <c r="P62" s="44"/>
       <c r="Q62" s="31" t="s">
         <v>29</v>
       </c>
       <c r="R62" s="1">
-        <v>0.83438570293307701</v>
+        <v>1.1692225136694301</v>
       </c>
       <c r="S62" s="1">
-        <v>3.3488447870679602E-2</v>
+        <v>0.196811825263492</v>
       </c>
       <c r="T62" s="1">
-        <v>30.8586362068467</v>
+        <v>23.0448591919385</v>
       </c>
       <c r="U62" s="1">
-        <v>-4.5112113615864997</v>
-      </c>
-      <c r="V62" s="2">
-        <v>4.8479551006386202E-4</v>
+        <v>0.92878103054844996</v>
+      </c>
+      <c r="V62" s="1">
+        <v>0.78983763251570405</v>
       </c>
       <c r="W62" s="1"/>
       <c r="X62" s="1">
-        <v>0.86166002670741904</v>
+        <v>-0.27405008386437302</v>
       </c>
       <c r="Y62" s="1">
-        <v>3.6912066142334603E-2</v>
+        <v>0.23047768278960401</v>
       </c>
       <c r="Z62" s="1">
-        <v>40.219886600149103</v>
+        <v>20.2025121535642</v>
       </c>
       <c r="AA62" s="1">
-        <v>-3.4757314012155298</v>
-      </c>
-      <c r="AB62" s="2">
-        <v>6.51926940610248E-3</v>
+        <v>-1.1890525822170199</v>
+      </c>
+      <c r="AB62" s="1">
+        <v>0.64042678790185603</v>
       </c>
       <c r="AC62" s="35"/>
     </row>
     <row r="63" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="49"/>
+      <c r="A63" s="56"/>
       <c r="B63" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C63" s="58"/>
-      <c r="D63" s="58"/>
-      <c r="E63" s="58"/>
-      <c r="F63" s="58"/>
-      <c r="G63" s="58"/>
-      <c r="H63" s="58"/>
+      <c r="C63" s="50"/>
+      <c r="D63" s="50"/>
+      <c r="E63" s="50"/>
+      <c r="F63" s="50"/>
+      <c r="G63" s="50"/>
+      <c r="H63" s="50"/>
       <c r="I63" s="9"/>
       <c r="J63" s="9">
-        <v>3.6858467316493698E-2</v>
+        <v>0.34951867520347901</v>
       </c>
       <c r="K63" s="9">
-        <v>1.8429233658246901E-2</v>
+        <v>0.17475933760173901</v>
       </c>
       <c r="L63" s="9">
         <v>2</v>
       </c>
       <c r="M63" s="9">
-        <v>120.00000000096099</v>
+        <v>106.790362785864</v>
       </c>
       <c r="N63" s="9">
-        <v>3.3604437171390802</v>
-      </c>
-      <c r="O63" s="19">
-        <v>3.8017401028842102E-2</v>
-      </c>
-      <c r="P63" s="49"/>
+        <v>0.55747654308262395</v>
+      </c>
+      <c r="O63" s="9">
+        <v>0.57430971602825098</v>
+      </c>
+      <c r="P63" s="56"/>
       <c r="Q63" s="32" t="s">
         <v>30</v>
       </c>
       <c r="R63" s="9">
-        <v>1.0135987535073001</v>
+        <v>0.78751115116799897</v>
       </c>
       <c r="S63" s="9">
-        <v>4.3185412023769597E-2</v>
+        <v>0.134642721113232</v>
       </c>
       <c r="T63" s="9">
-        <v>33.635517105315301</v>
+        <v>24.194803942637702</v>
       </c>
       <c r="U63" s="9">
-        <v>0.31702372661387901</v>
+        <v>-1.39717088969851</v>
       </c>
       <c r="V63" s="9">
-        <v>0.98877074255840203</v>
+        <v>0.513084729394649</v>
       </c>
       <c r="W63" s="9"/>
       <c r="X63" s="9">
-        <v>0.77134016691240403</v>
+        <v>0.17161763584574699</v>
       </c>
       <c r="Y63" s="9">
-        <v>3.3538164823331003E-2</v>
+        <v>0.22829681478081101</v>
       </c>
       <c r="Z63" s="9">
-        <v>47.071378613344201</v>
+        <v>20.376823491681002</v>
       </c>
       <c r="AA63" s="9">
-        <v>-5.9711021561995201</v>
-      </c>
-      <c r="AB63" s="40">
-        <v>1.7432415013729501E-6</v>
+        <v>0.75173031218380404</v>
+      </c>
+      <c r="AB63" s="9">
+        <v>0.87487377567923097</v>
       </c>
       <c r="AC63" s="36"/>
     </row>
     <row r="64" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="47" t="s">
-        <v>26</v>
+      <c r="A64" s="55" t="s">
+        <v>14</v>
       </c>
       <c r="B64" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C64" s="8">
-        <v>1.1481734714944201</v>
+        <v>0.48460569188395097</v>
       </c>
       <c r="D64" s="8">
-        <v>1.1481734714944201</v>
+        <v>0.48460569188395097</v>
       </c>
       <c r="E64" s="8">
         <v>1</v>
       </c>
       <c r="F64" s="8">
-        <v>57.458627569308902</v>
+        <v>66.433120310954493</v>
       </c>
       <c r="G64" s="8">
-        <v>62.871367396090498</v>
+        <v>275.25199949565803</v>
       </c>
       <c r="H64" s="20">
-        <v>8.5554572534297795E-11</v>
+        <v>2.5677289076389099E-25</v>
       </c>
       <c r="I64" s="8"/>
-      <c r="J64" s="57" t="s">
-        <v>31</v>
-      </c>
-      <c r="K64" s="57"/>
-      <c r="L64" s="57"/>
-      <c r="M64" s="57"/>
-      <c r="N64" s="57"/>
-      <c r="O64" s="57"/>
-      <c r="P64" s="47" t="s">
-        <v>26</v>
+      <c r="J64" s="8">
+        <v>0.251919036972449</v>
+      </c>
+      <c r="K64" s="8">
+        <v>0.251919036972449</v>
+      </c>
+      <c r="L64" s="8">
+        <v>1</v>
+      </c>
+      <c r="M64" s="8">
+        <v>120.000000000931</v>
+      </c>
+      <c r="N64" s="8">
+        <v>45.935699808275302</v>
+      </c>
+      <c r="O64" s="20">
+        <v>4.8525436598560696E-10</v>
+      </c>
+      <c r="P64" s="55" t="s">
+        <v>14</v>
       </c>
       <c r="Q64" s="33" t="s">
         <v>27</v>
       </c>
       <c r="R64" s="13">
-        <v>1.89134861613022</v>
+        <v>0.63093577454569305</v>
       </c>
       <c r="S64" s="13">
-        <v>0.21484737680985</v>
+        <v>2.1808374327603901E-2</v>
       </c>
       <c r="T64" s="13">
-        <v>62.148851945988298</v>
+        <v>68.208347437733096</v>
       </c>
       <c r="U64" s="13">
-        <v>5.6102048802882196</v>
-      </c>
-      <c r="V64" s="41">
-        <v>2.9455467435157701E-6</v>
+        <v>-13.3241582807534</v>
+      </c>
+      <c r="V64" s="15">
+        <v>0</v>
       </c>
       <c r="W64" s="13"/>
-      <c r="X64" s="56" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y64" s="56"/>
-      <c r="Z64" s="56"/>
-      <c r="AA64" s="56"/>
-      <c r="AB64" s="56"/>
+      <c r="X64" s="13">
+        <v>0.85281619998043701</v>
+      </c>
+      <c r="Y64" s="13">
+        <v>3.6402779797028099E-2</v>
+      </c>
+      <c r="Z64" s="13">
+        <v>109.756917022072</v>
+      </c>
+      <c r="AA64" s="13">
+        <v>-3.7298776773604998</v>
+      </c>
+      <c r="AB64" s="15">
+        <v>1.7132034310097799E-3</v>
+      </c>
       <c r="AC64" s="37"/>
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A65" s="48"/>
+      <c r="A65" s="44"/>
       <c r="B65" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C65" s="1">
-        <v>9.2911254906166099E-2</v>
+        <v>1.0223913414274E-2</v>
       </c>
       <c r="D65" s="1">
-        <v>9.2911254906166099E-2</v>
+        <v>1.0223913414274E-2</v>
       </c>
       <c r="E65" s="1">
         <v>1</v>
       </c>
       <c r="F65" s="1">
-        <v>14.883763903298201</v>
+        <v>16.820702919437998</v>
       </c>
       <c r="G65" s="1">
-        <v>5.0876089610695701</v>
+        <v>5.8070977231181704</v>
       </c>
       <c r="H65" s="2">
-        <v>3.9589780561885203E-2</v>
+        <v>2.77082234476239E-2</v>
       </c>
       <c r="I65" s="1"/>
-      <c r="J65" s="51"/>
-      <c r="K65" s="51"/>
-      <c r="L65" s="51"/>
-      <c r="M65" s="51"/>
-      <c r="N65" s="51"/>
-      <c r="O65" s="51"/>
-      <c r="P65" s="48"/>
+      <c r="J65" s="1">
+        <v>0.24754938321325901</v>
+      </c>
+      <c r="K65" s="1">
+        <v>0.24754938321325901</v>
+      </c>
+      <c r="L65" s="1">
+        <v>1</v>
+      </c>
+      <c r="M65" s="1">
+        <v>120.000000000876</v>
+      </c>
+      <c r="N65" s="1">
+        <v>45.138923567144403</v>
+      </c>
+      <c r="O65" s="4">
+        <v>6.5162497916437297E-10</v>
+      </c>
+      <c r="P65" s="44"/>
       <c r="Q65" s="31" t="s">
         <v>28</v>
       </c>
       <c r="R65" s="1">
-        <v>1.66799515271489</v>
+        <v>0.76645094993192597</v>
       </c>
       <c r="S65" s="1">
-        <v>0.15075896963304</v>
+        <v>2.07855368671831E-2</v>
       </c>
       <c r="T65" s="1">
-        <v>61.514580454863498</v>
+        <v>65.367738446356398</v>
       </c>
       <c r="U65" s="1">
-        <v>5.6605831266398603</v>
-      </c>
-      <c r="V65" s="6">
-        <v>2.49244059158382E-6</v>
+        <v>-9.8079800133367101</v>
+      </c>
+      <c r="V65" s="2">
+        <v>0</v>
       </c>
       <c r="W65" s="1"/>
-      <c r="X65" s="51"/>
-      <c r="Y65" s="51"/>
-      <c r="Z65" s="51"/>
-      <c r="AA65" s="51"/>
-      <c r="AB65" s="51"/>
+      <c r="X65" s="1">
+        <v>0.763423356833838</v>
+      </c>
+      <c r="Y65" s="1">
+        <v>3.3116417525027302E-2</v>
+      </c>
+      <c r="Z65" s="1">
+        <v>108.18375969063101</v>
+      </c>
+      <c r="AA65" s="1">
+        <v>-6.22290869573379</v>
+      </c>
+      <c r="AB65" s="6">
+        <v>5.6421459060373997E-8</v>
+      </c>
       <c r="AC65" s="35"/>
     </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A66" s="48"/>
+    <row r="66" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="44"/>
       <c r="B66" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C66" s="1">
-        <v>1.37366591368214E-2</v>
+        <v>3.4754513300900097E-2</v>
       </c>
       <c r="D66" s="1">
-        <v>1.37366591368214E-2</v>
+        <v>3.4754513300900097E-2</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
       </c>
       <c r="F66" s="1">
-        <v>57.458627570771498</v>
+        <v>66.433120314017799</v>
       </c>
       <c r="G66" s="1">
-        <v>0.75218820572632805</v>
-      </c>
-      <c r="H66" s="1">
-        <v>0.38939195861388898</v>
+        <v>19.740274284401199</v>
+      </c>
+      <c r="H66" s="4">
+        <v>3.4416590783058898E-5</v>
       </c>
       <c r="I66" s="1"/>
-      <c r="J66" s="51"/>
-      <c r="K66" s="51"/>
-      <c r="L66" s="51"/>
-      <c r="M66" s="51"/>
-      <c r="N66" s="51"/>
-      <c r="O66" s="51"/>
-      <c r="P66" s="48"/>
+      <c r="J66" s="1">
+        <v>1.81876043094546E-2</v>
+      </c>
+      <c r="K66" s="1">
+        <v>1.81876043094546E-2</v>
+      </c>
+      <c r="L66" s="1">
+        <v>1</v>
+      </c>
+      <c r="M66" s="1">
+        <v>120.000000000876</v>
+      </c>
+      <c r="N66" s="1">
+        <v>3.3163842710393201</v>
+      </c>
+      <c r="O66" s="3">
+        <v>7.1083850624745398E-2</v>
+      </c>
+      <c r="P66" s="44"/>
       <c r="Q66" s="31" t="s">
         <v>29</v>
       </c>
       <c r="R66" s="1">
-        <v>0.62197037241022901</v>
+        <v>0.83438570293307701</v>
       </c>
       <c r="S66" s="1">
-        <v>0.15294515378255399</v>
+        <v>3.3488447870679602E-2</v>
       </c>
       <c r="T66" s="1">
-        <v>21.507071906541999</v>
+        <v>30.8586362068467</v>
       </c>
       <c r="U66" s="1">
-        <v>-1.93108835287197</v>
-      </c>
-      <c r="V66" s="1">
-        <v>0.24503008385552599</v>
+        <v>-4.5112113615864997</v>
+      </c>
+      <c r="V66" s="2">
+        <v>4.8479551006386202E-4</v>
       </c>
       <c r="W66" s="1"/>
-      <c r="X66" s="51"/>
-      <c r="Y66" s="51"/>
-      <c r="Z66" s="51"/>
-      <c r="AA66" s="51"/>
-      <c r="AB66" s="51"/>
+      <c r="X66" s="1">
+        <v>0.86166002670741904</v>
+      </c>
+      <c r="Y66" s="1">
+        <v>3.6912066142334603E-2</v>
+      </c>
+      <c r="Z66" s="1">
+        <v>40.219886600149103</v>
+      </c>
+      <c r="AA66" s="1">
+        <v>-3.4757314012155298</v>
+      </c>
+      <c r="AB66" s="2">
+        <v>6.51926940610248E-3</v>
+      </c>
       <c r="AC66" s="35"/>
     </row>
     <row r="67" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="49"/>
+      <c r="A67" s="56"/>
       <c r="B67" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C67" s="58"/>
-      <c r="D67" s="58"/>
-      <c r="E67" s="58"/>
-      <c r="F67" s="58"/>
-      <c r="G67" s="58"/>
-      <c r="H67" s="58"/>
+      <c r="C67" s="50"/>
+      <c r="D67" s="50"/>
+      <c r="E67" s="50"/>
+      <c r="F67" s="50"/>
+      <c r="G67" s="50"/>
+      <c r="H67" s="50"/>
       <c r="I67" s="9"/>
-      <c r="J67" s="52"/>
-      <c r="K67" s="52"/>
-      <c r="L67" s="52"/>
-      <c r="M67" s="52"/>
-      <c r="N67" s="52"/>
-      <c r="O67" s="52"/>
-      <c r="P67" s="49"/>
+      <c r="J67" s="9">
+        <v>3.6858467316493698E-2</v>
+      </c>
+      <c r="K67" s="9">
+        <v>1.8429233658246901E-2</v>
+      </c>
+      <c r="L67" s="9">
+        <v>2</v>
+      </c>
+      <c r="M67" s="9">
+        <v>120.00000000096099</v>
+      </c>
+      <c r="N67" s="9">
+        <v>3.3604437171390802</v>
+      </c>
+      <c r="O67" s="19">
+        <v>3.8017401028842102E-2</v>
+      </c>
+      <c r="P67" s="56"/>
       <c r="Q67" s="32" t="s">
         <v>30</v>
       </c>
       <c r="R67" s="9">
-        <v>0.54852054109157</v>
+        <v>1.0135987535073001</v>
       </c>
       <c r="S67" s="9">
-        <v>0.138689132631619</v>
+        <v>4.3185412023769597E-2</v>
       </c>
       <c r="T67" s="9">
-        <v>23.424366595514599</v>
+        <v>33.635517105315301</v>
       </c>
       <c r="U67" s="9">
-        <v>-2.3751200702861999</v>
-      </c>
-      <c r="V67" s="42">
-        <v>0.109927732737644</v>
+        <v>0.31702372661387901</v>
+      </c>
+      <c r="V67" s="9">
+        <v>0.98877074255840203</v>
       </c>
       <c r="W67" s="9"/>
-      <c r="X67" s="52"/>
-      <c r="Y67" s="52"/>
-      <c r="Z67" s="52"/>
-      <c r="AA67" s="52"/>
-      <c r="AB67" s="52"/>
+      <c r="X67" s="9">
+        <v>0.77134016691240403</v>
+      </c>
+      <c r="Y67" s="9">
+        <v>3.3538164823331003E-2</v>
+      </c>
+      <c r="Z67" s="9">
+        <v>47.071378613344201</v>
+      </c>
+      <c r="AA67" s="9">
+        <v>-5.9711021561995201</v>
+      </c>
+      <c r="AB67" s="40">
+        <v>1.7432415013729501E-6</v>
+      </c>
       <c r="AC67" s="36"/>
     </row>
     <row r="68" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="47" t="s">
-        <v>18</v>
+      <c r="A68" s="55" t="s">
+        <v>26</v>
       </c>
       <c r="B68" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C68" s="8">
-        <v>10.9358082393645</v>
+        <v>1.1481734714944201</v>
       </c>
       <c r="D68" s="8">
-        <v>10.9358082393645</v>
+        <v>1.1481734714944201</v>
       </c>
       <c r="E68" s="8">
         <v>1</v>
       </c>
       <c r="F68" s="8">
-        <v>67.383586408567496</v>
+        <v>57.458627569308902</v>
       </c>
       <c r="G68" s="8">
-        <v>224.10765385608801</v>
+        <v>62.871367396090498</v>
       </c>
       <c r="H68" s="20">
-        <v>4.0821399088527701E-23</v>
+        <v>8.5554572534297795E-11</v>
       </c>
       <c r="I68" s="8"/>
-      <c r="J68" s="57" t="s">
+      <c r="J68" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="K68" s="57"/>
-      <c r="L68" s="57"/>
-      <c r="M68" s="57"/>
-      <c r="N68" s="57"/>
-      <c r="O68" s="57"/>
-      <c r="P68" s="47" t="s">
-        <v>41</v>
+      <c r="K68" s="51"/>
+      <c r="L68" s="51"/>
+      <c r="M68" s="51"/>
+      <c r="N68" s="51"/>
+      <c r="O68" s="51"/>
+      <c r="P68" s="55" t="s">
+        <v>26</v>
       </c>
       <c r="Q68" s="33" t="s">
         <v>27</v>
       </c>
       <c r="R68" s="13">
-        <v>5.1765111889964999</v>
+        <v>1.89134861613022</v>
       </c>
       <c r="S68" s="13">
-        <v>0.94034664213896701</v>
+        <v>0.21484737680985</v>
       </c>
       <c r="T68" s="13">
-        <v>66.362964163016898</v>
+        <v>62.148851945988298</v>
       </c>
       <c r="U68" s="13">
-        <v>9.0507731513692704</v>
-      </c>
-      <c r="V68" s="15">
-        <v>0</v>
+        <v>5.6102048802882196</v>
+      </c>
+      <c r="V68" s="41">
+        <v>2.9455467435157701E-6</v>
       </c>
       <c r="W68" s="13"/>
-      <c r="X68" s="56" t="s">
+      <c r="X68" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="Y68" s="56"/>
-      <c r="Z68" s="56"/>
-      <c r="AA68" s="56"/>
-      <c r="AB68" s="56"/>
+      <c r="Y68" s="46"/>
+      <c r="Z68" s="46"/>
+      <c r="AA68" s="46"/>
+      <c r="AB68" s="46"/>
       <c r="AC68" s="37"/>
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A69" s="48"/>
+      <c r="A69" s="44"/>
       <c r="B69" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C69" s="1">
-        <v>3.35549271707291E-3</v>
+        <v>9.2911254906166099E-2</v>
       </c>
       <c r="D69" s="1">
-        <v>3.35549271707291E-3</v>
+        <v>9.2911254906166099E-2</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
       </c>
       <c r="F69" s="1">
-        <v>19.7769266057722</v>
+        <v>14.883763903298201</v>
       </c>
       <c r="G69" s="1">
-        <v>6.8764153859934604E-2</v>
-      </c>
-      <c r="H69" s="1">
-        <v>0.79585674296255904</v>
+        <v>5.0876089610695701</v>
+      </c>
+      <c r="H69" s="2">
+        <v>3.9589780561885203E-2</v>
       </c>
       <c r="I69" s="1"/>
-      <c r="J69" s="51"/>
-      <c r="K69" s="51"/>
-      <c r="L69" s="51"/>
-      <c r="M69" s="51"/>
-      <c r="N69" s="51"/>
-      <c r="O69" s="51"/>
-      <c r="P69" s="48"/>
+      <c r="J69" s="47"/>
+      <c r="K69" s="47"/>
+      <c r="L69" s="47"/>
+      <c r="M69" s="47"/>
+      <c r="N69" s="47"/>
+      <c r="O69" s="47"/>
+      <c r="P69" s="44"/>
       <c r="Q69" s="31" t="s">
         <v>28</v>
       </c>
       <c r="R69" s="1">
-        <v>6.2310950070500803</v>
+        <v>1.66799515271489</v>
       </c>
       <c r="S69" s="1">
-        <v>0.90768007232021097</v>
+        <v>0.15075896963304</v>
       </c>
       <c r="T69" s="1">
-        <v>63.998198019156597</v>
+        <v>61.514580454863498</v>
       </c>
       <c r="U69" s="1">
-        <v>12.559615644592</v>
+        <v>5.6605831266398603</v>
       </c>
       <c r="V69" s="6">
-        <v>9.5166097224819201E-12</v>
+        <v>2.49244059158382E-6</v>
       </c>
       <c r="W69" s="1"/>
-      <c r="X69" s="51"/>
-      <c r="Y69" s="51"/>
-      <c r="Z69" s="51"/>
-      <c r="AA69" s="51"/>
-      <c r="AB69" s="51"/>
+      <c r="X69" s="47"/>
+      <c r="Y69" s="47"/>
+      <c r="Z69" s="47"/>
+      <c r="AA69" s="47"/>
+      <c r="AB69" s="47"/>
       <c r="AC69" s="35"/>
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A70" s="48"/>
+      <c r="A70" s="44"/>
       <c r="B70" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C70" s="1">
-        <v>3.11592623939527E-2</v>
+        <v>1.37366591368214E-2</v>
       </c>
       <c r="D70" s="1">
-        <v>3.11592623939527E-2</v>
+        <v>1.37366591368214E-2</v>
       </c>
       <c r="E70" s="1">
         <v>1</v>
       </c>
       <c r="F70" s="1">
-        <v>67.3835864091361</v>
+        <v>57.458627570771498</v>
       </c>
       <c r="G70" s="1">
-        <v>0.63854715062201595</v>
+        <v>0.75218820572632805</v>
       </c>
       <c r="H70" s="1">
-        <v>0.42704513346780898</v>
+        <v>0.38939195861388898</v>
       </c>
       <c r="I70" s="1"/>
-      <c r="J70" s="51"/>
-      <c r="K70" s="51"/>
-      <c r="L70" s="51"/>
-      <c r="M70" s="51"/>
-      <c r="N70" s="51"/>
-      <c r="O70" s="51"/>
-      <c r="P70" s="48"/>
+      <c r="J70" s="47"/>
+      <c r="K70" s="47"/>
+      <c r="L70" s="47"/>
+      <c r="M70" s="47"/>
+      <c r="N70" s="47"/>
+      <c r="O70" s="47"/>
+      <c r="P70" s="44"/>
       <c r="Q70" s="31" t="s">
         <v>29</v>
       </c>
       <c r="R70" s="1">
-        <v>0.87043623763491396</v>
+        <v>0.62197037241022901</v>
       </c>
       <c r="S70" s="1">
-        <v>0.179797852023692</v>
+        <v>0.15294515378255399</v>
       </c>
       <c r="T70" s="1">
-        <v>32.074175256944102</v>
+        <v>21.507071906541999</v>
       </c>
       <c r="U70" s="1">
-        <v>-0.67176777469391802</v>
+        <v>-1.93108835287197</v>
       </c>
       <c r="V70" s="1">
-        <v>0.90697094516344701</v>
+        <v>0.24503008385552599</v>
       </c>
       <c r="W70" s="1"/>
-      <c r="X70" s="51"/>
-      <c r="Y70" s="51"/>
-      <c r="Z70" s="51"/>
-      <c r="AA70" s="51"/>
-      <c r="AB70" s="51"/>
+      <c r="X70" s="47"/>
+      <c r="Y70" s="47"/>
+      <c r="Z70" s="47"/>
+      <c r="AA70" s="47"/>
+      <c r="AB70" s="47"/>
       <c r="AC70" s="35"/>
     </row>
     <row r="71" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="49"/>
+      <c r="A71" s="56"/>
       <c r="B71" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C71" s="58"/>
-      <c r="D71" s="58"/>
-      <c r="E71" s="58"/>
-      <c r="F71" s="58"/>
-      <c r="G71" s="58"/>
-      <c r="H71" s="58"/>
+      <c r="C71" s="50"/>
+      <c r="D71" s="50"/>
+      <c r="E71" s="50"/>
+      <c r="F71" s="50"/>
+      <c r="G71" s="50"/>
+      <c r="H71" s="50"/>
       <c r="I71" s="9"/>
-      <c r="J71" s="52"/>
-      <c r="K71" s="52"/>
-      <c r="L71" s="52"/>
-      <c r="M71" s="52"/>
-      <c r="N71" s="52"/>
-      <c r="O71" s="52"/>
-      <c r="P71" s="49"/>
+      <c r="J71" s="48"/>
+      <c r="K71" s="48"/>
+      <c r="L71" s="48"/>
+      <c r="M71" s="48"/>
+      <c r="N71" s="48"/>
+      <c r="O71" s="48"/>
+      <c r="P71" s="56"/>
       <c r="Q71" s="32" t="s">
         <v>30</v>
       </c>
       <c r="R71" s="9">
-        <v>1.0477657047880899</v>
+        <v>0.54852054109157</v>
       </c>
       <c r="S71" s="9">
-        <v>0.22829484029702099</v>
+        <v>0.138689132631619</v>
       </c>
       <c r="T71" s="9">
-        <v>33.7659320002318</v>
+        <v>23.424366595514599</v>
       </c>
       <c r="U71" s="9">
-        <v>0.21414739088603499</v>
-      </c>
-      <c r="V71" s="9">
-        <v>0.99646171487333202</v>
+        <v>-2.3751200702861999</v>
+      </c>
+      <c r="V71" s="42">
+        <v>0.109927732737644</v>
       </c>
       <c r="W71" s="9"/>
-      <c r="X71" s="52"/>
-      <c r="Y71" s="52"/>
-      <c r="Z71" s="52"/>
-      <c r="AA71" s="52"/>
-      <c r="AB71" s="52"/>
+      <c r="X71" s="48"/>
+      <c r="Y71" s="48"/>
+      <c r="Z71" s="48"/>
+      <c r="AA71" s="48"/>
+      <c r="AB71" s="48"/>
       <c r="AC71" s="36"/>
     </row>
     <row r="72" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="47" t="s">
-        <v>16</v>
+      <c r="A72" s="55" t="s">
+        <v>18</v>
       </c>
       <c r="B72" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C72" s="57" t="s">
+      <c r="C72" s="8">
+        <v>10.9358082393645</v>
+      </c>
+      <c r="D72" s="8">
+        <v>10.9358082393645</v>
+      </c>
+      <c r="E72" s="8">
+        <v>1</v>
+      </c>
+      <c r="F72" s="8">
+        <v>67.383586408567496</v>
+      </c>
+      <c r="G72" s="8">
+        <v>224.10765385608801</v>
+      </c>
+      <c r="H72" s="20">
+        <v>4.0821399088527701E-23</v>
+      </c>
+      <c r="I72" s="8"/>
+      <c r="J72" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="D72" s="57"/>
-      <c r="E72" s="57"/>
-      <c r="F72" s="57"/>
-      <c r="G72" s="57"/>
-      <c r="H72" s="57"/>
-      <c r="I72" s="8"/>
-      <c r="J72" s="8">
-        <v>7.7190184322692705E-4</v>
-      </c>
-      <c r="K72" s="8">
-        <v>7.7190184322692705E-4</v>
-      </c>
-      <c r="L72" s="8">
-        <v>1</v>
-      </c>
-      <c r="M72" s="8">
-        <v>109.162762099391</v>
-      </c>
-      <c r="N72" s="8">
-        <v>0.132778478118667</v>
-      </c>
-      <c r="O72" s="8">
-        <v>0.71627332791354703</v>
-      </c>
-      <c r="P72" s="47" t="s">
-        <v>52</v>
+      <c r="K72" s="51"/>
+      <c r="L72" s="51"/>
+      <c r="M72" s="51"/>
+      <c r="N72" s="51"/>
+      <c r="O72" s="51"/>
+      <c r="P72" s="55" t="s">
+        <v>41</v>
       </c>
       <c r="Q72" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="R72" s="56" t="s">
+      <c r="R72" s="13">
+        <v>5.1765111889964999</v>
+      </c>
+      <c r="S72" s="13">
+        <v>0.94034664213896701</v>
+      </c>
+      <c r="T72" s="13">
+        <v>66.362964163016898</v>
+      </c>
+      <c r="U72" s="13">
+        <v>9.0507731513692704</v>
+      </c>
+      <c r="V72" s="15">
+        <v>0</v>
+      </c>
+      <c r="W72" s="13"/>
+      <c r="X72" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="S72" s="56"/>
-      <c r="T72" s="56"/>
-      <c r="U72" s="56"/>
-      <c r="V72" s="56"/>
-      <c r="W72" s="13"/>
-      <c r="X72" s="13">
-        <v>0.96246045193694896</v>
-      </c>
-      <c r="Y72" s="13">
-        <v>4.2599246116571399E-2</v>
-      </c>
-      <c r="Z72" s="13">
-        <v>108.962352968753</v>
-      </c>
-      <c r="AA72" s="13">
-        <v>-0.86447428938717796</v>
-      </c>
-      <c r="AB72" s="13">
-        <v>0.82311476080453805</v>
-      </c>
-      <c r="AC72" s="13"/>
+      <c r="Y72" s="46"/>
+      <c r="Z72" s="46"/>
+      <c r="AA72" s="46"/>
+      <c r="AB72" s="46"/>
+      <c r="AC72" s="37"/>
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A73" s="48"/>
+      <c r="A73" s="44"/>
       <c r="B73" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C73" s="51"/>
-      <c r="D73" s="51"/>
-      <c r="E73" s="51"/>
-      <c r="F73" s="51"/>
-      <c r="G73" s="51"/>
-      <c r="H73" s="51"/>
+      <c r="C73" s="1">
+        <v>3.35549271707291E-3</v>
+      </c>
+      <c r="D73" s="1">
+        <v>3.35549271707291E-3</v>
+      </c>
+      <c r="E73" s="1">
+        <v>1</v>
+      </c>
+      <c r="F73" s="1">
+        <v>19.7769266057722</v>
+      </c>
+      <c r="G73" s="1">
+        <v>6.8764153859934604E-2</v>
+      </c>
+      <c r="H73" s="1">
+        <v>0.79585674296255904</v>
+      </c>
       <c r="I73" s="1"/>
-      <c r="J73" s="1">
-        <v>0.26383928794443301</v>
-      </c>
-      <c r="K73" s="1">
-        <v>0.26383928794443301</v>
-      </c>
-      <c r="L73" s="1">
-        <v>1</v>
-      </c>
-      <c r="M73" s="1">
-        <v>14.2035557007019</v>
-      </c>
-      <c r="N73" s="1">
-        <v>45.384240792485897</v>
-      </c>
-      <c r="O73" s="4">
-        <v>8.8402488312841299E-6</v>
-      </c>
-      <c r="P73" s="48"/>
+      <c r="J73" s="47"/>
+      <c r="K73" s="47"/>
+      <c r="L73" s="47"/>
+      <c r="M73" s="47"/>
+      <c r="N73" s="47"/>
+      <c r="O73" s="47"/>
+      <c r="P73" s="44"/>
       <c r="Q73" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="R73" s="51"/>
-      <c r="S73" s="51"/>
-      <c r="T73" s="51"/>
-      <c r="U73" s="51"/>
-      <c r="V73" s="51"/>
+      <c r="R73" s="1">
+        <v>6.2310950070500803</v>
+      </c>
+      <c r="S73" s="1">
+        <v>0.90768007232021097</v>
+      </c>
+      <c r="T73" s="1">
+        <v>63.998198019156597</v>
+      </c>
+      <c r="U73" s="1">
+        <v>12.559615644592</v>
+      </c>
+      <c r="V73" s="6">
+        <v>9.5166097224819201E-12</v>
+      </c>
       <c r="W73" s="1"/>
-      <c r="X73" s="1">
-        <v>1.0284695041493801</v>
-      </c>
-      <c r="Y73" s="1">
-        <v>4.5549624327727703E-2</v>
-      </c>
-      <c r="Z73" s="1">
-        <v>107.45069910040201</v>
-      </c>
-      <c r="AA73" s="1">
-        <v>0.63383549084379798</v>
-      </c>
-      <c r="AB73" s="1">
-        <v>0.92089225333951297</v>
-      </c>
-      <c r="AC73" s="1"/>
+      <c r="X73" s="47"/>
+      <c r="Y73" s="47"/>
+      <c r="Z73" s="47"/>
+      <c r="AA73" s="47"/>
+      <c r="AB73" s="47"/>
+      <c r="AC73" s="35"/>
     </row>
     <row r="74" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A74" s="48"/>
+      <c r="A74" s="44"/>
       <c r="B74" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C74" s="51"/>
-      <c r="D74" s="51"/>
-      <c r="E74" s="51"/>
-      <c r="F74" s="51"/>
-      <c r="G74" s="51"/>
-      <c r="H74" s="51"/>
+      <c r="C74" s="1">
+        <v>3.11592623939527E-2</v>
+      </c>
+      <c r="D74" s="1">
+        <v>3.11592623939527E-2</v>
+      </c>
+      <c r="E74" s="1">
+        <v>1</v>
+      </c>
+      <c r="F74" s="1">
+        <v>67.3835864091361</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0.63854715062201595</v>
+      </c>
+      <c r="H74" s="1">
+        <v>0.42704513346780898</v>
+      </c>
       <c r="I74" s="1"/>
-      <c r="J74" s="1">
-        <v>6.5298294112546198E-3</v>
-      </c>
-      <c r="K74" s="1">
-        <v>6.5298294112546198E-3</v>
-      </c>
-      <c r="L74" s="1">
-        <v>1</v>
-      </c>
-      <c r="M74" s="1">
-        <v>108.83042432675499</v>
-      </c>
-      <c r="N74" s="1">
-        <v>1.12322676673025</v>
-      </c>
-      <c r="O74" s="1">
-        <v>0.29157119540922299</v>
-      </c>
-      <c r="P74" s="48"/>
+      <c r="J74" s="47"/>
+      <c r="K74" s="47"/>
+      <c r="L74" s="47"/>
+      <c r="M74" s="47"/>
+      <c r="N74" s="47"/>
+      <c r="O74" s="47"/>
+      <c r="P74" s="44"/>
       <c r="Q74" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="R74" s="51"/>
-      <c r="S74" s="51"/>
-      <c r="T74" s="51"/>
-      <c r="U74" s="51"/>
-      <c r="V74" s="51"/>
+      <c r="R74" s="1">
+        <v>0.87043623763491396</v>
+      </c>
+      <c r="S74" s="1">
+        <v>0.179797852023692</v>
+      </c>
+      <c r="T74" s="1">
+        <v>32.074175256944102</v>
+      </c>
+      <c r="U74" s="1">
+        <v>-0.67176777469391802</v>
+      </c>
+      <c r="V74" s="1">
+        <v>0.90697094516344701</v>
+      </c>
       <c r="W74" s="1"/>
-      <c r="X74" s="1">
-        <v>0.59461928503453898</v>
-      </c>
-      <c r="Y74" s="1">
-        <v>4.7131673588795997E-2</v>
-      </c>
-      <c r="Z74" s="1">
-        <v>19.0015683617343</v>
-      </c>
-      <c r="AA74" s="1">
-        <v>-6.5582921084410204</v>
-      </c>
-      <c r="AB74" s="6">
-        <v>1.5527023819905699E-5</v>
-      </c>
-      <c r="AC74" s="1"/>
+      <c r="X74" s="47"/>
+      <c r="Y74" s="47"/>
+      <c r="Z74" s="47"/>
+      <c r="AA74" s="47"/>
+      <c r="AB74" s="47"/>
+      <c r="AC74" s="35"/>
     </row>
     <row r="75" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="49"/>
+      <c r="A75" s="56"/>
       <c r="B75" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C75" s="52"/>
-      <c r="D75" s="52"/>
-      <c r="E75" s="52"/>
-      <c r="F75" s="52"/>
-      <c r="G75" s="52"/>
-      <c r="H75" s="52"/>
+      <c r="C75" s="50"/>
+      <c r="D75" s="50"/>
+      <c r="E75" s="50"/>
+      <c r="F75" s="50"/>
+      <c r="G75" s="50"/>
+      <c r="H75" s="50"/>
       <c r="I75" s="9"/>
-      <c r="J75" s="9">
-        <v>7.3489818378573097E-3</v>
-      </c>
-      <c r="K75" s="9">
-        <v>3.6744909189286501E-3</v>
-      </c>
-      <c r="L75" s="9">
-        <v>2</v>
-      </c>
-      <c r="M75" s="9">
-        <v>108.867449329857</v>
-      </c>
-      <c r="N75" s="9">
-        <v>0.63206652031892696</v>
-      </c>
-      <c r="O75" s="9">
-        <v>0.53343128963438502</v>
-      </c>
-      <c r="P75" s="49"/>
+      <c r="J75" s="48"/>
+      <c r="K75" s="48"/>
+      <c r="L75" s="48"/>
+      <c r="M75" s="48"/>
+      <c r="N75" s="48"/>
+      <c r="O75" s="48"/>
+      <c r="P75" s="56"/>
       <c r="Q75" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="R75" s="52"/>
-      <c r="S75" s="52"/>
-      <c r="T75" s="52"/>
-      <c r="U75" s="52"/>
-      <c r="V75" s="52"/>
+      <c r="R75" s="9">
+        <v>1.0477657047880899</v>
+      </c>
+      <c r="S75" s="9">
+        <v>0.22829484029702099</v>
+      </c>
+      <c r="T75" s="9">
+        <v>33.7659320002318</v>
+      </c>
+      <c r="U75" s="9">
+        <v>0.21414739088603499</v>
+      </c>
+      <c r="V75" s="9">
+        <v>0.99646171487333202</v>
+      </c>
       <c r="W75" s="9"/>
-      <c r="X75" s="9">
-        <v>0.63540044685097696</v>
-      </c>
-      <c r="Y75" s="9">
-        <v>4.9887652727016403E-2</v>
-      </c>
-      <c r="Z75" s="9">
-        <v>18.992283236430701</v>
-      </c>
-      <c r="AA75" s="9">
-        <v>-5.7760586849782101</v>
-      </c>
-      <c r="AB75" s="40">
-        <v>7.9364409904192397E-5</v>
-      </c>
-      <c r="AC75" s="9"/>
+      <c r="X75" s="48"/>
+      <c r="Y75" s="48"/>
+      <c r="Z75" s="48"/>
+      <c r="AA75" s="48"/>
+      <c r="AB75" s="48"/>
+      <c r="AC75" s="36"/>
     </row>
     <row r="76" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="47" t="s">
-        <v>17</v>
+      <c r="A76" s="55" t="s">
+        <v>16</v>
       </c>
       <c r="B76" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C76" s="8">
-        <v>1628.5396493139699</v>
-      </c>
-      <c r="D76" s="8">
-        <v>1628.5396493139699</v>
-      </c>
-      <c r="E76" s="8">
-        <v>1</v>
-      </c>
-      <c r="F76" s="8">
-        <v>62.368989869052001</v>
-      </c>
-      <c r="G76" s="8">
-        <v>132.99387365734901</v>
-      </c>
-      <c r="H76" s="20">
-        <v>4.1643897411378698E-17</v>
-      </c>
+      <c r="C76" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="D76" s="51"/>
+      <c r="E76" s="51"/>
+      <c r="F76" s="51"/>
+      <c r="G76" s="51"/>
+      <c r="H76" s="51"/>
       <c r="I76" s="8"/>
-      <c r="J76" s="57" t="s">
-        <v>31</v>
-      </c>
-      <c r="K76" s="57"/>
-      <c r="L76" s="57"/>
-      <c r="M76" s="57"/>
-      <c r="N76" s="57"/>
-      <c r="O76" s="57"/>
-      <c r="P76" s="47" t="s">
-        <v>38</v>
+      <c r="J76" s="8">
+        <v>7.7190184322692705E-4</v>
+      </c>
+      <c r="K76" s="8">
+        <v>7.7190184322692705E-4</v>
+      </c>
+      <c r="L76" s="8">
+        <v>1</v>
+      </c>
+      <c r="M76" s="8">
+        <v>109.162762099391</v>
+      </c>
+      <c r="N76" s="8">
+        <v>0.132778478118667</v>
+      </c>
+      <c r="O76" s="8">
+        <v>0.71627332791354703</v>
+      </c>
+      <c r="P76" s="55" t="s">
+        <v>52</v>
       </c>
       <c r="Q76" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="R76" s="13">
-        <v>-8.3740558709758908</v>
-      </c>
-      <c r="S76" s="13">
-        <v>1.2709682312281201</v>
-      </c>
-      <c r="T76" s="13">
-        <v>65.411191277396298</v>
-      </c>
-      <c r="U76" s="13">
-        <v>-6.5887216259403703</v>
-      </c>
-      <c r="V76" s="41">
-        <v>5.3435041391658398E-8</v>
-      </c>
+      <c r="R76" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="S76" s="46"/>
+      <c r="T76" s="46"/>
+      <c r="U76" s="46"/>
+      <c r="V76" s="46"/>
       <c r="W76" s="13"/>
-      <c r="X76" s="56" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y76" s="56"/>
-      <c r="Z76" s="56"/>
-      <c r="AA76" s="56"/>
-      <c r="AB76" s="56"/>
+      <c r="X76" s="13">
+        <v>0.96246045193694896</v>
+      </c>
+      <c r="Y76" s="13">
+        <v>4.2599246116571399E-2</v>
+      </c>
+      <c r="Z76" s="13">
+        <v>108.962352968753</v>
+      </c>
+      <c r="AA76" s="13">
+        <v>-0.86447428938717796</v>
+      </c>
+      <c r="AB76" s="13">
+        <v>0.82311476080453805</v>
+      </c>
       <c r="AC76" s="13"/>
     </row>
     <row r="77" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A77" s="48"/>
+      <c r="A77" s="44"/>
       <c r="B77" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C77" s="1">
-        <v>230.82876413714999</v>
-      </c>
-      <c r="D77" s="1">
-        <v>230.82876413714999</v>
-      </c>
-      <c r="E77" s="1">
-        <v>1</v>
-      </c>
-      <c r="F77" s="1">
-        <v>16.563800911315401</v>
-      </c>
-      <c r="G77" s="1">
-        <v>18.8505152497026</v>
-      </c>
-      <c r="H77" s="2">
-        <v>4.6861954719532999E-4</v>
-      </c>
+      <c r="C77" s="47"/>
+      <c r="D77" s="47"/>
+      <c r="E77" s="47"/>
+      <c r="F77" s="47"/>
+      <c r="G77" s="47"/>
+      <c r="H77" s="47"/>
       <c r="I77" s="1"/>
-      <c r="J77" s="51"/>
-      <c r="K77" s="51"/>
-      <c r="L77" s="51"/>
-      <c r="M77" s="51"/>
-      <c r="N77" s="51"/>
-      <c r="O77" s="51"/>
-      <c r="P77" s="48"/>
+      <c r="J77" s="1">
+        <v>0.26383928794443301</v>
+      </c>
+      <c r="K77" s="1">
+        <v>0.26383928794443301</v>
+      </c>
+      <c r="L77" s="1">
+        <v>1</v>
+      </c>
+      <c r="M77" s="1">
+        <v>14.2035557007019</v>
+      </c>
+      <c r="N77" s="1">
+        <v>45.384240792485897</v>
+      </c>
+      <c r="O77" s="4">
+        <v>8.8402488312841299E-6</v>
+      </c>
+      <c r="P77" s="44"/>
       <c r="Q77" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="R77" s="1">
-        <v>-10.150777804234499</v>
-      </c>
-      <c r="S77" s="1">
-        <v>0.98850514491144503</v>
-      </c>
-      <c r="T77" s="1">
-        <v>63.624905985334699</v>
-      </c>
-      <c r="U77" s="1">
-        <v>-10.2688163602263</v>
-      </c>
-      <c r="V77" s="6">
-        <v>1.2034151453121901E-11</v>
-      </c>
+      <c r="R77" s="47"/>
+      <c r="S77" s="47"/>
+      <c r="T77" s="47"/>
+      <c r="U77" s="47"/>
+      <c r="V77" s="47"/>
       <c r="W77" s="1"/>
-      <c r="X77" s="51"/>
-      <c r="Y77" s="51"/>
-      <c r="Z77" s="51"/>
-      <c r="AA77" s="51"/>
-      <c r="AB77" s="51"/>
+      <c r="X77" s="1">
+        <v>1.0284695041493801</v>
+      </c>
+      <c r="Y77" s="1">
+        <v>4.5549624327727703E-2</v>
+      </c>
+      <c r="Z77" s="1">
+        <v>107.45069910040201</v>
+      </c>
+      <c r="AA77" s="1">
+        <v>0.63383549084379798</v>
+      </c>
+      <c r="AB77" s="1">
+        <v>0.92089225333951297</v>
+      </c>
       <c r="AC77" s="1"/>
     </row>
-    <row r="78" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="48"/>
+    <row r="78" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A78" s="44"/>
       <c r="B78" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C78" s="1">
-        <v>14.980580034264699</v>
-      </c>
-      <c r="D78" s="1">
-        <v>14.980580034264699</v>
-      </c>
-      <c r="E78" s="1">
-        <v>1</v>
-      </c>
-      <c r="F78" s="1">
-        <v>62.368989867379298</v>
-      </c>
-      <c r="G78" s="1">
-        <v>1.22338155489803</v>
-      </c>
-      <c r="H78" s="1">
-        <v>0.27294624360005199</v>
-      </c>
+      <c r="C78" s="47"/>
+      <c r="D78" s="47"/>
+      <c r="E78" s="47"/>
+      <c r="F78" s="47"/>
+      <c r="G78" s="47"/>
+      <c r="H78" s="47"/>
       <c r="I78" s="1"/>
-      <c r="J78" s="51"/>
-      <c r="K78" s="51"/>
-      <c r="L78" s="51"/>
-      <c r="M78" s="51"/>
-      <c r="N78" s="51"/>
-      <c r="O78" s="51"/>
-      <c r="P78" s="48"/>
+      <c r="J78" s="1">
+        <v>6.5298294112546198E-3</v>
+      </c>
+      <c r="K78" s="1">
+        <v>6.5298294112546198E-3</v>
+      </c>
+      <c r="L78" s="1">
+        <v>1</v>
+      </c>
+      <c r="M78" s="1">
+        <v>108.83042432675499</v>
+      </c>
+      <c r="N78" s="1">
+        <v>1.12322676673025</v>
+      </c>
+      <c r="O78" s="1">
+        <v>0.29157119540922299</v>
+      </c>
+      <c r="P78" s="44"/>
       <c r="Q78" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="R78" s="1">
-        <v>-7.86992683231641</v>
-      </c>
-      <c r="S78" s="1">
-        <v>2.1339595960546198</v>
-      </c>
-      <c r="T78" s="1">
-        <v>23.836498703257799</v>
-      </c>
-      <c r="U78" s="1">
-        <v>-3.6879455669482901</v>
-      </c>
-      <c r="V78" s="2">
-        <v>5.9764406718529903E-3</v>
-      </c>
+      <c r="R78" s="47"/>
+      <c r="S78" s="47"/>
+      <c r="T78" s="47"/>
+      <c r="U78" s="47"/>
+      <c r="V78" s="47"/>
       <c r="W78" s="1"/>
-      <c r="X78" s="51"/>
-      <c r="Y78" s="51"/>
-      <c r="Z78" s="51"/>
-      <c r="AA78" s="51"/>
-      <c r="AB78" s="51"/>
+      <c r="X78" s="1">
+        <v>0.59461928503453898</v>
+      </c>
+      <c r="Y78" s="1">
+        <v>4.7131673588795997E-2</v>
+      </c>
+      <c r="Z78" s="1">
+        <v>19.0015683617343</v>
+      </c>
+      <c r="AA78" s="1">
+        <v>-6.5582921084410204</v>
+      </c>
+      <c r="AB78" s="6">
+        <v>1.5527023819905699E-5</v>
+      </c>
       <c r="AC78" s="1"/>
     </row>
     <row r="79" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="49"/>
+      <c r="A79" s="56"/>
       <c r="B79" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C79" s="58"/>
-      <c r="D79" s="58"/>
-      <c r="E79" s="58"/>
-      <c r="F79" s="58"/>
-      <c r="G79" s="58"/>
-      <c r="H79" s="58"/>
+      <c r="C79" s="48"/>
+      <c r="D79" s="48"/>
+      <c r="E79" s="48"/>
+      <c r="F79" s="48"/>
+      <c r="G79" s="48"/>
+      <c r="H79" s="48"/>
       <c r="I79" s="9"/>
-      <c r="J79" s="52"/>
-      <c r="K79" s="52"/>
-      <c r="L79" s="52"/>
-      <c r="M79" s="52"/>
-      <c r="N79" s="52"/>
-      <c r="O79" s="52"/>
-      <c r="P79" s="49"/>
+      <c r="J79" s="9">
+        <v>7.3489818378573097E-3</v>
+      </c>
+      <c r="K79" s="9">
+        <v>3.6744909189286501E-3</v>
+      </c>
+      <c r="L79" s="9">
+        <v>2</v>
+      </c>
+      <c r="M79" s="9">
+        <v>108.867449329857</v>
+      </c>
+      <c r="N79" s="9">
+        <v>0.63206652031892696</v>
+      </c>
+      <c r="O79" s="9">
+        <v>0.53343128963438502</v>
+      </c>
+      <c r="P79" s="56"/>
       <c r="Q79" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="R79" s="9">
-        <v>-9.6466487655750495</v>
-      </c>
-      <c r="S79" s="9">
-        <v>2.2161369274627698</v>
-      </c>
-      <c r="T79" s="9">
-        <v>26.344347603992698</v>
-      </c>
-      <c r="U79" s="9">
-        <v>-4.3529118828498401</v>
-      </c>
-      <c r="V79" s="19">
-        <v>9.8108965488741305E-4</v>
-      </c>
+      <c r="R79" s="48"/>
+      <c r="S79" s="48"/>
+      <c r="T79" s="48"/>
+      <c r="U79" s="48"/>
+      <c r="V79" s="48"/>
       <c r="W79" s="9"/>
-      <c r="X79" s="52"/>
-      <c r="Y79" s="52"/>
-      <c r="Z79" s="52"/>
-      <c r="AA79" s="52"/>
-      <c r="AB79" s="52"/>
+      <c r="X79" s="9">
+        <v>0.63540044685097696</v>
+      </c>
+      <c r="Y79" s="9">
+        <v>4.9887652727016403E-2</v>
+      </c>
+      <c r="Z79" s="9">
+        <v>18.992283236430701</v>
+      </c>
+      <c r="AA79" s="9">
+        <v>-5.7760586849782101</v>
+      </c>
+      <c r="AB79" s="40">
+        <v>7.9364409904192397E-5</v>
+      </c>
       <c r="AC79" s="9"/>
     </row>
     <row r="80" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="47" t="s">
-        <v>19</v>
+      <c r="A80" s="55" t="s">
+        <v>17</v>
       </c>
       <c r="B80" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C80" s="8">
-        <v>5.0694430563116102</v>
+        <v>1628.5396493139699</v>
       </c>
       <c r="D80" s="8">
-        <v>5.0694430563116102</v>
+        <v>1628.5396493139699</v>
       </c>
       <c r="E80" s="8">
         <v>1</v>
       </c>
       <c r="F80" s="8">
-        <v>67.962550016506</v>
+        <v>62.368989869052001</v>
       </c>
       <c r="G80" s="8">
-        <v>123.23450697288</v>
-      </c>
-      <c r="H80" s="29">
-        <v>6.4779999000469503E-17</v>
+        <v>132.99387365734901</v>
+      </c>
+      <c r="H80" s="20">
+        <v>4.1643897411378698E-17</v>
       </c>
       <c r="I80" s="8"/>
-      <c r="J80" s="57" t="s">
+      <c r="J80" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="K80" s="57"/>
-      <c r="L80" s="57"/>
-      <c r="M80" s="57"/>
-      <c r="N80" s="57"/>
-      <c r="O80" s="57"/>
-      <c r="P80" s="47" t="s">
-        <v>39</v>
+      <c r="K80" s="51"/>
+      <c r="L80" s="51"/>
+      <c r="M80" s="51"/>
+      <c r="N80" s="51"/>
+      <c r="O80" s="51"/>
+      <c r="P80" s="55" t="s">
+        <v>38</v>
       </c>
       <c r="Q80" s="33" t="s">
         <v>27</v>
       </c>
       <c r="R80" s="13">
-        <v>2.9177136151243199</v>
+        <v>-8.3740558709758908</v>
       </c>
       <c r="S80" s="13">
-        <v>0.48713627626251899</v>
+        <v>1.2709682312281201</v>
       </c>
       <c r="T80" s="13">
-        <v>64.430590038735005</v>
+        <v>65.411191277396298</v>
       </c>
       <c r="U80" s="13">
-        <v>6.4135823376221897</v>
+        <v>-6.5887216259403703</v>
       </c>
       <c r="V80" s="41">
-        <v>1.14162453601629E-7</v>
+        <v>5.3435041391658398E-8</v>
       </c>
       <c r="W80" s="13"/>
-      <c r="X80" s="56" t="s">
+      <c r="X80" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="Y80" s="56"/>
-      <c r="Z80" s="56"/>
-      <c r="AA80" s="56"/>
-      <c r="AB80" s="56"/>
-      <c r="AC80" s="34"/>
+      <c r="Y80" s="46"/>
+      <c r="Z80" s="46"/>
+      <c r="AA80" s="46"/>
+      <c r="AB80" s="46"/>
+      <c r="AC80" s="13"/>
     </row>
     <row r="81" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A81" s="48"/>
+      <c r="A81" s="44"/>
       <c r="B81" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C81" s="1">
-        <v>0.289278337816473</v>
+        <v>230.82876413714999</v>
       </c>
       <c r="D81" s="1">
-        <v>0.289278337816473</v>
+        <v>230.82876413714999</v>
       </c>
       <c r="E81" s="1">
         <v>1</v>
       </c>
       <c r="F81" s="1">
-        <v>23.487577951072801</v>
+        <v>16.563800911315401</v>
       </c>
       <c r="G81" s="1">
-        <v>7.0321478992377502</v>
+        <v>18.8505152497026</v>
       </c>
       <c r="H81" s="2">
-        <v>1.4106574908243E-2</v>
+        <v>4.6861954719532999E-4</v>
       </c>
       <c r="I81" s="1"/>
-      <c r="J81" s="51"/>
-      <c r="K81" s="51"/>
-      <c r="L81" s="51"/>
-      <c r="M81" s="51"/>
-      <c r="N81" s="51"/>
-      <c r="O81" s="51"/>
-      <c r="P81" s="48"/>
+      <c r="J81" s="47"/>
+      <c r="K81" s="47"/>
+      <c r="L81" s="47"/>
+      <c r="M81" s="47"/>
+      <c r="N81" s="47"/>
+      <c r="O81" s="47"/>
+      <c r="P81" s="44"/>
       <c r="Q81" s="31" t="s">
         <v>28</v>
       </c>
       <c r="R81" s="1">
-        <v>3.7301111316362499</v>
+        <v>-10.150777804234499</v>
       </c>
       <c r="S81" s="1">
-        <v>0.51018600017349802</v>
+        <v>0.98850514491144503</v>
       </c>
       <c r="T81" s="1">
-        <v>62.737652543129002</v>
+        <v>63.624905985334699</v>
       </c>
       <c r="U81" s="1">
-        <v>9.6248429744420907</v>
+        <v>-10.2688163602263</v>
       </c>
       <c r="V81" s="6">
-        <v>1.6875612018907301E-11</v>
+        <v>1.2034151453121901E-11</v>
       </c>
       <c r="W81" s="1"/>
-      <c r="X81" s="51"/>
-      <c r="Y81" s="51"/>
-      <c r="Z81" s="51"/>
-      <c r="AA81" s="51"/>
-      <c r="AB81" s="51"/>
-      <c r="AC81" s="35"/>
-    </row>
-    <row r="82" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A82" s="48"/>
+      <c r="X81" s="47"/>
+      <c r="Y81" s="47"/>
+      <c r="Z81" s="47"/>
+      <c r="AA81" s="47"/>
+      <c r="AB81" s="47"/>
+      <c r="AC81" s="1"/>
+    </row>
+    <row r="82" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="44"/>
       <c r="B82" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C82" s="1">
-        <v>5.3673365621619298E-2</v>
+        <v>14.980580034264699</v>
       </c>
       <c r="D82" s="1">
-        <v>5.3673365621619298E-2</v>
+        <v>14.980580034264699</v>
       </c>
       <c r="E82" s="1">
         <v>1</v>
       </c>
       <c r="F82" s="1">
-        <v>67.962550017652504</v>
+        <v>62.368989867379298</v>
       </c>
       <c r="G82" s="1">
-        <v>1.30476083397765</v>
+        <v>1.22338155489803</v>
       </c>
       <c r="H82" s="1">
-        <v>0.25735376158301099</v>
+        <v>0.27294624360005199</v>
       </c>
       <c r="I82" s="1"/>
-      <c r="J82" s="51"/>
-      <c r="K82" s="51"/>
-      <c r="L82" s="51"/>
-      <c r="M82" s="51"/>
-      <c r="N82" s="51"/>
-      <c r="O82" s="51"/>
-      <c r="P82" s="48"/>
+      <c r="J82" s="47"/>
+      <c r="K82" s="47"/>
+      <c r="L82" s="47"/>
+      <c r="M82" s="47"/>
+      <c r="N82" s="47"/>
+      <c r="O82" s="47"/>
+      <c r="P82" s="44"/>
       <c r="Q82" s="31" t="s">
         <v>29</v>
       </c>
       <c r="R82" s="1">
-        <v>1.37224989644095</v>
+        <v>-7.86992683231641</v>
       </c>
       <c r="S82" s="1">
-        <v>0.26567786472642402</v>
+        <v>2.1339595960546198</v>
       </c>
       <c r="T82" s="1">
-        <v>31.114142203224599</v>
+        <v>23.836498703257799</v>
       </c>
       <c r="U82" s="1">
-        <v>1.6345010468947201</v>
-      </c>
-      <c r="V82" s="1">
-        <v>0.37476551599412999</v>
+        <v>-3.6879455669482901</v>
+      </c>
+      <c r="V82" s="2">
+        <v>5.9764406718529903E-3</v>
       </c>
       <c r="W82" s="1"/>
-      <c r="X82" s="51"/>
-      <c r="Y82" s="51"/>
-      <c r="Z82" s="51"/>
-      <c r="AA82" s="51"/>
-      <c r="AB82" s="51"/>
-      <c r="AC82" s="35"/>
+      <c r="X82" s="47"/>
+      <c r="Y82" s="47"/>
+      <c r="Z82" s="47"/>
+      <c r="AA82" s="47"/>
+      <c r="AB82" s="47"/>
+      <c r="AC82" s="1"/>
     </row>
     <row r="83" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="49"/>
+      <c r="A83" s="56"/>
       <c r="B83" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C83" s="58"/>
-      <c r="D83" s="58"/>
-      <c r="E83" s="58"/>
-      <c r="F83" s="58"/>
-      <c r="G83" s="58"/>
-      <c r="H83" s="58"/>
+      <c r="C83" s="50"/>
+      <c r="D83" s="50"/>
+      <c r="E83" s="50"/>
+      <c r="F83" s="50"/>
+      <c r="G83" s="50"/>
+      <c r="H83" s="50"/>
       <c r="I83" s="9"/>
-      <c r="J83" s="52"/>
-      <c r="K83" s="52"/>
-      <c r="L83" s="52"/>
-      <c r="M83" s="52"/>
-      <c r="N83" s="52"/>
-      <c r="O83" s="52"/>
-      <c r="P83" s="49"/>
+      <c r="J83" s="48"/>
+      <c r="K83" s="48"/>
+      <c r="L83" s="48"/>
+      <c r="M83" s="48"/>
+      <c r="N83" s="48"/>
+      <c r="O83" s="48"/>
+      <c r="P83" s="56"/>
       <c r="Q83" s="32" t="s">
         <v>30</v>
       </c>
       <c r="R83" s="9">
-        <v>1.7543341428603401</v>
+        <v>-9.6466487655750495</v>
       </c>
       <c r="S83" s="9">
-        <v>0.359117588774852</v>
+        <v>2.2161369274627698</v>
       </c>
       <c r="T83" s="9">
-        <v>32.4274243968759</v>
+        <v>26.344347603992698</v>
       </c>
       <c r="U83" s="9">
-        <v>2.7458766153504999</v>
+        <v>-4.3529118828498401</v>
       </c>
       <c r="V83" s="19">
-        <v>4.5827702542128403E-2</v>
+        <v>9.8108965488741305E-4</v>
       </c>
       <c r="W83" s="9"/>
-      <c r="X83" s="52"/>
-      <c r="Y83" s="52"/>
-      <c r="Z83" s="52"/>
-      <c r="AA83" s="52"/>
-      <c r="AB83" s="52"/>
-      <c r="AC83" s="36"/>
+      <c r="X83" s="48"/>
+      <c r="Y83" s="48"/>
+      <c r="Z83" s="48"/>
+      <c r="AA83" s="48"/>
+      <c r="AB83" s="48"/>
+      <c r="AC83" s="9"/>
     </row>
     <row r="84" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="47" t="s">
-        <v>46</v>
+      <c r="A84" s="55" t="s">
+        <v>19</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C84" s="26">
-        <v>1.2047850194397301E-5</v>
-      </c>
-      <c r="D84" s="26">
-        <v>1.2047850194397301E-5</v>
+      <c r="C84" s="8">
+        <v>5.0694430563116102</v>
+      </c>
+      <c r="D84" s="8">
+        <v>5.0694430563116102</v>
       </c>
       <c r="E84" s="8">
         <v>1</v>
       </c>
       <c r="F84" s="8">
-        <v>59.264824422698197</v>
+        <v>67.962550016506</v>
       </c>
       <c r="G84" s="8">
-        <v>0.77970315894266595</v>
-      </c>
-      <c r="H84" s="8">
-        <v>0.38079976992345599</v>
+        <v>123.23450697288</v>
+      </c>
+      <c r="H84" s="29">
+        <v>6.4779999000469503E-17</v>
       </c>
       <c r="I84" s="8"/>
-      <c r="J84" s="57" t="s">
+      <c r="J84" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="K84" s="57"/>
-      <c r="L84" s="57"/>
-      <c r="M84" s="57"/>
-      <c r="N84" s="57"/>
-      <c r="O84" s="57"/>
-      <c r="P84" s="47" t="s">
-        <v>40</v>
+      <c r="K84" s="51"/>
+      <c r="L84" s="51"/>
+      <c r="M84" s="51"/>
+      <c r="N84" s="51"/>
+      <c r="O84" s="51"/>
+      <c r="P84" s="55" t="s">
+        <v>39</v>
       </c>
       <c r="Q84" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="R84" s="39">
-        <v>-1.65441347008876E-5</v>
+      <c r="R84" s="13">
+        <v>2.9177136151243199</v>
       </c>
       <c r="S84" s="13">
-        <v>1.39477336460398E-3</v>
+        <v>0.48713627626251899</v>
       </c>
       <c r="T84" s="13">
-        <v>62.2695018953399</v>
+        <v>64.430590038735005</v>
       </c>
       <c r="U84" s="13">
-        <v>-1.1861521821923401E-2</v>
-      </c>
-      <c r="V84" s="43">
-        <v>0.99999939343423405</v>
+        <v>6.4135823376221897</v>
+      </c>
+      <c r="V84" s="41">
+        <v>1.14162453601629E-7</v>
       </c>
       <c r="W84" s="13"/>
-      <c r="X84" s="56" t="s">
+      <c r="X84" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="Y84" s="56"/>
-      <c r="Z84" s="56"/>
-      <c r="AA84" s="56"/>
-      <c r="AB84" s="56"/>
-      <c r="AC84" s="37"/>
+      <c r="Y84" s="46"/>
+      <c r="Z84" s="46"/>
+      <c r="AA84" s="46"/>
+      <c r="AB84" s="46"/>
+      <c r="AC84" s="34"/>
     </row>
     <row r="85" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A85" s="48"/>
+      <c r="A85" s="44"/>
       <c r="B85" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C85" s="1">
-        <v>1.70151152581477E-4</v>
+        <v>0.289278337816473</v>
       </c>
       <c r="D85" s="1">
-        <v>1.70151152581477E-4</v>
+        <v>0.289278337816473</v>
       </c>
       <c r="E85" s="1">
         <v>1</v>
       </c>
       <c r="F85" s="1">
-        <v>12.5741045864533</v>
+        <v>23.487577951072801</v>
       </c>
       <c r="G85" s="1">
-        <v>11.0117065721159</v>
+        <v>7.0321478992377502</v>
       </c>
       <c r="H85" s="2">
-        <v>5.7804446105462802E-3</v>
+        <v>1.4106574908243E-2</v>
       </c>
       <c r="I85" s="1"/>
-      <c r="J85" s="51"/>
-      <c r="K85" s="51"/>
-      <c r="L85" s="51"/>
-      <c r="M85" s="51"/>
-      <c r="N85" s="51"/>
-      <c r="O85" s="51"/>
-      <c r="P85" s="48"/>
+      <c r="J85" s="47"/>
+      <c r="K85" s="47"/>
+      <c r="L85" s="47"/>
+      <c r="M85" s="47"/>
+      <c r="N85" s="47"/>
+      <c r="O85" s="47"/>
+      <c r="P85" s="44"/>
       <c r="Q85" s="31" t="s">
         <v>28</v>
       </c>
       <c r="R85" s="1">
-        <v>1.6280035456013801E-3</v>
+        <v>3.7301111316362499</v>
       </c>
       <c r="S85" s="1">
-        <v>1.1877502326311899E-3</v>
+        <v>0.51018600017349802</v>
       </c>
       <c r="T85" s="1">
-        <v>60.830326285509202</v>
+        <v>62.737652543129002</v>
       </c>
       <c r="U85" s="1">
-        <v>1.37066152535698</v>
-      </c>
-      <c r="V85" s="1">
-        <v>0.52237983670065102</v>
+        <v>9.6248429744420907</v>
+      </c>
+      <c r="V85" s="6">
+        <v>1.6875612018907301E-11</v>
       </c>
       <c r="W85" s="1"/>
-      <c r="X85" s="51"/>
-      <c r="Y85" s="51"/>
-      <c r="Z85" s="51"/>
-      <c r="AA85" s="51"/>
-      <c r="AB85" s="51"/>
+      <c r="X85" s="47"/>
+      <c r="Y85" s="47"/>
+      <c r="Z85" s="47"/>
+      <c r="AA85" s="47"/>
+      <c r="AB85" s="47"/>
       <c r="AC85" s="35"/>
     </row>
     <row r="86" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A86" s="48"/>
+      <c r="A86" s="44"/>
       <c r="B86" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C86" s="5">
-        <v>1.25476892781706E-5</v>
-      </c>
-      <c r="D86" s="5">
-        <v>1.25476892781706E-5</v>
+      <c r="C86" s="1">
+        <v>5.3673365621619298E-2</v>
+      </c>
+      <c r="D86" s="1">
+        <v>5.3673365621619298E-2</v>
       </c>
       <c r="E86" s="1">
         <v>1</v>
       </c>
       <c r="F86" s="1">
-        <v>59.264824426186202</v>
+        <v>67.962550017652504</v>
       </c>
       <c r="G86" s="1">
-        <v>0.81205134607087903</v>
+        <v>1.30476083397765</v>
       </c>
       <c r="H86" s="1">
-        <v>0.37116202943872301</v>
+        <v>0.25735376158301099</v>
       </c>
       <c r="I86" s="1"/>
-      <c r="J86" s="51"/>
-      <c r="K86" s="51"/>
-      <c r="L86" s="51"/>
-      <c r="M86" s="51"/>
-      <c r="N86" s="51"/>
-      <c r="O86" s="51"/>
-      <c r="P86" s="48"/>
+      <c r="J86" s="47"/>
+      <c r="K86" s="47"/>
+      <c r="L86" s="47"/>
+      <c r="M86" s="47"/>
+      <c r="N86" s="47"/>
+      <c r="O86" s="47"/>
+      <c r="P86" s="44"/>
       <c r="Q86" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="R86" s="13">
-        <v>-4.7357111792336601E-3</v>
-      </c>
-      <c r="S86" s="13">
-        <v>1.45559347836175E-3</v>
-      </c>
-      <c r="T86" s="13">
-        <v>33.175075568647898</v>
-      </c>
-      <c r="U86" s="13">
-        <v>-3.25345726649148</v>
-      </c>
-      <c r="V86" s="15">
-        <v>1.33110134354993E-2</v>
+      <c r="R86" s="1">
+        <v>1.37224989644095</v>
+      </c>
+      <c r="S86" s="1">
+        <v>0.26567786472642402</v>
+      </c>
+      <c r="T86" s="1">
+        <v>31.114142203224599</v>
+      </c>
+      <c r="U86" s="1">
+        <v>1.6345010468947201</v>
+      </c>
+      <c r="V86" s="1">
+        <v>0.37476551599412999</v>
       </c>
       <c r="W86" s="1"/>
-      <c r="X86" s="51"/>
-      <c r="Y86" s="51"/>
-      <c r="Z86" s="51"/>
-      <c r="AA86" s="51"/>
-      <c r="AB86" s="51"/>
+      <c r="X86" s="47"/>
+      <c r="Y86" s="47"/>
+      <c r="Z86" s="47"/>
+      <c r="AA86" s="47"/>
+      <c r="AB86" s="47"/>
       <c r="AC86" s="35"/>
     </row>
     <row r="87" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="49"/>
+      <c r="A87" s="56"/>
       <c r="B87" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C87" s="58"/>
-      <c r="D87" s="58"/>
-      <c r="E87" s="58"/>
-      <c r="F87" s="58"/>
-      <c r="G87" s="58"/>
-      <c r="H87" s="58"/>
+      <c r="C87" s="50"/>
+      <c r="D87" s="50"/>
+      <c r="E87" s="50"/>
+      <c r="F87" s="50"/>
+      <c r="G87" s="50"/>
+      <c r="H87" s="50"/>
       <c r="I87" s="9"/>
-      <c r="J87" s="52"/>
-      <c r="K87" s="52"/>
-      <c r="L87" s="52"/>
-      <c r="M87" s="52"/>
-      <c r="N87" s="52"/>
-      <c r="O87" s="52"/>
-      <c r="P87" s="49"/>
+      <c r="J87" s="48"/>
+      <c r="K87" s="48"/>
+      <c r="L87" s="48"/>
+      <c r="M87" s="48"/>
+      <c r="N87" s="48"/>
+      <c r="O87" s="48"/>
+      <c r="P87" s="56"/>
       <c r="Q87" s="32" t="s">
         <v>30</v>
       </c>
       <c r="R87" s="9">
+        <v>1.7543341428603401</v>
+      </c>
+      <c r="S87" s="9">
+        <v>0.359117588774852</v>
+      </c>
+      <c r="T87" s="9">
+        <v>32.4274243968759</v>
+      </c>
+      <c r="U87" s="9">
+        <v>2.7458766153504999</v>
+      </c>
+      <c r="V87" s="19">
+        <v>4.5827702542128403E-2</v>
+      </c>
+      <c r="W87" s="9"/>
+      <c r="X87" s="48"/>
+      <c r="Y87" s="48"/>
+      <c r="Z87" s="48"/>
+      <c r="AA87" s="48"/>
+      <c r="AB87" s="48"/>
+      <c r="AC87" s="36"/>
+    </row>
+    <row r="88" spans="1:29" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="55" t="s">
+        <v>46</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C88" s="26">
+        <v>1.2047850194397301E-5</v>
+      </c>
+      <c r="D88" s="26">
+        <v>1.2047850194397301E-5</v>
+      </c>
+      <c r="E88" s="8">
+        <v>1</v>
+      </c>
+      <c r="F88" s="8">
+        <v>59.264824422698197</v>
+      </c>
+      <c r="G88" s="8">
+        <v>0.77970315894266595</v>
+      </c>
+      <c r="H88" s="8">
+        <v>0.38079976992345599</v>
+      </c>
+      <c r="I88" s="8"/>
+      <c r="J88" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="K88" s="51"/>
+      <c r="L88" s="51"/>
+      <c r="M88" s="51"/>
+      <c r="N88" s="51"/>
+      <c r="O88" s="51"/>
+      <c r="P88" s="55" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q88" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="R88" s="39">
+        <v>-1.65441347008876E-5</v>
+      </c>
+      <c r="S88" s="13">
+        <v>1.39477336460398E-3</v>
+      </c>
+      <c r="T88" s="13">
+        <v>62.2695018953399</v>
+      </c>
+      <c r="U88" s="13">
+        <v>-1.1861521821923401E-2</v>
+      </c>
+      <c r="V88" s="43">
+        <v>0.99999939343423405</v>
+      </c>
+      <c r="W88" s="13"/>
+      <c r="X88" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y88" s="46"/>
+      <c r="Z88" s="46"/>
+      <c r="AA88" s="46"/>
+      <c r="AB88" s="46"/>
+      <c r="AC88" s="37"/>
+    </row>
+    <row r="89" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A89" s="44"/>
+      <c r="B89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="1">
+        <v>1.70151152581477E-4</v>
+      </c>
+      <c r="D89" s="1">
+        <v>1.70151152581477E-4</v>
+      </c>
+      <c r="E89" s="1">
+        <v>1</v>
+      </c>
+      <c r="F89" s="1">
+        <v>12.5741045864533</v>
+      </c>
+      <c r="G89" s="1">
+        <v>11.0117065721159</v>
+      </c>
+      <c r="H89" s="2">
+        <v>5.7804446105462802E-3</v>
+      </c>
+      <c r="I89" s="1"/>
+      <c r="J89" s="47"/>
+      <c r="K89" s="47"/>
+      <c r="L89" s="47"/>
+      <c r="M89" s="47"/>
+      <c r="N89" s="47"/>
+      <c r="O89" s="47"/>
+      <c r="P89" s="44"/>
+      <c r="Q89" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="R89" s="1">
+        <v>1.6280035456013801E-3</v>
+      </c>
+      <c r="S89" s="1">
+        <v>1.1877502326311899E-3</v>
+      </c>
+      <c r="T89" s="1">
+        <v>60.830326285509202</v>
+      </c>
+      <c r="U89" s="1">
+        <v>1.37066152535698</v>
+      </c>
+      <c r="V89" s="1">
+        <v>0.52237983670065102</v>
+      </c>
+      <c r="W89" s="1"/>
+      <c r="X89" s="47"/>
+      <c r="Y89" s="47"/>
+      <c r="Z89" s="47"/>
+      <c r="AA89" s="47"/>
+      <c r="AB89" s="47"/>
+      <c r="AC89" s="35"/>
+    </row>
+    <row r="90" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A90" s="44"/>
+      <c r="B90" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C90" s="5">
+        <v>1.25476892781706E-5</v>
+      </c>
+      <c r="D90" s="5">
+        <v>1.25476892781706E-5</v>
+      </c>
+      <c r="E90" s="1">
+        <v>1</v>
+      </c>
+      <c r="F90" s="1">
+        <v>59.264824426186202</v>
+      </c>
+      <c r="G90" s="1">
+        <v>0.81205134607087903</v>
+      </c>
+      <c r="H90" s="1">
+        <v>0.37116202943872301</v>
+      </c>
+      <c r="I90" s="1"/>
+      <c r="J90" s="47"/>
+      <c r="K90" s="47"/>
+      <c r="L90" s="47"/>
+      <c r="M90" s="47"/>
+      <c r="N90" s="47"/>
+      <c r="O90" s="47"/>
+      <c r="P90" s="44"/>
+      <c r="Q90" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="R90" s="13">
+        <v>-4.7357111792336601E-3</v>
+      </c>
+      <c r="S90" s="13">
+        <v>1.45559347836175E-3</v>
+      </c>
+      <c r="T90" s="13">
+        <v>33.175075568647898</v>
+      </c>
+      <c r="U90" s="13">
+        <v>-3.25345726649148</v>
+      </c>
+      <c r="V90" s="15">
+        <v>1.33110134354993E-2</v>
+      </c>
+      <c r="W90" s="1"/>
+      <c r="X90" s="47"/>
+      <c r="Y90" s="47"/>
+      <c r="Z90" s="47"/>
+      <c r="AA90" s="47"/>
+      <c r="AB90" s="47"/>
+      <c r="AC90" s="35"/>
+    </row>
+    <row r="91" spans="1:29" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="56"/>
+      <c r="B91" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C91" s="50"/>
+      <c r="D91" s="50"/>
+      <c r="E91" s="50"/>
+      <c r="F91" s="50"/>
+      <c r="G91" s="50"/>
+      <c r="H91" s="50"/>
+      <c r="I91" s="9"/>
+      <c r="J91" s="48"/>
+      <c r="K91" s="48"/>
+      <c r="L91" s="48"/>
+      <c r="M91" s="48"/>
+      <c r="N91" s="48"/>
+      <c r="O91" s="48"/>
+      <c r="P91" s="56"/>
+      <c r="Q91" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="R91" s="9">
         <v>-3.0911634989313902E-3</v>
       </c>
-      <c r="S87" s="9">
+      <c r="S91" s="9">
         <v>1.5710422017598299E-3</v>
       </c>
-      <c r="T87" s="9">
+      <c r="T91" s="9">
         <v>35.526741286073303</v>
       </c>
-      <c r="U87" s="9">
+      <c r="U91" s="9">
         <v>-1.96758781875418</v>
       </c>
-      <c r="V87" s="9">
+      <c r="V91" s="9">
         <v>0.21931254615242901</v>
       </c>
-      <c r="W87" s="9"/>
-      <c r="X87" s="52"/>
-      <c r="Y87" s="52"/>
-      <c r="Z87" s="52"/>
-      <c r="AA87" s="52"/>
-      <c r="AB87" s="52"/>
-      <c r="AC87" s="36"/>
+      <c r="W91" s="9"/>
+      <c r="X91" s="48"/>
+      <c r="Y91" s="48"/>
+      <c r="Z91" s="48"/>
+      <c r="AA91" s="48"/>
+      <c r="AB91" s="48"/>
+      <c r="AC91" s="36"/>
     </row>
   </sheetData>
-  <mergeCells count="91">
+  <mergeCells count="95">
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="C31:H34"/>
+    <mergeCell ref="P31:P34"/>
+    <mergeCell ref="R31:V34"/>
+    <mergeCell ref="X1:AC1"/>
+    <mergeCell ref="P60:P63"/>
+    <mergeCell ref="P3:P6"/>
+    <mergeCell ref="X3:AB6"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="P48:P51"/>
+    <mergeCell ref="P52:P55"/>
+    <mergeCell ref="R1:W1"/>
+    <mergeCell ref="P56:P59"/>
+    <mergeCell ref="P15:P18"/>
+    <mergeCell ref="P7:P10"/>
+    <mergeCell ref="P35:P38"/>
+    <mergeCell ref="P39:P42"/>
+    <mergeCell ref="P11:P14"/>
+    <mergeCell ref="P23:P26"/>
+    <mergeCell ref="X80:AB83"/>
+    <mergeCell ref="X68:AB71"/>
+    <mergeCell ref="R11:V14"/>
+    <mergeCell ref="P84:P87"/>
+    <mergeCell ref="J72:O75"/>
+    <mergeCell ref="C75:H75"/>
+    <mergeCell ref="J68:O71"/>
+    <mergeCell ref="X88:AB91"/>
+    <mergeCell ref="P19:P22"/>
+    <mergeCell ref="R19:V22"/>
+    <mergeCell ref="P88:P91"/>
+    <mergeCell ref="P72:P75"/>
+    <mergeCell ref="X72:AB75"/>
+    <mergeCell ref="R76:V79"/>
+    <mergeCell ref="P80:P83"/>
+    <mergeCell ref="X84:AB87"/>
+    <mergeCell ref="R23:V26"/>
+    <mergeCell ref="P64:P67"/>
+    <mergeCell ref="P68:P71"/>
+    <mergeCell ref="P76:P79"/>
+    <mergeCell ref="J43:O46"/>
+    <mergeCell ref="C46:H46"/>
+    <mergeCell ref="P43:P46"/>
+    <mergeCell ref="X43:AB46"/>
+    <mergeCell ref="P27:P30"/>
+    <mergeCell ref="R27:V30"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="C19:H22"/>
     <mergeCell ref="A35:A38"/>
-    <mergeCell ref="J35:O38"/>
-    <mergeCell ref="X31:AB34"/>
-    <mergeCell ref="X35:AB38"/>
-    <mergeCell ref="C38:H38"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="J31:O34"/>
+    <mergeCell ref="A88:A91"/>
+    <mergeCell ref="J88:O91"/>
+    <mergeCell ref="C91:H91"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="C27:H30"/>
+    <mergeCell ref="A84:A87"/>
+    <mergeCell ref="J84:O87"/>
+    <mergeCell ref="C87:H87"/>
+    <mergeCell ref="A80:A83"/>
+    <mergeCell ref="J80:O83"/>
+    <mergeCell ref="C83:H83"/>
+    <mergeCell ref="A76:A79"/>
+    <mergeCell ref="C76:H79"/>
+    <mergeCell ref="A72:A75"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="C23:H26"/>
+    <mergeCell ref="A68:A71"/>
+    <mergeCell ref="C71:H71"/>
+    <mergeCell ref="A48:A51"/>
+    <mergeCell ref="C51:H51"/>
+    <mergeCell ref="A52:A55"/>
+    <mergeCell ref="C55:H55"/>
+    <mergeCell ref="A56:A59"/>
+    <mergeCell ref="C59:H59"/>
+    <mergeCell ref="A64:A67"/>
+    <mergeCell ref="C67:H67"/>
+    <mergeCell ref="A60:A63"/>
+    <mergeCell ref="C63:H63"/>
     <mergeCell ref="J3:O6"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="C1:I1"/>
@@ -6489,79 +6791,13 @@
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="A11:A14"/>
     <mergeCell ref="C11:H14"/>
-    <mergeCell ref="A68:A71"/>
     <mergeCell ref="A39:A42"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="C23:H26"/>
-    <mergeCell ref="A64:A67"/>
-    <mergeCell ref="C67:H67"/>
-    <mergeCell ref="A44:A47"/>
-    <mergeCell ref="C47:H47"/>
-    <mergeCell ref="A48:A51"/>
-    <mergeCell ref="C51:H51"/>
-    <mergeCell ref="A52:A55"/>
-    <mergeCell ref="C55:H55"/>
-    <mergeCell ref="A60:A63"/>
-    <mergeCell ref="C63:H63"/>
-    <mergeCell ref="A56:A59"/>
-    <mergeCell ref="C59:H59"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="C19:H22"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A84:A87"/>
-    <mergeCell ref="J84:O87"/>
-    <mergeCell ref="C87:H87"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="C27:H30"/>
-    <mergeCell ref="A80:A83"/>
-    <mergeCell ref="J80:O83"/>
-    <mergeCell ref="C83:H83"/>
-    <mergeCell ref="A76:A79"/>
-    <mergeCell ref="J76:O79"/>
-    <mergeCell ref="C79:H79"/>
-    <mergeCell ref="A72:A75"/>
-    <mergeCell ref="C72:H75"/>
+    <mergeCell ref="J39:O42"/>
+    <mergeCell ref="X35:AB38"/>
+    <mergeCell ref="X39:AB42"/>
     <mergeCell ref="C42:H42"/>
-    <mergeCell ref="P39:P42"/>
-    <mergeCell ref="X39:AB42"/>
-    <mergeCell ref="P27:P30"/>
-    <mergeCell ref="R27:V30"/>
-    <mergeCell ref="C71:H71"/>
-    <mergeCell ref="J64:O67"/>
-    <mergeCell ref="X84:AB87"/>
-    <mergeCell ref="P19:P22"/>
-    <mergeCell ref="R19:V22"/>
-    <mergeCell ref="P84:P87"/>
-    <mergeCell ref="P68:P71"/>
-    <mergeCell ref="X68:AB71"/>
-    <mergeCell ref="R72:V75"/>
-    <mergeCell ref="P76:P79"/>
-    <mergeCell ref="X80:AB83"/>
-    <mergeCell ref="R23:V26"/>
-    <mergeCell ref="P60:P63"/>
-    <mergeCell ref="P64:P67"/>
-    <mergeCell ref="P72:P75"/>
-    <mergeCell ref="J39:O42"/>
-    <mergeCell ref="X76:AB79"/>
-    <mergeCell ref="X64:AB67"/>
-    <mergeCell ref="R11:V14"/>
-    <mergeCell ref="P80:P83"/>
-    <mergeCell ref="J68:O71"/>
-    <mergeCell ref="X1:AC1"/>
-    <mergeCell ref="P56:P59"/>
-    <mergeCell ref="P3:P6"/>
-    <mergeCell ref="X3:AB6"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="P44:P47"/>
-    <mergeCell ref="P48:P51"/>
-    <mergeCell ref="R1:W1"/>
-    <mergeCell ref="P52:P55"/>
-    <mergeCell ref="P15:P18"/>
-    <mergeCell ref="P7:P10"/>
-    <mergeCell ref="P31:P34"/>
-    <mergeCell ref="P35:P38"/>
-    <mergeCell ref="P11:P14"/>
-    <mergeCell ref="P23:P26"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="J35:O38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
